--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.231550282710436e-08</v>
+        <v>1.231550282710426e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.046429760863976e-08</v>
+        <v>1.046429760863975e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.207590731906919e-08</v>
+        <v>1.207590731906912e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.207854358306318e-08</v>
+        <v>1.207854358306313e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.205717620159528e-08</v>
+        <v>1.205717620159521e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.257222413841896e-08</v>
+        <v>1.257222413841891e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.207853614581079e-08</v>
+        <v>1.207853614581072e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.206415573291504e-08</v>
+        <v>1.206415573291505e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.233459810750583e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.20894294630427e-08</v>
+        <v>1.208942946304265e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.242976844056205e-08</v>
+        <v>1.242976844056206e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.290861754720908e-08</v>
+        <v>1.290861754720907e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.205630494104412e-08</v>
+        <v>1.205630494104407e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.624085605210388e-08</v>
+        <v>1.624085605210384e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.225948148963147e-08</v>
+        <v>1.225948148963143e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.206255757577177e-08</v>
+        <v>1.20625575757717e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.204537916985664e-08</v>
+        <v>1.204537916985655e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232926709685788e-08</v>
+        <v>1.232926709685782e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.210422607353236e-08</v>
+        <v>1.210422607353232e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.258483120273507e-08</v>
+        <v>1.25848312027351e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.210179625344369e-08</v>
+        <v>1.210179625344366e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.234736024028431e-08</v>
+        <v>1.234736024028438e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.219772472303336e-08</v>
+        <v>1.219772472303339e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.21914218964326e-08</v>
+        <v>1.219142189643252e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.178863598917358e-08</v>
+        <v>1.178863598917354e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.215164430083513e-08</v>
+        <v>1.215164430083518e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.258676150356377e-08</v>
+        <v>1.258676150356376e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.450644649987066e-08</v>
+        <v>1.450644649987073e-08</v>
       </c>
       <c r="C3" t="n">
         <v>9.663189085490548e-09</v>
@@ -683,76 +683,76 @@
         <v>1.28100187746752e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.280312811155627e-08</v>
+        <v>1.280312811155631e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26778859725844e-08</v>
+        <v>1.267788597258443e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.633715462531958e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.283248263688584e-08</v>
+        <v>1.283248263688595e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.272668208547436e-08</v>
+        <v>1.272668208547441e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.464974526948595e-08</v>
+        <v>1.464974526948599e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.29062000614274e-08</v>
+        <v>1.290620006142732e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.533109456470327e-08</v>
+        <v>1.533109456470324e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.880973510767094e-08</v>
+        <v>1.880973510767093e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.266805329983276e-08</v>
+        <v>1.26680532998327e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.038087363450078e-08</v>
+        <v>2.038087363450077e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.410891726388571e-08</v>
+        <v>1.410891726388568e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.271333724008299e-08</v>
+        <v>1.2713337240083e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.259297305800334e-08</v>
+        <v>1.259297305800339e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.460846756713978e-08</v>
+        <v>1.460846756713976e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.301307875048599e-08</v>
+        <v>1.3013078750486e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.661999618002573e-08</v>
+        <v>1.661999618002571e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29885718238891e-08</v>
+        <v>1.298857182388919e-08</v>
       </c>
       <c r="W3" t="n">
         <v>1.357122987855405e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.368081093812912e-08</v>
+        <v>1.36808109381291e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.363211082589229e-08</v>
+        <v>1.363211082589232e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.279404488930076e-08</v>
+        <v>1.279404488930078e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.334798932652693e-08</v>
+        <v>1.334798932652692e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.646720004263909e-08</v>
+        <v>1.646720004263908e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.233683807430901e-08</v>
+        <v>1.233683807430899e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.643943223785173e-09</v>
+        <v>8.643943223785165e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.630496591672707e-09</v>
+        <v>9.630496591672692e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.660274406226265e-09</v>
+        <v>9.660274406226248e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.41892000306517e-09</v>
+        <v>9.418920003065165e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.523662338324537e-08</v>
+        <v>1.523662338324536e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.660190399039334e-09</v>
+        <v>9.66019039903932e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.497757020065473e-09</v>
+        <v>9.497757020065465e-09</v>
       </c>
       <c r="J4" t="n">
         <v>1.25413871605007e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.783235428347259e-09</v>
+        <v>9.783235428347248e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36275207430939e-08</v>
+        <v>1.362752074309389e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.909643513444846e-08</v>
+        <v>1.909643513444844e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.409078714340275e-09</v>
+        <v>9.409078714340266e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.108687384761883e-08</v>
+        <v>1.10868738476188e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.170405129646489e-08</v>
+        <v>1.170405129646488e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.479705099942924e-09</v>
+        <v>9.479705099942903e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>9.285667102674441e-09</v>
+        <v>9.285667102674423e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.249231183305186e-08</v>
+        <v>1.249231183305185e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>9.950369950605044e-09</v>
+        <v>9.950369950605034e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.568627022162403e-08</v>
+        <v>1.568627022162401e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.863664391419845e-09</v>
+        <v>9.863664391419838e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.028164402059421e-08</v>
+        <v>1.028164402059419e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.100648020822351e-08</v>
+        <v>1.100648020822349e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.086137856559e-08</v>
+        <v>1.086137856558998e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.058976882957904e-08</v>
+        <v>1.058976882957903e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>1.048598064145319e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.537645397946566e-08</v>
+        <v>1.537645397946564e-08</v>
       </c>
     </row>
     <row r="5">
@@ -856,79 +856,79 @@
         <v>3.450055480241608e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.545452492957042e-08</v>
+        <v>5.54545249295704e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.077594495769424e-08</v>
+        <v>4.077594495769412e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.211632787522715e-08</v>
+        <v>5.211632787522704e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.593739720289758e-07</v>
+        <v>1.593739720289764e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>5.825265494736031e-08</v>
+        <v>5.825265494736028e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.309939296677854e-08</v>
+        <v>5.309939296677842e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.103863577419363e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.833604647452311e-08</v>
+        <v>5.833604647452307e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.333019254056687e-07</v>
+        <v>1.333019254056689e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.603258858005188e-07</v>
+        <v>2.603258858005189e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.670094186610473e-07</v>
+        <v>1.670094186610469e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>7.792474640899847e-08</v>
+        <v>7.792474640899842e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.050747854823221e-08</v>
+        <v>9.050747854823205e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.158358953205005e-08</v>
+        <v>5.158358953204987e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.900680526229135e-08</v>
+        <v>4.900680526229133e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.072651158912048e-07</v>
+        <v>1.072651158912045e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.245930013298573e-08</v>
+        <v>6.245930013298538e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.733605184850643e-07</v>
+        <v>1.73360518485064e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>5.758871607434105e-08</v>
+        <v>5.758871607434101e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.669902970528619e-08</v>
+        <v>6.669902970528615e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.398127168820052e-08</v>
+        <v>8.398127168820023e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.033867593381881e-08</v>
+        <v>8.033867593381806e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.018843942841518e-08</v>
+        <v>7.018843942841507e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.1155806299473e-08</v>
+        <v>7.115580629947301e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.856876453977823e-07</v>
+        <v>1.856876453977821e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.519762328750087e-08</v>
+        <v>1.844843398392102e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.475553913339719e-08</v>
+        <v>1.475553913339721e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.249128180486458e-08</v>
+        <v>1.249128180486455e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.577187031583827e-08</v>
+        <v>1.252105961941811e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.227970521625704e-08</v>
+        <v>1.55305159126772e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.809740859643726e-08</v>
+        <v>2.134821929285739e-08</v>
       </c>
       <c r="H6" t="n">
         <v>1.577178630865134e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.56093529296775e-08</v>
+        <v>1.235854223325732e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.540217237369258e-08</v>
+        <v>1.865298307011273e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.264402064153913e-08</v>
+        <v>1.264402064153912e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.973911665270591e-08</v>
+        <v>1.648830595628574e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.195722034764031e-08</v>
+        <v>2.195722034764032e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.228133956026386e-08</v>
+        <v>1.228133956026391e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.722140006079764e-08</v>
+        <v>1.722140006079766e-08</v>
       </c>
       <c r="P6" t="n">
         <v>1.783858306554175e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.234049031313479e-08</v>
+        <v>1.234049031313477e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.539726301228645e-08</v>
+        <v>1.214645231586628e-08</v>
       </c>
       <c r="S6" t="n">
         <v>1.860390774266388e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.281115516379692e-08</v>
+        <v>1.281115516379689e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.862096375154916e-08</v>
+        <v>1.862096375154912e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.597526030103185e-08</v>
+        <v>1.597526030103186e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.331939509620685e-08</v>
+        <v>1.641617329687627e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.711807611783549e-08</v>
+        <v>1.711807611783551e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.394943193960767e-08</v>
+        <v>1.39494319396077e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.345055404277092e-08</v>
+        <v>1.34505540427709e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.659757655106521e-08</v>
+        <v>1.334676585464505e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.827461472189942e-08</v>
+        <v>1.827461472189941e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,13 +1026,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.984700840033516e-08</v>
+        <v>1.984700840033515e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.615411354981134e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.714066691769886e-08</v>
+        <v>1.714066691769885e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.717044473225242e-08</v>
@@ -1041,52 +1041,52 @@
         <v>1.692909032909133e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.274679370927152e-08</v>
+        <v>2.274679370927153e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.717036072506549e-08</v>
+        <v>1.71703607250655e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.700792734609164e-08</v>
+        <v>1.700792734609163e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.005155748652687e-08</v>
+        <v>2.005155748652686e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.729340575437342e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.113769106912003e-08</v>
+        <v>2.113769106912004e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.660660546047461e-08</v>
+        <v>2.660660546047462e-08</v>
       </c>
       <c r="N7" t="n">
         <v>1.691924904036643e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.859656288256719e-08</v>
+        <v>1.859656288256717e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.921374033141325e-08</v>
+        <v>1.921374033141326e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.698987542596905e-08</v>
+        <v>1.698987542596907e-08</v>
       </c>
       <c r="R7" t="n">
         <v>1.67958374287006e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.000248215907804e-08</v>
+        <v>2.0002482159078e-08</v>
       </c>
       <c r="T7" t="n">
         <v>1.746054027663119e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.326870961102522e-08</v>
+        <v>2.326870961102521e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.737383471744601e-08</v>
+        <v>1.737383471744599e-08</v>
       </c>
       <c r="W7" t="n">
         <v>1.779181434662038e-08</v>
@@ -1095,16 +1095,16 @@
         <v>1.851665053424966e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.844545720834942e-08</v>
+        <v>1.84454572083494e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>1.809993915560518e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.799615096747936e-08</v>
+        <v>1.799615096747934e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.288662430549183e-08</v>
+        <v>2.288662430549181e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.923131786339393e-08</v>
+        <v>3.923131786339396e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.312299606171089e-08</v>
+        <v>5.312299606171095e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.410954942959842e-08</v>
+        <v>5.410954942959849e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>5.413932724415196e-08</v>
+        <v>4.477606080758243e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.90528707581946e-08</v>
+        <v>3.905287075819461e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.971567622117104e-08</v>
+        <v>6.336195199587351e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.413924323696499e-08</v>
+        <v>5.413924323696511e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.397680985799119e-08</v>
+        <v>5.397680985799122e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.702043999842642e-08</v>
+        <v>5.702043999842647e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.426228826627295e-08</v>
+        <v>5.426228826627302e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.810657358101962e-08</v>
+        <v>5.810657358101971e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>6.357548797237419e-08</v>
+        <v>6.357548797237432e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.025714560506301e-08</v>
+        <v>4.025714560506304e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.568085403382984e-08</v>
+        <v>4.568085403382986e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.537981761985246e-08</v>
+        <v>4.537981761985251e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.291841493594905e-08</v>
+        <v>3.291841493594904e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.376471994060007e-08</v>
+        <v>5.376471994060018e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.697136467097756e-08</v>
+        <v>5.697136467097765e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.442942278853072e-08</v>
+        <v>5.442942278853083e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.941775807754896e-08</v>
+        <v>5.165553857896793e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>5.434271722934553e-08</v>
+        <v>4.953559847582251e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.476415273349574e-08</v>
+        <v>5.476415273349579e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.60568511067842e-08</v>
+        <v>3.605685110678424e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.289674527545646e-08</v>
+        <v>7.289674527545651e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.50688216675047e-08</v>
+        <v>3.715760614611786e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.49650334793789e-08</v>
+        <v>5.496503347937892e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.822406376735723e-08</v>
+        <v>7.822406376735722e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.54403093985285e-08</v>
+        <v>3.544030939852853e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.835273940865321e-08</v>
+        <v>3.835273940865319e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.933929277654069e-08</v>
+        <v>3.93392927765407e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.936907059109426e-08</v>
+        <v>3.784458892159093e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.912771618793321e-08</v>
+        <v>2.390063899937524e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.49454195681134e-08</v>
+        <v>4.494542004354635e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.936898658390737e-08</v>
+        <v>3.936898658390731e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.92065532049335e-08</v>
+        <v>3.920655320493346e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.225018334536871e-08</v>
+        <v>4.225018334536867e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.94920316132153e-08</v>
+        <v>3.949203161321528e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.333631692796194e-08</v>
+        <v>4.333631692796191e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.880523131931645e-08</v>
+        <v>4.880523131931643e-08</v>
       </c>
       <c r="N9" t="n">
         <v>3.911787489920831e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>4.298466667536257e-08</v>
+        <v>4.298466667536253e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.407791323377762e-08</v>
+        <v>4.407791323377763e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.918850176024393e-08</v>
+        <v>3.918850176024392e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.899446328754243e-08</v>
+        <v>3.899446328754244e-08</v>
       </c>
       <c r="S9" t="n">
         <v>4.220110801791986e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.965916613547302e-08</v>
+        <v>3.965916613547301e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.54689747232253e-08</v>
+        <v>4.546897472322526e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.957246057628787e-08</v>
+        <v>4.719485799663648e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.999044020546223e-08</v>
+        <v>3.999044020546221e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>4.071527639309153e-08</v>
+        <v>4.071527639309149e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.064408306719128e-08</v>
+        <v>4.064408306719125e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.029856501444707e-08</v>
+        <v>3.631614168066932e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.019477682632122e-08</v>
+        <v>4.019477682632119e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.508525016433369e-08</v>
+        <v>4.508525016433367e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.130782687244712e-08</v>
+        <v>1.130782687244707e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.787618711343175e-09</v>
+        <v>9.787618711343155e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.133019316304615e-08</v>
+        <v>1.133019316304612e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.129909065740392e-08</v>
+        <v>1.129909065740387e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.131091647212551e-08</v>
+        <v>1.131091647212547e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.135916988625822e-08</v>
+        <v>1.135916988625816e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.132842461376456e-08</v>
+        <v>1.132842461376451e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.132816233060083e-08</v>
+        <v>1.132816233060079e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.134252769411869e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.133479919733555e-08</v>
+        <v>1.133479919733551e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.133238553531357e-08</v>
+        <v>1.133238553531353e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.133301281792525e-08</v>
+        <v>1.133301281792523e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.132214773002581e-08</v>
+        <v>1.132214773002577e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.496239560995371e-08</v>
+        <v>1.496239560995369e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.131932095951881e-08</v>
+        <v>1.131932095951876e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.131734260205721e-08</v>
+        <v>1.131734260205715e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.133059271589391e-08</v>
+        <v>1.133059271589387e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.133441913088444e-08</v>
+        <v>1.133441913088441e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.132030541045848e-08</v>
+        <v>1.132030541045843e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.118407435464609e-08</v>
+        <v>1.118407435464607e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13412077087652e-08</v>
+        <v>1.134120770876516e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.146399559253283e-08</v>
+        <v>1.146399559253274e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.152750906584543e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.151235136162775e-08</v>
+        <v>1.151235136162773e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.084705639605069e-08</v>
+        <v>1.084705639605065e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.137205789460653e-08</v>
+        <v>1.137205789460647e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.13344176819939e-08</v>
+        <v>1.133441768199388e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.161440173890637e-08</v>
+        <v>1.161440173890636e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.080049154309572e-09</v>
+        <v>9.080049154309567e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.177776904238584e-08</v>
+        <v>1.177776904238583e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.15328139074415e-08</v>
+        <v>1.153281390744147e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.16401437682916e-08</v>
+        <v>1.164014376829156e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.198018679951639e-08</v>
+        <v>1.198018679951634e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.176652860185062e-08</v>
+        <v>1.17665286018506e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.176310059388327e-08</v>
+        <v>1.176310059388325e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.186308215810082e-08</v>
+        <v>1.186308215810076e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.181161188674327e-08</v>
+        <v>1.181161188674326e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.179167758324121e-08</v>
+        <v>1.179167758324122e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.187246877258888e-08</v>
+        <v>1.187246877258887e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.171786601954126e-08</v>
+        <v>1.171786601954125e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.765573031575726e-08</v>
+        <v>1.76557303157572e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.169600896671221e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.168438924439465e-08</v>
+        <v>1.168438924439466e-08</v>
       </c>
       <c r="R3" t="n">
         <v>1.178066521261712e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18039652744942e-08</v>
+        <v>1.180396527449422e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.170614795898995e-08</v>
+        <v>1.170614795898991e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.166458660534135e-08</v>
+        <v>1.166458660534132e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.185303708323833e-08</v>
+        <v>1.185303708323832e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.231358923819476e-08</v>
+        <v>1.231358923819472e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.318291489193686e-08</v>
+        <v>1.31829148919368e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.307615240822072e-08</v>
+        <v>1.307615240822071e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.09097057598919e-08</v>
+        <v>1.090970575989191e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.20736783122176e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.182246699741706e-08</v>
+        <v>1.182246699741705e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.462100298180055e-09</v>
+        <v>7.462100298180065e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.41803107903595e-09</v>
+        <v>7.418031079035938e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.714737839498196e-09</v>
+        <v>7.714737839498207e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.363420730409786e-09</v>
+        <v>7.363420730409816e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.496998747833657e-09</v>
+        <v>7.49699874783367e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.042043258129533e-09</v>
+        <v>8.042043258129559e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.694761261789701e-09</v>
+        <v>7.694761261789716e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.691798652799205e-09</v>
+        <v>7.691798652799225e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.844927871488507e-09</v>
+        <v>7.844927871488506e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.766765115677359e-09</v>
+        <v>7.766765115677378e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.73950169279972e-09</v>
+        <v>7.739501692799742e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.881641818552945e-09</v>
+        <v>7.881641818552969e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.478287973631608e-09</v>
+        <v>7.478287973631621e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.591931299196158e-09</v>
+        <v>7.591931299196163e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.56958484157798e-09</v>
+        <v>7.569584841577993e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.719250972717024e-09</v>
+        <v>7.719250972717036e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.762472090272876e-09</v>
+        <v>7.762472090272881e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.603051125429438e-09</v>
+        <v>7.603051125429449e-09</v>
       </c>
       <c r="U4" t="n">
         <v>7.971229992986793e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.793450644527009e-09</v>
+        <v>7.793450644527034e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.3696128035809e-09</v>
+        <v>8.369612803580925e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.943511731416124e-09</v>
+        <v>9.943511731416147e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.763586037189123e-09</v>
+        <v>9.763586037189113e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.576364236157854e-09</v>
+        <v>7.576364236157873e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.187619241200597e-09</v>
+        <v>8.18761924120061e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.786241482591938e-09</v>
+        <v>7.786241482591958e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1710,31 +1710,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.782237531586635e-08</v>
+        <v>2.782237531586633e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.909364819155355e-08</v>
+        <v>2.909364819155357e-08</v>
       </c>
       <c r="D5" t="n">
         <v>3.422779669872602e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.61079610727289e-08</v>
+        <v>1.610796107272894e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.035258783476081e-08</v>
+        <v>3.035258783476082e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.774143607409157e-08</v>
+        <v>3.774143607409198e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.459055245023676e-08</v>
+        <v>3.459055245023675e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3731754789359e-08</v>
+        <v>3.373175478935896e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.527376346544486e-08</v>
+        <v>3.527376346544471e-08</v>
       </c>
       <c r="K5" t="n">
         <v>3.565032499219213e-08</v>
@@ -1743,52 +1743,52 @@
         <v>3.37648375156117e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.780049738796017e-08</v>
+        <v>3.780049738796014e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.859127663393744e-08</v>
+        <v>2.859127663393745e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.98975530322341e-08</v>
+        <v>2.989755303223405e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.079783592865801e-08</v>
+        <v>3.079783592865798e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.433070148314193e-08</v>
+        <v>3.433070148314191e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.301744459684146e-08</v>
+        <v>3.301744459684144e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.170741583744852e-08</v>
+        <v>3.170741583744854e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.749438661704787e-08</v>
+        <v>3.749438661704784e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.464997695697806e-08</v>
+        <v>3.464997695697813e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.418966448159574e-08</v>
+        <v>4.418966448159558e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.203691334817182e-08</v>
+        <v>7.203691334817186e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>6.974398540133508e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.004564357514305e-08</v>
+        <v>3.004564357514302e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.109826872448798e-08</v>
+        <v>4.109826872448794e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.633409157017462e-08</v>
+        <v>3.633409157017473e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.229647609816861e-08</v>
+        <v>9.88319787252662e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.225240687902451e-08</v>
+        <v>9.839128653382519e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.254911363948673e-08</v>
+        <v>1.254911363948678e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.219779653039834e-08</v>
+        <v>9.784518304756363e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.233137454782221e-08</v>
+        <v>9.918096322180229e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.046314083247609e-08</v>
+        <v>1.287641905811811e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.011585883613627e-08</v>
+        <v>1.252913706177828e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.011289622714576e-08</v>
+        <v>1.25261744527878e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.026602544583507e-08</v>
+        <v>1.267930367147709e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.260114091566592e-08</v>
+        <v>1.018786269002393e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.016059926714629e-08</v>
+        <v>1.257387749278831e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.030273939289952e-08</v>
+        <v>1.271601761854154e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.233072428946454e-08</v>
+        <v>1.233072428946456e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.856712026840669e-09</v>
+        <v>1.244442471469667e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.240396064156655e-08</v>
+        <v>1.240396064156654e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01403485470636e-08</v>
+        <v>1.255362677270562e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.018356966461944e-08</v>
+        <v>1.259684789026145e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.243742692541798e-08</v>
+        <v>1.0024148699776e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.04010400195332e-08</v>
+        <v>1.281431824517522e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.021454821887357e-08</v>
+        <v>1.262782644451559e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.093838086694466e-08</v>
+        <v>1.093838086694465e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.236460930576268e-08</v>
+        <v>1.236460930576271e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.232206356254193e-08</v>
+        <v>1.232206356254195e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.241074003614642e-08</v>
+        <v>9.997461810504416e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.060871681554715e-08</v>
+        <v>1.060871681554717e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.021057361271166e-08</v>
+        <v>1.021057361271168e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.373608447738144e-08</v>
+        <v>1.373608447738143e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.369201525823734e-08</v>
+        <v>1.369201525823732e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.398872201869958e-08</v>
+        <v>1.398872201869955e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.363740490961116e-08</v>
+        <v>1.363740490961114e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.377098292703505e-08</v>
+        <v>1.377098292703504e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.431602743733093e-08</v>
+        <v>1.431602743733092e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.396874544099109e-08</v>
+        <v>1.396874544099107e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.39657828320006e-08</v>
+        <v>1.396578283200056e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.411891205068989e-08</v>
+        <v>1.411891205068986e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.404074929487875e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.401348587200111e-08</v>
+        <v>1.401348587200108e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.415562599775434e-08</v>
+        <v>1.415562599775431e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.375185599455451e-08</v>
+        <v>1.375185599455449e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.386549932011904e-08</v>
+        <v>1.386549932011905e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.384356902077937e-08</v>
+        <v>1.384356902077932e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.399323515191841e-08</v>
+        <v>1.399323515191838e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.403645626947426e-08</v>
+        <v>1.403645626947423e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.387703530463082e-08</v>
+        <v>1.387703530463079e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.425526738752215e-08</v>
+        <v>1.425526738752212e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.406743482372837e-08</v>
+        <v>1.406743482372836e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.464359698278229e-08</v>
+        <v>1.464359698278227e-08</v>
       </c>
       <c r="X7" t="n">
         <v>1.621749591061749e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.604628266859034e-08</v>
+        <v>1.604628266859033e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.385034841535925e-08</v>
+        <v>1.385034841535922e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.446160342040197e-08</v>
+        <v>1.446160342040196e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.406022566179331e-08</v>
+        <v>1.406022566179332e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.042800351347681e-08</v>
+        <v>3.042800351347689e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.534162514972802e-08</v>
+        <v>4.534162514972809e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.563833191019019e-08</v>
+        <v>4.56383319101903e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.528701480110182e-08</v>
+        <v>3.732248564441209e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.279313538443056e-08</v>
+        <v>3.279313538443057e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.596563732882153e-08</v>
+        <v>4.906721196815152e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.561835533248168e-08</v>
+        <v>4.561835533248174e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.561539272349123e-08</v>
+        <v>4.561539272349131e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.576852194218056e-08</v>
+        <v>4.576852194218055e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.569035918636938e-08</v>
+        <v>4.569035918636944e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.566309576349173e-08</v>
+        <v>4.566309576349171e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.580523588924494e-08</v>
+        <v>4.580523588924504e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.699349701302389e-08</v>
+        <v>3.699349701302387e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.632609441489578e-08</v>
+        <v>3.632609441489584e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.759596041053e-08</v>
+        <v>2.759596041053006e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.564284504340909e-08</v>
+        <v>4.564284504340912e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.568606616096493e-08</v>
+        <v>4.568606616096492e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.55266451961214e-08</v>
+        <v>4.55266451961215e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.670063087626028e-08</v>
+        <v>3.86042488197498e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.571704471521898e-08</v>
+        <v>4.163038404403439e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.62961464913986e-08</v>
+        <v>4.629614649139864e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.134078939005781e-08</v>
+        <v>3.134078939005784e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.257031337096922e-08</v>
+        <v>6.257031337096932e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.549995830684985e-08</v>
+        <v>3.026442066431549e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.611121331189263e-08</v>
+        <v>4.611121331189265e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.133439439566407e-08</v>
+        <v>6.133439439566423e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.234133845118177e-08</v>
+        <v>2.234133845118174e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.65712475865566e-08</v>
+        <v>2.657124758655657e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.686795434701884e-08</v>
+        <v>2.686795434701883e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.651663723793042e-08</v>
+        <v>2.553022163800623e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.665021525535432e-08</v>
+        <v>1.679752668163861e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.719525976565019e-08</v>
+        <v>2.719526128807921e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.684797776931034e-08</v>
+        <v>2.684797776931031e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.684501516031984e-08</v>
+        <v>2.68450151603198e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.699814437900918e-08</v>
+        <v>2.699814437900915e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.691998162319801e-08</v>
+        <v>2.691998162319799e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.689271820032038e-08</v>
+        <v>2.689271820032037e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.703485832607359e-08</v>
+        <v>2.703485832607357e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.133406587115019e-08</v>
+        <v>3.133406587115014e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.804789733850376e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.846958147823058e-08</v>
+        <v>2.846958147823053e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.672280287152764e-08</v>
+        <v>2.672280287152763e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.687246748023766e-08</v>
+        <v>2.687246748023764e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.691568859779352e-08</v>
+        <v>2.69156885977935e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.675626763295008e-08</v>
+        <v>2.675626763295007e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.713315895270727e-08</v>
+        <v>2.713315895270721e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.694666715204767e-08</v>
+        <v>3.187874496638954e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.752282931110153e-08</v>
+        <v>2.752282931110152e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.909672823893677e-08</v>
+        <v>2.909672823893678e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.892551499690959e-08</v>
+        <v>2.892551499690961e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.672958074367848e-08</v>
+        <v>2.415275245742747e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.734083574872125e-08</v>
+        <v>2.734083574872121e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.69394579901126e-08</v>
+        <v>2.693945799011258e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,82 +2306,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.224340938318364e-08</v>
+        <v>1.22434093831837e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.043857867635227e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.213954685254653e-08</v>
+        <v>1.213954685254659e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.204551733010426e-08</v>
+        <v>1.204551733010429e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.203206562114588e-08</v>
+        <v>1.203206562114593e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.254767615483817e-08</v>
+        <v>1.254767615483823e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.199063990117705e-08</v>
+        <v>1.19906399011771e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.201205944156433e-08</v>
+        <v>1.201205944156437e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.233348484935125e-08</v>
+        <v>1.233348484935127e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.206747550769704e-08</v>
+        <v>1.206747550769702e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.241673895990177e-08</v>
+        <v>1.241673895990183e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.284069338533137e-08</v>
+        <v>1.284069338533138e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.204475883243057e-08</v>
+        <v>1.204475883243061e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.62088274805725e-08</v>
+        <v>1.620882748057247e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.231887980766374e-08</v>
+        <v>1.231887980766379e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.203827269655647e-08</v>
+        <v>1.203827269655654e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.199778050311607e-08</v>
+        <v>1.199778050311611e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232024806759268e-08</v>
+        <v>1.232024806759273e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.210229891846802e-08</v>
+        <v>1.210229891846807e-08</v>
       </c>
       <c r="U2" t="n">
         <v>1.249407657053903e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.203409059163857e-08</v>
+        <v>1.203409059163863e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.232588302185591e-08</v>
+        <v>1.232588302185589e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.22096433801918e-08</v>
+        <v>1.220964338019185e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.216006299446636e-08</v>
+        <v>1.216006299446646e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.173084831675041e-08</v>
+        <v>1.173084831675052e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.213238344064578e-08</v>
+        <v>1.213238344064587e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.255979968769122e-08</v>
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.410540403537576e-08</v>
+        <v>1.410540403537588e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.579231543508192e-09</v>
+        <v>9.579231543508198e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.337842766682263e-08</v>
+        <v>1.337842766682276e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.267990489730203e-08</v>
+        <v>1.267990489730212e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26105969547234e-08</v>
+        <v>1.261059695472343e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.627279893177573e-08</v>
+        <v>1.627279893177583e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.231497292194515e-08</v>
+        <v>1.231497292194523e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.246640510941615e-08</v>
+        <v>1.246640510941625e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.475413900354642e-08</v>
+        <v>1.475413900354648e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.28616895694476e-08</v>
+        <v>1.286168956944773e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.535055612057949e-08</v>
+        <v>1.535055612057959e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.843611720259555e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.269815145798144e-08</v>
+        <v>1.269815145798155e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.02396471333524e-08</v>
+        <v>2.023964713335242e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.464333907712713e-08</v>
+        <v>1.464333907712726e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.265230199828984e-08</v>
+        <v>1.265230199828987e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.236474597851781e-08</v>
+        <v>1.236474597851788e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.465530201216944e-08</v>
+        <v>1.465530201216949e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.311203984240534e-08</v>
+        <v>1.311203984240543e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.602171952988179e-08</v>
+        <v>1.60217195298818e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.261950930097119e-08</v>
+        <v>1.261950930097129e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.344394980973772e-08</v>
+        <v>1.344394980973775e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.387839371472875e-08</v>
+        <v>1.387839371472881e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352028457641898e-08</v>
+        <v>1.352028457641905e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.255784744203579e-08</v>
+        <v>1.255784744203584e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.332273557542562e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.638607315568992e-08</v>
+        <v>1.638607315568991e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2482,43 +2482,43 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.168549805152911e-08</v>
+        <v>1.168549805152912e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.488305219962662e-09</v>
+        <v>8.488305219962657e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.051232298885831e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.45021627715549e-09</v>
+        <v>9.450216277155501e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.298273036378652e-09</v>
+        <v>9.298273036378648e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.512233120699711e-08</v>
+        <v>1.512233120699708e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.830350472558068e-09</v>
+        <v>8.830350472558078e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.072294034707763e-09</v>
+        <v>9.072294034707752e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.269155551498671e-08</v>
+        <v>1.269155551498673e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.698243994326574e-09</v>
+        <v>9.698243994326567e-09</v>
       </c>
       <c r="L4" t="n">
         <v>1.36433353561052e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.849558045650647e-08</v>
+        <v>1.849558045650646e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.441648697004963e-09</v>
+        <v>9.441648697004946e-09</v>
       </c>
       <c r="O4" t="n">
         <v>1.083578682563609e-08</v>
@@ -2527,40 +2527,40 @@
         <v>1.253797121414245e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.368384808537199e-09</v>
+        <v>9.368384808537191e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.911006856298336e-09</v>
+        <v>8.911006856298348e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.255342633947042e-08</v>
+        <v>1.255342633947044e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.009159043854525e-08</v>
+        <v>1.009159043854523e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.469221719450922e-08</v>
+        <v>1.469221719450925e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.260220409870853e-09</v>
+        <v>9.260220409870856e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.002412249156866e-08</v>
+        <v>1.002412249156865e-08</v>
       </c>
       <c r="X4" t="n">
         <v>1.130409551460757e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.066869606512839e-08</v>
+        <v>1.066869606512842e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>1.023083362073113e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.043140895610748e-08</v>
+        <v>1.043140895610749e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.523314725017255e-08</v>
+        <v>1.523314725017252e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.495811187956469e-08</v>
+        <v>8.495811187956464e-08</v>
       </c>
       <c r="C5" t="n">
         <v>3.096597508242675e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.072641020637365e-08</v>
+        <v>7.072641020637361e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.538928630937668e-08</v>
+        <v>3.538928630937671e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.736427439335596e-08</v>
+        <v>4.7364274393356e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.476210347778324e-07</v>
+        <v>1.476210347778335e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.853541238527826e-08</v>
+        <v>3.853541238527834e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.230912100659918e-08</v>
+        <v>4.230912100659923e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.074445516072179e-07</v>
+        <v>1.074445516072184e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>5.402063094680321e-08</v>
+        <v>5.402063094680322e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.264761264035741e-07</v>
+        <v>1.264761264035743e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.322840164919511e-07</v>
+        <v>2.322840164919515e-07</v>
       </c>
       <c r="N5" t="n">
         <v>1.399036843519626e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>6.962124503731193e-08</v>
+        <v>6.962124503731199e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.006866523810279e-07</v>
+        <v>1.006866523810282e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.724663529879976e-08</v>
+        <v>4.724663529879978e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.939875929736282e-08</v>
+        <v>3.939875929736291e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0220107422253e-07</v>
+        <v>1.022010742225303e-07</v>
       </c>
       <c r="T5" t="n">
-        <v>6.246676708888575e-08</v>
+        <v>6.246676708888561e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.452296190340734e-07</v>
+        <v>1.452296190340733e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.465476251863949e-08</v>
+        <v>4.465476251863922e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.875159543216971e-08</v>
+        <v>5.875159543216974e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.552122277017376e-08</v>
+        <v>8.552122277017393e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.256771172409133e-08</v>
+        <v>7.256771172409153e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.027350292521676e-08</v>
+        <v>6.02735029252167e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.665684641487861e-08</v>
+        <v>6.665684641487879e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.724863825317982e-07</v>
+        <v>1.72486382531798e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,82 +2658,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.735907268953771e-08</v>
+        <v>1.432018863509626e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.416187985797124e-08</v>
+        <v>1.416187985797128e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.314701357242545e-08</v>
+        <v>1.618589762686693e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.208490686072261e-08</v>
+        <v>1.208490686072263e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.497184767438724e-08</v>
+        <v>1.19329636199458e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.079590584500569e-08</v>
+        <v>1.775702179056421e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.14650410561252e-08</v>
+        <v>1.450392511056666e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.170698461827489e-08</v>
+        <v>1.170698461827491e-08</v>
       </c>
       <c r="J6" t="n">
         <v>1.836513015299529e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.23329345778937e-08</v>
+        <v>1.537181863233518e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.627802593967234e-08</v>
+        <v>1.627802593967235e-08</v>
       </c>
       <c r="M6" t="n">
         <v>2.113027104007358e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.208457388840045e-08</v>
+        <v>1.208457388840057e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.653145735841693e-08</v>
+        <v>1.653145735841696e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.823366753372165e-08</v>
+        <v>1.823366753372171e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.200307539210434e-08</v>
+        <v>1.504195944654581e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.154569743986547e-08</v>
+        <v>1.458458149430692e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.518811692303755e-08</v>
+        <v>1.822700097747906e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.576516507655383e-08</v>
+        <v>1.272628102211239e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.044115801712416e-08</v>
+        <v>1.740227396268271e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.493379504787943e-08</v>
+        <v>1.493379504787946e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.571977492047054e-08</v>
+        <v>1.571977492047057e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.39387860981747e-08</v>
+        <v>1.697767015261615e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.351735287732651e-08</v>
+        <v>1.351735287732662e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.286552420429826e-08</v>
+        <v>1.590440825873974e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.610498359411606e-08</v>
+        <v>1.306609953967462e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>1.790319446925375e-08</v>
@@ -2746,46 +2746,46 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.874997097250431e-08</v>
+        <v>1.87499709725043e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.555277814093784e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.75767959098335e-08</v>
+        <v>1.757679590983353e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.651468919813068e-08</v>
+        <v>1.651468919813067e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.636274595735384e-08</v>
+        <v>1.636274595735385e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.218680412797229e-08</v>
+        <v>2.218680412797228e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.589482339353327e-08</v>
+        <v>1.589482339353328e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.613676695568295e-08</v>
+        <v>1.613676695568298e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.97560284359619e-08</v>
+        <v>1.975602843596189e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.676271691530176e-08</v>
+        <v>1.676271691530178e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.070780827708038e-08</v>
+        <v>2.07078082770804e-08</v>
       </c>
       <c r="M7" t="n">
         <v>2.556005337748165e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.650612161798014e-08</v>
+        <v>1.650612161798016e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.789981128435931e-08</v>
+        <v>1.789981128435932e-08</v>
       </c>
       <c r="P7" t="n">
         <v>1.960199567286566e-08</v>
@@ -2794,31 +2794,31 @@
         <v>1.64328577295124e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.597547977727353e-08</v>
+        <v>1.597547977727355e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.961789926044561e-08</v>
+        <v>1.961789926044564e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.715606335952043e-08</v>
+        <v>1.715606335952044e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.183033660328385e-08</v>
+        <v>2.183033660328386e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.632469333084602e-08</v>
+        <v>1.632469333084603e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.708859541254384e-08</v>
+        <v>1.708859541254385e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.836856843558275e-08</v>
+        <v>1.836856843558277e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.780853517070994e-08</v>
+        <v>1.780853517070995e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.729530654170632e-08</v>
+        <v>1.729530654170633e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>1.749588187708266e-08</v>
@@ -2840,16 +2840,16 @@
         <v>5.020335068878922e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.22273684576849e-08</v>
+        <v>5.222736845768492e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>5.116526174598205e-08</v>
+        <v>4.238100954730972e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.708622142923442e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.683737667582367e-08</v>
+        <v>6.025817071259356e-08</v>
       </c>
       <c r="H8" t="n">
         <v>5.054539594138465e-08</v>
@@ -2858,61 +2858,61 @@
         <v>5.078733950353435e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.440660098381328e-08</v>
+        <v>5.440660098381325e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.141328946315315e-08</v>
+        <v>5.141328946315318e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.535838082493177e-08</v>
+        <v>5.535838082493178e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>6.0210625925333e-08</v>
+        <v>6.021062592533302e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.836863360086804e-08</v>
+        <v>3.8368633600868e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.327704181087224e-08</v>
+        <v>4.327704181087225e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.411779368562817e-08</v>
+        <v>4.41177936856282e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.134419925926889e-08</v>
+        <v>3.134419925926886e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.062605232512496e-08</v>
+        <v>5.062605232512495e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.426847180829697e-08</v>
+        <v>5.426847180829703e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.180663590737188e-08</v>
+        <v>5.180663590737182e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.633020918237922e-08</v>
+        <v>4.842959902346643e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>5.097526587869745e-08</v>
+        <v>4.646525610314606e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.174241012782138e-08</v>
+        <v>5.174241012782135e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.479190765633947e-08</v>
+        <v>3.47919076563395e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.886017517625397e-08</v>
+        <v>6.886017517625401e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.194587908955771e-08</v>
+        <v>3.514227370350201e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.214645442493405e-08</v>
+        <v>5.2146454424934e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.418085803588416e-08</v>
+        <v>7.418085803588411e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.168450648794628e-08</v>
+        <v>3.16845064879463e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.422445526501505e-08</v>
+        <v>3.422445526501508e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.62484730339107e-08</v>
+        <v>3.624847303391078e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.518636632220788e-08</v>
+        <v>3.386225785901492e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.503442308143103e-08</v>
+        <v>2.180874514851621e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.08584812520495e-08</v>
+        <v>4.085848179638582e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.456650051761045e-08</v>
+        <v>3.456650051761054e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.480844407976016e-08</v>
+        <v>3.480844407976021e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.842770556003911e-08</v>
+        <v>3.842770556003916e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.543439403937896e-08</v>
+        <v>3.543439403937902e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.93794854011576e-08</v>
+        <v>3.937948540115767e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.423173050155883e-08</v>
+        <v>4.423173050155891e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.517779874205736e-08</v>
+        <v>3.517779874205738e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.847321881237379e-08</v>
+        <v>3.847321881237385e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05888992843078e-08</v>
+        <v>4.05888992843079e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.510453539792585e-08</v>
+        <v>3.510453539792586e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.464715690135072e-08</v>
+        <v>3.464715690135074e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.828957638452283e-08</v>
+        <v>3.828957638452292e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.582774048359764e-08</v>
+        <v>3.582774048359765e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.050373342416799e-08</v>
+        <v>4.050373342416805e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.499637045492328e-08</v>
+        <v>4.161690346990091e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.576027253662103e-08</v>
+        <v>3.576027253662109e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.704024555965994e-08</v>
+        <v>3.704024555965999e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.648021229478717e-08</v>
+        <v>3.648021229478721e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.596698366578353e-08</v>
+        <v>3.250799765846364e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.616755900115988e-08</v>
+        <v>3.616755900115994e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.096929729522496e-08</v>
+        <v>4.096929729522502e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,82 +3166,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.222204257552981e-08</v>
+        <v>1.22220425755298e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.047702278292213e-08</v>
+        <v>1.047702278292214e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.220930952668195e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.206364265036837e-08</v>
+        <v>1.206364265036835e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.209009660797501e-08</v>
+        <v>1.209009660797499e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.25476883835978e-08</v>
+        <v>1.254768838359777e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.201037879433954e-08</v>
+        <v>1.201037879433953e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.217306717643697e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.235382708893095e-08</v>
+        <v>1.235382708893091e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.223805252800372e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.239882972524644e-08</v>
+        <v>1.239882972524641e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.276599552206994e-08</v>
+        <v>1.276599552206995e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.206948801992679e-08</v>
+        <v>1.206948801992676e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.621707679570405e-08</v>
+        <v>1.621707679570401e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.235119923087212e-08</v>
+        <v>1.235119923087214e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.207318102372558e-08</v>
+        <v>1.207318102372555e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.201603270366862e-08</v>
+        <v>1.201603270366864e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.23291160314355e-08</v>
+        <v>1.232911603143551e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.213822792157666e-08</v>
+        <v>1.213822792157665e-08</v>
       </c>
       <c r="U2" t="n">
         <v>1.234969313525541e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.21032057015974e-08</v>
+        <v>1.210320570159738e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.24046956437618e-08</v>
+        <v>1.240469564376179e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.233171448838235e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.238423062395229e-08</v>
+        <v>1.238423062395231e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.179453502266138e-08</v>
+        <v>1.179453502266135e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.220425674571706e-08</v>
+        <v>1.220425674571705e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.255601116977759e-08</v>
@@ -3254,31 +3254,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377641011016024e-08</v>
+        <v>1.377641011016023e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.651740053110901e-09</v>
+        <v>9.65174005311092e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.369766366835806e-08</v>
+        <v>1.369766366835808e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.263024295058712e-08</v>
+        <v>1.26302429505871e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.284594883448853e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.60917139300358e-08</v>
+        <v>1.609171393003582e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.227623352815057e-08</v>
+        <v>1.22762335281506e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.343983434836434e-08</v>
+        <v>1.343983434836439e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.471996351268392e-08</v>
+        <v>1.471996351268396e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.389581041641711e-08</v>
@@ -3287,52 +3287,52 @@
         <v>1.504314932479232e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.772954121170161e-08</v>
+        <v>1.772954121170163e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.269560748503783e-08</v>
+        <v>1.269560748503784e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.006639434933802e-08</v>
+        <v>2.00663943493381e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.469362801406775e-08</v>
+        <v>1.469362801406777e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.272209451063563e-08</v>
+        <v>1.272209451063565e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.231563395760759e-08</v>
+        <v>1.231563395760755e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.453902614555597e-08</v>
+        <v>1.453902614555598e-08</v>
       </c>
       <c r="T3" t="n">
         <v>1.318962412048735e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.461507706303979e-08</v>
+        <v>1.461507706303982e-08</v>
       </c>
       <c r="V3" t="n">
         <v>1.293198041915899e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.355874554613969e-08</v>
+        <v>1.355874554613967e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.45712905822761e-08</v>
+        <v>1.457129058227619e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.494095885411183e-08</v>
+        <v>1.494095885411191e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.268057308096731e-08</v>
+        <v>1.268057308096733e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.365684114733314e-08</v>
+        <v>1.365684114733309e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.618263433278754e-08</v>
+        <v>1.618263433278757e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.109252965728991e-08</v>
+        <v>1.109252965728992e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.521641508875818e-09</v>
+        <v>8.521641508875817e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.094870401306145e-08</v>
+        <v>1.094870401306144e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>9.303329635025793e-09</v>
+        <v>9.303329635025835e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.602139255614526e-09</v>
+        <v>9.602139255614537e-09</v>
       </c>
       <c r="G4" t="n">
         <v>1.477084886389075e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.7016898785959e-09</v>
+        <v>8.701689878595914e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.053932999473949e-08</v>
+        <v>1.053932999473952e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.257008142116102e-08</v>
+        <v>1.257008142116103e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.127336943542464e-08</v>
+        <v>1.127336943542476e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.30894218394458e-08</v>
+        <v>1.308942183944582e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.731417122303113e-08</v>
+        <v>1.731417122303116e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.369355773190934e-09</v>
+        <v>9.369355773190948e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>1.046616412310547e-08</v>
+        <v>1.046616412310563e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>1.255141349437833e-08</v>
+        <v>1.255141349437857e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.411069949963884e-09</v>
+        <v>9.411069949963924e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.765553385394967e-09</v>
+        <v>8.765553385394989e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2301973597968e-08</v>
+        <v>1.230197359796808e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.014580458424346e-08</v>
+        <v>1.014580458424352e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.231584568437296e-08</v>
+        <v>1.231584568437315e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.691793069201426e-09</v>
+        <v>9.691793069201411e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.000957505019945e-08</v>
+        <v>1.000957505019946e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.23313243645317e-08</v>
+        <v>1.233132436453184e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.286306551411937e-08</v>
+        <v>1.286306551411938e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.028917068240766e-08</v>
+        <v>1.028917068240767e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.089163052766888e-08</v>
+        <v>1.08916305276689e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.484447145765022e-08</v>
+        <v>1.484447145765026e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,82 +3430,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.109321560532075e-08</v>
+        <v>7.10932156053209e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.089320199306453e-08</v>
+        <v>3.08932019930646e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.483546771354457e-08</v>
+        <v>7.483546771354619e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.133338204358003e-08</v>
+        <v>3.133338204358058e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.055995058907564e-08</v>
+        <v>5.055995058907568e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.315658618294521e-07</v>
+        <v>1.315658618294517e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.423742205193687e-08</v>
+        <v>3.423742205193688e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.80272848485027e-08</v>
+        <v>6.802728484850395e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.89650273625021e-08</v>
+        <v>9.896502736250189e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.695351479727633e-08</v>
+        <v>7.695351479727607e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.090029386948719e-07</v>
+        <v>1.090029386948718e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.960765209563658e-07</v>
+        <v>1.960765209563662e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>9.183640473751671e-08</v>
+        <v>9.183640473751808e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.985094269519264e-08</v>
+        <v>5.985094269519191e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.452273017874786e-08</v>
+        <v>9.45227301787488e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.556010897239138e-08</v>
+        <v>4.556010897239183e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.487370560287141e-08</v>
+        <v>3.487370560287147e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>9.166928947552341e-08</v>
+        <v>9.166928947552712e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.025833024274342e-08</v>
+        <v>6.025833024274376e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.484434740898969e-08</v>
+        <v>9.484434740899073e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.921890822321505e-08</v>
+        <v>4.921890822321251e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.548386656345435e-08</v>
+        <v>5.548386656345436e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>9.929799273332147e-08</v>
+        <v>9.92979927333224e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.071248915985309e-07</v>
+        <v>1.071248915985334e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.690802207206773e-08</v>
+        <v>5.690802207206782e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.1358983371743e-08</v>
+        <v>7.135898337174446e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>1.549428080246395e-07</v>
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.637929165920768e-08</v>
+        <v>1.354405380071956e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.097316565230544e-08</v>
+        <v>1.097316565230548e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.623546601497923e-08</v>
+        <v>1.623546601497941e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.175485377845541e-08</v>
+        <v>1.175485377845545e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.205366339904417e-08</v>
+        <v>1.488890125753235e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.005761086580853e-08</v>
+        <v>1.722237300732037e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.115321402202554e-08</v>
+        <v>1.115321402202558e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.582609199665727e-08</v>
+        <v>1.299085413816926e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.785684342307879e-08</v>
+        <v>1.785684342307882e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.372489357885426e-08</v>
+        <v>1.65601314373425e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.837618384136361e-08</v>
+        <v>1.554094598287545e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.260093322494894e-08</v>
+        <v>2.260093322494897e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.182833811227066e-08</v>
+        <v>1.182833811227067e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.57750056392143e-08</v>
+        <v>1.29251464621853e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.786030003917068e-08</v>
+        <v>1.786030003917076e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.469783195188166e-08</v>
+        <v>1.469783195188173e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.405231538731276e-08</v>
+        <v>1.405231538731278e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.475349774139759e-08</v>
+        <v>1.475349774139766e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.259732872767312e-08</v>
+        <v>1.259732872767318e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.766406044658197e-08</v>
+        <v>1.482882258809389e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.497855507111921e-08</v>
+        <v>1.497855507111922e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.531837994023915e-08</v>
+        <v>1.261565683051006e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.478284850796134e-08</v>
+        <v>1.478284850796156e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.550739921112446e-08</v>
+        <v>1.550739921112456e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.557593268432546e-08</v>
+        <v>1.274069482583731e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.334315467109851e-08</v>
+        <v>1.617839252958672e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.732759647096994e-08</v>
+        <v>1.732759647096998e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.773352039852839e-08</v>
+        <v>1.773352039852843e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.516263225011431e-08</v>
+        <v>1.516263225011433e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.758969475429995e-08</v>
+        <v>1.758969475430001e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.594432037626429e-08</v>
+        <v>1.594432037626434e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.624312999685302e-08</v>
+        <v>1.624312999685305e-08</v>
       </c>
       <c r="G7" t="n">
         <v>2.141183960512924e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.534268061983439e-08</v>
+        <v>1.534268061983442e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.718032073597799e-08</v>
+        <v>1.718032073597807e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.921107216239951e-08</v>
+        <v>1.92110721623995e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.791436017666311e-08</v>
+        <v>1.791436017666321e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.973041258068429e-08</v>
+        <v>1.973041258068431e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.395516196426964e-08</v>
+        <v>2.395516196426963e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.601034651442942e-08</v>
+        <v>1.601034651442947e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.710673529910009e-08</v>
+        <v>1.71067352991002e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.919198467037282e-08</v>
+        <v>1.919198467037312e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.605206069120236e-08</v>
+        <v>1.605206069120243e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.540654412663347e-08</v>
+        <v>1.540654412663351e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.894296433920646e-08</v>
+        <v>1.894296433920667e-08</v>
       </c>
       <c r="T7" t="n">
         <v>1.678679532548197e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.901748532910038e-08</v>
+        <v>1.901748532910052e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.633278381043993e-08</v>
+        <v>1.633278381043991e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.665056579143794e-08</v>
+        <v>1.665056579143797e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.897231510577021e-08</v>
+        <v>1.897231510577028e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.956550901564908e-08</v>
+        <v>1.956550901564909e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.693016142364614e-08</v>
+        <v>1.693016142364616e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.753262126890737e-08</v>
+        <v>1.753262126890741e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.148546219888873e-08</v>
+        <v>2.148546219888875e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3697,82 +3697,82 @@
         <v>3.465225555387223e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.750701876281311e-08</v>
+        <v>4.75070187628131e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.993408126699883e-08</v>
+        <v>4.993408126699885e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.828870688896314e-08</v>
+        <v>4.007500256896525e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.556500135052547e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.375622611782805e-08</v>
+        <v>5.695483541571374e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.768706713253321e-08</v>
+        <v>4.768706713253326e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.952470724867688e-08</v>
+        <v>4.952470724867693e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.155545867509834e-08</v>
+        <v>5.155545867509836e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.025874668936198e-08</v>
+        <v>5.025874668936208e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.20747990933831e-08</v>
+        <v>5.207479909338315e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.629954847696851e-08</v>
+        <v>5.629954847696843e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.639727257048307e-08</v>
+        <v>3.63972725704831e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.078009487994625e-08</v>
+        <v>4.078009487994637e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.20598628283779e-08</v>
+        <v>4.205986282837817e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.993930328090838e-08</v>
+        <v>2.993930328090839e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.775093063933228e-08</v>
+        <v>4.775093063933235e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.128735085190522e-08</v>
+        <v>5.128735085190539e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.913118183818084e-08</v>
+        <v>4.913118183818086e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.187025339103028e-08</v>
+        <v>4.383332333973724e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.867717032313878e-08</v>
+        <v>4.446077873490294e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.899798388884428e-08</v>
+        <v>4.89979838888444e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.427334929498121e-08</v>
+        <v>3.427334929498133e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.724676008564194e-08</v>
+        <v>6.724676008564209e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.9274547936345e-08</v>
+        <v>3.356235718528231e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.987700778160623e-08</v>
+        <v>4.987700778160636e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.994323142842255e-08</v>
+        <v>6.994323142842258e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.866461847577327e-08</v>
+        <v>2.866461847577331e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.115188778599336e-08</v>
+        <v>3.115188778599341e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.357895029017899e-08</v>
+        <v>3.35789502901791e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.193357591214332e-08</v>
+        <v>3.076617436917966e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.223238553273207e-08</v>
+        <v>2.057195112689308e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.740109514100831e-08</v>
+        <v>3.740109587766659e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.133193615571349e-08</v>
+        <v>3.133193615571353e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.316957627185705e-08</v>
+        <v>3.316957627185718e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.52003276982786e-08</v>
+        <v>3.520032769827862e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.390361571254222e-08</v>
+        <v>3.39036157125423e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.571966811656335e-08</v>
+        <v>3.571966811656339e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.994441750014869e-08</v>
+        <v>3.994441750014872e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.199960205030849e-08</v>
+        <v>3.199960205030852e-08</v>
       </c>
       <c r="O9" t="n">
         <v>3.477267813970929e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.722248682419821e-08</v>
+        <v>3.722248682419828e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.204131696373974e-08</v>
+        <v>3.204131696373978e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.139579966251253e-08</v>
+        <v>3.139579966251257e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.493221987508555e-08</v>
+        <v>3.493221987508575e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.277605086136104e-08</v>
+        <v>3.277605086136114e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.500754472178171e-08</v>
+        <v>3.500754472178188e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.2322039346319e-08</v>
+        <v>3.815904010438273e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.263982132731698e-08</v>
+        <v>3.263982132731702e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.496157064164928e-08</v>
+        <v>3.496157064164936e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.555476455152818e-08</v>
+        <v>3.555476455152827e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.291941695952521e-08</v>
+        <v>2.98697980933985e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.352187680478646e-08</v>
+        <v>3.352187680478654e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.747471773476776e-08</v>
+        <v>3.747471773476781e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.218602150873123e-08</v>
+        <v>1.21860215087312e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.04815027511208e-08</v>
+        <v>1.048150275112079e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.216317890132622e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.203779715301927e-08</v>
+        <v>1.203779715301929e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.210896906389297e-08</v>
+        <v>1.210896906389299e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.247308513149659e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.201375935258792e-08</v>
+        <v>1.20137593525879e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.21773489466193e-08</v>
+        <v>1.217734894661931e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.231769313214694e-08</v>
+        <v>1.231769313214691e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.228382658479464e-08</v>
+        <v>1.22838265847946e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.232653594982819e-08</v>
+        <v>1.232653594982822e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.263698086562964e-08</v>
+        <v>1.263698086562963e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.205144860607006e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.611638914288491e-08</v>
+        <v>1.611638914288483e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.231850436736137e-08</v>
+        <v>1.231850436736138e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.208017287927799e-08</v>
+        <v>1.2080172879278e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.205038041617649e-08</v>
+        <v>1.20503804161765e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.230049892740104e-08</v>
+        <v>1.230049892740105e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.214872113790187e-08</v>
+        <v>1.21487211379019e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.236276168141119e-08</v>
+        <v>1.236276168141124e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.218453016949294e-08</v>
+        <v>1.218453016949295e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.245594096693889e-08</v>
+        <v>1.245594096693893e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.23660599752484e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.259628464145029e-08</v>
+        <v>1.259628464145028e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.180635514154248e-08</v>
+        <v>1.18063551415425e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.222749106853393e-08</v>
+        <v>1.222749106853395e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.250766625094064e-08</v>
+        <v>1.250766625094062e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.35398327342254e-08</v>
+        <v>1.353983273422543e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.696731092076823e-09</v>
+        <v>9.696731092076807e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.338735340562456e-08</v>
+        <v>1.33873534056246e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.246791168797102e-08</v>
+        <v>1.2467911687971e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.300179920210506e-08</v>
+        <v>1.300179920210508e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.557769165334338e-08</v>
+        <v>1.557769165334336e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.232160904983656e-08</v>
+        <v>1.232160904983655e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.349092688908253e-08</v>
+        <v>1.349092688908252e-08</v>
       </c>
       <c r="J3" t="n">
         <v>1.448130253805366e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.424236741835704e-08</v>
+        <v>1.424236741835703e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.454489049378554e-08</v>
+        <v>1.454489049378555e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.682371578654098e-08</v>
+        <v>1.682371578654095e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.25878933605202e-08</v>
+        <v>1.258789336052014e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.954536699180837e-08</v>
+        <v>1.954536699180836e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.447918707943719e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.27926250643269e-08</v>
+        <v>1.279262506432689e-08</v>
       </c>
       <c r="R3" t="n">
         <v>1.258308100044638e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.435529914926012e-08</v>
+        <v>1.43552991492601e-08</v>
       </c>
       <c r="T3" t="n">
         <v>1.328597035864209e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.45251359199463e-08</v>
+        <v>1.452513591994629e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352947434861071e-08</v>
+        <v>1.352947434861069e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.37159367883317e-08</v>
+        <v>1.371593678833169e-08</v>
       </c>
       <c r="X3" t="n">
         <v>1.483393844431067e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.647934226069075e-08</v>
+        <v>1.647934226069073e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.266057831946844e-08</v>
+        <v>1.266057831946842e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.384422244496378e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.585562530059285e-08</v>
+        <v>1.585562530059284e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.066541254433781e-08</v>
+        <v>1.066541254433779e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.535420558961487e-09</v>
+        <v>8.535420558961477e-09</v>
       </c>
       <c r="D4" t="n">
         <v>1.040739478557986e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>8.991150259999245e-09</v>
+        <v>8.991150259999232e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.79506973401435e-09</v>
+        <v>9.79506973401433e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.390792821926367e-08</v>
+        <v>1.390792821926366e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.719632246192328e-09</v>
+        <v>8.719632246192313e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.056745196570834e-08</v>
+        <v>1.056745196570833e-08</v>
       </c>
       <c r="J4" t="n">
         <v>1.214256065753087e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.177016587103183e-08</v>
+        <v>1.177016587103182e-08</v>
       </c>
       <c r="L4" t="n">
         <v>1.225258779636497e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.584947076400648e-08</v>
+        <v>1.584947076400647e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.14534970218629e-09</v>
+        <v>9.145349702186262e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>9.665729689336474e-09</v>
+        <v>9.665729689336466e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.216186737769141e-08</v>
+        <v>1.216186737769138e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.46980358188844e-09</v>
+        <v>9.469803581888416e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>9.13328400594698e-09</v>
+        <v>9.133284005946973e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.195848765042807e-08</v>
+        <v>1.195848765042805e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.024408769680229e-08</v>
+        <v>1.024408769680228e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.20464477448071e-08</v>
+        <v>1.204644774480708e-08</v>
       </c>
       <c r="V4" t="n">
         <v>1.059605004936539e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>1.009510280291556e-08</v>
+        <v>1.009510280291555e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.269902984543583e-08</v>
+        <v>1.26990298454358e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.525631756693662e-08</v>
+        <v>1.525631756693659e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>1.01469775725978e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.113383029924977e-08</v>
+        <v>1.113383029924976e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.428152873127148e-08</v>
+        <v>1.428152873127147e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,82 +4290,82 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.369209997418196e-08</v>
+        <v>6.3692099974182e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.169434606788303e-08</v>
+        <v>3.169434606788302e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.459564097115539e-08</v>
+        <v>6.459564097115538e-08</v>
       </c>
       <c r="E5" t="n">
         <v>2.680598417151026e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.44622123201114e-08</v>
+        <v>5.446221232011133e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.153779388430848e-07</v>
+        <v>1.153779388430847e-07</v>
       </c>
       <c r="H5" t="n">
         <v>3.509219969083649e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.869158763918336e-08</v>
+        <v>6.869158763918335e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.087999230696591e-08</v>
+        <v>9.087999230696588e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.556089536205168e-08</v>
+        <v>8.556089536205166e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.290358712083869e-08</v>
+        <v>9.290358712083873e-08</v>
       </c>
       <c r="M5" t="n">
         <v>1.638386421570501e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>8.58574480366615e-08</v>
+        <v>8.585744803666165e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.772287529868853e-08</v>
+        <v>4.772287529868843e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.69554897292543e-08</v>
+        <v>8.695548972925437e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.681557833553195e-08</v>
+        <v>4.681557833553197e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.246303513404622e-08</v>
+        <v>4.246303513404627e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>8.575143764214664e-08</v>
+        <v>8.575143764214654e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.264150548821239e-08</v>
+        <v>6.264150548821234e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>8.880175187111097e-08</v>
+        <v>8.880175187111068e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>6.348953416112135e-08</v>
+        <v>6.348953416112134e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.752310677386376e-08</v>
+        <v>5.752310677386363e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.044080554502483e-07</v>
+        <v>1.04408055450248e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.515830548165091e-07</v>
+        <v>1.515830548165093e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.414220210642376e-08</v>
+        <v>5.414220210642372e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.633997922767664e-08</v>
+        <v>7.633997922767662e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>1.429053123474062e-07</v>
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.313872235625933e-08</v>
+        <v>1.594719715245404e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.100873037088302e-08</v>
+        <v>1.100873037088301e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.28807045975014e-08</v>
+        <v>1.288070459750138e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.146446007192076e-08</v>
+        <v>1.427293486811547e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.226837954593587e-08</v>
+        <v>1.226837954593586e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.63812380311852e-08</v>
+        <v>1.918971282737991e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.400141685430856e-08</v>
+        <v>1.119294205811383e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.304076177762987e-08</v>
+        <v>1.304076177762985e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.46158704694524e-08</v>
+        <v>1.74243452656471e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.705195047914803e-08</v>
+        <v>1.705195047914804e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.472589760828652e-08</v>
+        <v>1.753437240448121e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.832278057592802e-08</v>
+        <v>1.832278057592799e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.163028016105319e-08</v>
+        <v>1.163028016105316e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.215066014820333e-08</v>
+        <v>1.497153563829247e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.746773162000648e-08</v>
+        <v>1.44746986808153e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>1.475158819000466e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.441506861406323e-08</v>
+        <v>1.441506861406322e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.724027225854431e-08</v>
+        <v>1.72402722585443e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.271739750872382e-08</v>
+        <v>1.552587230491854e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.737143814475177e-08</v>
+        <v>1.456296334855709e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.587783465748162e-08</v>
+        <v>1.30693598612869e-08</v>
       </c>
       <c r="W6" t="n">
         <v>1.540088852305944e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.517233965735731e-08</v>
+        <v>1.517233965735732e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.791364897424255e-08</v>
+        <v>1.791364897424254e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.542876218071404e-08</v>
+        <v>1.542876218071403e-08</v>
       </c>
       <c r="AA6" t="n">
         <v>1.641561490736601e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.678503767118449e-08</v>
+        <v>1.678503767118447e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4472,79 +4472,79 @@
         <v>1.520833627251639e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.708031049913479e-08</v>
+        <v>1.708031049913478e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.566406597355413e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.646798544756925e-08</v>
+        <v>1.646798544756923e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.058084393281859e-08</v>
+        <v>2.058084393281857e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.539254795974723e-08</v>
+        <v>1.539254795974722e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.724036767926325e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.88154763710858e-08</v>
+        <v>1.881547637108578e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.844308158458672e-08</v>
+        <v>1.844308158458671e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.892550350991989e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.25223864775614e-08</v>
+        <v>2.252238647756138e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.58182654157412e-08</v>
+        <v>1.581826541574117e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.633822380497862e-08</v>
+        <v>1.633822380497861e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.883436149333357e-08</v>
+        <v>1.883436149333356e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.614271929544334e-08</v>
+        <v>1.614271929544333e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.580619971950191e-08</v>
+        <v>1.580619971950189e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.863140336398296e-08</v>
+        <v>1.863140336398295e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.69170034103572e-08</v>
+        <v>1.691700341035719e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.87638790985017e-08</v>
+        <v>1.876387909850169e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.72689657629203e-08</v>
+        <v>1.726896576292029e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.676801851647047e-08</v>
+        <v>1.676801851647045e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.937194555899073e-08</v>
+        <v>1.93719455589907e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.197243907231998e-08</v>
+        <v>2.197243907231996e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.68198932861527e-08</v>
+        <v>1.681989328615269e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.780674601280469e-08</v>
+        <v>1.780674601280467e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.095444444482638e-08</v>
+        <v>2.095444444482637e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.424071216482829e-08</v>
+        <v>3.424071216482825e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755280799739833e-08</v>
+        <v>4.755280799739827e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.94247822240167e-08</v>
+        <v>4.942478222401661e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.800853769843607e-08</v>
+        <v>3.978608144801551e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.577606616129719e-08</v>
+        <v>3.577606616129714e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.292531565770052e-08</v>
+        <v>5.61273331627647e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.773701968462919e-08</v>
+        <v>4.773701968462906e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.958483940414518e-08</v>
+        <v>4.958483940414511e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.115994809596771e-08</v>
+        <v>5.115994809596759e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.078755330946871e-08</v>
+        <v>5.078755330946861e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.12699752348018e-08</v>
+        <v>5.12699752348017e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.48668582024433e-08</v>
+        <v>5.486685820244332e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.619253567726203e-08</v>
+        <v>3.619253567726196e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.00024309632411e-08</v>
+        <v>4.000243096324104e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.169222896589256e-08</v>
+        <v>4.169222896589247e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.001038049708658e-08</v>
+        <v>3.001038049708656e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.815067144438385e-08</v>
+        <v>4.815067144438375e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.097587508886494e-08</v>
+        <v>5.097587508886482e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.926147513523915e-08</v>
+        <v>4.926147513523911e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.160604412820318e-08</v>
+        <v>4.35713058440186e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.961343748780228e-08</v>
+        <v>4.539436204733845e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.911552505630734e-08</v>
+        <v>4.911552505630724e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.465490479441954e-08</v>
+        <v>3.465490479441947e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.967292270842831e-08</v>
+        <v>6.967292270842833e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.916436501103467e-08</v>
+        <v>3.343543248368451e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.015121773768665e-08</v>
+        <v>5.015121773768654e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.942946814403825e-08</v>
+        <v>6.942946814403812e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.732690185401206e-08</v>
+        <v>2.732690185401202e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.000608333837673e-08</v>
+        <v>3.000608333837669e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.18780575649951e-08</v>
+        <v>3.187805756499507e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.046181303941448e-08</v>
+        <v>2.935187606811659e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.126573251342959e-08</v>
+        <v>2.017927401597394e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.537859099867889e-08</v>
+        <v>3.537859184274236e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.019029502560757e-08</v>
+        <v>3.019029502560752e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.203811474512358e-08</v>
+        <v>3.203811474512353e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.36132234369461e-08</v>
+        <v>3.361322343694605e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.324082865044706e-08</v>
+        <v>3.324082865044703e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.372325057578024e-08</v>
+        <v>3.372325057578019e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.732013354342172e-08</v>
+        <v>3.732013354342168e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.061601248160152e-08</v>
+        <v>3.061601248160147e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.27301473833346e-08</v>
+        <v>3.273014738333457e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.557289923781208e-08</v>
+        <v>3.557289923781204e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.094046720536715e-08</v>
+        <v>3.094046720536712e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.060394678536225e-08</v>
+        <v>3.060394678536218e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.342915042984331e-08</v>
+        <v>3.342915042984328e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.171475047621751e-08</v>
+        <v>3.171475047621749e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.356031631605079e-08</v>
+        <v>3.356031631605077e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.206671282878062e-08</v>
+        <v>3.761639196806134e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.156576558233078e-08</v>
+        <v>3.156576558233075e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.416969262485106e-08</v>
+        <v>3.416969262485105e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.67701861381803e-08</v>
+        <v>3.677018613818027e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.161764035201303e-08</v>
+        <v>2.871813673331817e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.260449307866499e-08</v>
+        <v>3.260449307866498e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.575219151068671e-08</v>
+        <v>3.575219151068668e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.150216456407201e-08</v>
+        <v>1.150216456407211e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.944313695759267e-09</v>
+        <v>9.944313695759249e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150641526892467e-08</v>
+        <v>1.150641526892469e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.14757486818634e-08</v>
+        <v>1.147574868186346e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.147884321817148e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.162502878046837e-08</v>
+        <v>1.16250287804684e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.152066253797581e-08</v>
+        <v>1.152066253797585e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.148789483668296e-08</v>
+        <v>1.148789483668303e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.156945887225357e-08</v>
+        <v>1.15694588722536e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.150874645349394e-08</v>
+        <v>1.150874645349397e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.159638253827176e-08</v>
+        <v>1.159638253827177e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.173490471667883e-08</v>
+        <v>1.173490471667882e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.149844694584095e-08</v>
+        <v>1.149844694584096e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.525465275464967e-08</v>
+        <v>1.525465275464969e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.155056738434172e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.149475393747077e-08</v>
+        <v>1.149475393747083e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.149305250888512e-08</v>
+        <v>1.149305250888518e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.153566459200754e-08</v>
+        <v>1.153566459200762e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.149074668519433e-08</v>
+        <v>1.149074668519435e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.153140307666895e-08</v>
+        <v>1.153140307666906e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.148737714661293e-08</v>
+        <v>1.148737714661295e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.171990679209027e-08</v>
+        <v>1.171990679209037e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.154352813333265e-08</v>
+        <v>1.154352813333279e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.149814518352035e-08</v>
+        <v>1.149814518352037e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>1.110036999892063e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.154932941288148e-08</v>
+        <v>1.154932941288149e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.160871171638397e-08</v>
+        <v>1.160871171638396e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.19544759064843e-08</v>
+        <v>1.195447590648435e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.142312200058722e-09</v>
+        <v>9.142312200058705e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.198865990744679e-08</v>
+        <v>1.198865990744687e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.174533728943195e-08</v>
+        <v>1.1745337289432e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.179265939369791e-08</v>
+        <v>1.179265939369797e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.282666104398394e-08</v>
+        <v>1.282666104398405e-08</v>
       </c>
       <c r="H3" t="n">
         <v>1.20931883836564e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.185656681063986e-08</v>
+        <v>1.185656681063985e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.243394185971586e-08</v>
+        <v>1.243394185971597e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.200665675968472e-08</v>
+        <v>1.200665675968487e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.262610614192908e-08</v>
+        <v>1.262610614192917e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.367986754050406e-08</v>
+        <v>1.367986754050405e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.193026113213563e-08</v>
+        <v>1.19302611321357e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.808505799838027e-08</v>
+        <v>1.808505799838031e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.229781223870137e-08</v>
+        <v>1.229781223870147e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.190446166941887e-08</v>
+        <v>1.190446166941892e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18937013516576e-08</v>
+        <v>1.189370135165767e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.219264207339632e-08</v>
+        <v>1.219264207339638e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.187793671590563e-08</v>
+        <v>1.187793671590571e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.269261923879276e-08</v>
+        <v>1.269261923879281e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.185122843218633e-08</v>
+        <v>1.18512284321865e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.266046608050011e-08</v>
+        <v>1.266046608050028e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.225337558093303e-08</v>
+        <v>1.225337558093308e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.192817706918988e-08</v>
+        <v>1.192817706919e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.14089528872403e-08</v>
+        <v>1.140895288724035e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.229293962315e-08</v>
+        <v>1.229293962315008e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.273185773665326e-08</v>
+        <v>1.273185773665323e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5068,10 +5068,10 @@
         <v>7.577196002123143e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.1141814627891e-09</v>
+        <v>8.114181462789094e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.767788254604873e-09</v>
+        <v>7.767788254604865e-09</v>
       </c>
       <c r="F4" t="n">
         <v>7.802742465761692e-09</v>
@@ -5080,67 +5080,67 @@
         <v>9.453975640586419e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.275110920789403e-09</v>
+        <v>8.275110920789387e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.904984660799967e-09</v>
+        <v>7.904984660799957e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.816556300424621e-09</v>
+        <v>8.816556300424613e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.140513264896922e-09</v>
+        <v>8.140513264896902e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.130403157052957e-09</v>
+        <v>9.130403157052947e-09</v>
       </c>
       <c r="M4" t="n">
         <v>1.080807708751276e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.024175587948659e-09</v>
+        <v>8.024175587948649e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.932344960743577e-09</v>
+        <v>7.932344960743573e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>8.61289991740107e-09</v>
+        <v>8.612899917401061e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.982461359540187e-09</v>
+        <v>7.982461359540171e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.963242940969527e-09</v>
+        <v>7.963242940969511e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>8.444566022364066e-09</v>
+        <v>8.444566022364068e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.937197601650179e-09</v>
+        <v>7.937197601650158e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>9.45145158054379e-09</v>
+        <v>9.451451580543797e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.84939383337794e-09</v>
+        <v>7.849393833377918e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.776526766731599e-09</v>
+        <v>8.776526766731589e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>8.533388339038753e-09</v>
+        <v>8.533388339038757e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.987747883679175e-09</v>
+        <v>7.987747883679168e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.309930690511271e-09</v>
+        <v>8.309930690511241e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.598916460262736e-09</v>
+        <v>8.598916460262743e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.284593392706055e-09</v>
+        <v>9.284593392706047e-09</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.53094500766483e-08</v>
+        <v>3.530945007664827e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.825048836178237e-08</v>
+        <v>2.825048836178232e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.835653227900063e-08</v>
+        <v>3.835653227900064e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.820700596638695e-08</v>
+        <v>1.820700596638697e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.290311098434678e-08</v>
+        <v>3.290311098434681e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.893445988167202e-08</v>
+        <v>5.893445988167219e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.298162800648342e-08</v>
+        <v>4.298162800648334e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.445008471313883e-08</v>
+        <v>3.445008471313879e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.921768885755838e-08</v>
+        <v>4.921768885755837e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.961026229451302e-08</v>
+        <v>3.961026229451291e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.498245990069387e-08</v>
+        <v>5.498245990069388e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.877561691700847e-08</v>
+        <v>8.877561691700835e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.013471988140346e-08</v>
+        <v>6.013471988140336e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.356500268073874e-08</v>
+        <v>3.356500268073866e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.446962948266611e-08</v>
+        <v>4.446962948266613e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.532610518870075e-08</v>
+        <v>3.532610518870071e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.573180746691153e-08</v>
+        <v>3.573180746691148e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.19496141481018e-08</v>
+        <v>4.194961414810174e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.562428149914858e-08</v>
+        <v>3.562428149914851e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.159501503403923e-08</v>
+        <v>6.159501503403911e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.337568550910955e-08</v>
+        <v>3.337568550910904e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.959467353088393e-08</v>
+        <v>4.959467353088405e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>4.619348779020246e-08</v>
+        <v>4.619348779020238e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>3.577893175063407e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.953660612160386e-08</v>
+        <v>3.953660612160377e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.64091787136532e-08</v>
+        <v>4.640917871365318e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.32635035975958e-08</v>
+        <v>6.326350359759568e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.065331287348658e-08</v>
+        <v>1.065331287348656e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.285605788230521e-08</v>
+        <v>1.285605788230522e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.339304334297116e-08</v>
+        <v>1.070132654021796e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.304665013478693e-08</v>
+        <v>1.035493333203372e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.308160434594372e-08</v>
+        <v>1.308160434594375e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.204112071801529e-08</v>
+        <v>1.473283752076848e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.086225599821827e-08</v>
+        <v>1.086225599821825e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.318384654098201e-08</v>
+        <v>1.049212973822881e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.140370137785348e-08</v>
+        <v>1.140370137785347e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.341937514507898e-08</v>
+        <v>1.072765834232576e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.440926503723502e-08</v>
+        <v>1.171754823448181e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.339522216494164e-08</v>
+        <v>1.608693896769482e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.061530671750559e-08</v>
+        <v>1.061530671750557e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.323038909645416e-08</v>
+        <v>1.323038909645419e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.391096952664539e-08</v>
+        <v>1.103029807535649e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.326132323972224e-08</v>
+        <v>1.326132323972223e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.324210482115156e-08</v>
+        <v>1.055038801839837e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.372342790254612e-08</v>
+        <v>1.103171109979292e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.052434267907902e-08</v>
+        <v>1.321605948183223e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.476333262076656e-08</v>
+        <v>1.207161581801336e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.043653891080683e-08</v>
+        <v>1.312825571355999e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.152349933907488e-08</v>
+        <v>1.152349933907489e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.112053341646763e-08</v>
+        <v>1.112053341646761e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.074403939277202e-08</v>
+        <v>1.0744039392772e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.089707576794011e-08</v>
+        <v>1.358879257069332e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.118606153769161e-08</v>
+        <v>1.38777783404448e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.188174608705795e-08</v>
+        <v>1.188174608705794e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,19 +5326,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.489450811646691e-08</v>
+        <v>1.48945081164669e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.440553632253234e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.494252178319829e-08</v>
+        <v>1.494252178319831e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459612857501406e-08</v>
+        <v>1.459612857501405e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.463108278617089e-08</v>
+        <v>1.46310827861709e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.628231596099561e-08</v>
@@ -5347,13 +5347,13 @@
         <v>1.510345124119861e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.473332498120917e-08</v>
+        <v>1.473332498120916e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.564489662083382e-08</v>
+        <v>1.564489662083381e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.496885358530612e-08</v>
+        <v>1.496885358530611e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.595874347746215e-08</v>
@@ -5365,19 +5365,19 @@
         <v>1.485251590835784e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.476023780297758e-08</v>
+        <v>1.476023780297756e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.544079275963505e-08</v>
+        <v>1.544079275963506e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.481080167994936e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.479158326137873e-08</v>
+        <v>1.479158326137871e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.527290634277326e-08</v>
+        <v>1.527290634277325e-08</v>
       </c>
       <c r="T7" t="n">
         <v>1.476553792205936e-08</v>
@@ -5386,16 +5386,16 @@
         <v>1.631318217060615e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.467773415378713e-08</v>
+        <v>1.467773415378712e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.56048670871408e-08</v>
+        <v>1.560486708714082e-08</v>
       </c>
       <c r="X7" t="n">
         <v>1.536172865944795e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.484910736412906e-08</v>
+        <v>1.484910736412907e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>1.513827101092043e-08</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.284261684533686e-08</v>
+        <v>3.284261684533683e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.851273839935148e-08</v>
+        <v>4.851273839935144e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.904972386001747e-08</v>
+        <v>4.904972386001745e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.870333065183321e-08</v>
+        <v>4.009909010698267e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.509658940361103e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.038951803781474e-08</v>
+        <v>5.374021131039677e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.921065331801777e-08</v>
+        <v>4.921065331801769e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.884052705802828e-08</v>
+        <v>4.884052705802825e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.975209869765297e-08</v>
+        <v>4.975209869765292e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.907605566212524e-08</v>
+        <v>4.907605566212516e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.006594555428125e-08</v>
+        <v>5.006594555428123e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.174361948474108e-08</v>
+        <v>5.174361948474115e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.643371728370586e-08</v>
+        <v>3.643371728370585e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.978414041199669e-08</v>
+        <v>3.978414041199664e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.962091579653053e-08</v>
+        <v>3.962091579653048e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.958327975197065e-08</v>
+        <v>2.958327975197063e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.889878533819781e-08</v>
+        <v>4.889878533819779e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.938010841959243e-08</v>
+        <v>4.938010841959237e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.887273999887847e-08</v>
+        <v>4.88727399988784e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.047714414225957e-08</v>
+        <v>4.25336097345772e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.878493623060633e-08</v>
+        <v>4.436911207899095e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.971524489125765e-08</v>
+        <v>4.971524489125764e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.161521974692195e-08</v>
+        <v>3.161521974692186e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.502401340167613e-08</v>
+        <v>6.502401340167605e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.92454730877396e-08</v>
+        <v>3.278621628453653e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.953445885749104e-08</v>
+        <v>4.953445885749102e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.709965999557856e-08</v>
+        <v>6.709965999557846e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.669133699348525e-08</v>
+        <v>2.669133699348528e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.153449910644469e-08</v>
+        <v>3.15344991064447e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.207148456711063e-08</v>
+        <v>3.207148456711066e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.17250913589264e-08</v>
+        <v>3.049445759027667e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.176004557008325e-08</v>
+        <v>1.946801996126502e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.341127874490791e-08</v>
+        <v>3.341128002894092e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.223241402511091e-08</v>
+        <v>3.223241402511095e-08</v>
       </c>
       <c r="I9" t="n">
         <v>3.186228776512149e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.277385940474617e-08</v>
+        <v>3.277385940474616e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.209781636921843e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.308770626137448e-08</v>
+        <v>3.30877062613745e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.476538019183428e-08</v>
+        <v>3.476538019183429e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.198147869227017e-08</v>
+        <v>3.198147869227018e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.365671196953687e-08</v>
+        <v>3.365671196953691e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.472157272845044e-08</v>
+        <v>3.472157272845046e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.193976574789469e-08</v>
+        <v>3.193976574789468e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.192054604529105e-08</v>
+        <v>3.192054604529106e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.240186912668563e-08</v>
+        <v>3.240186912668562e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.189450070597167e-08</v>
+        <v>3.18945007059717e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.344177384490605e-08</v>
+        <v>3.344177384490607e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.180669693769946e-08</v>
+        <v>3.795986242531797e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.273382987105314e-08</v>
+        <v>3.273382987105312e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.249069144336033e-08</v>
+        <v>3.249069144336032e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.197807014804143e-08</v>
+        <v>3.197807014804142e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.226723379483279e-08</v>
+        <v>2.905243171069815e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.25562195645843e-08</v>
+        <v>3.255621956458429e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.324189649702759e-08</v>
+        <v>3.324189649702761e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,82 +5746,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.141598036317069e-08</v>
+        <v>1.141598036317063e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.900367226784625e-09</v>
+        <v>9.900367226784618e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.142855957129146e-08</v>
+        <v>1.142855957129139e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.141132986757012e-08</v>
+        <v>1.141132986757005e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.141919819191038e-08</v>
+        <v>1.141919819191033e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.144885324904674e-08</v>
+        <v>1.144885324904668e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.143839636658858e-08</v>
+        <v>1.14383963665885e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.143322309229535e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.144056855098275e-08</v>
+        <v>1.144056855098277e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.143510105483802e-08</v>
+        <v>1.1435101054838e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.143075791047793e-08</v>
+        <v>1.143075791047784e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.141735017412256e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.143796449696579e-08</v>
+        <v>1.143796449696574e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.521546212954767e-08</v>
+        <v>1.521546212954762e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.141790183130242e-08</v>
+        <v>1.141790183130236e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.141620970855016e-08</v>
+        <v>1.14162097085501e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.143637095297512e-08</v>
+        <v>1.143637095297505e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.143415936546268e-08</v>
+        <v>1.143415936546262e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.141374134056445e-08</v>
+        <v>1.141374134056439e-08</v>
       </c>
       <c r="U2" t="n">
         <v>1.136428425701439e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.143704071938223e-08</v>
+        <v>1.143704071938217e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.166462004629618e-08</v>
+        <v>1.16646200462961e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.15697187523109e-08</v>
+        <v>1.156971875231085e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.150338035670229e-08</v>
+        <v>1.150338035670226e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.104047921961989e-08</v>
+        <v>1.104047921961982e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.145937880416409e-08</v>
+        <v>1.145937880416403e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.14179418687784e-08</v>
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.174181812916351e-08</v>
+        <v>1.174181812916346e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.188794602987971e-09</v>
+        <v>9.188794602987961e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.183632724272589e-08</v>
+        <v>1.183632724272583e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.168779742266214e-08</v>
+        <v>1.168779742266206e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.176916506120813e-08</v>
+        <v>1.17691650612081e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.197802107628955e-08</v>
+        <v>1.197802107628951e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.190764853258295e-08</v>
+        <v>1.190764853258293e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.186922899153349e-08</v>
+        <v>1.186922899153342e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.191937465468678e-08</v>
+        <v>1.191937465468677e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.188364272670842e-08</v>
+        <v>1.18836427267084e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.185283260383882e-08</v>
+        <v>1.185283260383873e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.183574276936817e-08</v>
+        <v>1.183574276936816e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.190055083369709e-08</v>
+        <v>1.190055083369706e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.812403729207701e-08</v>
+        <v>1.812403729207696e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.17552481831427e-08</v>
+        <v>1.175524818314272e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.174673493347568e-08</v>
+        <v>1.174673493347562e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.189208574851979e-08</v>
+        <v>1.189208574851975e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.187255102746422e-08</v>
+        <v>1.187255102746419e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.17310458672212e-08</v>
+        <v>1.173104586722116e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.171530600620946e-08</v>
+        <v>1.171530600620942e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.189386379456829e-08</v>
+        <v>1.18938637945682e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.243897016980735e-08</v>
+        <v>1.243897016980727e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.284038517747579e-08</v>
+        <v>1.284038517747576e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.236732614208986e-08</v>
+        <v>1.236732614208982e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.127536999471916e-08</v>
+        <v>1.127536999471913e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.205295366825263e-08</v>
+        <v>1.205295366825258e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.17772415418125e-08</v>
+        <v>1.177724154181249e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.641287701113835e-09</v>
+        <v>7.641287701113838e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.541802651822504e-09</v>
+        <v>7.541802651822492e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.783375643559501e-09</v>
+        <v>7.783375643559496e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.588758213971732e-09</v>
+        <v>7.588758213971714e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.677634557003182e-09</v>
+        <v>7.677634557003192e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.012602069358463e-09</v>
+        <v>8.012602069358452e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.894486771590028e-09</v>
+        <v>7.894486771590009e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.836052258624518e-09</v>
+        <v>7.836052258624512e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.909882733474279e-09</v>
+        <v>7.909882733474272e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.857264709449689e-09</v>
+        <v>7.857264709449662e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.808206895956775e-09</v>
+        <v>7.80820689595677e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.79678518785564e-09</v>
+        <v>7.796785187855623e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.889608605530803e-09</v>
+        <v>7.889608605530805e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.867645007454622e-09</v>
+        <v>7.86764500745463e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.662991567580881e-09</v>
+        <v>7.662991567580874e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.643878262679126e-09</v>
+        <v>7.643878262679119e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.871608793089656e-09</v>
+        <v>7.871608793089651e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.846627894756201e-09</v>
+        <v>7.846627894756184e-09</v>
       </c>
       <c r="T4" t="n">
         <v>7.615996910775276e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.733093038544008e-09</v>
+        <v>7.733093038544003e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.833430999422737e-09</v>
+        <v>7.833430999422767e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.228223140424215e-09</v>
+        <v>8.228223140424195e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.377833529605705e-09</v>
+        <v>9.377833529605735e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.611979327103055e-09</v>
+        <v>8.611979327103052e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.957960831026158e-09</v>
+        <v>7.957960831026134e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.131493056403577e-09</v>
+        <v>8.131493056403558e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.69236489151997e-09</v>
+        <v>7.69236489151998e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6010,22 +6010,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.8811089878924e-08</v>
+        <v>2.881108987892403e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.93950094386149e-08</v>
+        <v>2.939500943861491e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.377570374268244e-08</v>
+        <v>3.377570374268241e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.708745744465109e-08</v>
+        <v>1.708745744465111e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.172435260463821e-08</v>
+        <v>3.17243526046382e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.620109019842803e-08</v>
+        <v>3.6201090198428e-08</v>
       </c>
       <c r="H5" t="n">
         <v>3.631901440338121e-08</v>
@@ -6034,61 +6034,61 @@
         <v>3.450939763198956e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478656576977881e-08</v>
+        <v>3.478656576977877e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.540830454858506e-08</v>
+        <v>3.540830454858508e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.463760374619722e-08</v>
+        <v>3.463760374619727e-08</v>
       </c>
       <c r="M5" t="n">
         <v>3.574335520734972e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.307188055970901e-08</v>
+        <v>3.307188055970902e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.309129804389978e-08</v>
+        <v>3.309129804389976e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.904801085140972e-08</v>
+        <v>2.904801085140973e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.055666180942258e-08</v>
+        <v>3.055666180942257e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.534054623781097e-08</v>
+        <v>3.5340546237811e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.29551106153515e-08</v>
+        <v>3.295511061535146e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.10625671672564e-08</v>
+        <v>3.106256716725635e-08</v>
       </c>
       <c r="U5" t="n">
         <v>3.293189649965595e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.387284071402185e-08</v>
+        <v>3.387284071402247e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.004385501373956e-08</v>
+        <v>4.004385501373958e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.021323031298554e-08</v>
+        <v>6.021323031298587e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.716823795436404e-08</v>
+        <v>4.716823795436406e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.419047158671769e-08</v>
+        <v>3.41904715867177e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.82060224985537e-08</v>
+        <v>3.820602249855365e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.267387176896842e-08</v>
+        <v>3.267387176896839e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6101,82 +6101,82 @@
         <v>1.003172285816491e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.238689268215258e-08</v>
+        <v>9.932237808873579e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.017381080061061e-08</v>
+        <v>1.017381080061059e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.243384824430181e-08</v>
+        <v>1.243384824430179e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.252272458733327e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.285769209968853e-08</v>
+        <v>1.040303722640954e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.27395768019201e-08</v>
+        <v>1.028492192864111e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.022648741567562e-08</v>
+        <v>1.022648741567561e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.275497276380437e-08</v>
+        <v>1.030031789052536e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.024769986650075e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.265329692628685e-08</v>
+        <v>1.265329692628683e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.018722034490672e-08</v>
+        <v>1.264187521818569e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.028245813963331e-08</v>
+        <v>1.028245813963337e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.026049454155712e-08</v>
+        <v>1.026049454155713e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.252543696432781e-08</v>
+        <v>9.894479336668273e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.248896829300923e-08</v>
+        <v>1.003431341973022e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.271669882341974e-08</v>
+        <v>1.271669882341971e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.269171792508628e-08</v>
+        <v>1.023706305180728e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.246108694110536e-08</v>
+        <v>1.246108694110535e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.014005970252884e-08</v>
+        <v>1.014005970252883e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.022386615647388e-08</v>
+        <v>1.267852102975284e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.076510349554225e-08</v>
+        <v>1.076510349554226e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.176826868665681e-08</v>
+        <v>1.176826868665682e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.114657877332008e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.280305086135623e-08</v>
+        <v>1.280305086135621e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.052192821345467e-08</v>
+        <v>1.297658308673363e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.008431584222684e-08</v>
+        <v>1.008431584222683e-08</v>
       </c>
     </row>
     <row r="7">
@@ -6186,82 +6186,82 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.403348809189748e-08</v>
+        <v>1.403348809189745e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.393400304260613e-08</v>
+        <v>1.393400304260611e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.417557603434314e-08</v>
+        <v>1.417557603434312e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.398095860475536e-08</v>
+        <v>1.398095860475533e-08</v>
       </c>
       <c r="F7" t="n">
         <v>1.406983494778682e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.440480246014208e-08</v>
+        <v>1.440480246014206e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.428668716237365e-08</v>
+        <v>1.428668716237363e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.422825264940815e-08</v>
+        <v>1.422825264940814e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.430208312425791e-08</v>
+        <v>1.43020831242579e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.424946510023329e-08</v>
+        <v>1.424946510023328e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.420040728674041e-08</v>
+        <v>1.420040728674039e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.418898557863925e-08</v>
+        <v>1.418898557863923e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.428180899631444e-08</v>
+        <v>1.428180899631443e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.425942750349945e-08</v>
+        <v>1.425942750349943e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.405477406362569e-08</v>
+        <v>1.405477406362566e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.403607865346277e-08</v>
+        <v>1.403607865346275e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.426380918387328e-08</v>
+        <v>1.426380918387326e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.423882828553983e-08</v>
+        <v>1.423882828553981e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.40081973015589e-08</v>
+        <v>1.400819730155889e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.41431664164512e-08</v>
+        <v>1.414316641645116e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.422563139020642e-08</v>
+        <v>1.422563139020638e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.462042353120785e-08</v>
+        <v>1.462042353120782e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.577003392038935e-08</v>
+        <v>1.577003392038934e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.502071122482041e-08</v>
+        <v>1.50207112248204e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.435016122180978e-08</v>
+        <v>1.435016122180975e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.45236934471872e-08</v>
+        <v>1.452369344718718e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>1.408456528230362e-08</v>
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.072088946986909e-08</v>
+        <v>3.07208894698691e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.568089549526479e-08</v>
+        <v>4.568089549526478e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.592246848700182e-08</v>
+        <v>4.59224684870018e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.572785105741404e-08</v>
+        <v>3.770911628686976e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.310332903146007e-08</v>
+        <v>3.310332903146005e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.615169491280069e-08</v>
+        <v>4.927437849076794e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.603357961503233e-08</v>
+        <v>4.603357961503229e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.597514510206677e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.604897557691657e-08</v>
+        <v>4.604897557691658e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.599635755289196e-08</v>
+        <v>4.599635755289193e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.594729973939904e-08</v>
+        <v>4.5947299739399e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.593587803129792e-08</v>
+        <v>4.593587803129805e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.435507646869319e-08</v>
+        <v>3.435507646869315e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.754112637679309e-08</v>
+        <v>3.754112637679308e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.655011130995102e-08</v>
+        <v>3.655011130995096e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>2.776394631852154e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.601070163653193e-08</v>
+        <v>4.601070163653195e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.598572073819845e-08</v>
+        <v>4.598572073819841e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.575508975421755e-08</v>
+        <v>4.575508975421754e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.662317098028321e-08</v>
+        <v>3.853974426588308e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.597252384286502e-08</v>
+        <v>4.185804173399258e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.637027560765417e-08</v>
+        <v>4.63702756076542e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.087813386751716e-08</v>
+        <v>3.087813386751717e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.174324538205314e-08</v>
+        <v>6.174324538205315e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.609705367446842e-08</v>
+        <v>3.075782482130441e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.627058589984584e-08</v>
+        <v>4.627058589984581e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.156235541879038e-08</v>
+        <v>6.15623554187904e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.382222815553338e-08</v>
+        <v>2.382222815553334e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.836957870561092e-08</v>
+        <v>2.836957870561089e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.861115169734792e-08</v>
+        <v>2.86111516973479e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.841653426776016e-08</v>
+        <v>2.734406483687837e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.850541061079163e-08</v>
+        <v>1.77931841551049e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.884037812314688e-08</v>
+        <v>2.884037977596631e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.872226282537843e-08</v>
+        <v>2.872226282537841e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.866382831241293e-08</v>
+        <v>2.866382831241291e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.87376587872627e-08</v>
+        <v>2.873765878726268e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.86850407632381e-08</v>
+        <v>2.868504076323803e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.86359829497452e-08</v>
+        <v>2.863598294974518e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.862456124164405e-08</v>
+        <v>2.862456124164401e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.871738465931923e-08</v>
+        <v>2.871738465931919e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.023537849492452e-08</v>
+        <v>3.023537849492446e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.036563901619602e-08</v>
+        <v>3.036563901619598e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.847165596928706e-08</v>
+        <v>2.847165596928698e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.869938484687807e-08</v>
+        <v>2.869938484687804e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.867440394854461e-08</v>
+        <v>2.867440394854456e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.844377296456368e-08</v>
+        <v>2.844377296456365e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.857740059926619e-08</v>
+        <v>2.857740059926614e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.866120705321122e-08</v>
+        <v>3.402355436600406e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.905599919421261e-08</v>
+        <v>2.905599919421257e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.020560958339414e-08</v>
+        <v>3.020560958339409e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.945628688782519e-08</v>
+        <v>2.945628688782515e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.878573688481458e-08</v>
+        <v>2.598410888745541e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.895926911019199e-08</v>
+        <v>2.895926911019196e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.852014094530841e-08</v>
+        <v>2.852014094530835e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,82 +6606,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.146209735398591e-08</v>
+        <v>1.146209735398593e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.941884959730424e-09</v>
+        <v>9.941884959730431e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.147193323396106e-08</v>
+        <v>1.147193323396109e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.146376492137128e-08</v>
+        <v>1.146376492137132e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.145454802320307e-08</v>
+        <v>1.145454802320309e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.15013209472366e-08</v>
+        <v>1.150132094723665e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.147022749707944e-08</v>
+        <v>1.147022749707946e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.147081282417367e-08</v>
+        <v>1.14708128241737e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.148262791217602e-08</v>
+        <v>1.148262791217604e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.147567181203992e-08</v>
+        <v>1.147567181203996e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.146786455126717e-08</v>
+        <v>1.146786455126721e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.146160493765184e-08</v>
+        <v>1.146160493765183e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.146601389859846e-08</v>
+        <v>1.14660138985985e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.529066745310038e-08</v>
+        <v>1.52906674531004e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.146296983103352e-08</v>
+        <v>1.146296983103357e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.145549804924758e-08</v>
+        <v>1.145549804924761e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.148366166184138e-08</v>
+        <v>1.14836616618414e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.146297057357717e-08</v>
+        <v>1.146297057357723e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.145597969214155e-08</v>
+        <v>1.145597969214156e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.143461778078538e-08</v>
+        <v>1.143461778078536e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.14828751694856e-08</v>
+        <v>1.148287516948562e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.178049596972645e-08</v>
+        <v>1.178049596972643e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.165038070440907e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.154292165502243e-08</v>
+        <v>1.154292165502245e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.107255952860364e-08</v>
+        <v>1.107255952860367e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.150850570202033e-08</v>
+        <v>1.150850570202034e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.14686515434305e-08</v>
@@ -6694,37 +6694,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.183633745196357e-08</v>
+        <v>1.183633745196355e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.227312811783789e-09</v>
+        <v>9.227312811783791e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.191078352181398e-08</v>
+        <v>1.191078352181394e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.18288183278507e-08</v>
+        <v>1.182881832785069e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.17866960535584e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.211623330232242e-08</v>
+        <v>1.211623330232244e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.190034010638702e-08</v>
+        <v>1.1900340106387e-08</v>
       </c>
       <c r="I3" t="n">
         <v>1.190269091980139e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.198456564849216e-08</v>
+        <v>1.198456564849213e-08</v>
       </c>
       <c r="K3" t="n">
         <v>1.193767204721653e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.188159673673939e-08</v>
+        <v>1.18815967367394e-08</v>
       </c>
       <c r="M3" t="n">
         <v>1.191414153611276e-08</v>
@@ -6733,7 +6733,7 @@
         <v>1.186625989686638e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.823792189206988e-08</v>
+        <v>1.823792189206987e-08</v>
       </c>
       <c r="P3" t="n">
         <v>1.184264921685001e-08</v>
@@ -6742,31 +6742,31 @@
         <v>1.179203751754296e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.199504163615797e-08</v>
+        <v>1.199504163615795e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.18435131536868e-08</v>
+        <v>1.184351315368682e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.179680196034816e-08</v>
+        <v>1.179680196034817e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.179756879041891e-08</v>
+        <v>1.179756879041889e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.198553146486273e-08</v>
+        <v>1.198553146486279e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.281348297408562e-08</v>
+        <v>1.281348297408563e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.318000898202077e-08</v>
+        <v>1.318000898202076e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.241510162414146e-08</v>
+        <v>1.241510162414145e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.122753339144171e-08</v>
+        <v>1.122753339144175e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.216903393379201e-08</v>
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.790228979717446e-09</v>
+        <v>7.790228979717479e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.591861562622522e-09</v>
+        <v>7.591861562622568e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.901329768765129e-09</v>
+        <v>7.901329768765149e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.809064920454244e-09</v>
+        <v>7.809064920454272e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.704955815661475e-09</v>
+        <v>7.704955815661534e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.233277509228529e-09</v>
+        <v>8.233277509228615e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.88206268600946e-09</v>
+        <v>7.882062686009493e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.888674224802634e-09</v>
+        <v>7.888674224802669e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.013015369687105e-09</v>
+        <v>8.013015369687131e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.943558727996798e-09</v>
+        <v>7.943558727996819e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.855372126051267e-09</v>
+        <v>7.855372126051287e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.923205987348093e-09</v>
+        <v>7.923205987348126e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.834468152815856e-09</v>
+        <v>7.8344681528159e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.958083370573739e-09</v>
+        <v>7.958083370573775e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.80008400932963e-09</v>
+        <v>7.800084009329648e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.715686796867974e-09</v>
+        <v>7.715686796868005e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.033807757016654e-09</v>
+        <v>8.033807757016697e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.800092396701895e-09</v>
+        <v>7.80009239670193e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.721127174921681e-09</v>
+        <v>7.721127174921718e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.777364476672409e-09</v>
+        <v>7.777364476672413e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.979346803713321e-09</v>
+        <v>7.979346803713349e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.717946054963341e-09</v>
+        <v>8.717946054963371e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.916976037367134e-09</v>
+        <v>9.916976037367159e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.687719952657687e-09</v>
+        <v>8.687719952657722e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.859700015965869e-09</v>
+        <v>7.859700015965914e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.314432619660746e-09</v>
+        <v>8.314432619660779e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.890498481365182e-09</v>
+        <v>7.890498481365222e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.047985068920982e-08</v>
+        <v>3.047985068920984e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.914103958202357e-08</v>
+        <v>2.914103958202359e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.464570199916311e-08</v>
+        <v>3.464570199916305e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.074874271604076e-08</v>
+        <v>2.074874271604075e-08</v>
       </c>
       <c r="F5" t="n">
         <v>3.116817618177142e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.829263189280476e-08</v>
+        <v>3.829263189280482e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.520172676855064e-08</v>
+        <v>3.52017267685506e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.43720241912386e-08</v>
+        <v>3.437202419123854e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.545358840193567e-08</v>
+        <v>3.54535884019358e-08</v>
       </c>
       <c r="K5" t="n">
         <v>3.54994007043708e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.375596389312472e-08</v>
+        <v>3.375596389312469e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.596569423424678e-08</v>
+        <v>3.596569423424679e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.232189050964842e-08</v>
+        <v>3.232189050964841e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.360374363896308e-08</v>
+        <v>3.36037436389631e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.069812591461518e-08</v>
+        <v>3.069812591461517e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.061228782401048e-08</v>
+        <v>3.06122878240105e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.727471904747464e-08</v>
+        <v>3.727471904747467e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.114324127957936e-08</v>
+        <v>3.114324127957935e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.139615955231025e-08</v>
+        <v>3.139615955231028e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.228024352178761e-08</v>
+        <v>3.228024352178762e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.50525288839121e-08</v>
+        <v>3.505252888391212e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.738806254303005e-08</v>
+        <v>4.738806254302988e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.803470131196364e-08</v>
+        <v>6.803470131196333e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.762032842339066e-08</v>
+        <v>4.762032842339071e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.194505514431074e-08</v>
+        <v>3.194505514431077e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.051708346298475e-08</v>
+        <v>4.051708346298474e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.526949011437402e-08</v>
+        <v>3.526949011437405e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,46 +6958,46 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.26603123583838e-08</v>
+        <v>1.266031235838383e-08</v>
       </c>
       <c r="C6" t="n">
         <v>1.246194494128888e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.27714131474315e-08</v>
+        <v>1.277141314743148e-08</v>
       </c>
       <c r="E6" t="n">
         <v>1.267914829912062e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.009112561048575e-08</v>
+        <v>1.257503919432785e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.06194473040528e-08</v>
+        <v>1.310336088789496e-08</v>
       </c>
       <c r="H6" t="n">
         <v>1.026823248083373e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.275875760346901e-08</v>
+        <v>1.027484401962692e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.288309874835347e-08</v>
+        <v>1.039918516451137e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.032972852282107e-08</v>
+        <v>1.281364210666316e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.272545550471762e-08</v>
+        <v>1.272545550471761e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.279328936601445e-08</v>
+        <v>1.279328936601447e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.022234890884381e-08</v>
+        <v>1.022234890884382e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.034596412660168e-08</v>
+        <v>1.284014111527929e-08</v>
       </c>
       <c r="P6" t="n">
         <v>1.26821579128396e-08</v>
@@ -7006,37 +7006,37 @@
         <v>1.258577017553433e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.290389113568301e-08</v>
+        <v>1.041997755184092e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.018626219152617e-08</v>
+        <v>1.018626219152616e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.259121055358804e-08</v>
+        <v>1.259121055358805e-08</v>
       </c>
       <c r="U6" t="n">
         <v>1.266290454362143e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.03655165985376e-08</v>
+        <v>1.036551659853759e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.359997681167945e-08</v>
+        <v>1.359997681167946e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.478705941603351e-08</v>
+        <v>1.23031458321914e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.121713356496396e-08</v>
+        <v>1.121713356496397e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.272978339463222e-08</v>
+        <v>1.024586981079013e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.318451599832709e-08</v>
+        <v>1.070060241448501e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.027803516759464e-08</v>
+        <v>1.027803516759465e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7046,43 +7046,43 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.423685474476327e-08</v>
+        <v>1.423685474476326e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.403848732766835e-08</v>
+        <v>1.403848732766834e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.434795553381095e-08</v>
+        <v>1.434795553381093e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.425569068550006e-08</v>
+        <v>1.425569068550005e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.415158158070729e-08</v>
+        <v>1.415158158070728e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.467990327427434e-08</v>
+        <v>1.467990327427444e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.432868845105528e-08</v>
+        <v>1.432868845105527e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.433529998984845e-08</v>
+        <v>1.433529998984844e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.445964113473292e-08</v>
+        <v>1.445964113473289e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.439018449304262e-08</v>
+        <v>1.439018449304261e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.430199789109709e-08</v>
+        <v>1.430199789109707e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.436983175239391e-08</v>
+        <v>1.43698317523939e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.42810939178617e-08</v>
+        <v>1.428109391786167e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.440429081587303e-08</v>
@@ -7091,13 +7091,13 @@
         <v>1.424629145462892e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.416231256191379e-08</v>
+        <v>1.416231256191378e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.448043352206246e-08</v>
+        <v>1.448043352206247e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.424671816174772e-08</v>
+        <v>1.424671816174771e-08</v>
       </c>
       <c r="T7" t="n">
         <v>1.416775293996749e-08</v>
@@ -7109,22 +7109,22 @@
         <v>1.442597256875914e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.516457182000916e-08</v>
+        <v>1.516457182000914e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.63636018024129e-08</v>
+        <v>1.636360180241293e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.514980240598615e-08</v>
+        <v>1.514980240598616e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.430632578101169e-08</v>
+        <v>1.430632578101167e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.476105838470656e-08</v>
+        <v>1.476105838470654e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.4337124246411e-08</v>
+        <v>1.433712424641099e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.093521410118763e-08</v>
+        <v>3.093521410118762e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.585266856617465e-08</v>
+        <v>4.585266856617464e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.616213677231725e-08</v>
+        <v>4.616213677231726e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.606987192400639e-08</v>
+        <v>3.8021142660184e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.320480932427055e-08</v>
+        <v>3.32048093242705e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.649408451278066e-08</v>
+        <v>4.962844865062016e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.614286968956164e-08</v>
+        <v>4.614286968956155e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.614948122835482e-08</v>
+        <v>4.614948122835473e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.627382237323932e-08</v>
+        <v>4.62738223732392e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.620436573154891e-08</v>
+        <v>4.620436573154888e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.611617912960342e-08</v>
+        <v>4.611617912960341e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.618401299090024e-08</v>
+        <v>4.618401299090055e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.437798437641193e-08</v>
+        <v>3.437798437641187e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.772161284122813e-08</v>
+        <v>3.772161284122811e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.677431042657235e-08</v>
+        <v>3.677431042657227e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>2.789006791609077e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.629461476056882e-08</v>
+        <v>4.629461476056877e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.606089940025409e-08</v>
+        <v>4.606089940025403e-08</v>
       </c>
       <c r="T8" t="n">
         <v>4.598193417847379e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.675364995634869e-08</v>
+        <v>3.867740699846302e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.624015380726548e-08</v>
+        <v>4.211054726603315e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.698172375289662e-08</v>
+        <v>4.698172375289654e-08</v>
       </c>
       <c r="X8" t="n">
         <v>3.147675226907276e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.199605508201936e-08</v>
+        <v>6.199605508201925e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.612050701951809e-08</v>
+        <v>3.072390098529349e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.657523962321285e-08</v>
+        <v>4.657523962321281e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.194104540735214e-08</v>
+        <v>6.194104540735206e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.328500477267024e-08</v>
+        <v>2.328500477267026e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.755014675876944e-08</v>
+        <v>2.755014675876943e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.785961496491205e-08</v>
+        <v>2.785961496491204e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.776735011660115e-08</v>
+        <v>2.673719159460332e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.766324101180835e-08</v>
+        <v>1.73736315226925e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.819156270537543e-08</v>
+        <v>2.819156431994843e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.784034788215635e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.78469594209495e-08</v>
+        <v>2.784695942094955e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.797130056583402e-08</v>
+        <v>2.797130056583399e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.790184392414369e-08</v>
+        <v>2.790184392414372e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.781365732219816e-08</v>
+        <v>2.781365732219818e-08</v>
       </c>
       <c r="M9" t="n">
         <v>2.788149118349498e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.779275334896275e-08</v>
+        <v>2.779275334896273e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.939557188811377e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.955927351927514e-08</v>
+        <v>2.955927351927516e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.767397360758791e-08</v>
+        <v>2.767397360758795e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.799209295316354e-08</v>
+        <v>2.799209295316352e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.775837759284879e-08</v>
+        <v>2.775837759284878e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.767941237106856e-08</v>
+        <v>2.767941237106857e-08</v>
       </c>
       <c r="U9" t="n">
         <v>2.775110636110197e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>2.793763199986022e-08</v>
+        <v>3.308842472683518e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.867623125111022e-08</v>
+        <v>2.867623125111023e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.987526123351407e-08</v>
+        <v>2.987526123351406e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.866146183708722e-08</v>
+        <v>2.866146183708727e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.781798521211275e-08</v>
+        <v>2.512688659385838e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.827271781580763e-08</v>
+        <v>2.827271781580766e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.784878367751204e-08</v>
+        <v>2.784878367751208e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,82 +7466,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.202540794120403e-08</v>
+        <v>1.202540794120398e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.034499686236582e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.195686193615624e-08</v>
+        <v>1.195686193615625e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.192770506015921e-08</v>
+        <v>1.192770506015924e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.190745010065631e-08</v>
+        <v>1.190745010065633e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.242690614561071e-08</v>
+        <v>1.242690614561073e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.189748303023093e-08</v>
+        <v>1.189748303023095e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.190927144727671e-08</v>
+        <v>1.190927144727674e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.219139038763251e-08</v>
+        <v>1.219139038763248e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.193034265877086e-08</v>
+        <v>1.193034265877088e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.226780326062034e-08</v>
+        <v>1.22678032606203e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.27176284400984e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.193964204618801e-08</v>
+        <v>1.193964204618803e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.588282411394407e-08</v>
+        <v>1.588282411394406e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.212684078387469e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.192794577278674e-08</v>
+        <v>1.192794577278675e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.191292706330459e-08</v>
+        <v>1.191292706330461e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.207629186019212e-08</v>
+        <v>1.20762918601921e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.193960089029893e-08</v>
+        <v>1.193960089029895e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.220828102415577e-08</v>
+        <v>1.22082810241558e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.191982981178092e-08</v>
+        <v>1.191982981178094e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.217568458790232e-08</v>
+        <v>1.21756845879023e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.211111791038933e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.205910822110308e-08</v>
+        <v>1.205910822110311e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.158232449045554e-08</v>
+        <v>1.158232449045549e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.201334649762844e-08</v>
+        <v>1.201334649762846e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.238347645069956e-08</v>
@@ -7554,82 +7554,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.315232235264162e-08</v>
+        <v>1.315232235264157e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.49699840728747e-09</v>
+        <v>9.496998407287471e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.267187830140883e-08</v>
+        <v>1.267187830140879e-08</v>
       </c>
       <c r="E3" t="n">
         <v>1.243834682586689e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.23197181937981e-08</v>
+        <v>1.231971819379808e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.600315383700109e-08</v>
+        <v>1.60031538370011e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.224937447346445e-08</v>
+        <v>1.224937447346451e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.233204466535323e-08</v>
+        <v>1.23320446653532e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.433475252236816e-08</v>
+        <v>1.433475252236815e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.248300615709592e-08</v>
+        <v>1.248300615709591e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.488257207759e-08</v>
+        <v>1.488257207759006e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.812910712551742e-08</v>
+        <v>1.812910712551743e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.254700763856708e-08</v>
+        <v>1.254700763856705e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.917096313552262e-08</v>
+        <v>1.917096313552254e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.387411905724219e-08</v>
+        <v>1.387411905724215e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.246372251097905e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.235863675783525e-08</v>
+        <v>1.235863675783523e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.35128690721134e-08</v>
+        <v>1.351286907211339e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.254862461989303e-08</v>
+        <v>1.2548624619893e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.477670819217995e-08</v>
+        <v>1.477670819217992e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.240403415036683e-08</v>
+        <v>1.240403415036685e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.316295189544937e-08</v>
+        <v>1.316295189544938e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.377426685962265e-08</v>
+        <v>1.377426685962263e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.339884047537189e-08</v>
+        <v>1.339884047537188e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.22233218299267e-08</v>
+        <v>1.222332182992668e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.30722974050107e-08</v>
+        <v>1.307229740501068e-08</v>
       </c>
       <c r="AB3" t="n">
         <v>1.572598827476185e-08</v>
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.011736098980485e-08</v>
+        <v>1.011736098980486e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.298201586142558e-09</v>
+        <v>8.29820158614256e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.343102330070648e-09</v>
+        <v>9.343102330070655e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.013762002858707e-09</v>
+        <v>9.013762002858717e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.784972917531521e-09</v>
+        <v>8.784972917531532e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.465246790687818e-08</v>
+        <v>1.46524679068782e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.67239027199811e-09</v>
+        <v>8.672390271998122e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.805545865470079e-09</v>
+        <v>8.805545865470084e-09</v>
       </c>
       <c r="J4" t="n">
         <v>1.198091464635587e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.043554892532569e-09</v>
+        <v>9.043554892532576e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.285532762996816e-08</v>
+        <v>1.285532762996815e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.799645852037977e-08</v>
+        <v>1.799645852037979e-08</v>
       </c>
       <c r="N4" t="n">
         <v>9.148595751338816e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>9.394643995223364e-09</v>
+        <v>9.394643995223368e-09</v>
       </c>
       <c r="P4" t="n">
         <v>1.126309160918364e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.016480962719894e-09</v>
+        <v>9.016480962719903e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.846837730171326e-09</v>
+        <v>8.846837730171333e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.069211826253491e-08</v>
+        <v>1.069211826253494e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>9.14813087663907e-09</v>
+        <v>9.148130876639075e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.276216638002939e-08</v>
+        <v>1.27621663800294e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.864492325196762e-09</v>
+        <v>8.864492325196754e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.616776170968488e-09</v>
+        <v>9.616776170968499e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.108549452028723e-08</v>
+        <v>1.108549452028726e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.042549652013646e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.707366287968332e-09</v>
+        <v>9.707366287968345e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.981121436081331e-09</v>
+        <v>9.981121436081341e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.414175701958058e-08</v>
+        <v>1.414175701958059e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.0329820968314e-08</v>
+        <v>6.032982096831404e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.044456838973388e-08</v>
+        <v>3.044456838973386e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.056889314389147e-08</v>
+        <v>5.056889314389137e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.019469149592522e-08</v>
+        <v>3.019469149592536e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.029092266654689e-08</v>
+        <v>4.029092266654684e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.379141981677207e-07</v>
+        <v>1.379141981677205e-07</v>
       </c>
       <c r="H5" t="n">
         <v>3.860255884491637e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.030586264125083e-08</v>
+        <v>4.030586264125086e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.454731829460958e-08</v>
+        <v>9.454731829460959e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.512601607922537e-08</v>
+        <v>4.512601607922535e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.12244881665421e-07</v>
+        <v>1.122448816654209e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.11360718198238e-07</v>
+        <v>2.113607181982378e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.084296111421203e-07</v>
+        <v>1.084296111421205e-07</v>
       </c>
       <c r="O5" t="n">
-        <v>4.794569381327032e-08</v>
+        <v>4.794569381327033e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.080605122860608e-08</v>
+        <v>8.08060512286059e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.34033883994932e-08</v>
+        <v>4.340338839949326e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.136567060286668e-08</v>
+        <v>4.13656706028667e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.974330161945102e-08</v>
+        <v>6.974330161945095e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.684861264872122e-08</v>
+        <v>4.684861264872123e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.121157064048346e-07</v>
+        <v>1.121157064048348e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.062847631513449e-08</v>
+        <v>4.062847631513448e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.404135552708636e-08</v>
+        <v>5.404135552708635e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.432362492898931e-08</v>
+        <v>8.432362492898959e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.086285519881473e-08</v>
+        <v>7.086285519881457e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.342866520740127e-08</v>
+        <v>5.342866520740121e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.112308497316995e-08</v>
+        <v>6.112308497316993e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.525858244113069e-07</v>
+        <v>1.525858244113067e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572243785687857e-08</v>
+        <v>1.572243785687856e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091068990921073e-08</v>
+        <v>1.091068990921074e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.494817919714438e-08</v>
+        <v>1.494817919714437e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.461883886993244e-08</v>
+        <v>1.461883886993245e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.439004978460523e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.726495622994636e-08</v>
+        <v>1.726495622994635e-08</v>
       </c>
       <c r="H6" t="n">
         <v>1.427746713907183e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.141803418853826e-08</v>
+        <v>1.141803418853827e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.758599151342959e-08</v>
+        <v>1.459340296942405e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.165604321560075e-08</v>
+        <v>1.165604321560076e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.546781595303633e-08</v>
+        <v>1.846040449704186e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.360153538745351e-08</v>
+        <v>2.360153538745349e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.176726372481438e-08</v>
+        <v>1.176726372481447e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.201331196869886e-08</v>
+        <v>1.201331196869906e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.689537465721778e-08</v>
+        <v>1.689537465721775e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.162896928578807e-08</v>
+        <v>1.462155782979361e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.445191459724504e-08</v>
+        <v>1.445191459724505e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.629719512960864e-08</v>
+        <v>1.629719512960866e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.475320774371279e-08</v>
+        <v>1.176061919970725e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.843976788112684e-08</v>
+        <v>1.843976788112683e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.147698064826494e-08</v>
+        <v>1.446956919227047e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.239152614450868e-08</v>
+        <v>1.23915261445087e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.669057138736097e-08</v>
+        <v>1.369798284335544e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.324577083210313e-08</v>
+        <v>1.324577083210337e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>1.231985461103651e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.558619830315507e-08</v>
+        <v>1.558619830315505e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.678571643337439e-08</v>
+        <v>1.67857164333744e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,16 +7906,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.712175218651837e-08</v>
+        <v>1.71217521865184e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.530259278285609e-08</v>
+        <v>1.530259278285611e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.634749352678419e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.601815319957224e-08</v>
+        <v>1.601815319957227e-08</v>
       </c>
       <c r="F7" t="n">
         <v>1.578936411424505e-08</v>
@@ -7924,67 +7924,67 @@
         <v>2.165685910359174e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.567678146871165e-08</v>
+        <v>1.567678146871167e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.580993706218362e-08</v>
+        <v>1.580993706218363e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.898530584306942e-08</v>
+        <v>1.898530584306943e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.604794608924611e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.98597188266817e-08</v>
+        <v>1.985971882668169e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.50008497170933e-08</v>
+        <v>2.500084971709332e-08</v>
       </c>
       <c r="N7" t="n">
         <v>1.615298694805236e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.639858717909553e-08</v>
+        <v>1.639858717909555e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.826703479305582e-08</v>
+        <v>1.826703479305579e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.602087215943345e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.585122892688486e-08</v>
+        <v>1.585122892688487e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.769650945924844e-08</v>
+        <v>1.769650945924847e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.61525220733526e-08</v>
+        <v>1.615252207335263e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.98376396292435e-08</v>
+        <v>1.983763962924352e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.58688835219103e-08</v>
+        <v>1.586888352191029e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.662116736768201e-08</v>
+        <v>1.662116736768202e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.808988571700077e-08</v>
+        <v>1.808988571700081e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>1.750241235087372e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.671175748468187e-08</v>
+        <v>1.671175748468188e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>1.698551263279487e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.11461482162941e-08</v>
+        <v>2.114614821629411e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.522854828761303e-08</v>
+        <v>3.522854828761301e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.982757956772728e-08</v>
+        <v>4.982757956772738e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.087248031165535e-08</v>
+        <v>5.087248031165538e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>5.054313998444349e-08</v>
+        <v>4.180093775117365e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.645392244068965e-08</v>
+        <v>3.645392244068968e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.618184588846288e-08</v>
+        <v>5.958626468148554e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.020176825358286e-08</v>
+        <v>5.020176825358281e-08</v>
       </c>
       <c r="I8" t="n">
         <v>5.033492384705478e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.351029262794059e-08</v>
+        <v>5.351029262794065e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.057293287411727e-08</v>
+        <v>5.057293287411733e-08</v>
       </c>
       <c r="L8" t="n">
         <v>5.438470561155285e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.952583650196448e-08</v>
+        <v>5.95258365019646e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.795112925012806e-08</v>
+        <v>3.795112925012805e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.169462486447607e-08</v>
+        <v>4.169462486447604e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.270576361762351e-08</v>
+        <v>4.270576361762358e-08</v>
       </c>
       <c r="Q8" t="n">
         <v>3.090111906360238e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.037621571175607e-08</v>
+        <v>5.037621571175608e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.222149624411962e-08</v>
+        <v>5.222149624411965e-08</v>
       </c>
       <c r="T8" t="n">
         <v>5.067750885822382e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.426044557315252e-08</v>
+        <v>4.634979848912138e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>5.039387030678143e-08</v>
+        <v>4.59056811052655e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.11493807998286e-08</v>
+        <v>5.114938079982863e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.447489242224008e-08</v>
+        <v>3.447489242224009e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.83503138741995e-08</v>
+        <v>6.835031387419955e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>5.123674426955305e-08</v>
+        <v>3.451357726449644e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.151049941766604e-08</v>
+        <v>5.151049941766608e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.282130803937781e-08</v>
+        <v>7.282130803937783e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.992350300183963e-08</v>
+        <v>2.992350300183964e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.378328187494201e-08</v>
+        <v>3.378328187494203e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.482818261887014e-08</v>
+        <v>3.482818261887012e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.449884229165819e-08</v>
+        <v>3.318816682179831e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.4270053206331e-08</v>
+        <v>2.117855000530542e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.013754819567767e-08</v>
+        <v>4.013754861227728e-08</v>
       </c>
       <c r="H9" t="n">
         <v>3.41574705607976e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.429062615426956e-08</v>
+        <v>3.429062615426954e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.746599493515532e-08</v>
+        <v>3.746599493515537e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.452863518133206e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.834040791876763e-08</v>
+        <v>3.83404079187676e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.348153880917924e-08</v>
+        <v>4.348153880917925e-08</v>
       </c>
       <c r="N9" t="n">
         <v>3.463367604013828e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.676171754766857e-08</v>
+        <v>3.676171754766861e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.903946631630145e-08</v>
+        <v>3.903946631630143e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.450156166811894e-08</v>
+        <v>3.450156166811896e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.43319180189708e-08</v>
+        <v>3.433191801897079e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.617719855133439e-08</v>
+        <v>3.61771985513344e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.463321116543853e-08</v>
+        <v>3.463321116543857e-08</v>
       </c>
       <c r="U9" t="n">
         <v>3.831977130285258e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.434957261399623e-08</v>
+        <v>4.090294018417002e-08</v>
       </c>
       <c r="W9" t="n">
         <v>3.510185645976795e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.65705748090867e-08</v>
+        <v>3.657057480908672e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.598310144295967e-08</v>
+        <v>3.59831014429597e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.519244657676781e-08</v>
+        <v>3.176855195220083e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.546620172488081e-08</v>
+        <v>3.54662017248808e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.962683730838005e-08</v>
+        <v>3.962683730838008e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8329,46 +8329,46 @@
         <v>1.168336414549539e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.017966423406816e-08</v>
+        <v>1.017966423406815e-08</v>
       </c>
       <c r="D2" t="n">
         <v>1.171092110034996e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.16836998165518e-08</v>
+        <v>1.168369981655179e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.168059669211717e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.211650161784663e-08</v>
+        <v>1.211650161784661e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.169494368364333e-08</v>
+        <v>1.169494368364331e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.170307267765074e-08</v>
+        <v>1.170307267765075e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.184214668303245e-08</v>
+        <v>1.184214668303243e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.171840296247871e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.18179058220382e-08</v>
+        <v>1.181790582203819e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.175452857528273e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.171030334328463e-08</v>
+        <v>1.171030334328462e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.55410950855805e-08</v>
+        <v>1.554109508558046e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.179806237925439e-08</v>
+        <v>1.179806237925437e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.170018400415324e-08</v>
@@ -8380,31 +8380,31 @@
         <v>1.171629858841774e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.16935846030668e-08</v>
+        <v>1.169358460306677e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.169453769838882e-08</v>
+        <v>1.169453769838881e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.170347611934748e-08</v>
+        <v>1.170347611934749e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.195923231538676e-08</v>
+        <v>1.195923231538673e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.188523963928019e-08</v>
+        <v>1.188523963928017e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.203406230347355e-08</v>
+        <v>1.203406230347354e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.127901795738182e-08</v>
+        <v>1.127901795738183e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.173018447682907e-08</v>
+        <v>1.173018447682908e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.199104318919588e-08</v>
+        <v>1.199104318919584e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.191841413059557e-08</v>
+        <v>1.191841413059554e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.430624234323366e-09</v>
+        <v>9.430624234323356e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.211874273739217e-08</v>
+        <v>1.211874273739215e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.189959420884426e-08</v>
+        <v>1.189959420884424e-08</v>
       </c>
       <c r="F3" t="n">
         <v>1.19028031006586e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.49897490862493e-08</v>
+        <v>1.498974908624921e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.200565263350539e-08</v>
+        <v>1.200565263350537e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.206248962793396e-08</v>
+        <v>1.206248962793398e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.304693013587271e-08</v>
+        <v>1.304693013587268e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.217361554853389e-08</v>
+        <v>1.217361554853391e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.287704969925784e-08</v>
+        <v>1.287704969925785e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.250923453626661e-08</v>
+        <v>1.250923453626659e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.211241465097028e-08</v>
+        <v>1.211241465097026e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.836342637176944e-08</v>
+        <v>1.83634263717694e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.273303581846022e-08</v>
+        <v>1.273303581846019e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.204102870872086e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.20865625588615e-08</v>
+        <v>1.208656255886152e-08</v>
       </c>
       <c r="S3" t="n">
         <v>1.215354077189208e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.199456322013867e-08</v>
+        <v>1.199456322013862e-08</v>
       </c>
       <c r="U3" t="n">
         <v>1.227897805549033e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.206370357309789e-08</v>
+        <v>1.206370357309787e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.272660943096717e-08</v>
+        <v>1.27266094309672e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.336210641127034e-08</v>
+        <v>1.336210641127032e-08</v>
       </c>
       <c r="Y3" t="n">
         <v>1.442221014707998e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.137810642758055e-08</v>
+        <v>1.137810642758052e-08</v>
       </c>
       <c r="AA3" t="n">
         <v>1.22537828930608e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.412505573896337e-08</v>
+        <v>1.412505573896333e-08</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.976139218562397e-09</v>
+        <v>7.976139218562402e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.969714145244461e-09</v>
+        <v>7.969714145244407e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.287407700470369e-09</v>
+        <v>8.287407700470333e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.979930777560976e-09</v>
+        <v>7.979930777560936e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.944879559564064e-09</v>
+        <v>7.944879559564023e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.286862622185126e-08</v>
+        <v>1.286862622185107e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.106935428794134e-09</v>
+        <v>8.106935428794108e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.198756155629712e-09</v>
+        <v>8.198756155629724e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.758939198141923e-09</v>
+        <v>9.758939198141886e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.371918775041158e-09</v>
+        <v>8.371918775041111e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.495849347342251e-09</v>
+        <v>9.495849347342191e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.922439770707374e-09</v>
+        <v>8.922439770707334e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>8.280429850235142e-09</v>
+        <v>8.280429850235144e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.13300053250782e-09</v>
+        <v>8.133000532507762e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.271708532664605e-09</v>
+        <v>9.271708532664633e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.166127259619907e-09</v>
+        <v>8.166127259619864e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.235985731671395e-09</v>
+        <v>8.235985731671356e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>8.348148901962538e-09</v>
+        <v>8.348148901962533e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>8.091583988474203e-09</v>
+        <v>8.091583988474178e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>8.62269987369602e-09</v>
+        <v>8.622699873696023e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>8.146846830605349e-09</v>
+        <v>8.146846830605336e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.700652676001826e-09</v>
+        <v>8.700652676001828e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.025641578817691e-08</v>
+        <v>1.025641578817689e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.188499746016888e-08</v>
+        <v>1.188499746016887e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.23800093261916e-09</v>
+        <v>8.238000932619122e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.504996399393074e-09</v>
+        <v>8.504996399393064e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.144594131478554e-08</v>
+        <v>1.144594131478555e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.840414304182706e-08</v>
+        <v>2.840414304182703e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.058248285478567e-08</v>
+        <v>3.058248285478557e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.580264212960848e-08</v>
+        <v>3.580264212960842e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.747674371942628e-08</v>
+        <v>1.747674371942623e-08</v>
       </c>
       <c r="F5" t="n">
         <v>2.999693365477137e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.045771712761903e-07</v>
+        <v>1.04577171276188e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.309860884871129e-08</v>
+        <v>3.309860884871121e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.411108352670329e-08</v>
+        <v>3.411108352670324e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.766730053110618e-08</v>
+        <v>5.766730053110553e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.806142425844103e-08</v>
+        <v>3.8061424258441e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.445611250282532e-08</v>
+        <v>5.445611250282523e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.799744121947994e-08</v>
+        <v>4.799744121947986e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.071515105048747e-08</v>
+        <v>4.071515105048743e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.166111786322218e-08</v>
+        <v>3.166111786322219e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.925313076431743e-08</v>
+        <v>4.925313076431748e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.309644410858801e-08</v>
+        <v>3.309644410858799e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.50542517777893e-08</v>
+        <v>3.505425177778921e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.502099830954226e-08</v>
+        <v>3.502099830954223e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.210697473986504e-08</v>
+        <v>3.210697473986481e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.110985985582827e-08</v>
+        <v>4.110985985582823e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.327214503299392e-08</v>
+        <v>3.327214503299393e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.169399355747021e-08</v>
+        <v>4.169399355747018e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.023579932032321e-08</v>
+        <v>7.023579932032313e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.890452163030163e-08</v>
+        <v>9.890452163030158e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.300954191788924e-08</v>
+        <v>3.300954191788918e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.838476361789225e-08</v>
+        <v>3.838476361789213e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.689866570998249e-08</v>
+        <v>9.689866570998241e-08</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.304414334495171e-08</v>
+        <v>1.035462448151597e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.303771827163373e-08</v>
+        <v>1.303771827163367e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.066589296342397e-08</v>
+        <v>1.066589296342388e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.035841604051455e-08</v>
+        <v>1.304793490395019e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.032336482251756e-08</v>
+        <v>1.301288368595328e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.793663034824047e-08</v>
+        <v>1.524711148480462e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.048542069174769e-08</v>
+        <v>1.317493955518338e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.05772414185833e-08</v>
+        <v>1.326676028201899e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.482694332453125e-08</v>
+        <v>1.213742446109543e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.075040403799463e-08</v>
+        <v>1.343992290143038e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.456385347373155e-08</v>
+        <v>1.187433461029575e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.130092503366096e-08</v>
+        <v>1.399044389709659e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.066275875511106e-08</v>
+        <v>1.066275875511089e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.322353830851118e-08</v>
+        <v>1.051532943738354e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.149040669294127e-08</v>
+        <v>1.149040669294111e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.05446125225735e-08</v>
+        <v>1.323413138600915e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.33039898580607e-08</v>
+        <v>1.330398985806061e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.072663416491612e-08</v>
+        <v>1.072663416491608e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.04700692514278e-08</v>
+        <v>1.047006925142772e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.374314278196527e-08</v>
+        <v>1.10536239185295e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.321485095699465e-08</v>
+        <v>1.321485095699461e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.122803811301908e-08</v>
+        <v>1.122803811301911e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.532441991456625e-08</v>
+        <v>1.263490105113043e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.443977835277727e-08</v>
+        <v>1.443977835277725e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.061648619557275e-08</v>
+        <v>1.061648619557268e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.357300052578237e-08</v>
+        <v>1.357300052578233e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.384453125890906e-08</v>
+        <v>1.38445312589091e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,55 +8766,55 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.446578387914888e-08</v>
+        <v>1.446578387914886e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.445935880583089e-08</v>
+        <v>1.445935880583088e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.477705236105682e-08</v>
+        <v>1.47770523610568e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.446957543814743e-08</v>
+        <v>1.446957543814741e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.443452422015054e-08</v>
+        <v>1.443452422015048e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.935827088243772e-08</v>
+        <v>1.935827088243748e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.459658008938059e-08</v>
+        <v>1.459658008938058e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.468840081621618e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.624858385872841e-08</v>
+        <v>1.624858385872834e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.486156343562761e-08</v>
+        <v>1.486156343562759e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.598549400792869e-08</v>
+        <v>1.598549400792866e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.54120844312938e-08</v>
+        <v>1.541208443129379e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.477007451082163e-08</v>
+        <v>1.47700745108216e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.46222267825649e-08</v>
+        <v>1.462222678256486e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.576093478272174e-08</v>
+        <v>1.576093478272172e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.465577192020642e-08</v>
+        <v>1.465577192020634e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.472563039225784e-08</v>
+        <v>1.472563039225782e-08</v>
       </c>
       <c r="S7" t="n">
         <v>1.4837793562549e-08</v>
@@ -8823,28 +8823,28 @@
         <v>1.458122864906065e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.516436243127973e-08</v>
+        <v>1.516436243127972e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.46364914911918e-08</v>
+        <v>1.463649149119181e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.519029733658833e-08</v>
+        <v>1.519029733658827e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.674606044876344e-08</v>
+        <v>1.674606044876334e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.84270809026353e-08</v>
+        <v>1.842708090263525e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.472764559320561e-08</v>
+        <v>1.472764559320559e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.499464105997951e-08</v>
+        <v>1.499464105997952e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.793558597537203e-08</v>
+        <v>1.793558597537201e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8857,82 +8857,82 @@
         <v>3.125293760495072e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.646410669818871e-08</v>
+        <v>4.64641066981886e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.678180025341466e-08</v>
+        <v>4.678180025341456e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.64743233305053e-08</v>
+        <v>3.837140332730028e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.359240126557246e-08</v>
+        <v>3.35924012655724e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.136301877479542e-08</v>
+        <v>5.451848605880376e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.660132798173836e-08</v>
+        <v>4.660132798173833e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.669314870857406e-08</v>
+        <v>4.669314870857396e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.82533317510862e-08</v>
+        <v>4.825333175108607e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.686631132798535e-08</v>
+        <v>4.68663113279853e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.799024190028651e-08</v>
+        <v>4.799024190028641e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.741683232365163e-08</v>
+        <v>4.741683232365147e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.497864107661851e-08</v>
+        <v>3.497864107661846e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.807290481313986e-08</v>
+        <v>3.807290481313987e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.841699551528665e-08</v>
+        <v>3.84169955152865e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.845232106703006e-08</v>
+        <v>2.845232106703005e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.673037828461567e-08</v>
+        <v>4.673037828461557e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.684254145490687e-08</v>
+        <v>4.684254145490671e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.658597654141849e-08</v>
+        <v>4.65859765414184e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.780541430788668e-08</v>
+        <v>3.974202468654971e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.664123938354959e-08</v>
+        <v>4.248203933058813e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.719803592447482e-08</v>
+        <v>4.719803592447475e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.193733234015224e-08</v>
+        <v>3.19373323401522e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.556233302020111e-08</v>
+        <v>6.556233302020113e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>4.673239348556344e-08</v>
+        <v>3.123212469443355e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.699938895233733e-08</v>
+        <v>4.699938895233729e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.583638345133558e-08</v>
+        <v>6.583638345133548e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.49660407125594e-08</v>
+        <v>2.496604071255936e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.984445245751384e-08</v>
+        <v>2.98444524575137e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.016214601273976e-08</v>
+        <v>3.016214601273966e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.985466908983035e-08</v>
+        <v>2.872727015678432e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.981961787183335e-08</v>
+        <v>1.85587332962938e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.474336453412055e-08</v>
+        <v>3.474336645782945e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.998167374106349e-08</v>
+        <v>2.998167374106342e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.007349446789912e-08</v>
+        <v>3.007349446789899e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.163367751041128e-08</v>
+        <v>3.163367751041121e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.024665708731047e-08</v>
+        <v>3.024665708731039e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.137058765961162e-08</v>
+        <v>3.13705876596115e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.079717808297676e-08</v>
+        <v>3.079717808297665e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.015516816250455e-08</v>
+        <v>3.015516816250442e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.162656993142929e-08</v>
+        <v>3.162656993142925e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.311734550009475e-08</v>
+        <v>3.311734550009472e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.00408674955984e-08</v>
+        <v>3.004086749559831e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.01107240439408e-08</v>
+        <v>3.011072404394067e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.022288721423193e-08</v>
+        <v>3.022288721423185e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.996632230074355e-08</v>
+        <v>2.996632230074349e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.054987696784539e-08</v>
+        <v>3.054987696784526e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.002158514287469e-08</v>
+        <v>3.565858083318147e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.057539098827121e-08</v>
+        <v>3.057539098827112e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.213115410044625e-08</v>
+        <v>3.213115410044616e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.381217455431815e-08</v>
+        <v>3.38121745543181e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.01127392448885e-08</v>
+        <v>2.716761778399194e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.037973471166249e-08</v>
+        <v>3.037973471166236e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.332067962705499e-08</v>
+        <v>3.332067962705485e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.231550282710426e-08</v>
+        <v>1.213865291037201e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.046429760863975e-08</v>
+        <v>1.025308702849028e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.207590731906912e-08</v>
+        <v>1.188454034573308e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.207854358306313e-08</v>
+        <v>1.187299594628184e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.205717620159521e-08</v>
+        <v>1.185131203875431e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.257222413841891e-08</v>
+        <v>1.219613403884771e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.207853614581072e-08</v>
+        <v>1.184068895291671e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.206415573291505e-08</v>
+        <v>1.183362529011217e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.233459810750583e-08</v>
+        <v>1.208287922756938e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.208942946304265e-08</v>
+        <v>1.186953817672822e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.242976844056206e-08</v>
+        <v>1.23031245224255e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.290861754720907e-08</v>
+        <v>1.259351219136386e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.205630494104407e-08</v>
+        <v>1.185262907761087e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.624085605210384e-08</v>
+        <v>1.581343175363934e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.225948148963143e-08</v>
+        <v>1.200823482323903e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.20625575757717e-08</v>
+        <v>1.186785267238396e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.204537916985655e-08</v>
+        <v>1.182117453065315e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232926709685782e-08</v>
+        <v>1.208451858537173e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.210422607353232e-08</v>
+        <v>1.185187494012945e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.25848312027351e-08</v>
+        <v>1.231928390110743e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.210179625344366e-08</v>
+        <v>1.19251896305271e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.234736024028438e-08</v>
+        <v>1.200665471067468e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.219772472303339e-08</v>
+        <v>1.200732940840246e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.219142189643252e-08</v>
+        <v>1.204580064465203e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.178863598917354e-08</v>
+        <v>1.155164040929262e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.215164430083518e-08</v>
+        <v>1.193985004639763e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.258676150356376e-08</v>
+        <v>1.297684091735405e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.450644649987073e-08</v>
+        <v>1.447874293198165e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.663189085490548e-09</v>
+        <v>9.472153586682455e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.28100187746752e-08</v>
+        <v>1.26792635693619e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.280312811155631e-08</v>
+        <v>1.257115513522187e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.267788597258443e-08</v>
+        <v>1.244321819219725e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.633715462531958e-08</v>
+        <v>1.489123555606786e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.283248263688595e-08</v>
+        <v>1.236819779952835e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.272668208547441e-08</v>
+        <v>1.231538545733659e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.464974526948599e-08</v>
+        <v>1.408915821864344e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.290620006142732e-08</v>
+        <v>1.257133980786608e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.533109456470324e-08</v>
+        <v>1.566213823898984e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.880973510767093e-08</v>
+        <v>1.779770161651943e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.26680532998327e-08</v>
+        <v>1.244930630533407e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.038087363450077e-08</v>
+        <v>1.95499655233988e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.410891726388568e-08</v>
+        <v>1.355202600546948e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.2713337240083e-08</v>
+        <v>1.255869264131637e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.259297305800339e-08</v>
+        <v>1.222681891796653e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.460846756713976e-08</v>
+        <v>1.409752729780076e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.3013078750486e-08</v>
+        <v>1.244565916774316e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.661999618002571e-08</v>
+        <v>1.665168517499226e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.298857182388919e-08</v>
+        <v>1.29626284487921e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.357122987855405e-08</v>
+        <v>1.316885977047194e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.36808109381291e-08</v>
+        <v>1.355698497525673e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.363211082589232e-08</v>
+        <v>1.382787028058435e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.279404488930078e-08</v>
+        <v>1.257739639720191e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.334798932652692e-08</v>
+        <v>1.307131642852322e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.646720004263908e-08</v>
+        <v>2.045413022508703e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.233683807430899e-08</v>
+        <v>1.154997632009052e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.643943223785165e-09</v>
+        <v>7.637153295395883e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.630496591672692e-09</v>
+        <v>8.679658004938345e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.660274406226248e-09</v>
+        <v>8.549258702450244e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.418920003065165e-09</v>
+        <v>8.304328991837084e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.523662338324536e-08</v>
+        <v>1.219925210884874e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.66019039903932e-09</v>
+        <v>8.18433635044028e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.497757020065465e-09</v>
+        <v>8.104549029617305e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.25413871605007e-08</v>
+        <v>1.090962630829707e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.783235428347248e-09</v>
+        <v>8.510201604689821e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.362752074309389e-08</v>
+        <v>1.340775883891377e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.909643513444844e-08</v>
+        <v>1.675733834123674e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.409078714340266e-09</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.10868738476188e-08</v>
+        <v>9.492752089491204e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.170405129646488e-08</v>
+        <v>1.007684403063902e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.479705099942903e-09</v>
+        <v>8.491163057750626e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>9.285667102674423e-09</v>
+        <v>7.963911973895554e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.249231183305185e-08</v>
+        <v>1.093850421619243e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>9.950369950605034e-09</v>
+        <v>8.31068722181647e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.568627022162401e-08</v>
+        <v>1.53550621483701e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.863664391419838e-09</v>
+        <v>9.084846658521196e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.028164402059419e-08</v>
+        <v>9.279222638217893e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.100648020822349e-08</v>
+        <v>1.006661695354843e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.086137856558998e-08</v>
+        <v>1.045919710961838e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.058976882957903e-08</v>
+        <v>9.617272090290721e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.048598064145319e-08</v>
+        <v>9.304406517663903e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.537645397946564e-08</v>
+        <v>2.089226990867005e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.018847212390887e-07</v>
+        <v>1.044267412487091e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>3.450055480241608e-08</v>
+        <v>3.288416047604671e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.54545249295704e-08</v>
+        <v>5.502564677895101e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.077594495769412e-08</v>
+        <v>3.711569738866994e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.211632787522704e-08</v>
+        <v>4.812509830034597e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.593739720289764e-07</v>
+        <v>1.188372299508601e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>5.825265494736028e-08</v>
+        <v>4.61824610727156e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.309939296677842e-08</v>
+        <v>4.315009182699524e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.103863577419363e-07</v>
+        <v>9.676676854868964e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.833604647452307e-08</v>
+        <v>5.110645637896072e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.333019254056689e-07</v>
+        <v>1.47516434288176e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.603258858005189e-07</v>
+        <v>2.299961227913915e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.670094186610469e-07</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>7.792474640899842e-08</v>
+        <v>6.570335064605461e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.050747854823205e-08</v>
+        <v>7.718803059222063e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.158358953204987e-08</v>
+        <v>5.035596801741584e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.900680526229133e-08</v>
+        <v>4.049338728589628e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.072651158912045e-07</v>
+        <v>9.517018991446336e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.245930013298538e-08</v>
+        <v>4.731615916549348e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.73360518485064e-07</v>
+        <v>1.844339919233378e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>5.758871607434101e-08</v>
+        <v>6.020551430599571e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.669902970528615e-08</v>
+        <v>6.520180227248396e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.398127168820023e-08</v>
+        <v>8.377012388165912e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.033867593381806e-08</v>
+        <v>9.033036304513735e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>7.018843942841507e-08</v>
+        <v>6.929057875678671e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.115580629947301e-08</v>
+        <v>6.600482779799028e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.856876453977821e-07</v>
+        <v>3.290201742866335e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.844843398392102e-08</v>
+        <v>1.447391998926052e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.475553913339721e-08</v>
+        <v>1.369188478276489e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.249128180486455e-08</v>
+        <v>1.473438949230735e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.252105961941811e-08</v>
+        <v>1.460399018981925e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.55305159126772e-08</v>
+        <v>1.122827266100711e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.134821929285739e-08</v>
+        <v>1.825398359621776e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.577178630865134e-08</v>
+        <v>1.423906783780932e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.235854223325732e-08</v>
+        <v>1.102849269878732e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.865298307011273e-08</v>
+        <v>1.38335699774671e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.264402064153912e-08</v>
+        <v>1.456493309205883e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.648830595628574e-08</v>
+        <v>1.946249032628281e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.195722034764032e-08</v>
+        <v>2.281206982860578e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.228133956026391e-08</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.722140006079766e-08</v>
+        <v>1.24301183971107e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.783858306554175e-08</v>
+        <v>1.614335125790314e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.234049031313477e-08</v>
+        <v>1.454589454511965e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.214645231586628e-08</v>
+        <v>1.401864346126457e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.860390774266388e-08</v>
+        <v>1.386244788536244e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.281115516379689e-08</v>
+        <v>1.123463089098648e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.862096375154912e-08</v>
+        <v>1.832097597255214e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.597526030103186e-08</v>
+        <v>1.513957814589022e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.641617329687627e-08</v>
+        <v>1.534572743442472e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.711807611783551e-08</v>
+        <v>1.612134844091746e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.39494319396077e-08</v>
+        <v>1.358313730903426e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.34505540427709e-08</v>
+        <v>1.254121575946075e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.334676585464505e-08</v>
+        <v>1.535913800503292e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.827461472189941e-08</v>
+        <v>2.389556454695249e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.984700840033515e-08</v>
+        <v>1.885423465042767e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.615411354981134e-08</v>
+        <v>1.494141162573302e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.714066691769885e-08</v>
+        <v>1.598391633527553e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.717044473225242e-08</v>
+        <v>1.58535170327874e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.692909032909133e-08</v>
+        <v>1.560858732217424e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.274679370927153e-08</v>
+        <v>1.950351043918591e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.71703607250655e-08</v>
+        <v>1.548859468077743e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.700792734609163e-08</v>
+        <v>1.540880735995446e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.005155748652686e-08</v>
+        <v>1.821388463863422e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.729340575437342e-08</v>
+        <v>1.581445993502698e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.113769106912004e-08</v>
+        <v>2.071201716925094e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.660660546047462e-08</v>
+        <v>2.406159667157388e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.691924904036643e-08</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.859656288256717e-08</v>
+        <v>1.679653039892844e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.921374033141326e-08</v>
+        <v>1.738062234007622e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.698987542596907e-08</v>
+        <v>1.579542138808779e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.67958374287006e-08</v>
+        <v>1.526817030423272e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>2.0002482159078e-08</v>
+        <v>1.824276254652959e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.746054027663119e-08</v>
+        <v>1.561494555215363e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.326870961102521e-08</v>
+        <v>2.270004766575629e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.737383471744599e-08</v>
+        <v>1.638910498885835e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.779181434662038e-08</v>
+        <v>1.658348096855504e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.851665053424966e-08</v>
+        <v>1.737087528388561e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.84454572083494e-08</v>
+        <v>1.780542559496757e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.809993915560518e-08</v>
+        <v>1.692153042062789e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.799615096747934e-08</v>
+        <v>1.660866484800106e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.288662430549181e-08</v>
+        <v>2.81965282390072e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.923131786339396e-08</v>
+        <v>3.819488019003748e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.312299606171095e-08</v>
+        <v>5.164560202293805e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.410954942959849e-08</v>
+        <v>5.268810673248049e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.477606080758243e-08</v>
+        <v>4.331213198533714e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.905287075819461e-08</v>
+        <v>3.765427021884337e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>6.336195199587351e-08</v>
+        <v>5.980814497577374e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.413924323696511e-08</v>
+        <v>5.219278507798243e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.397680985799122e-08</v>
+        <v>5.21129977571595e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.702043999842647e-08</v>
+        <v>5.491807503583931e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.426228826627302e-08</v>
+        <v>5.251865033223196e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.810657358101971e-08</v>
+        <v>5.741620756645593e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>6.357548797237432e-08</v>
+        <v>6.076578706877909e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.025714560506304e-08</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.568085403382986e-08</v>
+        <v>4.374037796785079e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.537981761985251e-08</v>
+        <v>4.341779747789603e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.291841493594904e-08</v>
+        <v>3.172373405892045e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.376471994060018e-08</v>
+        <v>5.19723607014377e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.697136467097765e-08</v>
+        <v>5.494695294373462e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.442942278853083e-08</v>
+        <v>5.231913594935862e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.165553857896793e-08</v>
+        <v>5.092997527082238e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.953559847582251e-08</v>
+        <v>4.834692461913759e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.476415273349579e-08</v>
+        <v>5.329108380236302e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.605685110678424e-08</v>
+        <v>3.489059134435565e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.289674527545651e-08</v>
+        <v>7.177278194214744e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.715760614611786e-08</v>
+        <v>3.593963919981977e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.496503347937892e-08</v>
+        <v>5.331285524520606e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.822406376735722e-08</v>
+        <v>8.303839315834566e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,85 +1202,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.544030939852853e-08</v>
+        <v>3.402471437820303e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.835273940865319e-08</v>
+        <v>3.651615515703712e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.93392927765407e-08</v>
+        <v>3.755865986657955e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.784458892159093e-08</v>
+        <v>3.595018285987866e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.390063899937524e-08</v>
+        <v>2.241975445720662e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.494542004354635e-08</v>
+        <v>4.10782543073647e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.936898658390731e-08</v>
+        <v>3.706333821208153e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.920655320493346e-08</v>
+        <v>3.698355089125852e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.225018334536867e-08</v>
+        <v>3.978862816993836e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.949203161321528e-08</v>
+        <v>3.738920346633108e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>4.333631692796191e-08</v>
+        <v>4.228676070055507e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.880523131931643e-08</v>
+        <v>4.563634020287798e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.911787489920831e-08</v>
+        <v>4.645639674541524e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>4.298466667536253e-08</v>
+        <v>4.049411903846936e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.407791323377763e-08</v>
+        <v>4.153978889919543e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.918850176024392e-08</v>
+        <v>3.737016525626658e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.899446328754244e-08</v>
+        <v>3.68429138355368e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>4.220110801791986e-08</v>
+        <v>3.98175060778337e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.965916613547301e-08</v>
+        <v>3.718968908345773e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.546897472322526e-08</v>
+        <v>4.427603416502338e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>4.719485799663648e-08</v>
+        <v>4.535422585572641e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.999044020546221e-08</v>
+        <v>3.815822449985912e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>4.071527639309149e-08</v>
+        <v>3.894561881518968e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.064408306719125e-08</v>
+        <v>3.938016912627163e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.631614168066932e-08</v>
+        <v>3.463507250153074e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>4.019477682632119e-08</v>
+        <v>3.818340837930518e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.508525016433367e-08</v>
+        <v>4.977127177031128e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.130782687244707e-08</v>
+        <v>1.134762365869344e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.787618711343155e-09</v>
+        <v>9.828775943552308e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.133019316304612e-08</v>
+        <v>1.136979469707403e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.129909065740387e-08</v>
+        <v>1.133862939251848e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.131091647212547e-08</v>
+        <v>1.135051244107919e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.135916988625816e-08</v>
+        <v>1.139449799014903e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.132842461376451e-08</v>
+        <v>1.136812993694069e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.132816233060079e-08</v>
+        <v>1.136775044338862e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.134252769411869e-08</v>
+        <v>1.138110433251288e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.133479919733551e-08</v>
+        <v>1.137416663440046e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.133238553531353e-08</v>
+        <v>1.13726498932548e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.133301281792523e-08</v>
+        <v>1.137174279354704e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.132214773002577e-08</v>
+        <v>1.136197552008248e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.496239560995369e-08</v>
+        <v>1.501377936816859e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.131932095951876e-08</v>
+        <v>1.135882106154829e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.131734260205715e-08</v>
+        <v>1.135704423371346e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.133059271589387e-08</v>
+        <v>1.137034897720795e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.133441913088441e-08</v>
+        <v>1.137306233379068e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.132030541045843e-08</v>
+        <v>1.135986529328681e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.118407435464607e-08</v>
+        <v>1.124191740573238e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.134120770876516e-08</v>
+        <v>1.138102069092448e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.146399559253274e-08</v>
+        <v>1.151381354246876e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.152750906584543e-08</v>
+        <v>1.156694874729175e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.151235136162773e-08</v>
+        <v>1.155213011398589e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.084705639605065e-08</v>
+        <v>1.08902829289131e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.137205789460647e-08</v>
+        <v>1.141157853357003e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.133441768199388e-08</v>
+        <v>1.137864578109885e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.161440173890636e-08</v>
+        <v>1.165707786572558e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.080049154309567e-09</v>
+        <v>9.123522028671046e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.177776904238583e-08</v>
+        <v>1.181908479070447e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.153281390744147e-08</v>
+        <v>1.157377334456472e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.164014376829156e-08</v>
+        <v>1.168140940765457e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.198018679951634e-08</v>
+        <v>1.199120760756652e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.17665286018506e-08</v>
+        <v>1.18085762826402e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.176310059388325e-08</v>
+        <v>1.180430500442473e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.186308215810076e-08</v>
+        <v>1.189712597057274e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.181161188674326e-08</v>
+        <v>1.185130240279711e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.179167758324122e-08</v>
+        <v>1.183770697337409e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.187246877258887e-08</v>
+        <v>1.190764167956329e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.171786601954125e-08</v>
+        <v>1.176075919350984e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.76557303157572e-08</v>
+        <v>1.771652001884816e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.169600896671221e-08</v>
+        <v>1.173658340566555e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.168438924439466e-08</v>
+        <v>1.172640424721806e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.178066521261712e-08</v>
+        <v>1.182306544279231e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.180396527449422e-08</v>
+        <v>1.183846636296469e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.170614795898991e-08</v>
+        <v>1.17471382900955e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.166458660534132e-08</v>
+        <v>1.178440098361863e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.185303708323832e-08</v>
+        <v>1.18958529573129e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.231358923819472e-08</v>
+        <v>1.237266695217827e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.31829148919368e-08</v>
+        <v>1.322306808529053e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.307615240822071e-08</v>
+        <v>1.31186924086249e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.090970575989191e-08</v>
+        <v>1.095838415243407e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.20736783122176e-08</v>
+        <v>1.211437392664704e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.182246699741705e-08</v>
+        <v>1.189648929740171e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.462100298180065e-09</v>
+        <v>7.242913267740088e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.418031079035938e-09</v>
+        <v>7.195796851402907e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.714737839498207e-09</v>
+        <v>7.493345345430244e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.363420730409816e-09</v>
+        <v>7.141318893727053e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.49699874783367e-09</v>
+        <v>7.275543393692579e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.042043258129559e-09</v>
+        <v>7.77238040478881e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.694761261789716e-09</v>
+        <v>7.474541113896801e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.691798652799225e-09</v>
+        <v>7.470254559650477e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.844927871488506e-09</v>
+        <v>7.611975575708714e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.766765115677378e-09</v>
+        <v>7.54272838872226e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.739501692799742e-09</v>
+        <v>7.525596099747335e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.881641818552969e-09</v>
+        <v>7.650534813393276e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.478287973631621e-09</v>
+        <v>7.256954737772854e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.591931299196163e-09</v>
+        <v>7.369393084045398e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.569584841577993e-09</v>
+        <v>7.34932299626973e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.719250972717036e-09</v>
+        <v>7.499606194524471e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.762472090272881e-09</v>
+        <v>7.530254805331889e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.603051125429449e-09</v>
+        <v>7.381188161902139e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.971229992986793e-09</v>
+        <v>7.848145974461317e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.793450644527034e-09</v>
+        <v>7.574564515908215e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.369612803580925e-09</v>
+        <v>8.15014675637763e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.943511731416147e-09</v>
+        <v>9.72029103798375e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.763586037189113e-09</v>
+        <v>9.542102572065399e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.576364236157873e-09</v>
+        <v>7.357850773989662e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.18761924120061e-09</v>
+        <v>7.965313000167178e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.786241482591958e-09</v>
+        <v>7.616312679362867e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.782237531586633e-08</v>
+        <v>2.770988159522123e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.909364819155357e-08</v>
+        <v>2.894732433433881e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.422779669872602e-08</v>
+        <v>3.409347295360887e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.610796107272894e-08</v>
+        <v>1.600870994792588e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.035258783476082e-08</v>
+        <v>3.02117675657291e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.774143607409198e-08</v>
+        <v>3.685947458925857e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.459055245023675e-08</v>
+        <v>3.447239498849876e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.373175478935896e-08</v>
+        <v>3.358669151694466e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.527376346544471e-08</v>
+        <v>3.495688173991382e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.565032499219213e-08</v>
+        <v>3.549282809956268e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.37648375156117e-08</v>
+        <v>3.375414002930823e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.780049738796014e-08</v>
+        <v>3.74978833495586e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.859127663393745e-08</v>
+        <v>2.845616345653516e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.989755303223405e-08</v>
+        <v>2.973395643077938e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.079783592865798e-08</v>
+        <v>3.067565988914386e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.433070148314191e-08</v>
+        <v>3.421702061522113e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.301744459684144e-08</v>
+        <v>3.270462069851467e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.170741583744854e-08</v>
+        <v>3.155018276657897e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.749438661704784e-08</v>
+        <v>3.89397558351438e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.464997695697813e-08</v>
+        <v>3.455335514672666e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.418966448159558e-08</v>
+        <v>4.406982322154632e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.203691334817186e-08</v>
+        <v>7.186641741551289e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.974398540133508e-08</v>
+        <v>6.962404487899692e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.004564357514302e-08</v>
+        <v>2.995215196572592e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.109826872448794e-08</v>
+        <v>4.092561328125654e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.633409157017473e-08</v>
+        <v>3.717151784110141e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.88319787252662e-09</v>
+        <v>9.669866987036873e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>9.839128653382519e-09</v>
+        <v>1.204558312281591e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.254911363948678e-08</v>
+        <v>9.920299064727045e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.784518304756363e-09</v>
+        <v>1.199110516514004e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>9.918096322180229e-09</v>
+        <v>1.21253296651056e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.287641905811811e-08</v>
+        <v>1.019933412408563e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.252913706177828e-08</v>
+        <v>9.901494833193593e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.25261744527878e-08</v>
+        <v>9.897208278947287e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.267930367147709e-08</v>
+        <v>1.246176184712172e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.018786269002393e-08</v>
+        <v>9.969682108019032e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.257387749278831e-08</v>
+        <v>1.237538237116035e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.271601761854154e-08</v>
+        <v>1.007748853269006e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.233072428946456e-08</v>
+        <v>1.212771806625636e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.244442471469667e-08</v>
+        <v>9.639447542100945e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.240396064156654e-08</v>
+        <v>9.776276715566525e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.255362677270562e-08</v>
+        <v>9.926559913821277e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.259684789026145e-08</v>
+        <v>1.238004107674491e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.0024148699776e-08</v>
+        <v>9.808141881198949e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.281431824517522e-08</v>
+        <v>1.270873743169448e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.262782644451559e-08</v>
+        <v>1.000151823520503e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.093838086694465e-08</v>
+        <v>1.072516255751564e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.236460930576271e-08</v>
+        <v>1.457007730939677e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.232206356254195e-08</v>
+        <v>1.21090072087665e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.997461810504416e-09</v>
+        <v>9.784804493286477e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.060871681554717e-08</v>
+        <v>1.28150992715802e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.021057361271168e-08</v>
+        <v>1.004664365339435e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.373608447738143e-08</v>
+        <v>1.352448492537922e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.369201525823732e-08</v>
+        <v>1.347736850904203e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.398872201869955e-08</v>
+        <v>1.377491700306937e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.363740490961114e-08</v>
+        <v>1.342289055136618e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.377098292703504e-08</v>
+        <v>1.355711505133172e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.431602743733092e-08</v>
+        <v>1.405395206242794e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.396874544099107e-08</v>
+        <v>1.375611277153593e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.396578283200056e-08</v>
+        <v>1.375182621728961e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.411891205068986e-08</v>
+        <v>1.389354723334782e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.404074929487875e-08</v>
+        <v>1.382430004636139e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.401348587200108e-08</v>
+        <v>1.380716775738646e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.415562599775431e-08</v>
+        <v>1.39321064710324e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.375185599455449e-08</v>
+        <v>1.353811045717938e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.386549932011905e-08</v>
+        <v>1.365054880345191e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.384356902077932e-08</v>
+        <v>1.363089465390885e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.399323515191838e-08</v>
+        <v>1.378117785216359e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.403645626947423e-08</v>
+        <v>1.381182646297103e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.387703530463079e-08</v>
+        <v>1.366275981954125e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.425526738752212e-08</v>
+        <v>1.414119625975311e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.406743482372836e-08</v>
+        <v>1.385613617354736e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.464359698278227e-08</v>
+        <v>1.443171841401675e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.621749591061749e-08</v>
+        <v>1.600186269562289e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.604628266859033e-08</v>
+        <v>1.583447941552467e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.385034841535922e-08</v>
+        <v>1.363942243162878e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.446160342040196e-08</v>
+        <v>1.424688465780631e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.406022566179332e-08</v>
+        <v>1.389788433700199e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.042800351347689e-08</v>
+        <v>3.02221388876981e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.534162514972809e-08</v>
+        <v>4.514411447139273e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.56383319101903e-08</v>
+        <v>4.544166296542006e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.732248564441209e-08</v>
+        <v>3.711903658383298e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.279313538443057e-08</v>
+        <v>3.258677860003048e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.906721196815152e-08</v>
+        <v>4.882463676571561e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.561835533248174e-08</v>
+        <v>4.542285873388654e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.561539272349131e-08</v>
+        <v>4.541857217964024e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.576852194218055e-08</v>
+        <v>4.556029319569851e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.569035918636944e-08</v>
+        <v>4.549104600871205e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.566309576349171e-08</v>
+        <v>4.547391371973712e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.580523588924504e-08</v>
+        <v>4.559885243338294e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.699349701302387e-08</v>
+        <v>3.679047823461344e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.632609441489584e-08</v>
+        <v>3.612127532349661e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.759596041053006e-08</v>
+        <v>2.738678038476017e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.564284504340912e-08</v>
+        <v>4.544792381451423e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.568606616096492e-08</v>
+        <v>4.547857242532168e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.55266451961215e-08</v>
+        <v>4.532950578189192e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.86042488197498e-08</v>
+        <v>3.850189900942185e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.163038404403439e-08</v>
+        <v>4.14325347621233e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.629614649139864e-08</v>
+        <v>4.610140623408482e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.134078939005784e-08</v>
+        <v>3.112969545368754e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.257031337096932e-08</v>
+        <v>6.238609708938824e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.026442066431549e-08</v>
+        <v>3.005901782469922e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.611121331189265e-08</v>
+        <v>4.591363062015695e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.133439439566423e-08</v>
+        <v>6.120109859059668e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.234133845118174e-08</v>
+        <v>2.258278115982264e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.657124758655657e-08</v>
+        <v>2.693831059837476e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.686795434701883e-08</v>
+        <v>2.723585909240205e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.553022163800623e-08</v>
+        <v>2.586772110849263e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.679752668163861e-08</v>
+        <v>1.686875485854566e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.719526128807921e-08</v>
+        <v>2.751489567676149e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.684797776931031e-08</v>
+        <v>2.721705486086861e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.68450151603198e-08</v>
+        <v>2.721276830662229e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.699814437900915e-08</v>
+        <v>2.735448932268053e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.691998162319799e-08</v>
+        <v>2.728524213569408e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.689271820032037e-08</v>
+        <v>2.726810984671916e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.703485832607357e-08</v>
+        <v>2.739304856036509e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.133406587115014e-08</v>
+        <v>3.12255746960903e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.804789733850376e-08</v>
+        <v>2.845850158666728e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.846958147823053e-08</v>
+        <v>2.888825426815359e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.672280287152763e-08</v>
+        <v>2.709183826824243e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.687246748023764e-08</v>
+        <v>2.724211994149629e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.69156885977935e-08</v>
+        <v>2.727276855230374e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.675626763295007e-08</v>
+        <v>2.712370190887396e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.713315895270721e-08</v>
+        <v>2.76014649072533e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.187874496638954e-08</v>
+        <v>3.239763564882838e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.752282931110152e-08</v>
+        <v>2.789266050334947e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.909672823893678e-08</v>
+        <v>2.946280478495559e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.892551499690961e-08</v>
+        <v>2.929542150485735e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.415275245742747e-08</v>
+        <v>2.44459611745689e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.734083574872121e-08</v>
+        <v>2.770782674713901e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.693945799011258e-08</v>
+        <v>2.735882642633467e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.22434093831837e-08</v>
+        <v>1.203346931499849e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.043857867635227e-08</v>
+        <v>1.020238665030071e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.213954685254659e-08</v>
+        <v>1.192210603746629e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.204551733010429e-08</v>
+        <v>1.181456428875206e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.203206562114593e-08</v>
+        <v>1.179781392370274e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.254767615483823e-08</v>
+        <v>1.214371165378669e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.19906399011771e-08</v>
+        <v>1.176341002612214e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.201205944156437e-08</v>
+        <v>1.177312139330814e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.233348484935127e-08</v>
+        <v>1.204161889796917e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.206747550769702e-08</v>
+        <v>1.181583177373166e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.241673895990183e-08</v>
+        <v>1.225733564115019e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.284069338533138e-08</v>
+        <v>1.249587348173704e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.204475883243061e-08</v>
+        <v>1.18066066630663e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.620882748057247e-08</v>
+        <v>1.572702033415185e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.231887980766379e-08</v>
+        <v>1.201907951416343e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.203827269655654e-08</v>
+        <v>1.181640103162666e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.199778050311611e-08</v>
+        <v>1.176734484146557e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232024806759273e-08</v>
+        <v>1.204340987798239e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.210229891846807e-08</v>
+        <v>1.180964025493743e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.249407657053903e-08</v>
+        <v>1.219476483951507e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.203409059163863e-08</v>
+        <v>1.182276677862165e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.232588302185589e-08</v>
+        <v>1.193529609496812e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.220964338019185e-08</v>
+        <v>1.198970410693886e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.216006299446646e-08</v>
+        <v>1.197640786662189e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.173084831675052e-08</v>
+        <v>1.145469409999425e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.213238344064587e-08</v>
+        <v>1.185049277404947e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.255979968769122e-08</v>
+        <v>1.289908621850389e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.410540403537588e-08</v>
+        <v>1.400344458558989e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.579231543508198e-09</v>
+        <v>9.373839155411704e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.337842766682276e-08</v>
+        <v>1.322330528411681e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.267990489730212e-08</v>
+        <v>1.24283475102951e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.261059695472343e-08</v>
+        <v>1.233509696544626e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.627279893177583e-08</v>
+        <v>1.479036065854287e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.231497292194523e-08</v>
+        <v>1.208963113260472e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.246640510941625e-08</v>
+        <v>1.215729395190015e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.475413900354648e-08</v>
+        <v>1.406903391950091e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.286168956944773e-08</v>
+        <v>1.246263866880831e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.535055612057959e-08</v>
+        <v>1.560953080085905e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.843611720259555e-08</v>
+        <v>1.737389533347156e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.269815145798155e-08</v>
+        <v>1.239499515438124e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.023964713335242e-08</v>
+        <v>1.932753339338332e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.464333907712726e-08</v>
+        <v>1.390222297820657e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.265230199828987e-08</v>
+        <v>1.246547973554087e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.236474597851788e-08</v>
+        <v>1.211647932288831e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.465530201216949e-08</v>
+        <v>1.407737233708759e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.311203984240543e-08</v>
+        <v>1.241850144937985e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.60217195298818e-08</v>
+        <v>1.608918946979916e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.261950930097129e-08</v>
+        <v>1.250758012880965e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.344394980973775e-08</v>
+        <v>1.297509749878226e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.387839371472881e-08</v>
+        <v>1.370537756075101e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.352028457641905e-08</v>
+        <v>1.360612947704957e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.255784744203584e-08</v>
+        <v>1.228066212255002e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.332273557542562e-08</v>
+        <v>1.270750551330621e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.638607315568991e-08</v>
+        <v>2.017341293696489e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.168549805152912e-08</v>
+        <v>1.074877821490463e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.488305219962657e-09</v>
+        <v>7.427846901221639e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.051232298885831e-08</v>
+        <v>9.490878765539755e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.450216277155501e-09</v>
+        <v>8.27614524216401e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.298273036378648e-09</v>
+        <v>8.086942163383318e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.512233120699708e-08</v>
+        <v>1.199401614549869e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.830350472558078e-09</v>
+        <v>7.698334313635566e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>9.072294034707752e-09</v>
+        <v>7.808028673451086e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.269155551498673e-08</v>
+        <v>1.083016251127838e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.698243994326567e-09</v>
+        <v>8.290462068080586e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.36433353561052e-08</v>
+        <v>1.327745135238583e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.849558045650646e-08</v>
+        <v>1.604472291150549e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.441648697004946e-09</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.083578682563609e-08</v>
+        <v>9.149695473826556e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.253797121414245e-08</v>
+        <v>1.058623879483725e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.368384808537191e-09</v>
+        <v>8.296892097875913e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.911006856298348e-09</v>
+        <v>7.742779863044101e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.255342633947044e-08</v>
+        <v>1.086106144669259e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.009159043854523e-08</v>
+        <v>8.220526015060258e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.469221719450925e-08</v>
+        <v>1.443623944405177e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.260220409870856e-09</v>
+        <v>8.312742994362277e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.002412249156865e-08</v>
+        <v>8.945290696902717e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.130409551460757e-08</v>
+        <v>1.025443005688072e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.066869606512842e-08</v>
+        <v>1.005631419638889e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.023083362073113e-08</v>
+        <v>9.157615158546408e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.043140895610749e-08</v>
+        <v>8.681974011517901e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.523314725017252e-08</v>
+        <v>2.040276683672851e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.495811187956464e-08</v>
+        <v>8.578911900862369e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.096597508242675e-08</v>
+        <v>2.960898381515028e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.072641020637361e-08</v>
+        <v>7.016138410497566e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.538928630937671e-08</v>
+        <v>3.193975748368136e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.7364274393356e-08</v>
+        <v>4.298781852538606e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.476210347778335e-07</v>
+        <v>1.093956946945469e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.853541238527834e-08</v>
+        <v>3.568260366576135e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.230912100659923e-08</v>
+        <v>3.684032628435434e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.074445516072184e-07</v>
+        <v>9.164861214208046e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.402063094680322e-08</v>
+        <v>4.625055286099937e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.264761264035743e-07</v>
+        <v>1.382399426209144e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.322840164919515e-07</v>
+        <v>2.029724422783494e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.399036843519626e-07</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.962124503731199e-08</v>
+        <v>5.772507386104593e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>1.006866523810282e-07</v>
+        <v>8.353845427998986e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.724663529879978e-08</v>
+        <v>4.569264932108299e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.939875929736291e-08</v>
+        <v>3.58362485345205e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>1.022010742225303e-07</v>
+        <v>8.957030417169407e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.246676708888561e-08</v>
+        <v>4.495710568888196e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.452296190340733e-07</v>
+        <v>1.582100642454846e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.465476251863922e-08</v>
+        <v>4.514290681932904e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.875159543216974e-08</v>
+        <v>5.7075569934782e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.552122277017393e-08</v>
+        <v>8.438802698939681e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.256771172409153e-08</v>
+        <v>7.912784259192337e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.02735029252167e-08</v>
+        <v>5.873051941759031e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.665684641487879e-08</v>
+        <v>5.225703494636975e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.72486382531798e-07</v>
+        <v>3.012199460760816e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.432018863509626e-08</v>
+        <v>1.344360673046945e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.416187985797128e-08</v>
+        <v>1.303840793111201e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.618589762686693e-08</v>
+        <v>1.218570728110461e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.208490686072263e-08</v>
+        <v>1.388670627205439e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.19329636199458e-08</v>
+        <v>1.078177067894817e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.775702179056421e-08</v>
+        <v>1.760457717538904e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.450392511056666e-08</v>
+        <v>1.330889534352594e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.170698461827491e-08</v>
+        <v>1.341858970334145e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.836513015299529e-08</v>
+        <v>1.644072354116875e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.537181863233518e-08</v>
+        <v>1.098529058364543e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.627802593967235e-08</v>
+        <v>1.888801238227621e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.113027104007358e-08</v>
+        <v>2.165528394139584e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.208457388840057e-08</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.653145735841696e-08</v>
+        <v>1.18547217409935e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.823366753372171e-08</v>
+        <v>1.621073004936331e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.504195944654581e-08</v>
+        <v>1.099172061344076e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.458458149430692e-08</v>
+        <v>1.335334089293449e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.822700097747906e-08</v>
+        <v>1.355588996225744e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.272628102211239e-08</v>
+        <v>1.091535453062511e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.740227396268271e-08</v>
+        <v>1.717899666915553e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.493379504787946e-08</v>
+        <v>1.100757150992712e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.571977492047057e-08</v>
+        <v>1.180261543653765e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.697767015261615e-08</v>
+        <v>1.586499108677111e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.351735287732662e-08</v>
+        <v>1.2941610273693e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.590440825873974e-08</v>
+        <v>1.185244367411127e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.306609953967462e-08</v>
+        <v>1.429253504140828e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.790319446925375e-08</v>
+        <v>2.31704960969773e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.87499709725043e-08</v>
+        <v>1.758816392457814e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.555277814093784e-08</v>
+        <v>1.426723261089517e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.757679590983353e-08</v>
+        <v>1.63302644752133e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.651468919813067e-08</v>
+        <v>1.511553095183754e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.636274595735385e-08</v>
+        <v>1.492632787305685e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.218680412797228e-08</v>
+        <v>1.88334018551722e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.589482339353328e-08</v>
+        <v>1.453772002330911e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.613676695568298e-08</v>
+        <v>1.464741438312462e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.975602843596189e-08</v>
+        <v>1.766954822095191e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.676271691530178e-08</v>
+        <v>1.512984777775412e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.07078082770804e-08</v>
+        <v>2.011683706205939e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.556005337748165e-08</v>
+        <v>2.288410862117901e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.650612161798016e-08</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.789981128435932e-08</v>
+        <v>1.598863470783531e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.960199567286566e-08</v>
+        <v>1.742517802884596e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.64328577295124e-08</v>
+        <v>1.513627780754945e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.597547977727355e-08</v>
+        <v>1.458216557271764e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.961789926044564e-08</v>
+        <v>1.770044715636613e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.715606335952044e-08</v>
+        <v>1.50599117247338e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.183033660328386e-08</v>
+        <v>2.132192940549541e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.632469333084603e-08</v>
+        <v>1.515212870403581e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.708859541254385e-08</v>
+        <v>1.578467640657625e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.836856843558277e-08</v>
+        <v>1.709381576655426e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.780853517070995e-08</v>
+        <v>1.694362861560136e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.729530654170633e-08</v>
+        <v>1.599700086821994e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.749588187708266e-08</v>
+        <v>1.552135972119143e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.229762017114774e-08</v>
+        <v>2.724215254640205e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.690338139073054e-08</v>
+        <v>3.568688687018099e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.020335068878922e-08</v>
+        <v>4.862181788705412e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.222736845768492e-08</v>
+        <v>5.068484975137224e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.238100954730972e-08</v>
+        <v>4.081434905443505e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.708622142923442e-08</v>
+        <v>3.555752418374617e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>6.025817071259356e-08</v>
+        <v>5.655874608284177e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.054539594138465e-08</v>
+        <v>4.889230529946806e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.078733950353435e-08</v>
+        <v>4.900199965928358e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.440660098381325e-08</v>
+        <v>5.202413349711085e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.141328946315318e-08</v>
+        <v>4.94844330539131e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.535838082493178e-08</v>
+        <v>5.447142233821834e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>6.021062592533302e-08</v>
+        <v>5.723869389733817e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.8368633600868e-08</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.327704181087225e-08</v>
+        <v>4.120552135330396e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.41177936856282e-08</v>
+        <v>4.179323211507965e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.134419925926886e-08</v>
+        <v>3.004035278260594e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.062605232512495e-08</v>
+        <v>4.893675084887664e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.426847180829703e-08</v>
+        <v>5.205503243252506e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.180663590737182e-08</v>
+        <v>4.941449700089278e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.842959902346643e-08</v>
+        <v>4.774295679462546e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.646525610314606e-08</v>
+        <v>4.506273478795982e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.174241012782135e-08</v>
+        <v>5.014245642780949e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.47919076563395e-08</v>
+        <v>3.34877728265399e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.886017517625401e-08</v>
+        <v>6.74594860817078e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.514227370350201e-08</v>
+        <v>3.379376282504571e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.2146454424934e-08</v>
+        <v>4.98759449973504e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.418085803588411e-08</v>
+        <v>7.857734532213375e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.16845064879463e-08</v>
+        <v>3.016577729620912e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.422445526501508e-08</v>
+        <v>3.239337657700111e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.624847303391078e-08</v>
+        <v>3.445640844131922e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.386225785901492e-08</v>
+        <v>3.196109701946443e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.180874514851621e-08</v>
+        <v>2.026159392008615e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.085848179638582e-08</v>
+        <v>3.695954625117928e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.456650051761054e-08</v>
+        <v>3.266386398941504e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.480844407976021e-08</v>
+        <v>3.277355834923054e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.842770556003916e-08</v>
+        <v>3.579569218705786e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.543439403937902e-08</v>
+        <v>3.325599174386001e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.937948540115767e-08</v>
+        <v>3.82429810281653e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.423173050155891e-08</v>
+        <v>4.101025258728492e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.517779874205738e-08</v>
+        <v>4.327732681729049e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.847321881237385e-08</v>
+        <v>3.595400149580489e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.05888992843079e-08</v>
+        <v>3.779044703052804e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.510453539792586e-08</v>
+        <v>3.326242220355648e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.464715690135074e-08</v>
+        <v>3.270830953882357e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.828957638452292e-08</v>
+        <v>3.582659112247206e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.582774048359765e-08</v>
+        <v>3.318605569083971e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.050373342416805e-08</v>
+        <v>3.944969782937014e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>4.161690346990091e-08</v>
+        <v>3.968115271279295e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.576027253662109e-08</v>
+        <v>3.391082037268219e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.704024555965999e-08</v>
+        <v>3.521995973266022e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.648021229478721e-08</v>
+        <v>3.50697725817073e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.250799765846364e-08</v>
+        <v>3.07778744511579e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.616755900115994e-08</v>
+        <v>3.364750368729734e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.096929729522502e-08</v>
+        <v>4.536829651250797e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.22220425755298e-08</v>
+        <v>1.200825001805864e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.047702278292214e-08</v>
+        <v>1.024256840721428e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.220930952668195e-08</v>
+        <v>1.198981828295091e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.206364265036835e-08</v>
+        <v>1.183524683557787e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.209009660797499e-08</v>
+        <v>1.185249425025777e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.254768838359777e-08</v>
+        <v>1.215013689107299e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.201037879433953e-08</v>
+        <v>1.179102796092937e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.217306717643697e-08</v>
+        <v>1.187815724695612e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.235382708893091e-08</v>
+        <v>1.206243034609608e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.223805252800372e-08</v>
+        <v>1.190202010149274e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.239882972524641e-08</v>
+        <v>1.222703673953905e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.276599552206995e-08</v>
+        <v>1.243087829117748e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.206948801992676e-08</v>
+        <v>1.182363094677188e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.621707679570401e-08</v>
+        <v>1.573923474663776e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.235119923087214e-08</v>
+        <v>1.204713299399118e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.207318102372555e-08</v>
+        <v>1.185180741583577e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.201603270366864e-08</v>
+        <v>1.179043105743728e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.232911603143551e-08</v>
+        <v>1.205363860561448e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.213822792157665e-08</v>
+        <v>1.184263429953694e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.234969313525541e-08</v>
+        <v>1.210383904541563e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.210320570159738e-08</v>
+        <v>1.189685744436718e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.240469564376179e-08</v>
+        <v>1.20104222360788e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.233171448838235e-08</v>
+        <v>1.210920898499043e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.238423062395231e-08</v>
+        <v>1.222076776491932e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.179453502266135e-08</v>
+        <v>1.151354497640631e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.220425674571705e-08</v>
+        <v>1.188158795141885e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.255601116977759e-08</v>
+        <v>1.284690012958392e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.377641011016023e-08</v>
+        <v>1.363915638273298e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.65174005311092e-09</v>
+        <v>9.447419575219333e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.369766366835808e-08</v>
+        <v>1.351982016626432e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26302429505871e-08</v>
+        <v>1.238890666540753e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.284594883448853e-08</v>
+        <v>1.253854729502955e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.609171393003582e-08</v>
+        <v>1.464800678773028e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.22762335281506e-08</v>
+        <v>1.209936780838894e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.343983434836439e-08</v>
+        <v>1.272185154790219e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.471996351268396e-08</v>
+        <v>1.403038412573704e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.389581041641711e-08</v>
+        <v>1.288940967368554e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.504314932479232e-08</v>
+        <v>1.520560473955875e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.772954121170163e-08</v>
+        <v>1.672785631082853e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.269560748503784e-08</v>
+        <v>1.232934579509985e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.00663943493381e-08</v>
+        <v>1.917978648826997e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.469362801406777e-08</v>
+        <v>1.391456990772766e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.272209451063565e-08</v>
+        <v>1.253082809858333e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.231563395760755e-08</v>
+        <v>1.209396981249265e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.453902614555598e-08</v>
+        <v>1.396298824023166e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.318962412048735e-08</v>
+        <v>1.24669662308348e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.461507706303982e-08</v>
+        <v>1.506681526739682e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.293198041915899e-08</v>
+        <v>1.284737980587742e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.355874554613967e-08</v>
+        <v>1.308796945419425e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.457129058227619e-08</v>
+        <v>1.437190464327741e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.494095885411191e-08</v>
+        <v>1.5162935883283e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.268057308096733e-08</v>
+        <v>1.238129017431289e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.365684114733309e-08</v>
+        <v>1.27424007784887e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.618263433278757e-08</v>
+        <v>1.961956346493402e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.109252965728992e-08</v>
+        <v>1.014435917867496e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>8.521641508875817e-09</v>
+        <v>7.506045709498645e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.094870401306144e-08</v>
+        <v>9.936164251614035e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.303329635025835e-09</v>
+        <v>8.190208647158473e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.602139255614537e-09</v>
+        <v>8.385026130170591e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.477084886389075e-08</v>
+        <v>1.174703668055867e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.701689878595914e-09</v>
+        <v>7.690736116315988e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.053932999473952e-08</v>
+        <v>8.67490148344061e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.257008142116103e-08</v>
+        <v>1.074606944949117e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.127336943542476e-08</v>
+        <v>8.94444340288574e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.308942183944582e-08</v>
+        <v>1.261565584466022e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.731417122303116e-08</v>
+        <v>1.500345460983163e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.369355773190948e-09</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>1.046616412310563e-08</v>
+        <v>8.867555374669926e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.255141349437857e-08</v>
+        <v>1.058356027888393e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.411069949963924e-09</v>
+        <v>8.377268019414346e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.765553385394989e-09</v>
+        <v>7.683993816783611e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.230197359796808e-08</v>
+        <v>1.065704415489997e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.014580458424352e-08</v>
+        <v>8.273653450975939e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.231584568437315e-08</v>
+        <v>1.271942566794539e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.691793069201411e-09</v>
+        <v>8.832690877408519e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.000957505019946e-08</v>
+        <v>8.987869278929664e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.233132436453184e-08</v>
+        <v>1.128473715359058e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.286306551411938e-08</v>
+        <v>1.25100671174363e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.028917068240767e-08</v>
+        <v>9.235168123413599e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.08916305276689e-08</v>
+        <v>8.713652868549407e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.484447145765026e-08</v>
+        <v>1.950717503320114e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.10932156053209e-08</v>
+        <v>7.094813373978445e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.08932019930646e-08</v>
+        <v>2.959534868339294e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.483546771354619e-08</v>
+        <v>7.3594420524252e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.133338204358058e-08</v>
+        <v>2.834426803809838e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.055995058907568e-08</v>
+        <v>4.554619586745804e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.315658618294517e-07</v>
+        <v>9.732317589348254e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.423742205193688e-08</v>
+        <v>3.301181584733114e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.802728484850395e-08</v>
+        <v>5.074886669489173e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.896502736250189e-08</v>
+        <v>8.411469706549081e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.695351479727607e-08</v>
+        <v>5.408987300180282e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.090029386948718e-07</v>
+        <v>1.172257353559268e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.960765209563662e-07</v>
+        <v>1.70377453566421e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>9.183640473751808e-08</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.985094269519191e-08</v>
+        <v>4.946370492984709e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>9.45227301787488e-08</v>
+        <v>7.762982082258628e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.556010897239183e-08</v>
+        <v>4.394902539169067e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.487370560287147e-08</v>
+        <v>3.230289695639456e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>9.166928947552712e-08</v>
+        <v>7.995945422537947e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.025833024274376e-08</v>
+        <v>4.29492803134802e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>9.484434740899073e-08</v>
+        <v>1.172583620680241e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.921890822321251e-08</v>
+        <v>5.031871036616475e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.548386656345436e-08</v>
+        <v>5.409595545904361e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>9.92979927333224e-08</v>
+        <v>9.743946458712621e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.071248915985334e-07</v>
+        <v>1.170476729642258e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.690802207206782e-08</v>
+        <v>5.504490100546147e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.135898337174446e-08</v>
+        <v>4.939457967731392e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.549428080246395e-07</v>
+        <v>2.649185272091996e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.354405380071956e-08</v>
+        <v>1.537617042666942e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.097316565230548e-08</v>
+        <v>1.001855804259564e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.623546601497941e-08</v>
+        <v>1.516797549960848e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.175485377845545e-08</v>
+        <v>1.342201989515292e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.488890125753235e-08</v>
+        <v>1.089753846326758e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.722237300732037e-08</v>
+        <v>1.425954901365565e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.115321402202558e-08</v>
+        <v>1.020324844941299e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.299085413816926e-08</v>
+        <v>1.11874138165376e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.785684342307882e-08</v>
+        <v>1.597788069748562e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.65601314373425e-08</v>
+        <v>1.417625465088022e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.554094598287545e-08</v>
+        <v>1.784746709265467e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.260093322494897e-08</v>
+        <v>1.751596694292864e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.182833811227067e-08</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.29251464621853e-08</v>
+        <v>1.411522790706966e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.786030003917076e-08</v>
+        <v>1.583139800366503e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.469783195188173e-08</v>
+        <v>1.360907926740881e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.405231538731278e-08</v>
+        <v>1.01965061498806e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.475349774139766e-08</v>
+        <v>1.588885540289442e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.259732872767318e-08</v>
+        <v>1.078616578407295e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.482882258809389e-08</v>
+        <v>1.526671577606461e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.497855507111922e-08</v>
+        <v>1.406450212540298e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.261565683051006e-08</v>
+        <v>1.423549123122324e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.478284850796156e-08</v>
+        <v>1.379724948668758e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.550739921112456e-08</v>
+        <v>1.519331356557972e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.274069482583731e-08</v>
+        <v>1.446697937140804e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.617839252958672e-08</v>
+        <v>1.394546411654384e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.732759647096998e-08</v>
+        <v>2.208306552519518e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.773352039852843e-08</v>
+        <v>1.656977125581746e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.516263225011433e-08</v>
+        <v>1.393145778664116e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.758969475430001e-08</v>
+        <v>1.636157632875654e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.594432037626434e-08</v>
+        <v>1.461562072430098e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.624312999685305e-08</v>
+        <v>1.481043820731307e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.141183960512924e-08</v>
+        <v>1.817244875770122e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.534268061983442e-08</v>
+        <v>1.41161481934585e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.718032073597807e-08</v>
+        <v>1.510031356058312e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.92110721623995e-08</v>
+        <v>1.717148152663366e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.791436017666321e-08</v>
+        <v>1.536985548002824e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.973041258068431e-08</v>
+        <v>1.904106792180272e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.395516196426963e-08</v>
+        <v>2.142886668697414e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.601034651442947e-08</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.71067352991002e-08</v>
+        <v>1.529254973459268e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.919198467037312e-08</v>
+        <v>1.700855463880671e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.605206069120243e-08</v>
+        <v>1.480268009655686e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.540654412663351e-08</v>
+        <v>1.410940589392611e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.894296433920667e-08</v>
+        <v>1.708245623204248e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.678679532548197e-08</v>
+        <v>1.469906552811845e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.901748532910052e-08</v>
+        <v>1.917887832340058e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.633278381043991e-08</v>
+        <v>1.525810295455103e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.665056579143797e-08</v>
+        <v>1.541328135607216e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.897231510577028e-08</v>
+        <v>1.771014923073309e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.956550901564909e-08</v>
+        <v>1.897025696960102e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.693016142364616e-08</v>
+        <v>1.566058020055612e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.753262126890741e-08</v>
+        <v>1.513906494569191e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.148546219888875e-08</v>
+        <v>2.593258711034368e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.465225555387223e-08</v>
+        <v>3.343521350472652e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.75070187628131e-08</v>
+        <v>4.599249870240794e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.993408126699885e-08</v>
+        <v>4.842261724452334e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.007500256896525e-08</v>
+        <v>3.858545359164062e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.556500135052547e-08</v>
+        <v>3.404317713404737e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.695483541571374e-08</v>
+        <v>5.338439604732228e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.768706713253326e-08</v>
+        <v>4.617718910922529e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.952470724867693e-08</v>
+        <v>4.71613544763499e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.155545867509836e-08</v>
+        <v>4.923252244240047e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.025874668936208e-08</v>
+        <v>4.743089639579504e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.207479909338315e-08</v>
+        <v>5.110210883756952e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.629954847696843e-08</v>
+        <v>5.348990760274132e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.63972725704831e-08</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.078009487994637e-08</v>
+        <v>3.881188474643176e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.205986282837817e-08</v>
+        <v>3.973442089192113e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.993930328090839e-08</v>
+        <v>2.868184038422191e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.775093063933235e-08</v>
+        <v>4.617044680969289e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.128735085190539e-08</v>
+        <v>4.914349714780925e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.913118183818086e-08</v>
+        <v>4.676010644388527e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.383332333973724e-08</v>
+        <v>4.382363995249539e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.446077873490294e-08</v>
+        <v>4.316568455088886e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.89979838888444e-08</v>
+        <v>4.747730864454611e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.427334929498133e-08</v>
+        <v>3.298201633166414e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.724676008564209e-08</v>
+        <v>6.613951221391073e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.356235718528231e-08</v>
+        <v>3.224375640259738e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.987700778160636e-08</v>
+        <v>4.720010586145875e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.994323142842258e-08</v>
+        <v>7.386670147097997e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.866461847577331e-08</v>
+        <v>2.721453000837692e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.115188778599341e-08</v>
+        <v>2.946979270155139e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.35789502901791e-08</v>
+        <v>3.189991124366683e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.076617436917966e-08</v>
+        <v>2.902453869142528e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.057195112689308e-08</v>
+        <v>1.906774368688869e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.740109587766659e-08</v>
+        <v>3.3710784283569e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.133193615571353e-08</v>
+        <v>2.965448310836876e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.316957627185718e-08</v>
+        <v>3.063864847549339e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.520032769827862e-08</v>
+        <v>3.270981644154392e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.39036157125423e-08</v>
+        <v>3.090819039493853e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.571966811656339e-08</v>
+        <v>3.457940283671301e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.994441750014872e-08</v>
+        <v>3.696720160188445e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.199960205030852e-08</v>
+        <v>3.812021875520142e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.477267813970929e-08</v>
+        <v>3.245302791276354e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.722248682419828e-08</v>
+        <v>3.452173016624357e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.204131696373978e-08</v>
+        <v>3.034101562242464e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.139579966251257e-08</v>
+        <v>2.964774080883636e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.493221987508575e-08</v>
+        <v>3.262079114695275e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.277605086136114e-08</v>
+        <v>3.02374004430287e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.500754472178188e-08</v>
+        <v>3.471795043502041e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.815904010438273e-08</v>
+        <v>3.644351541880995e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.263982132731702e-08</v>
+        <v>3.095161627098244e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.496157064164936e-08</v>
+        <v>3.324848414564336e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.555476455152827e-08</v>
+        <v>3.450859188451132e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.98697980933985e-08</v>
+        <v>2.824852408594428e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.352187680478654e-08</v>
+        <v>3.067739986060215e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.747471773476781e-08</v>
+        <v>4.147092202525398e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.21860215087312e-08</v>
+        <v>1.199563586921688e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.048150275112079e-08</v>
+        <v>1.027110172678946e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.216317890132622e-08</v>
+        <v>1.196863855200409e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.203779715301929e-08</v>
+        <v>1.183674444224597e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.210896906389299e-08</v>
+        <v>1.189277856585598e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.247308513149659e-08</v>
+        <v>1.212731634521484e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.20137593525879e-08</v>
+        <v>1.181894399229586e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.217734894661931e-08</v>
+        <v>1.190102461201903e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.231769313214691e-08</v>
+        <v>1.206357142694364e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.22838265847946e-08</v>
+        <v>1.194613077154587e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.232653594982822e-08</v>
+        <v>1.216957062051296e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.263698086562963e-08</v>
+        <v>1.234646677195877e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.205144860607006e-08</v>
+        <v>1.18352274570794e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.611638914288483e-08</v>
+        <v>1.5707739277267e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.231850436736138e-08</v>
+        <v>1.204697861659762e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.2080172879278e-08</v>
+        <v>1.188275750172841e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.20503804161765e-08</v>
+        <v>1.183714321252329e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.230049892740105e-08</v>
+        <v>1.205454323066635e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.21487211379019e-08</v>
+        <v>1.188065695156172e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.236276168141124e-08</v>
+        <v>1.217517741405798e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.218453016949295e-08</v>
+        <v>1.201217435493644e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.245594096693893e-08</v>
+        <v>1.208838183292688e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.23660599752484e-08</v>
+        <v>1.21678175284356e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.259628464145028e-08</v>
+        <v>1.250396072776024e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.18063551415425e-08</v>
+        <v>1.154580000128323e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.222749106853395e-08</v>
+        <v>1.192026751470033e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.250766625094062e-08</v>
+        <v>1.27685203768961e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.353983273422543e-08</v>
+        <v>1.34124897992263e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.696731092076807e-09</v>
+        <v>9.507316253180152e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.33873534056246e-08</v>
+        <v>1.323045781851146e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2467911687971e-08</v>
+        <v>1.226474021078345e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.300179920210508e-08</v>
+        <v>1.269011778242713e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.557769165334336e-08</v>
+        <v>1.434755315713458e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.232160904983655e-08</v>
+        <v>1.21627259008239e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.349092688908252e-08</v>
+        <v>1.274894230991513e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.448130253805366e-08</v>
+        <v>1.390091335638301e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.424236741835703e-08</v>
+        <v>1.306761323893e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.454489049378555e-08</v>
+        <v>1.465549800274322e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.682371578654095e-08</v>
+        <v>1.59844001542688e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.258789336052014e-08</v>
+        <v>1.227604310382457e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.954536699180836e-08</v>
+        <v>1.88832621077119e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.447918707943719e-08</v>
+        <v>1.377599622288602e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.279262506432689e-08</v>
+        <v>1.261525540371997e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.258308100044638e-08</v>
+        <v>1.229214330265141e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43552991492601e-08</v>
+        <v>1.383297816970376e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.328597035864209e-08</v>
+        <v>1.260269096000548e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.452513591994629e-08</v>
+        <v>1.520390009041469e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352947434861069e-08</v>
+        <v>1.352987558566009e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.371593678833169e-08</v>
+        <v>1.326674525342325e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.483393844431067e-08</v>
+        <v>1.465063600068217e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.647934226069073e-08</v>
+        <v>1.705267299883117e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.266057831946842e-08</v>
+        <v>1.237116489951259e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.384422244496378e-08</v>
+        <v>1.288261019340279e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.585562530059284e-08</v>
+        <v>1.892133627857158e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.066541254433779e-08</v>
+        <v>9.829700901428129e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.535420558961477e-09</v>
+        <v>7.640222531237019e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>1.040739478557986e-08</v>
+        <v>9.524753784130146e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.991150259999232e-09</v>
+        <v>8.03494914012417e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>9.79506973401433e-09</v>
+        <v>8.667880343269548e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.390792821926366e-08</v>
+        <v>1.131709245383674e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.719632246192313e-09</v>
+        <v>7.833884869325946e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>1.056745196570833e-08</v>
+        <v>8.761023228049717e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.214256065753087e-08</v>
+        <v>1.058763225869896e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>1.177016587103182e-08</v>
+        <v>9.270518049764025e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.225258779636497e-08</v>
+        <v>1.179437393125605e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.584947076400647e-08</v>
+        <v>1.388877978839953e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.145349702186262e-09</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>9.665729689336466e-09</v>
+        <v>8.467997982322334e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.216186737769138e-08</v>
+        <v>1.040964085192422e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.469803581888416e-09</v>
+        <v>8.554687814031295e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>9.133284005946973e-09</v>
+        <v>8.039453433849707e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.195848765042805e-08</v>
+        <v>1.049508664772502e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>1.024408769680228e-08</v>
+        <v>8.530961133597719e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.204644774480708e-08</v>
+        <v>1.289826222512668e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>1.059605004936539e-08</v>
+        <v>9.968824914268307e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>1.009510280291555e-08</v>
+        <v>9.19860851426613e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.26990298454358e-08</v>
+        <v>1.177457194977999e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.525631756693659e-08</v>
+        <v>1.555716600072708e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.01469775725978e-08</v>
+        <v>9.215199139318819e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.113383029924976e-08</v>
+        <v>8.97838066600763e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.428152873127147e-08</v>
+        <v>1.846278405943991e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.3692099974182e-08</v>
+        <v>6.341512229210371e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.169434606788302e-08</v>
+        <v>3.042270222857083e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.459564097115538e-08</v>
+        <v>6.354031694097923e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.680598417151026e-08</v>
+        <v>2.45549096852783e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>5.446221232011133e-08</v>
+        <v>4.894294785913378e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.153779388430847e-07</v>
+        <v>8.72622061358344e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.509219969083649e-08</v>
+        <v>3.396908495784152e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>6.869158763918335e-08</v>
+        <v>5.057586720185809e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.087999230696588e-08</v>
+        <v>7.882477978732852e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.556089536205166e-08</v>
+        <v>5.790083103727855e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.290358712083873e-08</v>
+        <v>9.900686848048308e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.638386421570501e-07</v>
+        <v>1.433430311188778e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>8.585744803666165e-08</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.772287529868843e-08</v>
+        <v>4.174851038037549e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.695548972925437e-08</v>
+        <v>7.215426934161182e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.681557833553197e-08</v>
+        <v>4.520928039612584e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.246303513404627e-08</v>
+        <v>3.736064411184846e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>8.575143764214654e-08</v>
+        <v>7.521652377281523e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>6.264150548821234e-08</v>
+        <v>4.604751520502847e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>8.880175187111068e-08</v>
+        <v>1.157192804354306e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>6.348953416112134e-08</v>
+        <v>6.633452097336513e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.752310677386363e-08</v>
+        <v>5.62393326495441e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.04408055450248e-07</v>
+        <v>1.026210065344772e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.515830548165093e-07</v>
+        <v>1.713124802793947e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.414220210642372e-08</v>
+        <v>5.238281442699082e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.633997922767662e-08</v>
+        <v>5.251847744302997e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.429053123474062e-07</v>
+        <v>2.396508982675625e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.594719715245404e-08</v>
+        <v>1.237089902539107e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.100873037088301e-08</v>
+        <v>1.018142065519993e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.288070459750138e-08</v>
+        <v>1.476914033495292e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.427293486811547e-08</v>
+        <v>1.327933569094696e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.226837954593586e-08</v>
+        <v>1.120907846723247e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.918971282737991e-08</v>
+        <v>1.38582905777997e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.119294205811383e-08</v>
+        <v>1.30782714201487e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.304076177762985e-08</v>
+        <v>1.130222135201263e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.74243452656471e-08</v>
+        <v>1.583201880952173e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.705195047914804e-08</v>
+        <v>1.451490460058682e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.753437240448121e-08</v>
+        <v>1.4335572055219e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.832278057592799e-08</v>
+        <v>1.642997791236244e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.163028016105316e-08</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.497153563829247e-08</v>
+        <v>1.102392825376451e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.44746986808153e-08</v>
+        <v>1.567206406948863e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.475158819000466e-08</v>
+        <v>1.379907436485406e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.441506861406322e-08</v>
+        <v>1.328383998467249e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.72402722585443e-08</v>
+        <v>1.303628477168797e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.552587230491854e-08</v>
+        <v>1.377534768442052e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.456296334855709e-08</v>
+        <v>1.815694679488564e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.30693598612869e-08</v>
+        <v>1.251002303823125e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.540088852305944e-08</v>
+        <v>1.189722248401862e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.517233965735732e-08</v>
+        <v>1.43157700737429e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.791364897424254e-08</v>
+        <v>1.825883013470514e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.542876218071403e-08</v>
+        <v>1.175639726328175e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.641561490736601e-08</v>
+        <v>1.422276721683042e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.678503767118447e-08</v>
+        <v>2.106238013675109e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.733832825789271e-08</v>
+        <v>1.629194126860596e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.520833627251639e-08</v>
+        <v>1.410246289841485e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.708031049913478e-08</v>
+        <v>1.598699415130798e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.566406597355413e-08</v>
+        <v>1.449718950730198e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.646798544756923e-08</v>
+        <v>1.513012071044738e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.058084393281857e-08</v>
+        <v>1.777933282101457e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.539254795974722e-08</v>
+        <v>1.429612523650379e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.724036767926325e-08</v>
+        <v>1.522326359522753e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.881547637108578e-08</v>
+        <v>1.70498726258768e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.844308158458671e-08</v>
+        <v>1.573275841694186e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.892550350991989e-08</v>
+        <v>1.825661429843387e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.252238647756138e-08</v>
+        <v>2.035102015557735e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.581826541574117e-08</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.633822380497861e-08</v>
+        <v>1.492981848184015e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.883436149333356e-08</v>
+        <v>1.687146135144204e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.614271929544333e-08</v>
+        <v>1.501692818120913e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.580619971950189e-08</v>
+        <v>1.450169380102755e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.863140336398295e-08</v>
+        <v>1.695732701490285e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.691700341035719e-08</v>
+        <v>1.499320150077555e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.876387909850169e-08</v>
+        <v>1.937586433393019e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.726896576292029e-08</v>
+        <v>1.643106528144614e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.676801851647045e-08</v>
+        <v>1.566084888144397e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.93719455589907e-08</v>
+        <v>1.823681231695781e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.197243907231996e-08</v>
+        <v>2.203370438684109e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.681989328615269e-08</v>
+        <v>1.567743950649664e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.780674601280467e-08</v>
+        <v>1.544062103318546e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.095444444482637e-08</v>
+        <v>2.492502442661776e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.424071216482825e-08</v>
+        <v>3.315004107686943e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.755280799739827e-08</v>
+        <v>4.618285064826624e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.942478222401661e-08</v>
+        <v>4.806738190115941e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.978608144801551e-08</v>
+        <v>3.847215795721822e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.577606616129714e-08</v>
+        <v>3.435967507361343e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.61273331627647e-08</v>
+        <v>5.301616113969887e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.773701968462906e-08</v>
+        <v>4.637651298635521e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.958483940414511e-08</v>
+        <v>4.7303651345079e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.115994809596759e-08</v>
+        <v>4.913026037572825e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.078755330946861e-08</v>
+        <v>4.781314616679333e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.12699752348017e-08</v>
+        <v>5.033700204828535e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.486685820244332e-08</v>
+        <v>5.243140790542949e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.619253567726196e-08</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.000243096324104e-08</v>
+        <v>3.845349924672528e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.169222896589247e-08</v>
+        <v>3.960027972342444e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.001038049708656e-08</v>
+        <v>2.88835009765934e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.815067144438375e-08</v>
+        <v>4.6582081550879e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.097587508886482e-08</v>
+        <v>4.903771476475431e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.926147513523911e-08</v>
+        <v>4.707358925062702e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.35713058440186e-08</v>
+        <v>4.402654253378965e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.539436204733845e-08</v>
+        <v>4.435224035011294e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.911552505630724e-08</v>
+        <v>4.774422824919945e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.465490479441947e-08</v>
+        <v>3.349853805066346e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.967292270842833e-08</v>
+        <v>6.92512334370141e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.343543248368451e-08</v>
+        <v>3.225277750091246e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.015121773768654e-08</v>
+        <v>4.752100878303693e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.942946814403812e-08</v>
+        <v>7.290636480050669e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.732690185401202e-08</v>
+        <v>2.608247536209565e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.000608333837669e-08</v>
+        <v>2.856398008273312e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.187805756499507e-08</v>
+        <v>3.04485113356263e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.935187606811659e-08</v>
+        <v>2.788066339095142e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.017927401597394e-08</v>
+        <v>1.882374611487605e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.537859184274236e-08</v>
+        <v>3.224085071268906e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.019029502560752e-08</v>
+        <v>2.875764242082204e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.203811474512353e-08</v>
+        <v>2.968478077954583e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.361322343694605e-08</v>
+        <v>3.151138981019508e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.324082865044703e-08</v>
+        <v>3.019427560126016e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.372325057578019e-08</v>
+        <v>3.271813148275218e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.732013354342168e-08</v>
+        <v>3.481253733989566e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.061601248160147e-08</v>
+        <v>3.572000053915798e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.273014738333457e-08</v>
+        <v>3.093971415576284e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.557289923781204e-08</v>
+        <v>3.321801131330187e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.094046720536712e-08</v>
+        <v>2.947844607288369e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.060394678536218e-08</v>
+        <v>2.896321098534579e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.342915042984328e-08</v>
+        <v>3.141884419922113e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.171475047621749e-08</v>
+        <v>2.945471868509381e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.356031631605077e-08</v>
+        <v>3.383631779555896e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.761639196806134e-08</v>
+        <v>3.628279292364542e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.156576558233075e-08</v>
+        <v>3.012236606576226e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.416969262485105e-08</v>
+        <v>3.269832950127611e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.677018613818027e-08</v>
+        <v>3.649522157115936e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.871813673331817e-08</v>
+        <v>2.732276952795143e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.260449307866498e-08</v>
+        <v>2.990213821750376e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.575219151068668e-08</v>
+        <v>3.938654161093604e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,85 +4886,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.150216456407211e-08</v>
+        <v>1.139152097196642e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.944313695759249e-09</v>
+        <v>9.823024575394107e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150641526892469e-08</v>
+        <v>1.139493105860044e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.147574868186346e-08</v>
+        <v>1.136361534692923e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.147884321817148e-08</v>
+        <v>1.136576876560803e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.16250287804684e-08</v>
+        <v>1.146841185979325e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.152066253797585e-08</v>
+        <v>1.140610300674653e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.148789483668303e-08</v>
+        <v>1.137033077003932e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.15694588722536e-08</v>
+        <v>1.144179793753664e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.150874645349397e-08</v>
+        <v>1.139709721850017e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.159638253827177e-08</v>
+        <v>1.14985667609058e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.173490471667882e-08</v>
+        <v>1.158560153203674e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.149844694584096e-08</v>
+        <v>1.138690284636507e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.525465275464969e-08</v>
+        <v>1.501488619051582e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.155056738434172e-08</v>
+        <v>1.142569227800417e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.149475393747083e-08</v>
+        <v>1.138303416016309e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.149305250888518e-08</v>
+        <v>1.13806843554431e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.153566459200762e-08</v>
+        <v>1.141822099371978e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.149074668519435e-08</v>
+        <v>1.137329749904475e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.153140307666906e-08</v>
+        <v>1.134597426002129e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.148737714661295e-08</v>
+        <v>1.137708083932969e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.171990679209037e-08</v>
+        <v>1.147076931713041e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.154352813333279e-08</v>
+        <v>1.143232596517721e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.149814518352037e-08</v>
+        <v>1.138933582772566e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.110036999892063e-08</v>
+        <v>1.093404526010627e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.154932941288149e-08</v>
+        <v>1.140844574373578e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.160871171638396e-08</v>
+        <v>1.161363539958097e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.195447590648435e-08</v>
+        <v>1.186546744332864e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.142312200058705e-09</v>
+        <v>9.033228345416061e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.198865990744687e-08</v>
+        <v>1.189365468696014e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1745337289432e-08</v>
+        <v>1.164572436488612e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.179265939369797e-08</v>
+        <v>1.16862765373418e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.282666104398405e-08</v>
+        <v>1.241210638285821e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.20931883836564e-08</v>
+        <v>1.197610968972338e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.185656681063985e-08</v>
+        <v>1.171803781759882e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.243394185971597e-08</v>
+        <v>1.222435374480784e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.200665675968487e-08</v>
+        <v>1.191046346331166e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.262610614192917e-08</v>
+        <v>1.262799659305531e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.367986754050405e-08</v>
+        <v>1.331722314324516e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.19302611321357e-08</v>
+        <v>1.183484020342173e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.808505799838031e-08</v>
+        <v>1.776135030866918e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.229781223870147e-08</v>
+        <v>1.210762999946393e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.190446166941892e-08</v>
+        <v>1.180778489586809e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.189370135165767e-08</v>
+        <v>1.179235396744776e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.219264207339638e-08</v>
+        <v>1.205553054517459e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.187793671590571e-08</v>
+        <v>1.174035676679038e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.269261923879281e-08</v>
+        <v>1.273302400602191e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18512284321865e-08</v>
+        <v>1.17646588873407e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.266046608050028e-08</v>
+        <v>1.233131684180525e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.225337558093308e-08</v>
+        <v>1.216038973283612e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.192817706919e-08</v>
+        <v>1.185226282606745e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.140895288724035e-08</v>
+        <v>1.122431254017351e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.229293962315008e-08</v>
+        <v>1.198810333893788e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.273185773665323e-08</v>
+        <v>1.345919398592483e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.066167796057702e-09</v>
+        <v>7.564312565146811e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.577196002123143e-09</v>
+        <v>7.070291424566473e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.114181462789094e-09</v>
+        <v>7.602831062395351e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.767788254604865e-09</v>
+        <v>7.249105693130086e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.802742465761692e-09</v>
+        <v>7.273429547728547e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>9.453975640586419e-09</v>
+        <v>8.432830514706901e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>8.275110920789387e-09</v>
+        <v>7.729023356055534e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.904984660799957e-09</v>
+        <v>7.324959486405841e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.816556300424613e-09</v>
+        <v>8.122615418080561e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.140513264896902e-09</v>
+        <v>7.627298834945792e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.130403157052947e-09</v>
+        <v>8.773443994712947e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>1.080807708751276e-08</v>
+        <v>9.872590568035475e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>8.024175587948649e-09</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.932344960743573e-09</v>
+        <v>7.385754969108375e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>8.612899917401061e-09</v>
+        <v>7.950293186420774e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.982461359540171e-09</v>
+        <v>7.468450121701954e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.963242940969511e-09</v>
+        <v>7.441907996426083e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>8.444566022364068e-09</v>
+        <v>7.865901593467848e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.937197601650158e-09</v>
+        <v>7.358470055284953e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>9.451451580543797e-09</v>
+        <v>9.483341607899915e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.849393833377918e-09</v>
+        <v>7.352371191241011e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.776526766731589e-09</v>
+        <v>8.250893144401382e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>8.533388339038757e-09</v>
+        <v>8.025223734686936e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.987747883679168e-09</v>
+        <v>7.5177840480774e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.309930690511241e-09</v>
+        <v>7.800374762027606e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.598916460262743e-09</v>
+        <v>7.755485648061491e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>9.284593392706047e-09</v>
+        <v>1.006774260731739e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.530945007664827e-08</v>
+        <v>3.487021820880906e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.825048836178232e-08</v>
+        <v>2.77163681150945e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.835653227900064e-08</v>
+        <v>3.773931097784959e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.820700596638697e-08</v>
+        <v>1.746512532678137e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.290311098434681e-08</v>
+        <v>3.193068511352237e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.893445988167219e-08</v>
+        <v>5.010459859076706e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.298162800648334e-08</v>
+        <v>4.16382170361202e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.445008471313879e-08</v>
+        <v>3.24612139069999e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.921768885755837e-08</v>
+        <v>4.563019781389247e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.961026229451291e-08</v>
+        <v>3.895207518848899e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.498245990069388e-08</v>
+        <v>5.691927502483056e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.877561691700835e-08</v>
+        <v>8.048449286739721e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>6.013471988140336e-08</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.356500268073866e-08</v>
+        <v>3.237458266726176e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.446962948266613e-08</v>
+        <v>4.121185534013219e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.532610518870071e-08</v>
+        <v>3.466396783779092e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.573180746691148e-08</v>
+        <v>3.490721407103543e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.194961414810174e-08</v>
+        <v>4.029662503879374e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.562428149914851e-08</v>
+        <v>3.373176545937035e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>6.159501503403911e-08</v>
+        <v>7.050204348924081e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.337568550910904e-08</v>
+        <v>3.298947132154817e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.959467353088405e-08</v>
+        <v>4.871598499842991e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>4.619348779020238e-08</v>
+        <v>4.564007558867522e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.577893175063407e-08</v>
+        <v>3.573321492585903e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.953660612160377e-08</v>
+        <v>3.896310537840948e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.640917871365318e-08</v>
+        <v>3.950986459975445e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.326350359759568e-08</v>
+        <v>8.857188276608727e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5238,85 +5238,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.065331287348656e-08</v>
+        <v>1.020019378248792e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.285605788230522e-08</v>
+        <v>9.706172641907588e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.070132654021796e-08</v>
+        <v>1.286890555758839e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.035493333203372e-08</v>
+        <v>1.251518018832312e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.308160434594375e-08</v>
+        <v>9.909310765069648e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.473283752076848e-08</v>
+        <v>1.106871173204799e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.086225599821825e-08</v>
+        <v>1.299509785124854e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.049212973822881e-08</v>
+        <v>1.259103398159888e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.140370137785347e-08</v>
+        <v>1.075849663542166e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.072765834232576e-08</v>
+        <v>1.289337333013884e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.171754823448181e-08</v>
+        <v>1.140932521205407e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.608693896769482e-08</v>
+        <v>1.513866506322847e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.061530671750557e-08</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.323038909645419e-08</v>
+        <v>1.266904748197766e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.103029807535649e-08</v>
+        <v>1.323365427952904e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.326132323972223e-08</v>
+        <v>1.273452461689494e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.055038801839837e-08</v>
+        <v>1.270798249161911e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.103171109979292e-08</v>
+        <v>1.050178281080894e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.321605948183223e-08</v>
+        <v>9.994351272626068e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.207161581801336e-08</v>
+        <v>1.214106913289511e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.312825571355999e-08</v>
+        <v>1.2618445686434e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.152349933907489e-08</v>
+        <v>1.353416628142604e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.112053341646761e-08</v>
+        <v>1.066110495202804e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.0744039392772e-08</v>
+        <v>1.031215330187037e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.358879257069332e-08</v>
+        <v>1.043625597936872e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.38777783404448e-08</v>
+        <v>1.302156014325448e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.188174608705794e-08</v>
+        <v>1.272120813300683e-08</v>
       </c>
     </row>
     <row r="7">
@@ -5326,85 +5326,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.48945081164669e-08</v>
+        <v>1.422266331773242e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.440553632253234e-08</v>
+        <v>1.372864217715209e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.494252178319831e-08</v>
+        <v>1.426118181498096e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.459612857501405e-08</v>
+        <v>1.39074564457157e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.46310827861709e-08</v>
+        <v>1.393178030031416e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.628231596099561e-08</v>
+        <v>1.509118126729251e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.510345124119861e-08</v>
+        <v>1.438737410864114e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.473332498120916e-08</v>
+        <v>1.398331023899145e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.564489662083381e-08</v>
+        <v>1.478096617066616e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.496885358530611e-08</v>
+        <v>1.42856495875314e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.595874347746215e-08</v>
+        <v>1.543179474729857e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.763641740792196e-08</v>
+        <v>1.653094132062109e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.485251590835784e-08</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.476023780297756e-08</v>
+        <v>1.404366012687072e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.544079275963506e-08</v>
+        <v>1.460819834418312e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.481080167994936e-08</v>
+        <v>1.412680087428754e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.479158326137871e-08</v>
+        <v>1.41002587490117e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.527290634277325e-08</v>
+        <v>1.452425234605346e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.476553792205936e-08</v>
+        <v>1.401682080787056e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.631318217060615e-08</v>
+        <v>1.6163717306089e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.467773415378712e-08</v>
+        <v>1.401072194382666e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.560486708714082e-08</v>
+        <v>1.490924389698699e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.536172865944795e-08</v>
+        <v>1.468357448727253e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.484910736412907e-08</v>
+        <v>1.419798110831711e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.513827101092043e-08</v>
+        <v>1.445872551461322e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.542725678067194e-08</v>
+        <v>1.44138364006471e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.611293371311525e-08</v>
+        <v>1.6726093359903e-08</v>
       </c>
     </row>
     <row r="8">
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.284261684533683e-08</v>
+        <v>3.215664446814883e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.851273839935144e-08</v>
+        <v>4.76607022622209e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.904972386001745e-08</v>
+        <v>4.81932419000498e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.009909010698267e-08</v>
+        <v>3.932101141140008e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.509658940361103e-08</v>
+        <v>3.435807517551741e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.374021131039677e-08</v>
+        <v>5.234054723743006e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.921065331801769e-08</v>
+        <v>4.831943419370994e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.884052705802825e-08</v>
+        <v>4.791537032406028e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.975209869765292e-08</v>
+        <v>4.871302625573491e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.907605566212516e-08</v>
+        <v>4.821770967260028e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.006594555428123e-08</v>
+        <v>4.93638548323674e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.174361948474115e-08</v>
+        <v>5.046300140568994e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.643371728370585e-08</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.978414041199664e-08</v>
+        <v>3.898293224251566e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.962091579653048e-08</v>
+        <v>3.871209857927128e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.958327975197063e-08</v>
+        <v>2.891679437506135e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.889878533819779e-08</v>
+        <v>4.803231883408049e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.938010841959237e-08</v>
+        <v>4.845631243112227e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.88727399988784e-08</v>
+        <v>4.794888089293935e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.25336097345772e-08</v>
+        <v>4.228763371566391e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.436911207899095e-08</v>
+        <v>4.357079941434432e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.971524489125764e-08</v>
+        <v>4.884444806534261e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.161521974692186e-08</v>
+        <v>3.093982371253986e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.502401340167605e-08</v>
+        <v>6.40373945202549e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.278621628453653e-08</v>
+        <v>3.209553413517434e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.953445885749102e-08</v>
+        <v>4.834589648571591e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.709965999557846e-08</v>
+        <v>6.736948463205885e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5502,85 +5502,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.669133699348528e-08</v>
+        <v>2.595479735634811e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.15344991064447e-08</v>
+        <v>3.070884339499433e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.207148456711066e-08</v>
+        <v>3.12413830328232e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.049445759027667e-08</v>
+        <v>2.967642615201772e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.946801996126502e-08</v>
+        <v>1.881375266184436e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.341128002894092e-08</v>
+        <v>3.207138376821319e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.223241402511095e-08</v>
+        <v>3.136757532648336e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.186228776512149e-08</v>
+        <v>3.096351145683369e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.277385940474616e-08</v>
+        <v>3.176116738850839e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.209781636921843e-08</v>
+        <v>3.126585080537363e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.30877062613745e-08</v>
+        <v>3.241199596514079e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.476538019183429e-08</v>
+        <v>3.351114253846332e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.198147869227018e-08</v>
+        <v>3.518116351001796e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.365671196953691e-08</v>
+        <v>3.276351123926414e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.472157272845046e-08</v>
+        <v>3.370629627299877e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.193976574789468e-08</v>
+        <v>3.110700337520821e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.192054604529106e-08</v>
+        <v>3.108045996685393e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.240186912668562e-08</v>
+        <v>3.150445356389568e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.18945007059717e-08</v>
+        <v>3.09970220257128e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.344177384490607e-08</v>
+        <v>3.314373988598188e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.795986242531797e-08</v>
+        <v>3.704707754174626e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.273382987105312e-08</v>
+        <v>3.188944511482921e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.249069144336032e-08</v>
+        <v>3.166377570511478e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.197807014804142e-08</v>
+        <v>3.117818232615937e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.905243171069815e-08</v>
+        <v>2.827480940922018e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.255621956458429e-08</v>
+        <v>3.139403761848932e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.324189649702761e-08</v>
+        <v>3.370629457774523e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,85 +5746,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.141598036317063e-08</v>
+        <v>1.132508230450343e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.900367226784618e-09</v>
+        <v>9.799869730262634e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.142855957129139e-08</v>
+        <v>1.133706504672695e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.141132986757005e-08</v>
+        <v>1.132080731072434e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.141919819191033e-08</v>
+        <v>1.132870519083257e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.144885324904668e-08</v>
+        <v>1.135741783367119e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14383963665885e-08</v>
+        <v>1.134765803233253e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.143322309229535e-08</v>
+        <v>1.134232003676063e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.144056855098277e-08</v>
+        <v>1.134960937396413e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.1435101054838e-08</v>
+        <v>1.134434052395287e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.143075791047784e-08</v>
+        <v>1.134002813362829e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.141735017412256e-08</v>
+        <v>1.132686932756374e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.143796449696574e-08</v>
+        <v>1.134721280151236e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.521546212954762e-08</v>
+        <v>1.499783897017278e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.141790183130236e-08</v>
+        <v>1.132756341014265e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.14162097085501e-08</v>
+        <v>1.132523746462746e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.143637095297505e-08</v>
+        <v>1.134571869313343e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.143415936546262e-08</v>
+        <v>1.134261154068105e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.141374134056439e-08</v>
+        <v>1.132321816856013e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.136428425701439e-08</v>
+        <v>1.113520624809808e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.143704071938217e-08</v>
+        <v>1.134644148126294e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16646200462961e-08</v>
+        <v>1.141757258958372e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.156971875231085e-08</v>
+        <v>1.147935535824727e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.150338035670226e-08</v>
+        <v>1.141284074638943e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.104047921961982e-08</v>
+        <v>1.088688883183394e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.145937880416403e-08</v>
+        <v>1.136816116940705e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14179418687784e-08</v>
+        <v>1.132730600510797e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.174181812916346e-08</v>
+        <v>1.165977471252854e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.188794602987961e-09</v>
+        <v>9.09410489623254e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.183632724272583e-08</v>
+        <v>1.1750009415285e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.168779742266206e-08</v>
+        <v>1.160840457264339e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17691650612081e-08</v>
+        <v>1.168997874495439e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.197802107628951e-08</v>
+        <v>1.189220345632133e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.190764853258293e-08</v>
+        <v>1.18266906656103e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.186922899153342e-08</v>
+        <v>1.178711025180938e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.191937465468677e-08</v>
+        <v>1.183690615387515e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.18836427267084e-08</v>
+        <v>1.180256942953655e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.185283260383873e-08</v>
+        <v>1.177201016076211e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.183574276936816e-08</v>
+        <v>1.175634319269621e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.190055083369706e-08</v>
+        <v>1.181953161936855e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.812403729207696e-08</v>
+        <v>1.783490123895378e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.175524818314272e-08</v>
+        <v>1.167718439406334e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.174673493347562e-08</v>
+        <v>1.166416989703634e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.189208574851975e-08</v>
+        <v>1.18117527980977e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.187255102746419e-08</v>
+        <v>1.178593831235222e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.173104586722116e-08</v>
+        <v>1.165164985974384e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.171530600620942e-08</v>
+        <v>1.140644567234576e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18938637945682e-08</v>
+        <v>1.181394391760403e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.243897016980727e-08</v>
+        <v>1.208979845063463e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.284038517747576e-08</v>
+        <v>1.276213069277081e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.236732614208982e-08</v>
+        <v>1.228781268234466e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.127536999471913e-08</v>
+        <v>1.109112149338934e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.205295366825258e-08</v>
+        <v>1.196860166706824e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.177724154181249e-08</v>
+        <v>1.169706250629287e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.641287701113838e-09</v>
+        <v>7.25263167744964e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.541802651822492e-09</v>
+        <v>7.159758569483855e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.783375643559496e-09</v>
+        <v>7.387982263198002e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.588758213971714e-09</v>
+        <v>7.20434365612052e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.677634557003192e-09</v>
+        <v>7.293553845147255e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.012602069358452e-09</v>
+        <v>7.617876354477651e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.894486771590009e-09</v>
+        <v>7.507634908627126e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.836052258624512e-09</v>
+        <v>7.447339793043229e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.909882733474272e-09</v>
+        <v>7.520490638592374e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.857264709449662e-09</v>
+        <v>7.470162125349589e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.80820689595677e-09</v>
+        <v>7.421451692835994e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.796785187855623e-09</v>
+        <v>7.412261742261944e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.889608605530805e-09</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.86764500745463e-09</v>
+        <v>7.483307365920803e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.662991567580874e-09</v>
+        <v>7.280656907009548e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.643878262679119e-09</v>
+        <v>7.254384282427493e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.871608793089651e-09</v>
+        <v>7.485729180233114e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.846627894756184e-09</v>
+        <v>7.450632463922783e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.615996910775276e-09</v>
+        <v>7.231575404425115e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.733093038544003e-09</v>
+        <v>7.35291775193341e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.833430999422767e-09</v>
+        <v>7.447848070989738e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.228223140424195e-09</v>
+        <v>7.820208835888847e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.377833529605735e-09</v>
+        <v>8.995216788597155e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.611979327103052e-09</v>
+        <v>8.233239148537504e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.957960831026134e-09</v>
+        <v>7.571932310978596e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.131493056403558e-09</v>
+        <v>7.73922727379289e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.69236489151998e-09</v>
+        <v>7.306727739816656e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.881108987892403e-08</v>
+        <v>2.830374784953837e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.939500943861491e-08</v>
+        <v>2.89893216412217e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.377570374268241e-08</v>
+        <v>3.314018127986158e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.708745744465111e-08</v>
+        <v>1.66398924732398e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.17243526046382e-08</v>
+        <v>3.128040831817292e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.6201090198428e-08</v>
+        <v>3.561797538577249e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.631901440338121e-08</v>
+        <v>3.581538459098047e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.450939763198956e-08</v>
+        <v>3.398050444150577e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.478656576977877e-08</v>
+        <v>3.427273081554413e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.540830454858508e-08</v>
+        <v>3.492251789090835e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.463760374619727e-08</v>
+        <v>3.417421314376581e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.574335520734972e-08</v>
+        <v>3.529942179363321e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.307188055970902e-08</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.309129804389976e-08</v>
+        <v>3.265662412979652e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.904801085140973e-08</v>
+        <v>2.864494107873296e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.055666180942257e-08</v>
+        <v>3.003856412167311e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.5340546237811e-08</v>
+        <v>3.485960502137977e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.295511061535146e-08</v>
+        <v>3.235325776393125e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.106256716725635e-08</v>
+        <v>3.061551824981167e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.293189649965595e-08</v>
+        <v>3.24729889171025e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.387284071402247e-08</v>
+        <v>3.342014885917003e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.004385501373958e-08</v>
+        <v>3.920836008844072e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.021323031298587e-08</v>
+        <v>5.979871296954571e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.716823795436406e-08</v>
+        <v>4.671783699859968e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.41904715867177e-08</v>
+        <v>3.373160446380495e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.820602249855365e-08</v>
+        <v>3.762045308419599e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.267387176896839e-08</v>
+        <v>3.22002166661228e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6098,85 +6098,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.003172285816491e-08</v>
+        <v>1.210158425062495e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.932237808873579e-09</v>
+        <v>9.596205122361243e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>1.017381080061059e-08</v>
+        <v>9.824428816075385e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.243384824430179e-08</v>
+        <v>9.640790208997903e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.252272458733327e-08</v>
+        <v>1.214250641832255e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.040303722640954e-08</v>
+        <v>1.246682892765294e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.028492192864111e-08</v>
+        <v>1.235658748180242e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.022648741567561e-08</v>
+        <v>1.229629236621854e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.030031789052536e-08</v>
+        <v>1.236944321176767e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.024769986650075e-08</v>
+        <v>1.231911469852488e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.265329692628683e-08</v>
+        <v>9.857898245713391e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.264187521818569e-08</v>
+        <v>1.226121431543723e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.028245813963337e-08</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.026049454155713e-08</v>
+        <v>1.234792732617022e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.894479336668273e-09</v>
+        <v>9.559032303982316e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.003431341973022e-08</v>
+        <v>1.21033368556028e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.271669882341971e-08</v>
+        <v>9.922175733110491e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.023706305180728e-08</v>
+        <v>1.229958503709808e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.246108694110535e-08</v>
+        <v>9.66802195730252e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.014005970252883e-08</v>
+        <v>9.800028805702905e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>1.267852102975284e-08</v>
+        <v>9.884294623867128e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.076510349554226e-08</v>
+        <v>1.040197468988395e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.176826868665682e-08</v>
+        <v>1.384416936177244e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.114657877332008e-08</v>
+        <v>1.080707611605725e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.280305086135621e-08</v>
+        <v>1.000837886385599e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.297658308673363e-08</v>
+        <v>1.258817984696819e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.008431584222683e-08</v>
+        <v>9.744461638887608e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6186,85 +6186,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.403348809189745e-08</v>
+        <v>1.348348158685519e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.393400304260611e-08</v>
+        <v>1.339060847888938e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.417557603434312e-08</v>
+        <v>1.361883217260353e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.398095860475533e-08</v>
+        <v>1.343519356552606e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.406983494778682e-08</v>
+        <v>1.35244037545528e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.440480246014206e-08</v>
+        <v>1.384872626388318e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.428668716237363e-08</v>
+        <v>1.373848481803267e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.422825264940814e-08</v>
+        <v>1.367818970244876e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.43020831242579e-08</v>
+        <v>1.375134054799792e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.424946510023328e-08</v>
+        <v>1.37010120347551e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.420040728674039e-08</v>
+        <v>1.365230160224153e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.418898557863923e-08</v>
+        <v>1.364311165166748e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.428180899631443e-08</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.425942750349943e-08</v>
+        <v>1.371374148949626e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.405477406362566e-08</v>
+        <v>1.351109103058501e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.403607865346275e-08</v>
+        <v>1.348523419183305e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.426380918387326e-08</v>
+        <v>1.371657908963865e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.423882828553981e-08</v>
+        <v>1.368148237332832e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.400819730155889e-08</v>
+        <v>1.346242531383066e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.414316641645116e-08</v>
+        <v>1.359517934686999e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.422563139020638e-08</v>
+        <v>1.367869798039529e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.462042353120782e-08</v>
+        <v>1.405105874529439e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.577003392038934e-08</v>
+        <v>1.522606669800269e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.50207112248204e-08</v>
+        <v>1.447475355883515e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.435016122180975e-08</v>
+        <v>1.380278222038414e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.452369344718718e-08</v>
+        <v>1.397007718319843e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.408456528230362e-08</v>
+        <v>1.35375776492222e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.07208894698691e-08</v>
+        <v>3.016251698340752e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.568089549526478e-08</v>
+        <v>4.498208658184861e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.59224684870018e-08</v>
+        <v>4.521031027556277e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.770911628686976e-08</v>
+        <v>3.708623581641139e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.310332903146005e-08</v>
+        <v>3.252662343961048e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.927437849076794e-08</v>
+        <v>4.853239650770912e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.603357961503229e-08</v>
+        <v>4.532996292099186e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.597514510206677e-08</v>
+        <v>4.526966780540795e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.604897557691658e-08</v>
+        <v>4.534281865095706e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.599635755289193e-08</v>
+        <v>4.529249013771432e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.5947299739399e-08</v>
+        <v>4.524377970520076e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.593587803129805e-08</v>
+        <v>4.523458975462663e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.435507646869315e-08</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.754112637679308e-08</v>
+        <v>3.692268634921149e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.655011130995096e-08</v>
+        <v>3.594135268976064e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.776394631852154e-08</v>
+        <v>2.723363423607782e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.601070163653195e-08</v>
+        <v>4.530805719259787e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.598572073819841e-08</v>
+        <v>4.527296047628748e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.575508975421754e-08</v>
+        <v>4.505390341678989e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.853974426588308e-08</v>
+        <v>3.79082472892145e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.185804173399258e-08</v>
+        <v>4.119537471893942e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.63702756076542e-08</v>
+        <v>4.564546757274207e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.087813386751717e-08</v>
+        <v>3.034122174912407e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.174324538205315e-08</v>
+        <v>6.0894875833102e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.075782482130441e-08</v>
+        <v>3.0204811337403e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.627058589984581e-08</v>
+        <v>4.556155528615756e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.15623554187904e-08</v>
+        <v>6.070634911927832e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,85 +6362,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.382222815553334e-08</v>
+        <v>2.329408471883078e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.836957870561089e-08</v>
+        <v>2.779240389437172e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.86111516973479e-08</v>
+        <v>2.802062758808584e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.734406483687837e-08</v>
+        <v>2.677736179095788e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.77931841551049e-08</v>
+        <v>1.734224576004133e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.884037977596631e-08</v>
+        <v>2.825052331982826e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.872226282537841e-08</v>
+        <v>2.814028023351494e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.866382831241291e-08</v>
+        <v>2.807998511793109e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.873765878726268e-08</v>
+        <v>2.815313596348024e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.868504076323803e-08</v>
+        <v>2.810280745023745e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.863598294974518e-08</v>
+        <v>2.805409701772386e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.862456124164401e-08</v>
+        <v>2.804490706714982e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.871738465931919e-08</v>
+        <v>3.366317110315441e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.023537849492446e-08</v>
+        <v>2.963746998602038e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.036563901619598e-08</v>
+        <v>2.976572307720409e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.847165596928698e-08</v>
+        <v>2.788703124777811e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.869938484687804e-08</v>
+        <v>2.811837450512097e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.867440394854456e-08</v>
+        <v>2.808327778881064e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.844377296456365e-08</v>
+        <v>2.786422072931298e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.857740059926614e-08</v>
+        <v>2.799622757771338e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.402355436600406e-08</v>
+        <v>3.337862952345598e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.905599919421257e-08</v>
+        <v>2.845285416077671e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.020560958339409e-08</v>
+        <v>2.9627862113485e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.945628688782515e-08</v>
+        <v>2.887654897431748e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.598410888745541e-08</v>
+        <v>2.543649760506879e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.895926911019196e-08</v>
+        <v>2.837187259868075e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.852014094530835e-08</v>
+        <v>2.793937306470452e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,85 +6606,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.146209735398593e-08</v>
+        <v>1.136347868403525e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.941884959730431e-09</v>
+        <v>9.832431474720821e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.147193323396109e-08</v>
+        <v>1.137330172214623e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.146376492137132e-08</v>
+        <v>1.136531464443593e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.145454802320309e-08</v>
+        <v>1.135602768815522e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.150132094723665e-08</v>
+        <v>1.140248629565285e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.147022749707946e-08</v>
+        <v>1.137152179707774e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.14708128241737e-08</v>
+        <v>1.137195043110633e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.148262791217604e-08</v>
+        <v>1.13839065120429e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.147567181203996e-08</v>
+        <v>1.137723181750266e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.146786455126721e-08</v>
+        <v>1.136929609067963e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.146160493765183e-08</v>
+        <v>1.136342634264023e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.14660138985985e-08</v>
+        <v>1.136728580941623e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.52906674531004e-08</v>
+        <v>1.505529870758283e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.146296983103357e-08</v>
+        <v>1.136483097580237e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.145549804924761e-08</v>
+        <v>1.135685863435409e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.14836616618414e-08</v>
+        <v>1.138508614398725e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.146297057357723e-08</v>
+        <v>1.136425318394594e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.145597969214156e-08</v>
+        <v>1.13576900554664e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.143461778078536e-08</v>
+        <v>1.119530059505075e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.148287516948562e-08</v>
+        <v>1.138419227910459e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.178049596972643e-08</v>
+        <v>1.152082241009952e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.165038070440907e-08</v>
+        <v>1.15522410943979e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.154292165502245e-08</v>
+        <v>1.144433348194387e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.107255952860367e-08</v>
+        <v>1.090573677472209e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.150850570202034e-08</v>
+        <v>1.140937137062874e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.14686515434305e-08</v>
+        <v>1.137006682877986e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.183633745196355e-08</v>
+        <v>1.174778152346868e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.227312811783791e-09</v>
+        <v>9.123441869817536e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.191078352181394e-08</v>
+        <v>1.182210332682881e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.182881832785069e-08</v>
+        <v>1.174144674833024e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17866960535584e-08</v>
+        <v>1.169879727788761e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.211623330232244e-08</v>
+        <v>1.202615690848128e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1900340106387e-08</v>
+        <v>1.181110236375206e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.190269091980139e-08</v>
+        <v>1.181234615080839e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.198456564849213e-08</v>
+        <v>1.189526999381481e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.193767204721653e-08</v>
+        <v>1.185036762982607e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.18815967367394e-08</v>
+        <v>1.179341187390211e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.191414153611276e-08</v>
+        <v>1.182831281070257e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.186625989686638e-08</v>
+        <v>1.177689437778702e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.823792189206987e-08</v>
+        <v>1.792508990481076e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.184264921685001e-08</v>
+        <v>1.175750612535127e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.179203751754296e-08</v>
+        <v>1.17033182603495e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.199504163615795e-08</v>
+        <v>1.19067398137974e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.184351315368682e-08</v>
+        <v>1.175426384442311e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.179680196034817e-08</v>
+        <v>1.171055801505362e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.179756879041889e-08</v>
+        <v>1.14775011611154e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.198553146486279e-08</v>
+        <v>1.189651787010639e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.281348297408563e-08</v>
+        <v>1.243803584130523e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.318000898202076e-08</v>
+        <v>1.309484535914432e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.241510162414145e-08</v>
+        <v>1.232672782297338e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.122753339144175e-08</v>
+        <v>1.102718832951096e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.216903393379201e-08</v>
+        <v>1.207676489704062e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.190319034214131e-08</v>
+        <v>1.181487849439278e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6782,85 +6782,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.790228979717479e-09</v>
+        <v>7.389327745146007e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.591861562622568e-09</v>
+        <v>7.196271382487133e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.901329768765149e-09</v>
+        <v>7.500283479431044e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.809064920454272e-09</v>
+        <v>7.410065762455408e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.704955815661534e-09</v>
+        <v>7.305165319054213e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.233277509228615e-09</v>
+        <v>7.829936662754799e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.882062686009493e-09</v>
+        <v>7.480178406975902e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.888674224802669e-09</v>
+        <v>7.485020025510633e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.013015369687131e-09</v>
+        <v>7.61090942048623e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.943558727996819e-09</v>
+        <v>7.54467571441457e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.855372126051287e-09</v>
+        <v>7.455038029333836e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.923205987348126e-09</v>
+        <v>7.526575655112833e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.8344681528159e-09</v>
+        <v>3.173270529966528e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>7.958083370573775e-09</v>
+        <v>7.560187720667435e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.800084009329648e-09</v>
+        <v>7.404602502740978e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.715686796868005e-09</v>
+        <v>7.314551238624296e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.033807757016697e-09</v>
+        <v>7.633393945227148e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.80009239670193e-09</v>
+        <v>7.398076077925467e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.721127174921718e-09</v>
+        <v>7.323942522560658e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.777364476672413e-09</v>
+        <v>7.383405538848841e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.979346803713349e-09</v>
+        <v>7.577426264044642e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.717946054963371e-09</v>
+        <v>8.273646617662584e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.916976037367159e-09</v>
+        <v>9.521486005191631e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.687719952657722e-09</v>
+        <v>8.292591621833832e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.859700015965914e-09</v>
+        <v>7.460411225207137e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.314432619660779e-09</v>
+        <v>7.907706751898721e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.890498481365222e-09</v>
+        <v>7.490085476111157e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6870,85 +6870,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.047985068920984e-08</v>
+        <v>2.996613889101076e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.914103958202359e-08</v>
+        <v>2.870485427196004e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.464570199916305e-08</v>
+        <v>3.411252356525061e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.074874271604075e-08</v>
+        <v>2.02596135212695e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.116817618177142e-08</v>
+        <v>3.065096141238107e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.829263189280482e-08</v>
+        <v>3.774665753428606e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.52017267685506e-08</v>
+        <v>3.463918423671086e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.437202419123854e-08</v>
+        <v>3.378403356670774e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.54535884019358e-08</v>
+        <v>3.491592196958781e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.54994007043708e-08</v>
+        <v>3.500910035853891e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.375596389312469e-08</v>
+        <v>3.325887412708315e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.596569423424679e-08</v>
+        <v>3.551024345152284e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.232189050964841e-08</v>
+        <v>3.173270529966527e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.36037436389631e-08</v>
+        <v>3.314066176272287e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.069812591461517e-08</v>
+        <v>3.027424680643416e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.06122878240105e-08</v>
+        <v>3.008651781203388e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.727471904747467e-08</v>
+        <v>3.674171005085942e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.114324127957935e-08</v>
+        <v>3.061560450400432e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.139615955231028e-08</v>
+        <v>3.092934744607919e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.228024352178762e-08</v>
+        <v>3.179382690710687e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.505252888391212e-08</v>
+        <v>3.452604473092634e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.738806254302988e-08</v>
+        <v>4.612673582089247e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.803470131196333e-08</v>
+        <v>6.760282317377751e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.762032842339071e-08</v>
+        <v>4.709429654076314e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.194505514431077e-08</v>
+        <v>3.146556573429791e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.051708346298474e-08</v>
+        <v>3.988335209802858e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.526949011437405e-08</v>
+        <v>3.473583889649678e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.266031235838383e-08</v>
+        <v>1.226112346925127e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.246194494128888e-08</v>
+        <v>1.206806710659239e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.277141314743148e-08</v>
+        <v>1.23720792035363e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.267914829912062e-08</v>
+        <v>9.843046358767716e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.257503919432785e-08</v>
+        <v>1.217696104315948e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.310336088789496e-08</v>
+        <v>1.270173238686005e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.026823248083373e-08</v>
+        <v>1.235197413108115e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.027484401962692e-08</v>
+        <v>1.235681574961588e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.039918516451137e-08</v>
+        <v>1.004389001679853e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.281364210666316e-08</v>
+        <v>9.977656310726866e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.272545550471761e-08</v>
+        <v>1.232683375343909e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.279328936601447e-08</v>
+        <v>1.239837137921808e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.022234890884382e-08</v>
+        <v>3.173270529966527e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.284014111527929e-08</v>
+        <v>9.994869466103749e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.26821579128396e-08</v>
+        <v>1.228504245119937e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.258577017553433e-08</v>
+        <v>1.218634696272955e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.041997755184092e-08</v>
+        <v>1.250518966933239e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.018626219152616e-08</v>
+        <v>1.226987180203072e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.259121055358805e-08</v>
+        <v>9.756923118872956e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.266290454362143e-08</v>
+        <v>1.2265229523689e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.036551659853759e-08</v>
+        <v>1.001040686035695e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.359997681167946e-08</v>
+        <v>1.315400686725218e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.23031458321914e-08</v>
+        <v>1.195446660150393e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.121713356496397e-08</v>
+        <v>1.08622774687039e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.024586981079013e-08</v>
+        <v>9.89339182151945e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.070060241448501e-08</v>
+        <v>1.277950247600397e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.027803516759465e-08</v>
+        <v>9.924171434013683e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7046,85 +7046,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.423685474476326e-08</v>
+        <v>1.366266038616374e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.403848732766834e-08</v>
+        <v>1.346960402350487e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.434795553381093e-08</v>
+        <v>1.377361612044878e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.425569068550005e-08</v>
+        <v>1.368339840347313e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.415158158070728e-08</v>
+        <v>1.357849796007194e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.467990327427444e-08</v>
+        <v>1.410326930377251e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.432868845105527e-08</v>
+        <v>1.375351104799363e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.433529998984844e-08</v>
+        <v>1.375835266652836e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.445964113473289e-08</v>
+        <v>1.388424206150394e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.439018449304261e-08</v>
+        <v>1.38180083554323e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.430199789109707e-08</v>
+        <v>1.372837067035156e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.43698317523939e-08</v>
+        <v>1.379990829613055e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.428109391786167e-08</v>
+        <v>3.173270529966527e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.440429081587303e-08</v>
+        <v>1.383310431892506e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.424629145462892e-08</v>
+        <v>1.36775191009986e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.416231256191378e-08</v>
+        <v>1.358788387964201e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.448043352206247e-08</v>
+        <v>1.390672658624488e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.424671816174771e-08</v>
+        <v>1.367140871894318e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.416775293996749e-08</v>
+        <v>1.359727516357838e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.424110576074295e-08</v>
+        <v>1.36677599657366e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.442597256875914e-08</v>
+        <v>1.385075890506238e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.516457182000914e-08</v>
+        <v>1.454697925868031e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.636360180241293e-08</v>
+        <v>1.579481864620935e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.514980240598616e-08</v>
+        <v>1.457595252358645e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.430632578101167e-08</v>
+        <v>1.373374386622485e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.476105838470654e-08</v>
+        <v>1.418103939291645e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.433712424641099e-08</v>
+        <v>1.376341811712887e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.093521410118762e-08</v>
+        <v>3.035160454078116e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.585266856617464e-08</v>
+        <v>4.511648438427387e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.616213677231726e-08</v>
+        <v>4.542049648121779e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.8021142660184e-08</v>
+        <v>3.736561896553153e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.32048093242705e-08</v>
+        <v>3.259771375875929e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.962844865062016e-08</v>
+        <v>4.885177517894172e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.614286968956155e-08</v>
+        <v>4.540039140876261e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.614948122835473e-08</v>
+        <v>4.540523302729734e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.62738223732392e-08</v>
+        <v>4.553112242227299e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.620436573154888e-08</v>
+        <v>4.54648887162013e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.611617912960341e-08</v>
+        <v>4.537525103112055e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.618401299090055e-08</v>
+        <v>4.544678865689977e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.437798437641187e-08</v>
+        <v>3.173270529966527e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.772161284122811e-08</v>
+        <v>3.707187776848681e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.677431042657227e-08</v>
+        <v>3.613523381539985e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.789006791609077e-08</v>
+        <v>2.733725217091752e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.629461476056877e-08</v>
+        <v>4.55536069470139e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.606089940025403e-08</v>
+        <v>4.531828907971218e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.598193417847379e-08</v>
+        <v>4.524415552434741e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.867740699846302e-08</v>
+        <v>3.801397016230656e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.211054726603315e-08</v>
+        <v>4.141061462734274e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.698172375289654e-08</v>
+        <v>4.619679928469848e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.147675226907276e-08</v>
+        <v>3.091511151400055e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.199605508201925e-08</v>
+        <v>6.109703713534907e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.072390098529349e-08</v>
+        <v>3.014483667619574e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.657523962321281e-08</v>
+        <v>4.582791975368546e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.194104540735206e-08</v>
+        <v>6.103511360956856e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,85 +7222,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.328500477267026e-08</v>
+        <v>2.273800599071787e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.755014675876943e-08</v>
+        <v>2.694986364064063e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.785961496491204e-08</v>
+        <v>2.725387573758456e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.673719159460332e-08</v>
+        <v>2.614702306434123e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.73736315226925e-08</v>
+        <v>1.690422647502653e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.819156431994843e-08</v>
+        <v>2.758353052063875e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.784034788215635e-08</v>
+        <v>2.723377066512939e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.784695942094955e-08</v>
+        <v>2.723861228366413e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.797130056583399e-08</v>
+        <v>2.736450167863972e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.790184392414372e-08</v>
+        <v>2.729826797256807e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.781365732219818e-08</v>
+        <v>2.720863028748732e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.788149118349498e-08</v>
+        <v>2.728016791326632e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.779275334896273e-08</v>
+        <v>3.173270529966527e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.939557188811377e-08</v>
+        <v>2.877356484472778e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.955927351927516e-08</v>
+        <v>2.893545744153118e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.767397360758795e-08</v>
+        <v>2.706814509650826e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.799209295316352e-08</v>
+        <v>2.738698620338064e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.775837759284878e-08</v>
+        <v>2.715166833607897e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.767941237106857e-08</v>
+        <v>2.707753478071414e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.775110636110197e-08</v>
+        <v>2.714702605773723e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.308842472683518e-08</v>
+        <v>3.241419343496684e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.867623125111023e-08</v>
+        <v>2.802723887581607e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.987526123351406e-08</v>
+        <v>2.927507826334514e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.866146183708727e-08</v>
+        <v>2.805621214072222e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.512688659385838e-08</v>
+        <v>2.455823266924628e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.827271781580766e-08</v>
+        <v>2.76612990100522e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.784878367751208e-08</v>
+        <v>2.724367773426467e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7466,85 +7466,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.202540794120398e-08</v>
+        <v>1.182515898979018e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.034499686236582e-08</v>
+        <v>1.012334221802107e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.195686193615625e-08</v>
+        <v>1.175121739092232e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.192770506015924e-08</v>
+        <v>1.171453041263725e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.190745010065633e-08</v>
+        <v>1.169494209875711e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.242690614561073e-08</v>
+        <v>1.204635952616789e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.189748303023095e-08</v>
+        <v>1.168604762169306e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.190927144727674e-08</v>
+        <v>1.169189195763748e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.219139038763248e-08</v>
+        <v>1.19225497045582e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.193034265877088e-08</v>
+        <v>1.171672598127539e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.22678032606203e-08</v>
+        <v>1.211465150114137e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.27176284400984e-08</v>
+        <v>1.239238733461688e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.193964204618803e-08</v>
+        <v>1.172792325041903e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.588282411394406e-08</v>
+        <v>1.548402403326667e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.212684078387469e-08</v>
+        <v>1.18676912838783e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.192794577278675e-08</v>
+        <v>1.172090661454947e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.191292706330461e-08</v>
+        <v>1.169685947059103e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.20762918601921e-08</v>
+        <v>1.184068035338279e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.193960089029895e-08</v>
+        <v>1.170665369549358e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.22082810241558e-08</v>
+        <v>1.194694681892618e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.191982981178094e-08</v>
+        <v>1.171983037736195e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.21756845879023e-08</v>
+        <v>1.180819010187412e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.211111791038933e-08</v>
+        <v>1.190544905555671e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.205910822110311e-08</v>
+        <v>1.188313410759305e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.158232449045549e-08</v>
+        <v>1.132247279419927e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.201334649762846e-08</v>
+        <v>1.175256204942341e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.238347645069956e-08</v>
+        <v>1.26610445845591e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.315232235264157e-08</v>
+        <v>1.302763865951015e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.496998407287471e-09</v>
+        <v>9.302877504323117e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.267187830140879e-08</v>
+        <v>1.250886602985088e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.243834682586689e-08</v>
+        <v>1.222163998258097e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.231971819379808e-08</v>
+        <v>1.210758190533288e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.60031538370011e-08</v>
+        <v>1.459849001789457e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.224937447346451e-08</v>
+        <v>1.204479749458612e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.23320446653532e-08</v>
+        <v>1.208501641716593e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.433475252236815e-08</v>
+        <v>1.372306889732792e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.248300615709591e-08</v>
+        <v>1.226321434740069e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.488257207759006e-08</v>
+        <v>1.509336781809775e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.812910712551743e-08</v>
+        <v>1.7118554514268e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.254700763856705e-08</v>
+        <v>1.234059518048295e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.917096313552254e-08</v>
+        <v>1.857665093290621e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.387411905724215e-08</v>
+        <v>1.333051928247929e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.246372251097905e-08</v>
+        <v>1.229074728174922e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.235863675783523e-08</v>
+        <v>1.212089252639542e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.351286907211339e-08</v>
+        <v>1.313729087950686e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2548624619893e-08</v>
+        <v>1.219018737043759e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.477670819217992e-08</v>
+        <v>1.498027687111413e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.240403415036685e-08</v>
+        <v>1.228103794727286e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.316295189544938e-08</v>
+        <v>1.272252103833586e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.377426685962263e-08</v>
+        <v>1.361107600179863e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.339884047537188e-08</v>
+        <v>1.344746419162536e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.222332182992668e-08</v>
+        <v>1.196270414297066e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.307229740501068e-08</v>
+        <v>1.251571766884469e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.572598827476185e-08</v>
+        <v>1.898398892515777e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.011736098980486e-08</v>
+        <v>9.23717677718754e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>8.29820158614256e-09</v>
+        <v>7.34799451722983e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.343102330070655e-09</v>
+        <v>8.401972403158889e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>9.013762002858717e-09</v>
+        <v>7.987576106585356e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.784972917531532e-09</v>
+        <v>7.766317090239568e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.46524679068782e-08</v>
+        <v>1.173573859284786e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.672390271998122e-09</v>
+        <v>7.665849880139611e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.805545865470084e-09</v>
+        <v>7.731864343159105e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.198091464635587e-08</v>
+        <v>1.032661704927854e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.043554892532576e-09</v>
+        <v>8.012376064364662e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.285532762996815e-08</v>
+        <v>1.250712786603384e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.799645852037979e-08</v>
+        <v>1.571369464450889e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>9.148595751338816e-09</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>9.394643995223368e-09</v>
+        <v>8.22015401827609e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.126309160918364e-08</v>
+        <v>9.717598604734596e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>9.016480962719903e-09</v>
+        <v>8.059598240381581e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.846837730171333e-09</v>
+        <v>7.787974687138311e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.069211826253494e-08</v>
+        <v>9.412497719146038e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>9.148130876639075e-09</v>
+        <v>7.898604962978724e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.27621663800294e-08</v>
+        <v>1.27932551418476e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.864492325196754e-09</v>
+        <v>7.991622908752981e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.616776170968499e-09</v>
+        <v>8.654514941950365e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.108549452028726e-08</v>
+        <v>1.014409000527547e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.042549652013646e-08</v>
+        <v>9.845543404240843e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.707366287968345e-09</v>
+        <v>8.749403763149065e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.981121436081341e-09</v>
+        <v>8.417160939502257e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.414175701958059e-08</v>
+        <v>1.857415643334285e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.032982096831404e-08</v>
+        <v>6.037594539556023e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.044456838973386e-08</v>
+        <v>2.925077311402724e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.056889314389137e-08</v>
+        <v>4.956279350589453e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.019469149592536e-08</v>
+        <v>2.760713693427339e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.029092266654684e-08</v>
+        <v>3.774156291727799e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.379141981677205e-07</v>
+        <v>1.032427649642062e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.860255884491637e-08</v>
+        <v>3.6228973456337e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.030586264125086e-08</v>
+        <v>3.664717010912992e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.454731829460959e-08</v>
+        <v>8.135884490331815e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.512601607922535e-08</v>
+        <v>4.24828881613575e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.122448816654209e-07</v>
+        <v>1.21985118798789e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.113607181982378e-07</v>
+        <v>1.855393013747389e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>1.084296111421205e-07</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.794569381327033e-08</v>
+        <v>4.301941780749784e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.08060512286059e-08</v>
+        <v>6.908460172077908e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.340338839949326e-08</v>
+        <v>4.209413341873268e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.13656706028667e-08</v>
+        <v>3.794319672677301e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.974330161945095e-08</v>
+        <v>6.306548950494958e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.684861264872123e-08</v>
+        <v>3.969738379107143e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.121157064048348e-07</v>
+        <v>1.284060967088337e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.062847631513448e-08</v>
+        <v>4.068048432206832e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.404135552708635e-08</v>
+        <v>5.264023867066807e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.432362492898959e-08</v>
+        <v>8.330950400950831e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.086285519881457e-08</v>
+        <v>7.612496455197855e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.342866520740121e-08</v>
+        <v>5.213168416670067e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.112308497316993e-08</v>
+        <v>4.832319672667705e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.525858244113067e-07</v>
+        <v>2.633339285935257e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7818,85 +7818,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.572243785687856e-08</v>
+        <v>1.190823528374766e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.091068990921074e-08</v>
+        <v>1.001905302378994e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.494817919714437e-08</v>
+        <v>1.107303090971901e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.461883886993245e-08</v>
+        <v>1.353038222563277e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.439004978460523e-08</v>
+        <v>1.043737559679968e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.726495622994635e-08</v>
+        <v>1.727854471189527e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.427746713907183e-08</v>
+        <v>1.033690838669972e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.141803418853827e-08</v>
+        <v>1.040292284971922e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.459340296942405e-08</v>
+        <v>1.299767555583865e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.165604321560076e-08</v>
+        <v>1.355518218341207e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.846040449704186e-08</v>
+        <v>1.804993398508126e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.360153538745349e-08</v>
+        <v>1.8384753151069e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.176726372481447e-08</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.201331196869906e-08</v>
+        <v>1.378351612209462e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.689537465721775e-08</v>
+        <v>1.528106238609577e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.462155782979361e-08</v>
+        <v>1.07306567469417e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.445191459724505e-08</v>
+        <v>1.333078080618571e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.629719512960866e-08</v>
+        <v>1.208355622570616e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.176061919970725e-08</v>
+        <v>1.056966346953885e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.843976788112683e-08</v>
+        <v>1.838255025929699e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.446956919227047e-08</v>
+        <v>1.06626814153131e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.23915261445087e-08</v>
+        <v>1.148626712927294e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.369798284335544e-08</v>
+        <v>1.568689612432286e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.324577083210337e-08</v>
+        <v>1.270196050262276e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.231985461103651e-08</v>
+        <v>1.429220988219647e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.558619830315505e-08</v>
+        <v>1.395996705854965e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.67857164333744e-08</v>
+        <v>2.130896310758198e-08</v>
       </c>
     </row>
     <row r="7">
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.71217521865184e-08</v>
+        <v>1.602652099402699e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.530259278285611e-08</v>
+        <v>1.413733873406927e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.634749352678419e-08</v>
+        <v>1.519131661999833e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.601815319957227e-08</v>
+        <v>1.477692032342478e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.578936411424505e-08</v>
+        <v>1.455566130707902e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.165685910359174e-08</v>
+        <v>1.85250828096873e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.567678146871167e-08</v>
+        <v>1.445519409697903e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.580993706218363e-08</v>
+        <v>1.452120855999854e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.898530584306943e-08</v>
+        <v>1.711596126611798e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.604794608924611e-08</v>
+        <v>1.48017202812041e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.985971882668169e-08</v>
+        <v>1.929647208287328e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.500084971709332e-08</v>
+        <v>2.250303886134831e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.615298694805236e-08</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.639858717909555e-08</v>
+        <v>1.500905212588541e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.826703479305579e-08</v>
+        <v>1.650649671234393e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.602087215943345e-08</v>
+        <v>1.484894245722104e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.585122892688487e-08</v>
+        <v>1.457731890397776e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.769650945924847e-08</v>
+        <v>1.620184193598549e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.615252207335263e-08</v>
+        <v>1.468794917981817e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.983763962924352e-08</v>
+        <v>1.962780345691808e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.586888352191029e-08</v>
+        <v>1.478096712559243e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.662116736768202e-08</v>
+        <v>1.544385915878979e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.808988571700081e-08</v>
+        <v>1.693343422211491e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.750241235087372e-08</v>
+        <v>1.668137661948225e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.671175748468188e-08</v>
+        <v>1.553874797998849e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.698551263279487e-08</v>
+        <v>1.52065051563417e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.114614821629411e-08</v>
+        <v>2.536350065018232e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.522854828761301e-08</v>
+        <v>3.408507699147708e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.982757956772738e-08</v>
+        <v>4.838620458284032e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.087248031165538e-08</v>
+        <v>4.944018246876936e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.180093775117365e-08</v>
+        <v>4.040492376015136e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.645392244068968e-08</v>
+        <v>3.51364783594783e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.958626468148554e-08</v>
+        <v>5.613111487636445e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.020176825358281e-08</v>
+        <v>4.870405994575007e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.033492384705478e-08</v>
+        <v>4.87700744087696e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.351029262794065e-08</v>
+        <v>5.136482711488897e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.057293287411733e-08</v>
+        <v>4.905058612997516e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.438470561155285e-08</v>
+        <v>5.354533793164424e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.95258365019646e-08</v>
+        <v>5.675190471011977e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.795112925012805e-08</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.169462486447604e-08</v>
+        <v>4.015706894926511e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.270576361762358e-08</v>
+        <v>4.080910393108603e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.090111906360238e-08</v>
+        <v>2.972573304245814e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.037621571175608e-08</v>
+        <v>4.88261847527488e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.222149624411965e-08</v>
+        <v>5.045070778475655e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.067750885822382e-08</v>
+        <v>4.893681502858918e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.634979848912138e-08</v>
+        <v>4.597503001607974e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.59056811052655e-08</v>
+        <v>4.46040601953214e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.114938079982863e-08</v>
+        <v>4.969590686968991e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.447489242224009e-08</v>
+        <v>3.329409887730179e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.835031387419955e-08</v>
+        <v>6.702678700540243e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.451357726449644e-08</v>
+        <v>3.329656065961862e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.151049941766608e-08</v>
+        <v>4.945537100511271e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.282130803937783e-08</v>
+        <v>7.652449895255086e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.992350300183964e-08</v>
+        <v>2.848781709571492e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.378328187494203e-08</v>
+        <v>3.209757381581579e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.482818261887012e-08</v>
+        <v>3.315155170174486e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.318816682179831e-08</v>
+        <v>3.146802297714107e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.117855000530542e-08</v>
+        <v>1.983934079778504e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.013754861227728e-08</v>
+        <v>3.648531822789036e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.41574705607976e-08</v>
+        <v>3.241542917872556e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.429062615426954e-08</v>
+        <v>3.248144364174506e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.746599493515537e-08</v>
+        <v>3.507619634786448e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.452863518133206e-08</v>
+        <v>3.276195536295064e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.83404079187676e-08</v>
+        <v>3.725670716461982e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.348153880917925e-08</v>
+        <v>4.046327394309484e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.463367604013828e-08</v>
+        <v>4.346468492927611e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.676171754766861e-08</v>
+        <v>3.479207494256601e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.903946631630143e-08</v>
+        <v>3.668584749332425e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.450156166811896e-08</v>
+        <v>3.28091778754241e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.433191801897079e-08</v>
+        <v>3.253755398572427e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.61771985513344e-08</v>
+        <v>3.416207701773199e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.463321116543857e-08</v>
+        <v>3.26481842615647e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.831977130285258e-08</v>
+        <v>3.758932343883554e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>4.090294018417002e-08</v>
+        <v>3.908685458360674e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.510185645976795e-08</v>
+        <v>3.340409424053632e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.657057480908672e-08</v>
+        <v>3.489366930386142e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.59831014429597e-08</v>
+        <v>3.464161170122878e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.176855195220083e-08</v>
+        <v>3.01836119750959e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.54662017248808e-08</v>
+        <v>3.316674023808822e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.962683730838008e-08</v>
+        <v>4.332373573192881e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.168336414549539e-08</v>
+        <v>1.150683444692226e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.017966423406815e-08</v>
+        <v>9.990809444543549e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.171092110034996e-08</v>
+        <v>1.153418132619901e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.168369981655179e-08</v>
+        <v>1.150719421263916e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.168059669211717e-08</v>
+        <v>1.150444061250385e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.211650161784661e-08</v>
+        <v>1.180482269958055e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.169494368364331e-08</v>
+        <v>1.15182671391071e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.170307267765075e-08</v>
+        <v>1.152464354379546e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.184214668303243e-08</v>
+        <v>1.16276058309565e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.171840296247871e-08</v>
+        <v>1.154169108628347e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.181790582203819e-08</v>
+        <v>1.165633947842667e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.175452857528273e-08</v>
+        <v>1.156932722540707e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.171030334328462e-08</v>
+        <v>1.153426215837317e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.554109508558046e-08</v>
+        <v>1.521009847628119e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.179806237925437e-08</v>
+        <v>1.159854189259925e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.170018400415324e-08</v>
+        <v>1.152304939976447e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.170636865461553e-08</v>
+        <v>1.152977646085343e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.171629858841774e-08</v>
+        <v>1.153861708506017e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.169358460306677e-08</v>
+        <v>1.151733410953986e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.169453769838881e-08</v>
+        <v>1.139196849473929e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.170347611934749e-08</v>
+        <v>1.152741363227078e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.195923231538673e-08</v>
+        <v>1.16276109648485e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.188523963928017e-08</v>
+        <v>1.170865765343972e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.203406230347354e-08</v>
+        <v>1.188171722040811e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.127901795738183e-08</v>
+        <v>1.104470275799158e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.173018447682908e-08</v>
+        <v>1.154525614555169e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.199104318919584e-08</v>
+        <v>1.207702470959155e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.191841413059554e-08</v>
+        <v>1.177361747046473e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.430624234323356e-09</v>
+        <v>9.268261867399515e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.211874273739215e-08</v>
+        <v>1.197240652144311e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.189959420884424e-08</v>
+        <v>1.175495000635697e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.19028031006586e-08</v>
+        <v>1.17606343788412e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.498974908624921e-08</v>
+        <v>1.38875265397059e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.200565263350537e-08</v>
+        <v>1.185972951523388e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.206248962793398e-08</v>
+        <v>1.19040401300355e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.304693013587268e-08</v>
+        <v>1.263297088293375e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.217361554853391e-08</v>
+        <v>1.202752320767787e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.287704969925785e-08</v>
+        <v>1.283847557574318e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.250923453626659e-08</v>
+        <v>1.230083978482899e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.211241465097026e-08</v>
+        <v>1.197106997821983e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.83634263717694e-08</v>
+        <v>1.794458355738258e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.273303581846019e-08</v>
+        <v>1.242491814857642e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.204102870872086e-08</v>
+        <v>1.189192518314324e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.208656255886152e-08</v>
+        <v>1.194125647215699e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.215354077189208e-08</v>
+        <v>1.200059311120198e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.199456322013862e-08</v>
+        <v>1.185171685500682e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.227897805549033e-08</v>
+        <v>1.197954681556747e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.206370357309787e-08</v>
+        <v>1.192222790215638e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.27266094309672e-08</v>
+        <v>1.231574704086637e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.336210641127032e-08</v>
+        <v>1.321690401367102e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.442221014707998e-08</v>
+        <v>1.444992516529109e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.137810642758052e-08</v>
+        <v>1.113702913167075e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.22537828930608e-08</v>
+        <v>1.204899770069507e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.412505573896333e-08</v>
+        <v>1.583547458346432e-08</v>
       </c>
     </row>
     <row r="4">
@@ -8502,85 +8502,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.976139218562402e-09</v>
+        <v>7.318261802764509e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.969714145244407e-09</v>
+        <v>7.317971317189422e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.287407700470333e-09</v>
+        <v>7.627157384381411e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.979930777560936e-09</v>
+        <v>7.322325522037303e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.944879559564023e-09</v>
+        <v>7.291222341790344e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.286862622185107e-08</v>
+        <v>1.068417619790878e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.106935428794108e-09</v>
+        <v>7.447399320290531e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.198756155629724e-09</v>
+        <v>7.519423744536578e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>9.758939198141886e-09</v>
+        <v>8.672189363129404e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>8.371918775041111e-09</v>
+        <v>7.711983579195716e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>9.495849347342191e-09</v>
+        <v>9.006989909319249e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.922439770707334e-09</v>
+        <v>8.16321813448244e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>8.280429850235144e-09</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>8.133000532507762e-09</v>
+        <v>7.435505048282283e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.271708532664633e-09</v>
+        <v>8.354139589195454e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.166127259619864e-09</v>
+        <v>7.501417154364161e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.235985731671356e-09</v>
+        <v>7.577402403964959e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>8.348148901962533e-09</v>
+        <v>7.677261321268003e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>8.091583988474178e-09</v>
+        <v>7.436860322113743e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>8.622699873696023e-09</v>
+        <v>8.093063170937316e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>8.146846830605336e-09</v>
+        <v>7.497518142677776e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.700652676001828e-09</v>
+        <v>8.022137137335018e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.025641578817689e-08</v>
+        <v>9.597947763641265e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.188499746016887e-08</v>
+        <v>1.15178669843725e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.238000932619122e-09</v>
+        <v>7.57822487721006e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.504996399393064e-09</v>
+        <v>7.752252563638551e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.144594131478555e-08</v>
+        <v>1.370608329672734e-08</v>
       </c>
     </row>
     <row r="5">
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.840414304182703e-08</v>
+        <v>2.762798926739042e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.058248285478557e-08</v>
+        <v>2.989989265070109e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.580264212960842e-08</v>
+        <v>3.496366843744505e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.747674371942623e-08</v>
+        <v>1.669529446228951e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.999693365477137e-08</v>
+        <v>2.9275418180894e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.04577171276188e-07</v>
+        <v>8.050161724006531e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.309860884871121e-08</v>
+        <v>3.225248374744857e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.411108352670324e-08</v>
+        <v>3.290546782483973e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.766730053110553e-08</v>
+        <v>5.039898132698175e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.8061424258441e-08</v>
+        <v>3.725122282971933e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.445611250282523e-08</v>
+        <v>5.637306514933903e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.799744121947986e-08</v>
+        <v>4.549927774436542e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.071515105048743e-08</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.166111786322219e-08</v>
+        <v>3.02738146621315e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.925313076431748e-08</v>
+        <v>4.428054826316841e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.309644410858799e-08</v>
+        <v>3.220482083065173e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.505425177778921e-08</v>
+        <v>3.423275978029461e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.502099830954223e-08</v>
+        <v>3.405074849320636e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.210697473986481e-08</v>
+        <v>3.136462473744216e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.110985985582823e-08</v>
+        <v>4.211569432911151e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.327214503299393e-08</v>
+        <v>3.258559387043525e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.169399355747018e-08</v>
+        <v>4.053502791387539e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.023579932032313e-08</v>
+        <v>6.943232593119837e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.890452163030158e-08</v>
+        <v>1.029106447432134e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.300954191788918e-08</v>
+        <v>3.221385590195877e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.838476361789213e-08</v>
+        <v>3.590634682552631e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>9.689866570998241e-08</v>
+        <v>1.515082094970004e-07</v>
       </c>
     </row>
     <row r="6">
@@ -8678,85 +8678,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.035462448151597e-08</v>
+        <v>1.233728891984336e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.303771827163367e-08</v>
+        <v>1.233699843426827e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.066589296342388e-08</v>
+        <v>1.264618450146027e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.304793490395019e-08</v>
+        <v>9.751347477647746e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.301288368595328e-08</v>
+        <v>9.720244297400786e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.524711148480462e-08</v>
+        <v>1.311319815351923e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.317493955518338e-08</v>
+        <v>9.876421275900964e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>1.326676028201899e-08</v>
+        <v>1.253845086161543e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.213742446109543e-08</v>
+        <v>1.369121648020827e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.343992290143038e-08</v>
+        <v>1.014100553480614e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.187433461029575e-08</v>
+        <v>1.402601702639809e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.399044389709659e-08</v>
+        <v>1.059224009009288e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.066275875511089e-08</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.051532943738354e-08</v>
+        <v>1.247255280927768e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.149040669294111e-08</v>
+        <v>1.062543258212337e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.323413138600915e-08</v>
+        <v>9.930439109974592e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>1.330398985806061e-08</v>
+        <v>1.259642952104382e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.072663416491608e-08</v>
+        <v>1.010628327687844e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.047006925142772e-08</v>
+        <v>9.865882277724171e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.10536239185295e-08</v>
+        <v>1.314695848752691e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.321485095699461e-08</v>
+        <v>9.92654009828822e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.122803811301911e-08</v>
+        <v>1.059828537453165e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.263490105113043e-08</v>
+        <v>1.461697488072013e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.443977835277725e-08</v>
+        <v>1.410673024402372e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.061648619557268e-08</v>
+        <v>1.259725199428891e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.357300052578233e-08</v>
+        <v>1.018127451924899e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.38445312589091e-08</v>
+        <v>1.617117919554211e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,85 +8766,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.446578387914886e-08</v>
+        <v>1.361729755403593e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.445935880583088e-08</v>
+        <v>1.361700706846085e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.47770523610568e-08</v>
+        <v>1.392619313565283e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.446957543814741e-08</v>
+        <v>1.362136127330872e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.443452422015048e-08</v>
+        <v>1.359025809306177e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.935827088243748e-08</v>
+        <v>1.698321194918019e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.459658008938058e-08</v>
+        <v>1.374643507156196e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.468840081621618e-08</v>
+        <v>1.3818459495808e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.624858385872834e-08</v>
+        <v>1.497122511440083e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.486156343562759e-08</v>
+        <v>1.401101933046712e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.598549400792866e-08</v>
+        <v>1.530602566059067e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.541208443129379e-08</v>
+        <v>1.446225388575387e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.47700745108216e-08</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.462222678256486e-08</v>
+        <v>1.373412480277861e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.576093478272172e-08</v>
+        <v>1.46527593436918e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.465577192020634e-08</v>
+        <v>1.380045290563557e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.472563039225782e-08</v>
+        <v>1.387643815523639e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4837793562549e-08</v>
+        <v>1.397629707253942e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.458122864906065e-08</v>
+        <v>1.373589607338516e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.516436243127972e-08</v>
+        <v>1.442640353669663e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.463649149119181e-08</v>
+        <v>1.379655389394921e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.519029733658827e-08</v>
+        <v>1.432117288860645e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.674606044876334e-08</v>
+        <v>1.589698351491271e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.842708090263525e-08</v>
+        <v>1.785177093515465e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.472764559320559e-08</v>
+        <v>1.387726062848149e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.499464105997952e-08</v>
+        <v>1.405128831490998e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.793558597537201e-08</v>
+        <v>2.000511904799876e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.125293760495072e-08</v>
+        <v>3.037103661239461e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.64641066981886e-08</v>
+        <v>4.539505026988952e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.678180025341456e-08</v>
+        <v>4.57042363370815e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.837140332730028e-08</v>
+        <v>3.739940570735151e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.35924012655724e-08</v>
+        <v>3.268460814440337e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.451848605880376e-08</v>
+        <v>5.187664248907665e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.660132798173833e-08</v>
+        <v>4.552447827299064e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.669314870857396e-08</v>
+        <v>4.559650269723669e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.825333175108607e-08</v>
+        <v>4.674926831582947e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.68663113279853e-08</v>
+        <v>4.57890625318958e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.799024190028641e-08</v>
+        <v>4.708406886201931e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.741683232365147e-08</v>
+        <v>4.624029708718236e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.497864107661846e-08</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.807290481313987e-08</v>
+        <v>3.706675267014583e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.84169955152865e-08</v>
+        <v>3.720086294053998e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.845232106703005e-08</v>
+        <v>2.760157328627687e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.673037828461557e-08</v>
+        <v>4.565448135666504e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.684254145490671e-08</v>
+        <v>4.57543402739681e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.65859765414184e-08</v>
+        <v>4.551393927481381e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.974202468654971e-08</v>
+        <v>3.887173362208809e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.248203933058813e-08</v>
+        <v>4.146810208049767e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.719803592447475e-08</v>
+        <v>4.610216879847808e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.19373323401522e-08</v>
+        <v>3.107511122535831e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.556233302020113e-08</v>
+        <v>6.456794210515113e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.123212469443355e-08</v>
+        <v>3.035191552369346e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.699938895233729e-08</v>
+        <v>4.582933151633863e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.583638345133548e-08</v>
+        <v>6.747730424079996e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,85 +8942,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.496604071255936e-08</v>
+        <v>2.389618095214516e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.98444524575137e-08</v>
+        <v>2.864461640074104e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.016214601273966e-08</v>
+        <v>2.895380246793303e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.872727015678432e-08</v>
+        <v>2.755298532658427e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.85587332962938e-08</v>
+        <v>1.767075589607594e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.474336645782945e-08</v>
+        <v>3.201082296749122e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.998167374106342e-08</v>
+        <v>2.877404440384214e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.007349446789899e-08</v>
+        <v>2.884606882808822e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.163367751041121e-08</v>
+        <v>2.999883444668101e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.024665708731039e-08</v>
+        <v>2.903862866274734e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.13705876596115e-08</v>
+        <v>3.033363499287083e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.079717808297665e-08</v>
+        <v>2.94898632180341e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.015516816250442e-08</v>
+        <v>3.398822181042189e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.162656993142925e-08</v>
+        <v>3.033587393327219e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.311734550009472e-08</v>
+        <v>3.159676603376157e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.004086749559831e-08</v>
+        <v>2.882806392394653e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.011072404394067e-08</v>
+        <v>2.890404748751661e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.022288721423185e-08</v>
+        <v>2.900390640481963e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.996632230074349e-08</v>
+        <v>2.876350540566535e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.054987696784526e-08</v>
+        <v>2.945457645399968e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.565858083318147e-08</v>
+        <v>3.430408957565152e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.057539098827112e-08</v>
+        <v>2.934878222088663e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.213115410044616e-08</v>
+        <v>3.09245928471929e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.38121745543181e-08</v>
+        <v>3.287938026743488e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.716761778399194e-08</v>
+        <v>2.604181116514683e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.037973471166236e-08</v>
+        <v>2.907889764719019e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.332067962705485e-08</v>
+        <v>3.503272838027894e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -798,7 +798,7 @@
         <v>1.675733834123674e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>8.31920555158959e-09</v>
       </c>
       <c r="O4" t="n">
         <v>9.492752089491204e-09</v>
@@ -974,7 +974,7 @@
         <v>2.281206982860578e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>1.125656862988707e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.24301183971107e-08</v>
@@ -1062,7 +1062,7 @@
         <v>2.406159667157388e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>1.562346388192676e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.679653039892844e-08</v>
@@ -1150,7 +1150,7 @@
         <v>6.076578706877909e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>3.886800215735484e-08</v>
       </c>
       <c r="O8" t="n">
         <v>4.374037796785079e-08</v>
@@ -1238,7 +1238,7 @@
         <v>4.563634020287798e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>3.719820741323084e-08</v>
       </c>
       <c r="O9" t="n">
         <v>4.049411903846936e-08</v>
@@ -1658,7 +1658,7 @@
         <v>7.650534813393276e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>7.405024144311598e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.256954737772854e-09</v>
@@ -1834,7 +1834,7 @@
         <v>1.007748853269006e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>9.836143907915557e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.212771806625636e-08</v>
@@ -1852,7 +1852,7 @@
         <v>1.238004107674491e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>9.808141881198949e-09</v>
+        <v>9.808141881198947e-09</v>
       </c>
       <c r="U6" t="n">
         <v>1.270873743169448e-08</v>
@@ -1922,7 +1922,7 @@
         <v>1.39321064710324e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>1.368659580195073e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.353811045717938e-08</v>
@@ -2010,7 +2010,7 @@
         <v>4.559885243338294e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>3.374979119029944e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.679047823461344e-08</v>
@@ -2098,7 +2098,7 @@
         <v>2.739304856036509e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>2.714753789128342e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.845850158666728e-08</v>
@@ -2518,7 +2518,7 @@
         <v>1.604472291150549e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>8.186260199354629e-09</v>
       </c>
       <c r="O4" t="n">
         <v>9.149695473826556e-09</v>
@@ -2694,7 +2694,7 @@
         <v>2.165528394139584e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>1.089145179111365e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.18547217409935e-08</v>
@@ -2782,7 +2782,7 @@
         <v>2.288410862117901e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>1.502564590902817e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.598863470783531e-08</v>
@@ -2870,7 +2870,7 @@
         <v>5.723869389733817e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>3.677921833307219e-08</v>
       </c>
       <c r="O8" t="n">
         <v>4.120552135330396e-08</v>
@@ -2958,7 +2958,7 @@
         <v>4.101025258728492e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>3.315178987513409e-08</v>
       </c>
       <c r="O9" t="n">
         <v>3.595400149580489e-08</v>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.200825001805864e-08</v>
+        <v>1.200825001805887e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.024256840721428e-08</v>
+        <v>1.024256840721447e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.198981828295091e-08</v>
+        <v>1.198981828295096e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183524683557787e-08</v>
+        <v>1.183524683557809e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.185249425025777e-08</v>
+        <v>1.185249425025795e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.215013689107299e-08</v>
+        <v>1.215013689107325e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.179102796092937e-08</v>
+        <v>1.179102796092953e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.187815724695612e-08</v>
+        <v>1.187815724695635e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.206243034609608e-08</v>
+        <v>1.206243034609629e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.190202010149274e-08</v>
+        <v>1.190202010149286e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.222703673953905e-08</v>
+        <v>1.222703673953925e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.243087829117748e-08</v>
+        <v>1.243087829117757e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.182363094677188e-08</v>
+        <v>1.182363094677184e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.573923474663776e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204713299399118e-08</v>
+        <v>1.204713299399125e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.185180741583577e-08</v>
+        <v>1.185180741583594e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.179043105743728e-08</v>
+        <v>1.179043105743746e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205363860561448e-08</v>
+        <v>1.205363860561473e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.184263429953694e-08</v>
+        <v>1.184263429953699e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.210383904541563e-08</v>
+        <v>1.210383904541575e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.189685744436718e-08</v>
+        <v>1.189685744436742e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.20104222360788e-08</v>
+        <v>1.201042223607883e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.210920898499043e-08</v>
+        <v>1.210920898499081e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.222076776491932e-08</v>
+        <v>1.222076776491943e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.151354497640631e-08</v>
+        <v>1.151354497640667e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.188158795141885e-08</v>
+        <v>1.188158795141911e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.284690012958392e-08</v>
+        <v>1.2846900129584e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3254,82 +3254,82 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363915638273298e-08</v>
+        <v>1.363915638273296e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.447419575219333e-09</v>
+        <v>9.447419575219331e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.351982016626432e-08</v>
+        <v>1.351982016626428e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.238890666540753e-08</v>
+        <v>1.238890666540751e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.253854729502955e-08</v>
+        <v>1.253854729502952e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.464800678773028e-08</v>
+        <v>1.464800678773027e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.209936780838894e-08</v>
+        <v>1.209936780838893e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.272185154790219e-08</v>
+        <v>1.272185154790217e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.403038412573704e-08</v>
+        <v>1.4030384125737e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.288940967368554e-08</v>
+        <v>1.28894096736855e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.520560473955875e-08</v>
+        <v>1.520560473955873e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.672785631082853e-08</v>
+        <v>1.672785631082852e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.232934579509985e-08</v>
+        <v>1.232934579509982e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.917978648826997e-08</v>
+        <v>1.917978648826999e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.391456990772766e-08</v>
+        <v>1.391456990772764e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.253082809858333e-08</v>
+        <v>1.253082809858331e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.209396981249265e-08</v>
+        <v>1.209396981249264e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.396298824023166e-08</v>
+        <v>1.396298824023164e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.24669662308348e-08</v>
+        <v>1.246696623083476e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.506681526739682e-08</v>
+        <v>1.506681526739686e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.284737980587742e-08</v>
+        <v>1.284737980587737e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.308796945419425e-08</v>
+        <v>1.308796945419421e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.437190464327741e-08</v>
+        <v>1.43719046432774e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5162935883283e-08</v>
+        <v>1.516293588328303e-08</v>
       </c>
       <c r="Z3" t="n">
         <v>1.238129017431289e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.27424007784887e-08</v>
+        <v>1.274240077848868e-08</v>
       </c>
       <c r="AB3" t="n">
         <v>1.961956346493402e-08</v>
@@ -3342,85 +3342,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.014435917867496e-08</v>
+        <v>1.014435917867495e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.506045709498645e-09</v>
+        <v>7.506045709498635e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.936164251614035e-09</v>
+        <v>9.936164251614032e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.190208647158473e-09</v>
+        <v>8.190208647158475e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.385026130170591e-09</v>
+        <v>8.385026130170566e-09</v>
       </c>
       <c r="G4" t="n">
         <v>1.174703668055867e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.690736116315988e-09</v>
+        <v>7.690736116315982e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.67490148344061e-09</v>
+        <v>8.674901483440594e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.074606944949117e-08</v>
+        <v>1.074606944949115e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.94444340288574e-09</v>
+        <v>8.944443402885738e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.261565584466022e-08</v>
+        <v>1.261565584466019e-08</v>
       </c>
       <c r="M4" t="n">
         <v>1.500345460983163e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>8.059001839519166e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.867555374669926e-09</v>
+        <v>8.867555374669909e-09</v>
       </c>
       <c r="P4" t="n">
         <v>1.058356027888393e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.377268019414346e-09</v>
+        <v>8.377268019414338e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.683993816783611e-09</v>
+        <v>7.683993816783588e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.065704415489997e-08</v>
+        <v>1.065704415489996e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.273653450975939e-09</v>
+        <v>8.273653450975932e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.271942566794539e-08</v>
+        <v>1.271942566794543e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.832690877408519e-09</v>
+        <v>8.832690877408509e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.987869278929664e-09</v>
+        <v>8.987869278929654e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.128473715359058e-08</v>
+        <v>1.128473715359057e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.25100671174363e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.235168123413599e-09</v>
+        <v>9.235168123413586e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.713652868549407e-09</v>
+        <v>8.713652868549387e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.950717503320114e-08</v>
+        <v>1.950717503320111e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.094813373978445e-08</v>
+        <v>7.094813373978428e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.959534868339294e-08</v>
+        <v>2.959534868339295e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.3594420524252e-08</v>
+        <v>7.359442052425195e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.834426803809838e-08</v>
+        <v>2.834426803809834e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.554619586745804e-08</v>
+        <v>4.554619586745801e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.732317589348254e-08</v>
+        <v>9.732317589348232e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.301181584733114e-08</v>
+        <v>3.301181584733122e-08</v>
       </c>
       <c r="I5" t="n">
         <v>5.074886669489173e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.411469706549081e-08</v>
+        <v>8.41146970654907e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.408987300180282e-08</v>
+        <v>5.408987300180269e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.172257353559268e-07</v>
+        <v>1.172257353559264e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.70377453566421e-07</v>
+        <v>1.703774535664204e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>3.812021875520146e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.946370492984709e-08</v>
+        <v>4.94637049298471e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.762982082258628e-08</v>
+        <v>7.762982082258629e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.394902539169067e-08</v>
+        <v>4.394902539169054e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.230289695639456e-08</v>
+        <v>3.230289695639452e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.995945422537947e-08</v>
+        <v>7.995945422537928e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.29492803134802e-08</v>
+        <v>4.294928031348018e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.172583620680241e-07</v>
+        <v>1.172583620680263e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>5.031871036616475e-08</v>
+        <v>5.031871036616493e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.409595545904361e-08</v>
+        <v>5.409595545904329e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>9.743946458712621e-08</v>
+        <v>9.743946458712639e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.170476729642258e-07</v>
+        <v>1.170476729642257e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.504490100546147e-08</v>
+        <v>5.504490100546127e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.939457967731392e-08</v>
+        <v>4.939457967731375e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.649185272091996e-07</v>
+        <v>2.64918527209199e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,85 +3518,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.537617042666942e-08</v>
+        <v>1.537617042666941e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.001855804259564e-08</v>
+        <v>1.001855804259563e-08</v>
       </c>
       <c r="D6" t="n">
         <v>1.516797549960848e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.342201989515292e-08</v>
+        <v>1.342201989515293e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.089753846326758e-08</v>
+        <v>1.089753846326757e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.425954901365565e-08</v>
+        <v>1.425954901365567e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.020324844941299e-08</v>
+        <v>1.020324844941298e-08</v>
       </c>
       <c r="I6" t="n">
         <v>1.11874138165376e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.597788069748562e-08</v>
+        <v>1.597788069748559e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.417625465088022e-08</v>
+        <v>1.417625465088019e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.784746709265467e-08</v>
+        <v>1.784746709265465e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.751596694292864e-08</v>
+        <v>1.751596694292861e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>1.058164117090719e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.411522790706966e-08</v>
+        <v>1.411522790706963e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.583139800366503e-08</v>
+        <v>1.583139800366501e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.360907926740881e-08</v>
+        <v>1.36090792674088e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.01965061498806e-08</v>
+        <v>1.019650614988059e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.588885540289442e-08</v>
+        <v>1.588885540289441e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.078616578407295e-08</v>
+        <v>1.078616578407292e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.526671577606461e-08</v>
+        <v>1.526671577606469e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.406450212540298e-08</v>
+        <v>1.406450212540296e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.423549123122324e-08</v>
+        <v>1.423549123122321e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.379724948668758e-08</v>
+        <v>1.379724948668759e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.519331356557972e-08</v>
+        <v>1.519331356557973e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.446697937140804e-08</v>
+        <v>1.446697937140803e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.394546411654384e-08</v>
+        <v>1.394546411654385e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.208306552519518e-08</v>
+        <v>2.208306552519517e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,10 +3606,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.656977125581746e-08</v>
+        <v>1.656977125581744e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.393145778664116e-08</v>
+        <v>1.393145778664114e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.636157632875654e-08</v>
@@ -3621,67 +3621,67 @@
         <v>1.481043820731307e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.817244875770122e-08</v>
+        <v>1.817244875770118e-08</v>
       </c>
       <c r="H7" t="n">
         <v>1.41161481934585e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.510031356058312e-08</v>
+        <v>1.51003135605831e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.717148152663366e-08</v>
+        <v>1.717148152663364e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.536985548002824e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.904106792180272e-08</v>
+        <v>1.90410679218027e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.142886668697414e-08</v>
+        <v>2.142886668697413e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>1.448441391666167e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.529254973459268e-08</v>
+        <v>1.529254973459267e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.700855463880671e-08</v>
+        <v>1.700855463880669e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.480268009655686e-08</v>
+        <v>1.480268009655684e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.410940589392611e-08</v>
+        <v>1.41094058939261e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.708245623204248e-08</v>
+        <v>1.708245623204247e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.469906552811845e-08</v>
+        <v>1.469906552811844e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.917887832340058e-08</v>
+        <v>1.917887832340074e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.525810295455103e-08</v>
+        <v>1.525810295455102e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.541328135607216e-08</v>
+        <v>1.541328135607214e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.771014923073309e-08</v>
+        <v>1.771014923073307e-08</v>
       </c>
       <c r="Y7" t="n">
         <v>1.897025696960102e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.566058020055612e-08</v>
+        <v>1.566058020055609e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.513906494569191e-08</v>
+        <v>1.51390649456919e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>2.593258711034368e-08</v>
@@ -3697,82 +3697,82 @@
         <v>3.343521350472652e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.599249870240794e-08</v>
+        <v>4.599249870240796e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.842261724452334e-08</v>
+        <v>4.842261724452332e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.858545359164062e-08</v>
+        <v>3.858545359164058e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.404317713404737e-08</v>
+        <v>3.404317713404738e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.338439604732228e-08</v>
+        <v>5.338439604732226e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.617718910922529e-08</v>
+        <v>4.617718910922534e-08</v>
       </c>
       <c r="I8" t="n">
         <v>4.71613544763499e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.923252244240047e-08</v>
+        <v>4.923252244240045e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.743089639579504e-08</v>
+        <v>4.743089639579503e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.110210883756952e-08</v>
+        <v>5.110210883756954e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.348990760274132e-08</v>
+        <v>5.34899076027413e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>3.476632369788132e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.881188474643176e-08</v>
+        <v>3.881188474643183e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.973442089192113e-08</v>
+        <v>3.973442089192109e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.868184038422191e-08</v>
+        <v>2.868184038422192e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.617044680969289e-08</v>
+        <v>4.617044680969288e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.914349714780925e-08</v>
+        <v>4.914349714780928e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.676010644388527e-08</v>
+        <v>4.676010644388524e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.382363995249539e-08</v>
+        <v>4.382363995249532e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.316568455088886e-08</v>
+        <v>4.316568455088892e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.747730864454611e-08</v>
+        <v>4.747730864454612e-08</v>
       </c>
       <c r="X8" t="n">
         <v>3.298201633166414e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.613951221391073e-08</v>
+        <v>6.61395122139107e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.224375640259738e-08</v>
+        <v>3.224375640259739e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.720010586145875e-08</v>
+        <v>4.720010586145872e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.386670147097997e-08</v>
+        <v>7.386670147097989e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,85 +3782,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.721453000837692e-08</v>
+        <v>2.721453000837689e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.946979270155139e-08</v>
+        <v>2.94697927015514e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.189991124366683e-08</v>
+        <v>3.18999112436668e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.902453869142528e-08</v>
+        <v>2.902453869142524e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.906774368688869e-08</v>
+        <v>1.906774368688868e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.3710784283569e-08</v>
+        <v>3.371078428356895e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.965448310836876e-08</v>
+        <v>2.965448310836872e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.063864847549339e-08</v>
+        <v>3.063864847549337e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.270981644154392e-08</v>
+        <v>3.27098164415439e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.090819039493853e-08</v>
+        <v>3.090819039493848e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.457940283671301e-08</v>
+        <v>3.457940283671295e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.696720160188445e-08</v>
+        <v>3.696720160188438e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.812021875520142e-08</v>
+        <v>3.002274883157196e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.245302791276354e-08</v>
+        <v>3.245302791276358e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.452173016624357e-08</v>
+        <v>3.452173016624359e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.034101562242464e-08</v>
+        <v>3.034101562242462e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.964774080883636e-08</v>
+        <v>2.964774080883631e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.262079114695275e-08</v>
+        <v>3.262079114695272e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.02374004430287e-08</v>
+        <v>3.023740044302871e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.471795043502041e-08</v>
+        <v>3.471795043502054e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.644351541880995e-08</v>
+        <v>3.644351541880991e-08</v>
       </c>
       <c r="W9" t="n">
         <v>3.095161627098244e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.324848414564336e-08</v>
+        <v>3.324848414564335e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.450859188451132e-08</v>
+        <v>3.450859188451129e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.824852408594428e-08</v>
+        <v>2.824852408594426e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.067739986060215e-08</v>
+        <v>3.067739986060217e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.147092202525398e-08</v>
+        <v>4.14709220252539e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,82 +4026,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.199563586921688e-08</v>
+        <v>1.199563586921686e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.027110172678946e-08</v>
+        <v>1.027110172678947e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.196863855200409e-08</v>
+        <v>1.196863855200411e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183674444224597e-08</v>
+        <v>1.183674444224599e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.189277856585598e-08</v>
+        <v>1.189277856585599e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.212731634521484e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.181894399229586e-08</v>
+        <v>1.181894399229588e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.190102461201903e-08</v>
+        <v>1.190102461201904e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.206357142694364e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.194613077154587e-08</v>
+        <v>1.194613077154588e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.216957062051296e-08</v>
+        <v>1.216957062051298e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.234646677195877e-08</v>
+        <v>1.234646677195875e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.18352274570794e-08</v>
+        <v>1.183522745707941e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.5707739277267e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204697861659762e-08</v>
+        <v>1.204697861659763e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.188275750172841e-08</v>
+        <v>1.188275750172842e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.183714321252329e-08</v>
+        <v>1.183714321252328e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205454323066635e-08</v>
+        <v>1.205454323066637e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.188065695156172e-08</v>
+        <v>1.188065695156173e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.217517741405798e-08</v>
+        <v>1.217517741405795e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.201217435493644e-08</v>
+        <v>1.201217435493646e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.208838183292688e-08</v>
+        <v>1.208838183292689e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.21678175284356e-08</v>
+        <v>1.216781752843562e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.250396072776024e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.154580000128323e-08</v>
+        <v>1.154580000128322e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.192026751470033e-08</v>
+        <v>1.192026751470035e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.27685203768961e-08</v>
@@ -4114,49 +4114,49 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.34124897992263e-08</v>
+        <v>1.341248979922629e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.507316253180152e-09</v>
+        <v>9.507316253180143e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.323045781851146e-08</v>
+        <v>1.32304578185114e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.226474021078345e-08</v>
+        <v>1.226474021078342e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.269011778242713e-08</v>
+        <v>1.26901177824271e-08</v>
       </c>
       <c r="G3" t="n">
         <v>1.434755315713458e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.21627259008239e-08</v>
+        <v>1.216272590082388e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.274894230991513e-08</v>
+        <v>1.274894230991508e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.390091335638301e-08</v>
+        <v>1.3900913356383e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.306761323893e-08</v>
+        <v>1.306761323892997e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.465549800274322e-08</v>
+        <v>1.465549800274321e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.59844001542688e-08</v>
+        <v>1.598440015426878e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.227604310382457e-08</v>
+        <v>1.227604310382453e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.88832621077119e-08</v>
+        <v>1.888326210771187e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.377599622288602e-08</v>
+        <v>1.3775996222886e-08</v>
       </c>
       <c r="Q3" t="n">
         <v>1.261525540371997e-08</v>
@@ -4165,34 +4165,34 @@
         <v>1.229214330265141e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.383297816970376e-08</v>
+        <v>1.383297816970377e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.260269096000548e-08</v>
+        <v>1.26026909600055e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.520390009041469e-08</v>
+        <v>1.52039000904147e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352987558566009e-08</v>
+        <v>1.352987558566014e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.326674525342325e-08</v>
+        <v>1.326674525342327e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.465063600068217e-08</v>
+        <v>1.465063600068214e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705267299883117e-08</v>
+        <v>1.705267299883107e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.237116489951259e-08</v>
+        <v>1.237116489951255e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.288261019340279e-08</v>
+        <v>1.288261019340275e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.892133627857158e-08</v>
+        <v>1.892133627857156e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.829700901428129e-09</v>
+        <v>9.829700901428145e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.640222531237019e-09</v>
+        <v>7.640222531237024e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.524753784130146e-09</v>
+        <v>9.524753784130145e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.03494914012417e-09</v>
+        <v>8.034949140124183e-09</v>
       </c>
       <c r="F4" t="n">
         <v>8.667880343269548e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.131709245383674e-08</v>
+        <v>1.131709245383668e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.833884869325946e-09</v>
+        <v>7.833884869325955e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.761023228049717e-09</v>
+        <v>8.761023228049718e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.058763225869896e-08</v>
+        <v>1.058763225869892e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.270518049764025e-09</v>
+        <v>9.270518049764022e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.179437393125605e-08</v>
+        <v>1.179437393125606e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.388877978839953e-08</v>
+        <v>1.388877978839951e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>8.017814094819927e-09</v>
       </c>
       <c r="O4" t="n">
         <v>8.467997982322334e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.040964085192422e-08</v>
+        <v>1.040964085192421e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.554687814031295e-09</v>
+        <v>8.554687814031289e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.039453433849707e-09</v>
+        <v>8.03945343384971e-09</v>
       </c>
       <c r="S4" t="n">
         <v>1.049508664772502e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.530961133597719e-09</v>
+        <v>8.53096113359772e-09</v>
       </c>
       <c r="U4" t="n">
         <v>1.289826222512668e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.968824914268307e-09</v>
+        <v>9.968824914268298e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.19860851426613e-09</v>
+        <v>9.198608514266139e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.177457194977999e-08</v>
+        <v>1.177457194977996e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.555716600072708e-08</v>
+        <v>1.555716600072709e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.215199139318819e-09</v>
+        <v>9.215199139318828e-09</v>
       </c>
       <c r="AA4" t="n">
         <v>8.97838066600763e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.846278405943991e-08</v>
+        <v>1.846278405943992e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4290,85 +4290,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.341512229210371e-08</v>
+        <v>6.341512229210378e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.042270222857083e-08</v>
+        <v>3.042270222857075e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.354031694097923e-08</v>
+        <v>6.354031694097854e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.45549096852783e-08</v>
+        <v>2.455490968527829e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.894294785913378e-08</v>
+        <v>4.894294785913342e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.72622061358344e-08</v>
+        <v>8.726220613583336e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.396908495784152e-08</v>
+        <v>3.39690849578415e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.057586720185809e-08</v>
+        <v>5.057586720185799e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.882477978732852e-08</v>
+        <v>7.882477978732803e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.790083103727855e-08</v>
+        <v>5.790083103727839e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.900686848048308e-08</v>
+        <v>9.900686848048306e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.433430311188778e-07</v>
+        <v>1.433430311188777e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>3.572000053915793e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.174851038037549e-08</v>
+        <v>4.174851038037492e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.215426934161182e-08</v>
+        <v>7.215426934161084e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.520928039612584e-08</v>
+        <v>4.520928039612577e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.736064411184846e-08</v>
+        <v>3.736064411184836e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.521652377281523e-08</v>
+        <v>7.521652377281512e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.604751520502847e-08</v>
+        <v>4.604751520502848e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.157192804354306e-07</v>
+        <v>1.157192804354305e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>6.633452097336513e-08</v>
+        <v>6.633452097336526e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.62393326495441e-08</v>
+        <v>5.623933264954412e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.026210065344772e-07</v>
+        <v>1.026210065344765e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.713124802793947e-07</v>
+        <v>1.713124802793936e-07</v>
       </c>
       <c r="Z5" t="n">
         <v>5.238281442699082e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.251847744302997e-08</v>
+        <v>5.251847744302988e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.396508982675625e-07</v>
+        <v>2.396508982675621e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,10 +4378,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.237089902539107e-08</v>
+        <v>1.237089902539106e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.018142065519993e-08</v>
+        <v>1.018142065519994e-08</v>
       </c>
       <c r="D6" t="n">
         <v>1.476914033495292e-08</v>
@@ -4393,70 +4393,70 @@
         <v>1.120907846723247e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.38582905777997e-08</v>
+        <v>1.385829057779959e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.30782714201487e-08</v>
+        <v>1.307827142014874e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.130222135201263e-08</v>
+        <v>1.130222135201264e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.583201880952173e-08</v>
+        <v>1.58320188095217e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.451490460058682e-08</v>
+        <v>1.451490460058681e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4335572055219e-08</v>
+        <v>1.433557205521899e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.642997791236244e-08</v>
+        <v>1.642997791236243e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>1.05737988312578e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.102392825376451e-08</v>
+        <v>1.102392825376458e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.567206406948863e-08</v>
+        <v>1.567206406948862e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.379907436485406e-08</v>
+        <v>1.379907436485407e-08</v>
       </c>
       <c r="R6" t="n">
         <v>1.328383998467249e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.303628477168797e-08</v>
+        <v>1.303628477168793e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.377534768442052e-08</v>
+        <v>1.37753476844205e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.815694679488564e-08</v>
+        <v>1.815694679488566e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.251002303823125e-08</v>
+        <v>1.25100230382312e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.189722248401862e-08</v>
+        <v>1.189722248401863e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.43157700737429e-08</v>
+        <v>1.431577007374286e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.825883013470514e-08</v>
+        <v>1.825883013470511e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>1.175639726328175e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.422276721683042e-08</v>
+        <v>1.422276721683041e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.106238013675109e-08</v>
+        <v>2.106238013675111e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.629194126860596e-08</v>
+        <v>1.629194126860595e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.410246289841485e-08</v>
+        <v>1.410246289841484e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.598699415130798e-08</v>
+        <v>1.598699415130796e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.449718950730198e-08</v>
+        <v>1.449718950730199e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.513012071044738e-08</v>
+        <v>1.513012071044736e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.777933282101457e-08</v>
+        <v>1.77793328210145e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.429612523650379e-08</v>
+        <v>1.429612523650376e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.522326359522753e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.70498726258768e-08</v>
+        <v>1.704987262587673e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.573275841694186e-08</v>
+        <v>1.573275841694184e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.825661429843387e-08</v>
+        <v>1.825661429843385e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.035102015557735e-08</v>
+        <v>2.035102015557733e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>1.448005446199775e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.492981848184015e-08</v>
+        <v>1.492981848184014e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.687146135144204e-08</v>
+        <v>1.687146135144201e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.501692818120913e-08</v>
+        <v>1.501692818120911e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.450169380102755e-08</v>
+        <v>1.450169380102751e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.695732701490285e-08</v>
+        <v>1.695732701490282e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.499320150077555e-08</v>
+        <v>1.499320150077554e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.937586433393019e-08</v>
+        <v>1.937586433393016e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.643106528144614e-08</v>
+        <v>1.643106528144611e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.566084888144397e-08</v>
+        <v>1.566084888144396e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.823681231695781e-08</v>
+        <v>1.823681231695775e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.203370438684109e-08</v>
+        <v>2.203370438684096e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.567743950649664e-08</v>
+        <v>1.567743950649663e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.544062103318546e-08</v>
+        <v>1.544062103318545e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.492502442661776e-08</v>
+        <v>2.492502442661775e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.315004107686943e-08</v>
+        <v>3.315004107686938e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.618285064826624e-08</v>
+        <v>4.618285064826618e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.806738190115941e-08</v>
+        <v>4.806738190115938e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.847215795721822e-08</v>
+        <v>3.847215795721819e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.435967507361343e-08</v>
+        <v>3.435967507361336e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.301616113969887e-08</v>
+        <v>5.301616113969869e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.637651298635521e-08</v>
+        <v>4.637651298635511e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.7303651345079e-08</v>
+        <v>4.730365134507894e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.913026037572825e-08</v>
+        <v>4.913026037572813e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.781314616679333e-08</v>
+        <v>4.781314616679325e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.033700204828535e-08</v>
+        <v>5.033700204828524e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.243140790542949e-08</v>
+        <v>5.243140790542939e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>3.47606224243646e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.845349924672528e-08</v>
+        <v>3.84534992467252e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.960027972342444e-08</v>
+        <v>3.960027972342439e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.88835009765934e-08</v>
+        <v>2.888350097659337e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.6582081550879e-08</v>
+        <v>4.658208155087889e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.903771476475431e-08</v>
+        <v>4.903771476475424e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.707358925062702e-08</v>
+        <v>4.707358925062692e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.402654253378965e-08</v>
+        <v>4.402654253378955e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.435224035011294e-08</v>
+        <v>4.435224035011287e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.774422824919945e-08</v>
+        <v>4.774422824919937e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.349853805066346e-08</v>
+        <v>3.349853805066334e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.92512334370141e-08</v>
+        <v>6.925123343701379e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.225277750091246e-08</v>
+        <v>3.225277750091243e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.752100878303693e-08</v>
+        <v>4.752100878303685e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.290636480050669e-08</v>
+        <v>7.290636480050653e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.608247536209565e-08</v>
+        <v>2.60824753620956e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.856398008273312e-08</v>
+        <v>2.856398008273306e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.04485113356263e-08</v>
+        <v>3.044851133562627e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.788066339095142e-08</v>
+        <v>2.788066339095136e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.882374611487605e-08</v>
+        <v>1.882374611487602e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.224085071268906e-08</v>
+        <v>3.224085071268904e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.875764242082204e-08</v>
+        <v>2.875764242082203e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.968478077954583e-08</v>
+        <v>2.968478077954578e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.151138981019508e-08</v>
+        <v>3.151138981019499e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.019427560126016e-08</v>
+        <v>3.019427560126009e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.271813148275218e-08</v>
+        <v>3.271813148275211e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.481253733989566e-08</v>
+        <v>3.481253733989558e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.572000053915798e-08</v>
+        <v>2.894157164631601e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.093971415576284e-08</v>
+        <v>3.093971415576276e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.321801131330187e-08</v>
+        <v>3.321801131330183e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.947844607288369e-08</v>
+        <v>2.947844607288366e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.896321098534579e-08</v>
+        <v>2.896321098534575e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.141884419922113e-08</v>
+        <v>3.141884419922111e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.945471868509381e-08</v>
+        <v>2.945471868509382e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.383631779555896e-08</v>
+        <v>3.383631779555894e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.628279292364542e-08</v>
+        <v>3.628279292364536e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.012236606576226e-08</v>
+        <v>3.012236606576224e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.269832950127611e-08</v>
+        <v>3.269832950127601e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.649522157115936e-08</v>
+        <v>3.649522157115939e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.732276952795143e-08</v>
+        <v>2.73227695279514e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.990213821750376e-08</v>
+        <v>2.99021382175037e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.938654161093604e-08</v>
+        <v>3.938654161093603e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5098,7 +5098,7 @@
         <v>9.872590568035475e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>7.512148712037126e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.385754969108375e-09</v>
@@ -5274,7 +5274,7 @@
         <v>1.513866506322847e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>1.015290516965277e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.266904748197766e-08</v>
@@ -5362,7 +5362,7 @@
         <v>1.653094132062109e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>1.417049946462273e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.404366012687072e-08</v>
@@ -5450,7 +5450,7 @@
         <v>5.046300140568994e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>3.570137195563397e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.898293224251566e-08</v>
@@ -5538,7 +5538,7 @@
         <v>3.351114253846332e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>3.115070068246494e-08</v>
       </c>
       <c r="O9" t="n">
         <v>3.276351123926414e-08</v>
@@ -5891,7 +5891,7 @@
         <v>1.165164985974384e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.140644567234576e-08</v>
+        <v>1.140644567234577e-08</v>
       </c>
       <c r="V3" t="n">
         <v>1.181394391760403e-08</v>
@@ -5958,7 +5958,7 @@
         <v>7.412261742261944e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>7.502605821696959e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.483307365920803e-09</v>
@@ -6107,7 +6107,7 @@
         <v>9.824428816075385e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.640790208997903e-09</v>
+        <v>9.640790208997905e-09</v>
       </c>
       <c r="F6" t="n">
         <v>1.214250641832255e-08</v>
@@ -6134,7 +6134,7 @@
         <v>1.226121431543723e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>9.941571840648406e-09</v>
       </c>
       <c r="O6" t="n">
         <v>1.234792732617022e-08</v>
@@ -6222,7 +6222,7 @@
         <v>1.364311165166748e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>1.373345573110251e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.371374148949626e-08</v>
@@ -6310,7 +6310,7 @@
         <v>4.523458975462663e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>3.376529593983473e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.692268634921149e-08</v>
@@ -6337,7 +6337,7 @@
         <v>4.119537471893942e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.564546757274207e-08</v>
+        <v>4.564546757274206e-08</v>
       </c>
       <c r="X8" t="n">
         <v>3.034122174912407e-08</v>
@@ -6398,7 +6398,7 @@
         <v>2.804490706714982e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>2.813525114658483e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.963746998602038e-08</v>
@@ -6818,7 +6818,7 @@
         <v>7.526575655112833e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.173270529966528e-08</v>
+        <v>7.432330977688594e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.560187720667435e-09</v>
@@ -6906,7 +6906,7 @@
         <v>3.551024345152284e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>3.173270529966528e-08</v>
       </c>
       <c r="O5" t="n">
         <v>3.314066176272287e-08</v>
@@ -6994,7 +6994,7 @@
         <v>1.239837137921808e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>9.867063077064906e-09</v>
       </c>
       <c r="O6" t="n">
         <v>9.994869466103749e-09</v>
@@ -7082,7 +7082,7 @@
         <v>1.379990829613055e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>1.370566361870631e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.383310431892506e-08</v>
@@ -7170,7 +7170,7 @@
         <v>4.544678865689977e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>3.375764101204525e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.707187776848681e-08</v>
@@ -7258,7 +7258,7 @@
         <v>2.728016791326632e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>2.718592323584211e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.877356484472778e-08</v>
@@ -7678,7 +7678,7 @@
         <v>1.571369464450889e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>8.138854370340337e-09</v>
       </c>
       <c r="O4" t="n">
         <v>8.22015401827609e-09</v>
@@ -7854,7 +7854,7 @@
         <v>1.8384753151069e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>1.081805312911642e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.378351612209462e-08</v>
@@ -7942,7 +7942,7 @@
         <v>2.250303886134831e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>1.492819858717977e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.500905212588541e-08</v>
@@ -8030,7 +8030,7 @@
         <v>5.675190471011977e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>3.662686572193296e-08</v>
       </c>
       <c r="O8" t="n">
         <v>4.015706894926511e-08</v>
@@ -8118,7 +8118,7 @@
         <v>4.046327394309484e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>3.288843366892628e-08</v>
       </c>
       <c r="O9" t="n">
         <v>3.479207494256601e-08</v>
@@ -8538,7 +8538,7 @@
         <v>8.16321813448244e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>7.62807042097332e-09</v>
       </c>
       <c r="O4" t="n">
         <v>7.435505048282283e-09</v>
@@ -8714,7 +8714,7 @@
         <v>1.059224009009288e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>1.006127790294228e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.247255280927768e-08</v>
@@ -8802,7 +8802,7 @@
         <v>1.446225388575387e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>1.392710617224476e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.373412480277861e-08</v>
@@ -8890,7 +8890,7 @@
         <v>4.624029708718236e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>3.405880015201632e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.706675267014583e-08</v>
@@ -8978,7 +8978,7 @@
         <v>2.94898632180341e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>2.895471550452492e-08</v>
       </c>
       <c r="O9" t="n">
         <v>3.033587393327219e-08</v>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.213865291037201e-08</v>
+        <v>1.213865291037203e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.025308702849028e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.188454034573308e-08</v>
+        <v>1.188454034573307e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.187299594628184e-08</v>
+        <v>1.187299594628182e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.185131203875431e-08</v>
+        <v>1.185131203875434e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.219613403884771e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.184068895291671e-08</v>
+        <v>1.184068895291672e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.183362529011217e-08</v>
+        <v>1.183362529011215e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.208287922756938e-08</v>
+        <v>1.208287922756941e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.186953817672822e-08</v>
+        <v>1.186953817672823e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23031245224255e-08</v>
+        <v>1.230312452242547e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.259351219136386e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.185262907761087e-08</v>
+        <v>1.185262907761089e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.581343175363934e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.200823482323903e-08</v>
+        <v>1.200823482323902e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.186785267238396e-08</v>
+        <v>1.186785267238392e-08</v>
       </c>
       <c r="R2" t="n">
         <v>1.182117453065315e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.208451858537173e-08</v>
+        <v>1.208451858537175e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.185187494012945e-08</v>
+        <v>1.185187494012946e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.231928390110743e-08</v>
+        <v>1.231928390110745e-08</v>
       </c>
       <c r="V2" t="n">
         <v>1.19251896305271e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.200665471067468e-08</v>
+        <v>1.200665471067466e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.200732940840246e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.204580064465203e-08</v>
+        <v>1.204580064465202e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.155164040929262e-08</v>
+        <v>1.15516404092926e-08</v>
       </c>
       <c r="AA2" t="n">
         <v>1.193985004639763e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.297684091735405e-08</v>
+        <v>1.297684091735404e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.447874293198165e-08</v>
+        <v>1.458361862255704e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.472153586682455e-09</v>
+        <v>9.490588217682871e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.26792635693619e-08</v>
+        <v>1.272114892133549e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.257115513522187e-08</v>
+        <v>1.260630999877185e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.244321819219725e-08</v>
+        <v>1.24767977721638e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.489123555606786e-08</v>
+        <v>1.501054587363084e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.236819779952835e-08</v>
+        <v>1.239911258332818e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.231538545733659e-08</v>
+        <v>1.234438356960832e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.408915821864344e-08</v>
+        <v>1.418050338862713e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.257133980786608e-08</v>
+        <v>1.260937096392817e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.566213823898984e-08</v>
+        <v>1.58090170102556e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.779770161651943e-08</v>
+        <v>1.802201159977072e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.244930630533407e-08</v>
+        <v>1.248297341584655e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.95499655233988e-08</v>
+        <v>1.960924668768151e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.355202600546948e-08</v>
+        <v>1.362416388621078e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.255869264131637e-08</v>
+        <v>1.259626091143695e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.222681891796653e-08</v>
+        <v>1.225268950718151e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.409752729780076e-08</v>
+        <v>1.418913061080305e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.244565916774316e-08</v>
+        <v>1.247926674637962e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.665168517499226e-08</v>
+        <v>1.684269079036678e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.29626284487921e-08</v>
+        <v>1.301421774864631e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.316885977047194e-08</v>
+        <v>1.322385636664947e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.355698497525673e-08</v>
+        <v>1.362998709903322e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.382787028058435e-08</v>
+        <v>1.391025362530873e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.257739639720191e-08</v>
+        <v>1.26395530520524e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.307131642852322e-08</v>
+        <v>1.312691503253008e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.045413022508703e-08</v>
+        <v>2.077064319895112e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.154997632009052e-08</v>
+        <v>1.154997632009053e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.637153295395883e-09</v>
+        <v>7.637153295395901e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.679658004938345e-09</v>
+        <v>8.679658004938319e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.549258702450244e-09</v>
+        <v>8.549258702450267e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.304328991837084e-09</v>
+        <v>8.304328991837097e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.219925210884874e-08</v>
+        <v>1.219925210884876e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.18433635044028e-09</v>
+        <v>8.184336350440295e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.104549029617305e-09</v>
+        <v>8.104549029617318e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.090962630829707e-08</v>
+        <v>1.090962630829709e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.510201604689821e-09</v>
+        <v>8.510201604689837e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.340775883891377e-08</v>
+        <v>1.34077588389138e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.675733834123674e-08</v>
+        <v>1.675733834123672e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.31920555158959e-09</v>
+        <v>8.319205551589615e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>9.492752089491204e-09</v>
+        <v>9.492752089491153e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.007684403063902e-08</v>
+        <v>1.0076844030639e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.491163057750626e-09</v>
+        <v>8.491163057750632e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.963911973895554e-09</v>
+        <v>7.963911973895574e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.093850421619243e-08</v>
+        <v>1.093850421619244e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.31068722181647e-09</v>
+        <v>8.310687221816479e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.53550621483701e-08</v>
+        <v>1.535506214837006e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.084846658521196e-09</v>
+        <v>9.084846658521227e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.279222638217893e-09</v>
+        <v>9.279222638217891e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.006661695354843e-08</v>
+        <v>1.006661695354846e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.045919710961838e-08</v>
+        <v>1.045919710961835e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.617272090290721e-09</v>
+        <v>9.617272090290739e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.304406517663903e-09</v>
+        <v>9.304406517663926e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.089226990867005e-08</v>
+        <v>2.089226990867009e-08</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.044267412487091e-07</v>
+        <v>1.044267412487084e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>3.288416047604671e-08</v>
+        <v>3.288416047604672e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.502564677895101e-08</v>
+        <v>5.502564677894987e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.711569738866994e-08</v>
+        <v>3.711569738866993e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.812509830034597e-08</v>
+        <v>4.812509830034587e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.188372299508601e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>4.61824610727156e-08</v>
+        <v>4.618246107271523e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.315009182699524e-08</v>
+        <v>4.315009182699526e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.676676854868964e-08</v>
+        <v>9.676676854868959e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.110645637896072e-08</v>
+        <v>5.110645637896058e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47516434288176e-07</v>
+        <v>1.475164342881759e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.299961227913915e-07</v>
+        <v>2.299961227913905e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.645639674541524e-08</v>
+        <v>4.645639674541518e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>6.570335064605461e-08</v>
+        <v>6.570335064605387e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.718803059222063e-08</v>
+        <v>7.718803059222039e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.035596801741584e-08</v>
+        <v>5.035596801741581e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.049338728589628e-08</v>
+        <v>4.049338728589624e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>9.517018991446336e-08</v>
+        <v>9.517018991446367e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.731615916549348e-08</v>
+        <v>4.731615916549346e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.844339919233378e-07</v>
+        <v>1.844339919233376e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>6.020551430599571e-08</v>
+        <v>6.020551430599573e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>6.520180227248396e-08</v>
+        <v>6.520180227248386e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.377012388165912e-08</v>
+        <v>8.37701238816587e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>9.033036304513735e-08</v>
+        <v>9.033036304513718e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>6.929057875678671e-08</v>
+        <v>6.929057875678666e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>6.600482779799028e-08</v>
+        <v>6.60048277979904e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.290201742866335e-07</v>
+        <v>3.29020174286634e-07</v>
       </c>
     </row>
     <row r="6">
@@ -938,22 +938,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.447391998926052e-08</v>
+        <v>1.447391998926053e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.369188478276489e-08</v>
+        <v>1.369188478276491e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.473438949230735e-08</v>
+        <v>1.473438949230736e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.460399018981925e-08</v>
+        <v>1.460399018981927e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.122827266100711e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.825398359621776e-08</v>
+        <v>1.825398359621778e-08</v>
       </c>
       <c r="H6" t="n">
         <v>1.423906783780932e-08</v>
@@ -962,58 +962,58 @@
         <v>1.102849269878732e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38335699774671e-08</v>
+        <v>1.383356997746709e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.456493309205883e-08</v>
+        <v>1.456493309205885e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.946249032628281e-08</v>
+        <v>1.946249032628283e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.281206982860578e-08</v>
+        <v>2.281206982860571e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.125656862988707e-08</v>
+        <v>1.125656862988703e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.24301183971107e-08</v>
+        <v>1.243011839711068e-08</v>
       </c>
       <c r="P6" t="n">
         <v>1.614335125790314e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.454589454511965e-08</v>
+        <v>1.454589454511966e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.401864346126457e-08</v>
+        <v>1.401864346126458e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.386244788536244e-08</v>
+        <v>1.386244788536243e-08</v>
       </c>
       <c r="T6" t="n">
         <v>1.123463089098648e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.832097597255214e-08</v>
+        <v>1.832097597255213e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.513957814589022e-08</v>
+        <v>1.513957814589025e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.534572743442472e-08</v>
+        <v>1.534572743442473e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.612134844091746e-08</v>
+        <v>1.612134844091747e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.358313730903426e-08</v>
+        <v>1.358313730903429e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>1.254121575946075e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.535913800503292e-08</v>
+        <v>1.535913800503293e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>2.389556454695249e-08</v>
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.885423465042767e-08</v>
+        <v>1.885423465042765e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.494141162573302e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.598391633527553e-08</v>
+        <v>1.598391633527543e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.58535170327874e-08</v>
+        <v>1.585351703278738e-08</v>
       </c>
       <c r="F7" t="n">
         <v>1.560858732217424e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.950351043918591e-08</v>
+        <v>1.95035104391859e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.548859468077743e-08</v>
+        <v>1.548859468077742e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.540880735995446e-08</v>
+        <v>1.540880735995445e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.821388463863422e-08</v>
+        <v>1.821388463863421e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.581445993502698e-08</v>
+        <v>1.581445993502696e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.071201716925094e-08</v>
+        <v>2.071201716925092e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.406159667157388e-08</v>
+        <v>2.406159667157383e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.562346388192676e-08</v>
+        <v>1.562346388192675e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.679653039892844e-08</v>
+        <v>1.679653039892834e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.738062234007622e-08</v>
+        <v>1.738062234007616e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.579542138808779e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.526817030423272e-08</v>
+        <v>1.526817030423268e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.824276254652959e-08</v>
+        <v>1.824276254652957e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.561494555215363e-08</v>
+        <v>1.561494555215361e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.270004766575629e-08</v>
+        <v>2.270004766575633e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.638910498885835e-08</v>
+        <v>1.638910498885836e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.658348096855504e-08</v>
+        <v>1.658348096855503e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.737087528388561e-08</v>
+        <v>1.73708752838856e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.780542559496757e-08</v>
+        <v>1.780542559496754e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.692153042062789e-08</v>
+        <v>1.692153042062787e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>1.660866484800106e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.81965282390072e-08</v>
+        <v>2.819652823900718e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1114,85 +1114,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.819488019003748e-08</v>
+        <v>3.819488019003753e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>5.164560202293805e-08</v>
+        <v>5.164560202293817e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.268810673248049e-08</v>
+        <v>5.268810673248063e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.331213198533714e-08</v>
+        <v>4.331213198533723e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.765427021884337e-08</v>
+        <v>3.765427021884343e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.980814497577374e-08</v>
+        <v>5.980814497577388e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.219278507798243e-08</v>
+        <v>5.219278507798257e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>5.21129977571595e-08</v>
+        <v>5.211299775715965e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.491807503583931e-08</v>
+        <v>5.491807503583947e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.251865033223196e-08</v>
+        <v>5.251865033223213e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.741620756645593e-08</v>
+        <v>5.741620756645605e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>6.076578706877909e-08</v>
+        <v>6.076578706877918e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.886800215735484e-08</v>
+        <v>3.886800215735496e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.374037796785079e-08</v>
+        <v>4.374037796785078e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.341779747789603e-08</v>
+        <v>4.341779747789609e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.172373405892045e-08</v>
+        <v>3.17237340589205e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>5.19723607014377e-08</v>
+        <v>5.197236070143785e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.494695294373462e-08</v>
+        <v>5.49469529437347e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>5.231913594935862e-08</v>
+        <v>5.231913594935871e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>5.092997527082238e-08</v>
+        <v>5.092997527082253e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.834692461913759e-08</v>
+        <v>4.834692461913779e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.329108380236302e-08</v>
+        <v>5.329108380236311e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.489059134435565e-08</v>
+        <v>3.489059134435568e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>7.177278194214744e-08</v>
+        <v>7.177278194214766e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.593963919981977e-08</v>
+        <v>3.593963919981983e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>5.331285524520606e-08</v>
+        <v>5.331285524520623e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>8.303839315834566e-08</v>
+        <v>8.303839315834577e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1202,31 +1202,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.402471437820303e-08</v>
+        <v>3.402471437820306e-08</v>
       </c>
       <c r="C9" t="n">
         <v>3.651615515703712e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.755865986657955e-08</v>
+        <v>3.755865986657956e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.595018285987866e-08</v>
+        <v>3.595018285987867e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.241975445720662e-08</v>
+        <v>2.241975445720663e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.10782543073647e-08</v>
+        <v>4.107825430736465e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.706333821208153e-08</v>
+        <v>3.706333821208156e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.698355089125852e-08</v>
+        <v>3.698355089125855e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.978862816993836e-08</v>
+        <v>3.978862816993837e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.738920346633108e-08</v>
@@ -1235,31 +1235,31 @@
         <v>4.228676070055507e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.563634020287798e-08</v>
+        <v>4.563634020287795e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.719820741323084e-08</v>
+        <v>3.719820741323087e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>4.049411903846936e-08</v>
+        <v>4.049411903846932e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>4.153978889919543e-08</v>
+        <v>4.153978889919544e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.737016525626658e-08</v>
+        <v>3.737016525626656e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.68429138355368e-08</v>
+        <v>3.684291383553683e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.98175060778337e-08</v>
+        <v>3.981750607783371e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.718968908345773e-08</v>
+        <v>3.718968908345772e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>4.427603416502338e-08</v>
+        <v>4.427603416502335e-08</v>
       </c>
       <c r="V9" t="n">
         <v>4.535422585572641e-08</v>
@@ -1271,16 +1271,16 @@
         <v>3.894561881518968e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.938016912627163e-08</v>
+        <v>3.938016912627164e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.463507250153074e-08</v>
+        <v>3.463507250153073e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.818340837930518e-08</v>
+        <v>3.818340837930517e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.977127177031128e-08</v>
+        <v>4.977127177031132e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.134762365869344e-08</v>
+        <v>1.134762365869355e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.828775943552308e-09</v>
+        <v>9.828775943552318e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.136979469707403e-08</v>
+        <v>1.136979469707401e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.133862939251848e-08</v>
+        <v>1.133862939251857e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.135051244107919e-08</v>
+        <v>1.135051244107918e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.139449799014903e-08</v>
+        <v>1.139449799014909e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.136812993694069e-08</v>
+        <v>1.136812993694066e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.136775044338862e-08</v>
+        <v>1.136775044338861e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.138110433251288e-08</v>
+        <v>1.138110433251285e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.137416663440046e-08</v>
+        <v>1.137416663440037e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.13726498932548e-08</v>
+        <v>1.137264989325477e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.137174279354704e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.136197552008248e-08</v>
+        <v>1.136197552008245e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.501377936816859e-08</v>
+        <v>1.50137793681686e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.135882106154829e-08</v>
+        <v>1.135882106154826e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.135704423371346e-08</v>
+        <v>1.135704423371341e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.137034897720795e-08</v>
+        <v>1.137034897720792e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.137306233379068e-08</v>
+        <v>1.137306233379077e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.135986529328681e-08</v>
+        <v>1.135986529328693e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.124191740573238e-08</v>
+        <v>1.124191740573246e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.138102069092448e-08</v>
+        <v>1.138102069092446e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.151381354246876e-08</v>
+        <v>1.151381354246882e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.156694874729175e-08</v>
+        <v>1.156694874729189e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.155213011398589e-08</v>
+        <v>1.155213011398587e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.08902829289131e-08</v>
+        <v>1.089028292891321e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.141157853357003e-08</v>
+        <v>1.141157853357002e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.137864578109885e-08</v>
+        <v>1.137864578109889e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.165707786572558e-08</v>
+        <v>1.167479420913465e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.123522028671046e-09</v>
+        <v>9.140341512518168e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.181908479070447e-08</v>
+        <v>1.184260533980532e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.157377334456472e-08</v>
+        <v>1.158580692644227e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.168140940765457e-08</v>
+        <v>1.170009265036584e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.199120760756652e-08</v>
+        <v>1.202065660671049e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.18085762826402e-08</v>
+        <v>1.183178672833414e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.180430500442473e-08</v>
+        <v>1.182733722087819e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.189712597057274e-08</v>
+        <v>1.192329852074483e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.185130240279711e-08</v>
+        <v>1.187590770653059e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.183770697337409e-08</v>
+        <v>1.186179032604796e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.190764167956329e-08</v>
+        <v>1.193477403475136e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.176075919350984e-08</v>
+        <v>1.178223125331675e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.771652001884816e-08</v>
+        <v>1.773453465078147e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.173658340566555e-08</v>
+        <v>1.17570719132269e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.172640424721806e-08</v>
+        <v>1.174665196209295e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.182306544279231e-08</v>
+        <v>1.184679434082881e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.183846636296469e-08</v>
+        <v>1.18625972229048e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.17471382900955e-08</v>
+        <v>1.176814657801784e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.178440098361863e-08</v>
+        <v>1.181588498467974e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.18958529573129e-08</v>
+        <v>1.192196268823544e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.237266695217827e-08</v>
+        <v>1.241071455508853e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.322306808529053e-08</v>
+        <v>1.329658910595301e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31186924086249e-08</v>
+        <v>1.318814018537209e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.095838415243407e-08</v>
+        <v>1.097865989733722e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.211437392664704e-08</v>
+        <v>1.214831993972749e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.189648929740171e-08</v>
+        <v>1.192277806370569e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.242913267740088e-09</v>
+        <v>7.24291326774017e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.195796851402907e-09</v>
+        <v>7.195796851402979e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.493345345430244e-09</v>
+        <v>7.493345345430323e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.141318893727053e-09</v>
+        <v>7.14131889372713e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.275543393692579e-09</v>
+        <v>7.275543393692664e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.77238040478881e-09</v>
+        <v>7.772380404788873e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.474541113896801e-09</v>
+        <v>7.474541113896873e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.470254559650477e-09</v>
+        <v>7.470254559650552e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.611975575708714e-09</v>
+        <v>7.611975575708755e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.54272838872226e-09</v>
+        <v>7.54272838872233e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.525596099747335e-09</v>
+        <v>7.525596099747415e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.650534813393276e-09</v>
+        <v>7.650534813393354e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.405024144311598e-09</v>
+        <v>7.405024144311689e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.256954737772854e-09</v>
+        <v>7.256954737772936e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.369393084045398e-09</v>
+        <v>7.369393084045472e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.34932299626973e-09</v>
+        <v>7.349322996269804e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.499606194524471e-09</v>
+        <v>7.49960619452455e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.530254805331889e-09</v>
+        <v>7.53025480533197e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.381188161902139e-09</v>
+        <v>7.381188161902215e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.848145974461317e-09</v>
+        <v>7.848145974461322e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.574564515908215e-09</v>
+        <v>7.57456451590829e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.15014675637763e-09</v>
+        <v>8.150146756377716e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.72029103798375e-09</v>
+        <v>9.72029103798382e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.542102572065399e-09</v>
+        <v>9.542102572065411e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.357850773989662e-09</v>
+        <v>7.357850773989739e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.965313000167178e-09</v>
+        <v>7.965313000167275e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.616312679362867e-09</v>
+        <v>7.616312679362943e-09</v>
       </c>
     </row>
     <row r="5">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.770988159522123e-08</v>
+        <v>2.770988159522125e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.894732433433881e-08</v>
+        <v>2.894732433433894e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.409347295360887e-08</v>
+        <v>3.409347295360895e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.600870994792588e-08</v>
+        <v>1.600870994792596e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.02117675657291e-08</v>
+        <v>3.021176756572918e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.685947458925857e-08</v>
+        <v>3.685947458925985e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.447239498849876e-08</v>
+        <v>3.44723949884988e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.358669151694466e-08</v>
+        <v>3.358669151694471e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.495688173991382e-08</v>
+        <v>3.495688173991421e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.549282809956268e-08</v>
+        <v>3.54928280995627e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.375414002930823e-08</v>
+        <v>3.375414002930828e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.74978833495586e-08</v>
+        <v>3.749788334955863e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>3.122557469609033e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>2.845616345653516e-08</v>
+        <v>2.84561634565352e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.973395643077938e-08</v>
+        <v>2.973395643077939e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.067565988914386e-08</v>
+        <v>3.067565988914392e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.421702061522113e-08</v>
+        <v>3.421702061522119e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.270462069851467e-08</v>
+        <v>3.270462069851473e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.155018276657897e-08</v>
+        <v>3.1550182766579e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.89397558351438e-08</v>
+        <v>3.893975583514387e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.455335514672666e-08</v>
+        <v>3.455335514672664e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.406982322154632e-08</v>
+        <v>4.406982322154625e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>7.186641741551289e-08</v>
+        <v>7.186641741551301e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.962404487899692e-08</v>
+        <v>6.962404487899714e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.995215196572592e-08</v>
+        <v>2.995215196572598e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.092561328125654e-08</v>
+        <v>4.092561328125675e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.717151784110141e-08</v>
+        <v>3.717151784110154e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1798,85 +1798,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9.669866987036873e-09</v>
+        <v>9.669866987036902e-09</v>
       </c>
       <c r="C6" t="n">
-        <v>1.204558312281591e-08</v>
+        <v>1.204558312281594e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>9.920299064727045e-09</v>
+        <v>9.920299064727052e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>1.199110516514004e-08</v>
+        <v>1.199110516514008e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.21253296651056e-08</v>
+        <v>1.212532966510562e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.019933412408563e-08</v>
+        <v>1.01993341240856e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.901494833193593e-09</v>
+        <v>9.901494833193603e-09</v>
       </c>
       <c r="I6" t="n">
-        <v>9.897208278947287e-09</v>
+        <v>9.897208278947293e-09</v>
       </c>
       <c r="J6" t="n">
-        <v>1.246176184712172e-08</v>
+        <v>1.246176184712176e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.969682108019032e-09</v>
+        <v>9.969682108019068e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.237538237116035e-08</v>
+        <v>1.237538237116039e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.007748853269006e-08</v>
+        <v>1.007748853269008e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>9.836143907915557e-09</v>
+        <v>9.836143907915567e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.212771806625636e-08</v>
+        <v>1.212771806625643e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.639447542100945e-09</v>
+        <v>9.639447542100959e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.776276715566525e-09</v>
+        <v>9.776276715566538e-09</v>
       </c>
       <c r="R6" t="n">
-        <v>9.926559913821277e-09</v>
+        <v>9.926559913821285e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.238004107674491e-08</v>
+        <v>1.238004107674492e-08</v>
       </c>
       <c r="T6" t="n">
         <v>9.808141881198947e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.270873743169448e-08</v>
+        <v>1.270873743169449e-08</v>
       </c>
       <c r="V6" t="n">
         <v>1.000151823520503e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.072516255751564e-08</v>
+        <v>1.072516255751562e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.457007730939677e-08</v>
+        <v>1.457007730939678e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.21090072087665e-08</v>
+        <v>1.210900720876652e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.784804493286477e-09</v>
+        <v>9.784804493286472e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.28150992715802e-08</v>
+        <v>1.281509927158022e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.004664365339435e-08</v>
+        <v>1.004664365339437e-08</v>
       </c>
     </row>
     <row r="7">
@@ -1886,85 +1886,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.352448492537922e-08</v>
+        <v>1.352448492537924e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.347736850904203e-08</v>
+        <v>1.347736850904206e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.377491700306937e-08</v>
+        <v>1.377491700306941e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.342289055136618e-08</v>
+        <v>1.342289055136621e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.355711505133172e-08</v>
+        <v>1.355711505133174e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.405395206242794e-08</v>
+        <v>1.405395206242796e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.375611277153593e-08</v>
+        <v>1.375611277153596e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.375182621728961e-08</v>
+        <v>1.375182621728964e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.389354723334782e-08</v>
+        <v>1.389354723334785e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.382430004636139e-08</v>
+        <v>1.38243000463614e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.380716775738646e-08</v>
+        <v>1.380716775738648e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.39321064710324e-08</v>
+        <v>1.393210647103244e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.368659580195073e-08</v>
+        <v>1.368659580195077e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.353811045717938e-08</v>
+        <v>1.353811045717939e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.365054880345191e-08</v>
+        <v>1.365054880345195e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.363089465390885e-08</v>
+        <v>1.363089465390888e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.378117785216359e-08</v>
+        <v>1.378117785216363e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.381182646297103e-08</v>
+        <v>1.381182646297105e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.366275981954125e-08</v>
+        <v>1.366275981954128e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.414119625975311e-08</v>
+        <v>1.414119625975313e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.385613617354736e-08</v>
+        <v>1.385613617354738e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.443171841401675e-08</v>
+        <v>1.443171841401677e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.600186269562289e-08</v>
+        <v>1.60018626956229e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.583447941552467e-08</v>
+        <v>1.583447941552469e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.363942243162878e-08</v>
+        <v>1.363942243162882e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.424688465780631e-08</v>
+        <v>1.424688465780636e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.389788433700199e-08</v>
+        <v>1.389788433700201e-08</v>
       </c>
     </row>
     <row r="8">
@@ -1974,85 +1974,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.02221388876981e-08</v>
+        <v>3.022213888769823e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.514411447139273e-08</v>
+        <v>4.514411447139288e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.544166296542006e-08</v>
+        <v>4.544166296542028e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.711903658383298e-08</v>
+        <v>3.711903658383321e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.258677860003048e-08</v>
+        <v>3.258677860003062e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.882463676571561e-08</v>
+        <v>4.882463676571576e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.542285873388654e-08</v>
+        <v>4.542285873388679e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.541857217964024e-08</v>
+        <v>4.541857217964049e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.556029319569851e-08</v>
+        <v>4.55602931956987e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.549104600871205e-08</v>
+        <v>4.549104600871228e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.547391371973712e-08</v>
+        <v>4.547391371973737e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.559885243338294e-08</v>
+        <v>4.559885243338313e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.374979119029944e-08</v>
+        <v>3.374979119029958e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.679047823461344e-08</v>
+        <v>3.679047823461358e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.612127532349661e-08</v>
+        <v>3.61212753234968e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.738678038476017e-08</v>
+        <v>2.738678038476026e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.544792381451423e-08</v>
+        <v>4.54479238145145e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.547857242532168e-08</v>
+        <v>4.547857242532199e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.532950578189192e-08</v>
+        <v>4.532950578189206e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.850189900942185e-08</v>
+        <v>3.850189900942203e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.14325347621233e-08</v>
+        <v>4.143253476212352e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.610140623408482e-08</v>
+        <v>4.610140623408506e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.112969545368754e-08</v>
+        <v>3.112969545368767e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.238609708938824e-08</v>
+        <v>6.238609708938851e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.005901782469922e-08</v>
+        <v>3.005901782469936e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.591363062015695e-08</v>
+        <v>4.591363062015722e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.120109859059668e-08</v>
+        <v>6.1201098590597e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2062,85 +2062,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.258278115982264e-08</v>
+        <v>2.258278115982269e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.693831059837476e-08</v>
+        <v>2.693831059837478e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.723585909240205e-08</v>
+        <v>2.723585909240209e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.586772110849263e-08</v>
+        <v>2.586772110849267e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.686875485854566e-08</v>
+        <v>1.68687548585457e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.751489567676149e-08</v>
+        <v>2.751489567676151e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.721705486086861e-08</v>
+        <v>2.721705486086867e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.721276830662229e-08</v>
+        <v>2.721276830662235e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.735448932268053e-08</v>
+        <v>2.735448932268057e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.728524213569408e-08</v>
+        <v>2.728524213569412e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.726810984671916e-08</v>
+        <v>2.726810984671921e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.739304856036509e-08</v>
+        <v>2.739304856036516e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.714753789128342e-08</v>
+        <v>2.714753789128347e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.845850158666728e-08</v>
+        <v>2.845850158666729e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.888825426815359e-08</v>
+        <v>2.888825426815361e-08</v>
       </c>
       <c r="Q9" t="n">
         <v>2.709183826824243e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.724211994149629e-08</v>
+        <v>2.724211994149633e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.727276855230374e-08</v>
+        <v>2.727276855230377e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.712370190887396e-08</v>
+        <v>2.712370190887401e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.76014649072533e-08</v>
+        <v>2.760146490725335e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.239763564882838e-08</v>
+        <v>3.239763564882841e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.789266050334947e-08</v>
+        <v>2.789266050334952e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.946280478495559e-08</v>
+        <v>2.946280478495564e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.929542150485735e-08</v>
+        <v>2.929542150485742e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.44459611745689e-08</v>
+        <v>2.444596117456894e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.770782674713901e-08</v>
+        <v>2.770782674713907e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.735882642633467e-08</v>
+        <v>2.735882642633474e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.203346931499849e-08</v>
+        <v>1.20334693149985e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.020238665030071e-08</v>
+        <v>1.020238665030072e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.192210603746629e-08</v>
+        <v>1.192210603746622e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.181456428875206e-08</v>
+        <v>1.181456428875198e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.179781392370274e-08</v>
+        <v>1.179781392370267e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.214371165378669e-08</v>
+        <v>1.214371165378664e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.176341002612214e-08</v>
+        <v>1.176341002612207e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.177312139330814e-08</v>
+        <v>1.177312139330808e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.204161889796917e-08</v>
+        <v>1.20416188979691e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.181583177373166e-08</v>
+        <v>1.181583177373172e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.225733564115019e-08</v>
+        <v>1.225733564115025e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.249587348173704e-08</v>
+        <v>1.249587348173707e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.18066066630663e-08</v>
+        <v>1.180660666306623e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.572702033415185e-08</v>
+        <v>1.572702033415189e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.201907951416343e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.181640103162666e-08</v>
+        <v>1.181640103162668e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.176734484146557e-08</v>
+        <v>1.176734484146551e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.204340987798239e-08</v>
+        <v>1.204340987798238e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.180964025493743e-08</v>
+        <v>1.180964025493736e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.219476483951507e-08</v>
+        <v>1.219476483951509e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.182276677862165e-08</v>
+        <v>1.182276677862162e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.193529609496812e-08</v>
+        <v>1.193529609496813e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.198970410693886e-08</v>
+        <v>1.198970410693879e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.197640786662189e-08</v>
+        <v>1.197640786662182e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.145469409999425e-08</v>
+        <v>1.14546940999943e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.185049277404947e-08</v>
+        <v>1.18504927740494e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.289908621850389e-08</v>
+        <v>1.2899086218504e-08</v>
       </c>
     </row>
     <row r="3">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.400344458558989e-08</v>
+        <v>1.409270548486942e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.373839155411704e-09</v>
+        <v>9.389726030131578e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.322330528411681e-08</v>
+        <v>1.328558302447175e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.24283475102951e-08</v>
+        <v>1.245955271567691e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.233509696544626e-08</v>
+        <v>1.236593151997354e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.479036065854287e-08</v>
+        <v>1.490724662785509e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.208963113260472e-08</v>
+        <v>1.211171610371706e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.215729395190015e-08</v>
+        <v>1.218177256622686e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.406903391950091e-08</v>
+        <v>1.416081819087825e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.246263866880831e-08</v>
+        <v>1.24978884730713e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.560953080085905e-08</v>
+        <v>1.575564100426448e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.737389533347156e-08</v>
+        <v>1.758428726509397e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.239499515438124e-08</v>
+        <v>1.242783140142684e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.932753339338332e-08</v>
+        <v>1.938134662608139e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.390222297820657e-08</v>
+        <v>1.398772957293745e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.246547973554087e-08</v>
+        <v>1.250084078598665e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.211647932288831e-08</v>
+        <v>1.213952282747078e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.407737233708759e-08</v>
+        <v>1.416938294138875e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.241850144937985e-08</v>
+        <v>1.245223717819991e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.608918946979916e-08</v>
+        <v>1.626201313115143e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.250758012880965e-08</v>
+        <v>1.254421981087124e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.297509749878226e-08</v>
+        <v>1.302478114119699e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.370537756075101e-08</v>
+        <v>1.3784750700688e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.360612947704957e-08</v>
+        <v>1.368178370119249e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.228066212255002e-08</v>
+        <v>1.233475526114724e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.270750551330621e-08</v>
+        <v>1.275134462846546e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.017341293696489e-08</v>
+        <v>2.048107411208357e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2482,85 +2482,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.074877821490463e-08</v>
+        <v>1.074877821490466e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.427846901221639e-09</v>
+        <v>7.427846901221651e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.490878765539755e-09</v>
+        <v>9.490878765539876e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.27614524216401e-09</v>
+        <v>8.276145242164005e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.086942163383318e-09</v>
+        <v>8.086942163383333e-09</v>
       </c>
       <c r="G4" t="n">
         <v>1.199401614549869e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.698334313635566e-09</v>
+        <v>7.698334313635571e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.808028673451086e-09</v>
+        <v>7.808028673451089e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.083016251127838e-08</v>
+        <v>1.083016251127842e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.290462068080586e-09</v>
+        <v>8.290462068080594e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.327745135238583e-08</v>
+        <v>1.327745135238611e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.604472291150549e-08</v>
+        <v>1.604472291150552e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.186260199354629e-09</v>
+        <v>8.186260199354642e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>9.149695473826556e-09</v>
+        <v>9.14969547382651e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.058623879483725e-08</v>
+        <v>1.058623879483724e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.296892097875913e-09</v>
+        <v>8.296892097875964e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.742779863044101e-09</v>
+        <v>7.742779863044121e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.086106144669259e-08</v>
+        <v>1.086106144669256e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.220526015060258e-09</v>
+        <v>8.220526015060276e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.443623944405177e-08</v>
+        <v>1.443623944405175e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.312742994362277e-09</v>
+        <v>8.312742994362296e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.945290696902717e-09</v>
+        <v>8.945290696902733e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.025443005688072e-08</v>
+        <v>1.025443005688087e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.005631419638889e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.157615158546408e-09</v>
+        <v>9.157615158546401e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.681974011517901e-09</v>
+        <v>8.681974011517916e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.040276683672851e-08</v>
+        <v>2.040276683672853e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2570,85 +2570,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.578911900862369e-08</v>
+        <v>8.578911900862971e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.960898381515028e-08</v>
+        <v>2.960898381515034e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.016138410497566e-08</v>
+        <v>7.016138410497672e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.193975748368136e-08</v>
+        <v>3.193975748368202e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.298781852538606e-08</v>
+        <v>4.29878185253862e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.093956946945469e-07</v>
+        <v>1.093956946945462e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.568260366576135e-08</v>
+        <v>3.568260366576138e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.684032628435434e-08</v>
+        <v>3.684032628435481e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.164861214208046e-08</v>
+        <v>9.16486121420815e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.625055286099937e-08</v>
+        <v>4.625055286099939e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.382399426209144e-07</v>
+        <v>1.382399426209218e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>2.029724422783494e-07</v>
+        <v>2.029724422783488e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.327732681729049e-08</v>
+        <v>4.32773268172907e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>5.772507386104593e-08</v>
+        <v>5.77250738610452e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>8.353845427998986e-08</v>
+        <v>8.353845427998981e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.569264932108299e-08</v>
+        <v>4.569264932108357e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.58362485345205e-08</v>
+        <v>3.583624853452054e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>8.957030417169407e-08</v>
+        <v>8.957030417169271e-08</v>
       </c>
       <c r="T5" t="n">
         <v>4.495710568888196e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.582100642454846e-07</v>
+        <v>1.582100642454848e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.514290681932904e-08</v>
+        <v>4.514290681932903e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.7075569934782e-08</v>
+        <v>5.707556993478232e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.438802698939681e-08</v>
+        <v>8.438802698939854e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.912784259192337e-08</v>
+        <v>7.912784259192413e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.873051941759031e-08</v>
+        <v>5.873051941759223e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.225703494636975e-08</v>
+        <v>5.225703494637019e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.012199460760816e-07</v>
+        <v>3.012199460760809e-07</v>
       </c>
     </row>
     <row r="6">
@@ -2658,85 +2658,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.344360673046945e-08</v>
+        <v>1.344360673046961e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.303840793111201e-08</v>
+        <v>1.303840793111204e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.218570728110461e-08</v>
+        <v>1.218570728110469e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.388670627205439e-08</v>
+        <v>1.388670627205444e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.078177067894817e-08</v>
+        <v>1.078177067894819e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.760457717538904e-08</v>
+        <v>1.760457717538909e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.330889534352594e-08</v>
+        <v>1.330889534352599e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.341858970334145e-08</v>
+        <v>1.341858970334147e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.644072354116875e-08</v>
+        <v>1.64407235411688e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.098529058364543e-08</v>
+        <v>1.098529058364545e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.888801238227621e-08</v>
+        <v>1.888801238227615e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.165528394139584e-08</v>
+        <v>2.165528394139587e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.089145179111365e-08</v>
+        <v>1.089145179111361e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.18547217409935e-08</v>
+        <v>1.185472174099342e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.621073004936331e-08</v>
+        <v>1.621073004936336e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.099172061344076e-08</v>
+        <v>1.099172061344082e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.335334089293449e-08</v>
+        <v>1.335334089293451e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.355588996225744e-08</v>
+        <v>1.355588996225745e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.091535453062511e-08</v>
+        <v>1.091535453062515e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.717899666915553e-08</v>
+        <v>1.717899666915563e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.100757150992712e-08</v>
+        <v>1.100757150992715e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.180261543653765e-08</v>
+        <v>1.180261543653766e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.586499108677111e-08</v>
+        <v>1.586499108677114e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.2941610273693e-08</v>
+        <v>1.294161027369288e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.185244367411127e-08</v>
+        <v>1.185244367411131e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.429253504140828e-08</v>
+        <v>1.429253504140831e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.31704960969773e-08</v>
+        <v>2.317049609697731e-08</v>
       </c>
     </row>
     <row r="7">
@@ -2746,85 +2746,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.758816392457814e-08</v>
+        <v>1.758816392457818e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.426723261089517e-08</v>
+        <v>1.426723261089521e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.63302644752133e-08</v>
+        <v>1.633026447521333e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.511553095183754e-08</v>
+        <v>1.511553095183761e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.492632787305685e-08</v>
+        <v>1.492632787305688e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.88334018551722e-08</v>
+        <v>1.883340185517222e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.453772002330911e-08</v>
+        <v>1.453772002330914e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.464741438312462e-08</v>
+        <v>1.464741438312464e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.766954822095191e-08</v>
+        <v>1.766954822095196e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.512984777775412e-08</v>
+        <v>1.512984777775413e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.011683706205939e-08</v>
+        <v>2.011683706205929e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.288410862117901e-08</v>
+        <v>2.288410862117902e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.502564590902817e-08</v>
+        <v>1.50256459090282e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.598863470783531e-08</v>
+        <v>1.598863470783529e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.742517802884596e-08</v>
+        <v>1.742517802884609e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.513627780754945e-08</v>
+        <v>1.51362778075495e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.458216557271764e-08</v>
+        <v>1.458216557271766e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.770044715636613e-08</v>
+        <v>1.770044715636619e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.50599117247338e-08</v>
+        <v>1.505991172473382e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>2.132192940549541e-08</v>
+        <v>2.132192940549547e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.515212870403581e-08</v>
+        <v>1.515212870403586e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.578467640657625e-08</v>
+        <v>1.578467640657626e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.709381576655426e-08</v>
+        <v>1.709381576655439e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.694362861560136e-08</v>
+        <v>1.694362861560134e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.599700086821994e-08</v>
+        <v>1.599700086821995e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.552135972119143e-08</v>
+        <v>1.552135972119147e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.724215254640205e-08</v>
+        <v>2.724215254640209e-08</v>
       </c>
     </row>
     <row r="8">
@@ -2834,85 +2834,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.568688687018099e-08</v>
+        <v>3.56868868701812e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.862181788705412e-08</v>
+        <v>4.86218178870542e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.068484975137224e-08</v>
+        <v>5.068484975137229e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.081434905443505e-08</v>
+        <v>4.081434905443518e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.555752418374617e-08</v>
+        <v>3.555752418374627e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.655874608284177e-08</v>
+        <v>5.655874608284188e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.889230529946806e-08</v>
+        <v>4.889230529946816e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.900199965928358e-08</v>
+        <v>4.900199965928363e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.202413349711085e-08</v>
+        <v>5.202413349711109e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.94844330539131e-08</v>
+        <v>4.948443305391325e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.447142233821834e-08</v>
+        <v>5.447142233821849e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.723869389733817e-08</v>
+        <v>5.723869389733842e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.677921833307219e-08</v>
+        <v>3.677921833307227e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.120552135330396e-08</v>
+        <v>4.120552135330406e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.179323211507965e-08</v>
+        <v>4.17932321150797e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.004035278260594e-08</v>
+        <v>3.0040352782606e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.893675084887664e-08</v>
+        <v>4.89367508488767e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>5.205503243252506e-08</v>
+        <v>5.205503243252523e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.941449700089278e-08</v>
+        <v>4.941449700089292e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.774295679462546e-08</v>
+        <v>4.774295679462564e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.506273478795982e-08</v>
+        <v>4.506273478795994e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>5.014245642780949e-08</v>
+        <v>5.014245642780966e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.34877728265399e-08</v>
+        <v>3.348777282654009e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.74594860817078e-08</v>
+        <v>6.745948608170788e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.379376282504571e-08</v>
+        <v>3.379376282504583e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.98759449973504e-08</v>
+        <v>4.987594499735052e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.857734532213375e-08</v>
+        <v>7.857734532213387e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2922,85 +2922,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.016577729620912e-08</v>
+        <v>3.016577729620925e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.239337657700111e-08</v>
+        <v>3.239337657700117e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.445640844131922e-08</v>
+        <v>3.445640844131925e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.196109701946443e-08</v>
+        <v>3.19610970194645e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>2.026159392008615e-08</v>
+        <v>2.02615939200862e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.695954625117928e-08</v>
+        <v>3.695954625117931e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.266386398941504e-08</v>
+        <v>3.266386398941512e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.277355834923054e-08</v>
+        <v>3.277355834923061e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.579569218705786e-08</v>
+        <v>3.579569218705792e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.325599174386001e-08</v>
+        <v>3.325599174386008e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.82429810281653e-08</v>
+        <v>3.824298102816533e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>4.101025258728492e-08</v>
+        <v>4.101025258728493e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.315178987513409e-08</v>
+        <v>3.315178987513415e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.595400149580489e-08</v>
+        <v>3.595400149580495e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.779044703052804e-08</v>
+        <v>3.779044703052805e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.326242220355648e-08</v>
+        <v>3.326242220355657e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.270830953882357e-08</v>
+        <v>3.270830953882364e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.582659112247206e-08</v>
+        <v>3.582659112247215e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.318605569083971e-08</v>
+        <v>3.31860556908398e-08</v>
       </c>
       <c r="U9" t="n">
         <v>3.944969782937014e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.968115271279295e-08</v>
+        <v>3.968115271279306e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.391082037268219e-08</v>
+        <v>3.391082037268226e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.521995973266022e-08</v>
+        <v>3.521995973266033e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.50697725817073e-08</v>
+        <v>3.506977258170739e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.07778744511579e-08</v>
+        <v>3.077787445115799e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.364750368729734e-08</v>
+        <v>3.364750368729744e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.536829651250797e-08</v>
+        <v>4.536829651250801e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3166,85 +3166,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.200825001805887e-08</v>
+        <v>1.200825001805876e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.024256840721447e-08</v>
+        <v>1.024256840721446e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.198981828295096e-08</v>
+        <v>1.198981828295086e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183524683557809e-08</v>
+        <v>1.183524683557803e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.185249425025795e-08</v>
+        <v>1.185249425025786e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.215013689107325e-08</v>
+        <v>1.215013689107319e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.179102796092953e-08</v>
+        <v>1.179102796092945e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.187815724695635e-08</v>
+        <v>1.187815724695625e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.206243034609629e-08</v>
+        <v>1.20624303460962e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.190202010149286e-08</v>
+        <v>1.190202010149275e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.222703673953925e-08</v>
+        <v>1.22270367395392e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.243087829117757e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.182363094677184e-08</v>
+        <v>1.182363094677174e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.573923474663776e-08</v>
+        <v>1.573923474663775e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204713299399125e-08</v>
+        <v>1.204713299399116e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.185180741583594e-08</v>
+        <v>1.185180741583583e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.179043105743746e-08</v>
+        <v>1.179043105743734e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205363860561473e-08</v>
+        <v>1.20536386056146e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.184263429953699e-08</v>
+        <v>1.18426342995369e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.210383904541575e-08</v>
+        <v>1.210383904541566e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.189685744436742e-08</v>
+        <v>1.189685744436731e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.201042223607883e-08</v>
+        <v>1.201042223607879e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.210920898499081e-08</v>
+        <v>1.210920898499071e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.222076776491943e-08</v>
+        <v>1.222076776491932e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.151354497640667e-08</v>
+        <v>1.151354497640662e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.188158795141911e-08</v>
+        <v>1.188158795141903e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2846900129584e-08</v>
+        <v>1.284690012958399e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3254,85 +3254,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.363915638273296e-08</v>
+        <v>1.371473168830749e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.447419575219331e-09</v>
+        <v>9.464747551129489e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.351982016626428e-08</v>
+        <v>1.359179302714396e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.238890666540751e-08</v>
+        <v>1.241788752826626e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.253854729502952e-08</v>
+        <v>1.257579769740052e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.464800678773027e-08</v>
+        <v>1.475911579217529e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.209936780838893e-08</v>
+        <v>1.212096133324676e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.272185154790217e-08</v>
+        <v>1.27655386567017e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4030384125737e-08</v>
+        <v>1.412004229878252e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.28894096736855e-08</v>
+        <v>1.293902639028291e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.520560473955873e-08</v>
+        <v>1.533666321693298e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.672785631082852e-08</v>
+        <v>1.691443206864407e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.232934579509982e-08</v>
+        <v>1.235902001263405e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.917978648826999e-08</v>
+        <v>1.922705523621431e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.391456990772764e-08</v>
+        <v>1.399971177417468e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.253082809858331e-08</v>
+        <v>1.256767742517738e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.209396981249264e-08</v>
+        <v>1.211536865730031e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.396298824023164e-08</v>
+        <v>1.405016046758385e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.246696623083476e-08</v>
+        <v>1.250158118087143e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.506681526739686e-08</v>
+        <v>1.520083278240119e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.284737980587737e-08</v>
+        <v>1.289518244397896e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.308796945419421e-08</v>
+        <v>1.313829190333043e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.43719046432774e-08</v>
+        <v>1.44741033430166e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.516293588328303e-08</v>
+        <v>1.529282120734492e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.238129017431289e-08</v>
+        <v>1.243679455892488e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.274240077848868e-08</v>
+        <v>1.278663561329075e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.961956346493402e-08</v>
+        <v>1.990677012477201e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3345,67 +3345,67 @@
         <v>1.014435917867495e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>7.506045709498635e-09</v>
+        <v>7.50604570949863e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.936164251614032e-09</v>
+        <v>9.936164251614025e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.190208647158475e-09</v>
+        <v>8.190208647158465e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.385026130170566e-09</v>
+        <v>8.385026130170561e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.174703668055867e-08</v>
+        <v>1.174703668055866e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.690736116315982e-09</v>
+        <v>7.690736116315978e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.674901483440594e-09</v>
+        <v>8.674901483440592e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.074606944949115e-08</v>
+        <v>1.07460694494911e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.944443402885738e-09</v>
+        <v>8.944443402885723e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.261565584466019e-08</v>
+        <v>1.26156558446602e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.500345460983163e-08</v>
+        <v>1.500345460983162e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.059001839519166e-09</v>
+        <v>8.059001839519156e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.867555374669909e-09</v>
+        <v>8.867555374669898e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.058356027888393e-08</v>
+        <v>1.058356027888391e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.377268019414338e-09</v>
+        <v>8.377268019414335e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.683993816783588e-09</v>
+        <v>7.683993816783601e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.065704415489996e-08</v>
+        <v>1.065704415489997e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.273653450975932e-09</v>
+        <v>8.273653450975919e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.271942566794543e-08</v>
+        <v>1.271942566794539e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>8.832690877408509e-09</v>
+        <v>8.832690877408506e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.987869278929654e-09</v>
+        <v>8.987869278929639e-09</v>
       </c>
       <c r="X4" t="n">
         <v>1.128473715359057e-08</v>
@@ -3414,13 +3414,13 @@
         <v>1.25100671174363e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.235168123413586e-09</v>
+        <v>9.235168123413594e-09</v>
       </c>
       <c r="AA4" t="n">
         <v>8.713652868549387e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.950717503320111e-08</v>
+        <v>1.950717503320112e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3430,85 +3430,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.094813373978428e-08</v>
+        <v>7.094813373978439e-08</v>
       </c>
       <c r="C5" t="n">
         <v>2.959534868339295e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.359442052425195e-08</v>
+        <v>7.359442052425202e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.834426803809834e-08</v>
+        <v>2.834426803809833e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.554619586745801e-08</v>
+        <v>4.5546195867458e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.732317589348232e-08</v>
+        <v>9.732317589348027e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.301181584733122e-08</v>
+        <v>3.301181584733115e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.074886669489173e-08</v>
+        <v>5.074886669489163e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.41146970654907e-08</v>
+        <v>8.411469706549028e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.408987300180269e-08</v>
+        <v>5.408987300180268e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.172257353559264e-07</v>
+        <v>1.172257353559266e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.703774535664204e-07</v>
+        <v>1.703774535664206e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.812021875520146e-08</v>
+        <v>3.812021875520144e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.94637049298471e-08</v>
+        <v>4.946370492984701e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.762982082258629e-08</v>
+        <v>7.762982082258626e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.394902539169054e-08</v>
+        <v>4.394902539169058e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.230289695639452e-08</v>
+        <v>3.230289695639453e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.995945422537928e-08</v>
+        <v>7.995945422537926e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.294928031348018e-08</v>
+        <v>4.294928031348017e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.172583620680263e-07</v>
+        <v>1.172583620680243e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>5.031871036616493e-08</v>
+        <v>5.031871036616466e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.409595545904329e-08</v>
+        <v>5.409595545904358e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>9.743946458712639e-08</v>
+        <v>9.743946458712623e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.170476729642257e-07</v>
+        <v>1.170476729642259e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.504490100546127e-08</v>
+        <v>5.504490100546144e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.939457967731375e-08</v>
+        <v>4.939457967731357e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.64918527209199e-07</v>
+        <v>2.649185272091992e-07</v>
       </c>
     </row>
     <row r="6">
@@ -3518,49 +3518,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.537617042666941e-08</v>
+        <v>1.537617042666938e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.001855804259563e-08</v>
+        <v>1.001855804259564e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.516797549960848e-08</v>
+        <v>1.516797549960846e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.342201989515293e-08</v>
+        <v>1.342201989515291e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.089753846326757e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.425954901365567e-08</v>
+        <v>1.425954901365564e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.020324844941298e-08</v>
+        <v>1.020324844941297e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.11874138165376e-08</v>
+        <v>1.118741381653758e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.597788069748559e-08</v>
+        <v>1.597788069748555e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.417625465088019e-08</v>
+        <v>1.417625465088018e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.784746709265465e-08</v>
+        <v>1.784746709265469e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.751596694292861e-08</v>
+        <v>1.751596694292863e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.058164117090719e-08</v>
+        <v>1.058164117090716e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.411522790706963e-08</v>
+        <v>1.411522790706962e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.583139800366501e-08</v>
+        <v>1.583139800366502e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>1.36090792674088e-08</v>
@@ -3569,13 +3569,13 @@
         <v>1.019650614988059e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.588885540289441e-08</v>
+        <v>1.588885540289442e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.078616578407292e-08</v>
+        <v>1.078616578407294e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.526671577606469e-08</v>
+        <v>1.526671577606462e-08</v>
       </c>
       <c r="V6" t="n">
         <v>1.406450212540296e-08</v>
@@ -3584,19 +3584,19 @@
         <v>1.423549123122321e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.379724948668759e-08</v>
+        <v>1.379724948668758e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.519331356557973e-08</v>
+        <v>1.519331356557971e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>1.446697937140803e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.394546411654385e-08</v>
+        <v>1.394546411654384e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.208306552519517e-08</v>
+        <v>2.208306552519521e-08</v>
       </c>
     </row>
     <row r="7">
@@ -3606,85 +3606,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.656977125581744e-08</v>
+        <v>1.656977125581746e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.393145778664114e-08</v>
+        <v>1.393145778664115e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.636157632875654e-08</v>
+        <v>1.636157632875653e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.461562072430098e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.481043820731307e-08</v>
+        <v>1.481043820731309e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.817244875770118e-08</v>
+        <v>1.817244875770116e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.41161481934585e-08</v>
+        <v>1.411614819345851e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.51003135605831e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.717148152663364e-08</v>
+        <v>1.717148152663368e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.536985548002824e-08</v>
+        <v>1.536985548002823e-08</v>
       </c>
       <c r="L7" t="n">
         <v>1.90410679218027e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.142886668697413e-08</v>
+        <v>2.142886668697412e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.448441391666167e-08</v>
+        <v>1.448441391666168e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.529254973459267e-08</v>
+        <v>1.529254973459268e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.700855463880669e-08</v>
+        <v>1.700855463880668e-08</v>
       </c>
       <c r="Q7" t="n">
         <v>1.480268009655684e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41094058939261e-08</v>
+        <v>1.410940589392611e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.708245623204247e-08</v>
+        <v>1.708245623204246e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.469906552811844e-08</v>
+        <v>1.469906552811843e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.917887832340074e-08</v>
+        <v>1.91788783234006e-08</v>
       </c>
       <c r="V7" t="n">
         <v>1.525810295455102e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.541328135607214e-08</v>
+        <v>1.541328135607217e-08</v>
       </c>
       <c r="X7" t="n">
         <v>1.771014923073307e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.897025696960102e-08</v>
+        <v>1.897025696960103e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.566058020055609e-08</v>
+        <v>1.566058020055611e-08</v>
       </c>
       <c r="AA7" t="n">
         <v>1.51390649456919e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.593258711034368e-08</v>
+        <v>2.59325871103437e-08</v>
       </c>
     </row>
     <row r="8">
@@ -3694,85 +3694,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.343521350472652e-08</v>
+        <v>3.343521350472651e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.599249870240796e-08</v>
+        <v>4.599249870240799e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.842261724452332e-08</v>
+        <v>4.842261724452334e-08</v>
       </c>
       <c r="E8" t="n">
         <v>3.858545359164058e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.404317713404738e-08</v>
+        <v>3.404317713404742e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.338439604732226e-08</v>
+        <v>5.338439604732219e-08</v>
       </c>
       <c r="H8" t="n">
         <v>4.617718910922534e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.71613544763499e-08</v>
+        <v>4.716135447634994e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.923252244240045e-08</v>
+        <v>4.923252244240048e-08</v>
       </c>
       <c r="K8" t="n">
         <v>4.743089639579503e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.110210883756954e-08</v>
+        <v>5.110210883756956e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.34899076027413e-08</v>
+        <v>5.348990760274134e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.476632369788132e-08</v>
+        <v>3.476632369788133e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.881188474643183e-08</v>
+        <v>3.881188474643182e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.973442089192109e-08</v>
+        <v>3.973442089192116e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.868184038422192e-08</v>
+        <v>2.868184038422193e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.617044680969288e-08</v>
+        <v>4.617044680969291e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.914349714780928e-08</v>
+        <v>4.914349714780932e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.676010644388524e-08</v>
+        <v>4.676010644388526e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.382363995249532e-08</v>
+        <v>4.382363995249538e-08</v>
       </c>
       <c r="V8" t="n">
         <v>4.316568455088892e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.747730864454612e-08</v>
+        <v>4.747730864454611e-08</v>
       </c>
       <c r="X8" t="n">
         <v>3.298201633166414e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.61395122139107e-08</v>
+        <v>6.613951221391074e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.224375640259739e-08</v>
+        <v>3.22437564025974e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.720010586145872e-08</v>
+        <v>4.720010586145873e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.386670147097989e-08</v>
+        <v>7.386670147097999e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3782,22 +3782,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.721453000837689e-08</v>
+        <v>2.721453000837691e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.94697927015514e-08</v>
+        <v>2.946979270155141e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.18999112436668e-08</v>
+        <v>3.189991124366681e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.902453869142524e-08</v>
+        <v>2.902453869142527e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.906774368688868e-08</v>
+        <v>1.90677436868887e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.371078428356895e-08</v>
+        <v>3.371078428356888e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.965448310836872e-08</v>
@@ -3806,61 +3806,61 @@
         <v>3.063864847549337e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.27098164415439e-08</v>
+        <v>3.270981644154391e-08</v>
       </c>
       <c r="K9" t="n">
         <v>3.090819039493848e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.457940283671295e-08</v>
+        <v>3.457940283671299e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.696720160188438e-08</v>
+        <v>3.696720160188443e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.002274883157196e-08</v>
+        <v>3.002274883157191e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.245302791276358e-08</v>
+        <v>3.24530279127636e-08</v>
       </c>
       <c r="P9" t="n">
         <v>3.452173016624359e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.034101562242462e-08</v>
+        <v>3.034101562242464e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.964774080883631e-08</v>
+        <v>2.964774080883635e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.262079114695272e-08</v>
+        <v>3.262079114695275e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.023740044302871e-08</v>
+        <v>3.023740044302869e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.471795043502054e-08</v>
+        <v>3.471795043502037e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.644351541880991e-08</v>
+        <v>3.644351541880993e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.095161627098244e-08</v>
+        <v>3.095161627098241e-08</v>
       </c>
       <c r="X9" t="n">
         <v>3.324848414564335e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.450859188451129e-08</v>
+        <v>3.45085918845113e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.824852408594426e-08</v>
+        <v>2.824852408594427e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.067739986060217e-08</v>
+        <v>3.067739986060215e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.14709220252539e-08</v>
+        <v>4.147092202525395e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4026,85 +4026,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.199563586921686e-08</v>
+        <v>1.199563586921685e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.027110172678947e-08</v>
+        <v>1.027110172678944e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.196863855200411e-08</v>
+        <v>1.196863855200404e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183674444224599e-08</v>
+        <v>1.183674444224595e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.189277856585599e-08</v>
+        <v>1.189277856585595e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.212731634521484e-08</v>
+        <v>1.212731634521479e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.181894399229588e-08</v>
+        <v>1.181894399229582e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.190102461201904e-08</v>
+        <v>1.1901024612019e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.206357142694364e-08</v>
+        <v>1.20635714269436e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.194613077154588e-08</v>
+        <v>1.194613077154584e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.216957062051298e-08</v>
+        <v>1.216957062051293e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.234646677195875e-08</v>
+        <v>1.234646677195873e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.183522745707941e-08</v>
+        <v>1.183522745707937e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.5707739277267e-08</v>
+        <v>1.570773927726694e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204697861659763e-08</v>
+        <v>1.204697861659758e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.188275750172842e-08</v>
+        <v>1.188275750172838e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.183714321252328e-08</v>
+        <v>1.183714321252326e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205454323066637e-08</v>
+        <v>1.205454323066632e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.188065695156173e-08</v>
+        <v>1.188065695156169e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.217517741405795e-08</v>
+        <v>1.217517741405792e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.201217435493646e-08</v>
+        <v>1.201217435493642e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.208838183292689e-08</v>
+        <v>1.208838183292683e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.216781752843562e-08</v>
+        <v>1.216781752843557e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.250396072776024e-08</v>
+        <v>1.25039607277602e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.154580000128322e-08</v>
+        <v>1.154580000128319e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.192026751470035e-08</v>
+        <v>1.19202675147003e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.27685203768961e-08</v>
+        <v>1.276852037689607e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4114,85 +4114,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.341248979922629e-08</v>
+        <v>1.347917130141955e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.507316253180143e-09</v>
+        <v>9.52569782217726e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.32304578185114e-08</v>
+        <v>1.329121966947217e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.226474021078342e-08</v>
+        <v>1.22883204184184e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.26901177824271e-08</v>
+        <v>1.273178591329457e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.434755315713458e-08</v>
+        <v>1.444721001390823e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.216272590082388e-08</v>
+        <v>1.218558298365461e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.274894230991508e-08</v>
+        <v>1.279260326797903e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3900913356383e-08</v>
+        <v>1.398514494634841e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.306761323892997e-08</v>
+        <v>1.31225913641029e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.465549800274321e-08</v>
+        <v>1.47663203088916e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.598440015426878e-08</v>
+        <v>1.614385083275092e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.227604310382453e-08</v>
+        <v>1.23028424198686e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.888326210771187e-08</v>
+        <v>1.891976971775416e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3775996222886e-08</v>
+        <v>1.385537134259549e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.261525540371997e-08</v>
+        <v>1.265412680245398e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.229214330265141e-08</v>
+        <v>1.231959461973505e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.383297816970377e-08</v>
+        <v>1.391461899493273e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.26026909600055e-08</v>
+        <v>1.264113098110679e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.52039000904147e-08</v>
+        <v>1.533950144942822e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.352987558566014e-08</v>
+        <v>1.360080907316131e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.326674525342327e-08</v>
+        <v>1.331982404382001e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.465063600068214e-08</v>
+        <v>1.47618764954253e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.705267299883107e-08</v>
+        <v>1.724824887216632e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.237116489951255e-08</v>
+        <v>1.242429564113918e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.288261019340275e-08</v>
+        <v>1.293080904150388e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.892133627857156e-08</v>
+        <v>1.918309573318447e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4202,85 +4202,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.829700901428145e-09</v>
+        <v>9.829700901428117e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.640222531237024e-09</v>
+        <v>7.640222531236996e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>9.524753784130145e-09</v>
+        <v>9.524753784130057e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>8.034949140124183e-09</v>
+        <v>8.03494914012416e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>8.667880343269548e-09</v>
+        <v>8.667880343269533e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.131709245383668e-08</v>
+        <v>1.131709245383665e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.833884869325955e-09</v>
+        <v>7.833884869325928e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>8.761023228049718e-09</v>
+        <v>8.76102322804969e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.058763225869892e-08</v>
+        <v>1.05876322586989e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>9.270518049764022e-09</v>
+        <v>9.270518049764006e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.179437393125606e-08</v>
+        <v>1.179437393125604e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.388877978839951e-08</v>
+        <v>1.38887797883995e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.017814094819927e-09</v>
+        <v>8.017814094819905e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.467997982322334e-09</v>
+        <v>8.467997982322271e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>1.040964085192421e-08</v>
+        <v>1.040964085192418e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.554687814031289e-09</v>
+        <v>8.554687814031272e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.03945343384971e-09</v>
+        <v>8.039453433849684e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>1.049508664772502e-08</v>
+        <v>1.049508664772498e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>8.53096113359772e-09</v>
+        <v>8.530961133597704e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>1.289826222512668e-08</v>
+        <v>1.289826222512665e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>9.968824914268298e-09</v>
+        <v>9.968824914268257e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>9.198608514266139e-09</v>
+        <v>9.198608514266112e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.177457194977996e-08</v>
+        <v>1.177457194977992e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.555716600072709e-08</v>
+        <v>1.5557166000727e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>9.215199139318828e-09</v>
+        <v>9.215199139318805e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.97838066600763e-09</v>
+        <v>8.9783806660076e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.846278405943992e-08</v>
+        <v>1.846278405943989e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4293,82 +4293,82 @@
         <v>6.341512229210378e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>3.042270222857075e-08</v>
+        <v>3.042270222857073e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>6.354031694097854e-08</v>
+        <v>6.354031694097789e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.455490968527829e-08</v>
+        <v>2.455490968527827e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>4.894294785913342e-08</v>
+        <v>4.894294785913367e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.726220613583336e-08</v>
+        <v>8.726220613583323e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.39690849578415e-08</v>
+        <v>3.396908495784148e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>5.057586720185799e-08</v>
+        <v>5.057586720185791e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.882477978732803e-08</v>
+        <v>7.882477978732804e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.790083103727839e-08</v>
+        <v>5.790083103727836e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.900686848048306e-08</v>
+        <v>9.900686848048303e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>1.433430311188777e-07</v>
+        <v>1.433430311188778e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>3.572000053915793e-08</v>
+        <v>3.572000053915787e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.174851038037492e-08</v>
+        <v>4.174851038037478e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>7.215426934161084e-08</v>
+        <v>7.215426934161149e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.520928039612577e-08</v>
+        <v>4.520928039612581e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.736064411184836e-08</v>
+        <v>3.736064411184833e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>7.521652377281512e-08</v>
+        <v>7.521652377281478e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.604751520502848e-08</v>
+        <v>4.604751520502833e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.157192804354305e-07</v>
+        <v>1.157192804354304e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>6.633452097336526e-08</v>
+        <v>6.63345209733649e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.623933264954412e-08</v>
+        <v>5.623933264954396e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>1.026210065344765e-07</v>
+        <v>1.026210065344764e-07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.713124802793936e-07</v>
+        <v>1.713124802793941e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.238281442699082e-08</v>
+        <v>5.238281442699075e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.251847744302988e-08</v>
+        <v>5.251847744302986e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.396508982675621e-07</v>
+        <v>2.396508982675625e-07</v>
       </c>
     </row>
     <row r="6">
@@ -4378,85 +4378,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.237089902539106e-08</v>
+        <v>1.237089902539104e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.018142065519994e-08</v>
+        <v>1.018142065519992e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.476914033495292e-08</v>
+        <v>1.476914033495283e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.327933569094696e-08</v>
+        <v>1.327933569094692e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.120907846723247e-08</v>
+        <v>1.120907846723245e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.385829057779959e-08</v>
+        <v>1.385829057779956e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.307827142014874e-08</v>
+        <v>1.30782714201487e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.130222135201264e-08</v>
+        <v>1.130222135201261e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.58320188095217e-08</v>
+        <v>1.583201880952167e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.451490460058681e-08</v>
+        <v>1.451490460058678e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.433557205521899e-08</v>
+        <v>1.433557205521895e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.642997791236243e-08</v>
+        <v>1.642997791236241e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.05737988312578e-08</v>
+        <v>1.057379883125786e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.102392825376458e-08</v>
+        <v>1.102392825376454e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.567206406948862e-08</v>
+        <v>1.567206406948857e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.379907436485407e-08</v>
+        <v>1.379907436485405e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.328383998467249e-08</v>
+        <v>1.328383998467245e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.303628477168793e-08</v>
+        <v>1.303628477168789e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.37753476844205e-08</v>
+        <v>1.377534768442047e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.815694679488566e-08</v>
+        <v>1.815694679488561e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.25100230382312e-08</v>
+        <v>1.251002303823118e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.189722248401863e-08</v>
+        <v>1.189722248401858e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.431577007374286e-08</v>
+        <v>1.431577007374285e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.825883013470511e-08</v>
+        <v>1.825883013470509e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.175639726328175e-08</v>
+        <v>1.175639726328173e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.422276721683041e-08</v>
+        <v>1.422276721683039e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.106238013675111e-08</v>
+        <v>2.106238013675106e-08</v>
       </c>
     </row>
     <row r="7">
@@ -4466,85 +4466,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.629194126860595e-08</v>
+        <v>1.629194126860591e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.410246289841484e-08</v>
+        <v>1.41024628984148e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.598699415130796e-08</v>
+        <v>1.598699415130786e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.449718950730199e-08</v>
+        <v>1.449718950730196e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.513012071044736e-08</v>
+        <v>1.513012071044734e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.77793328210145e-08</v>
+        <v>1.777933282101447e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.429612523650376e-08</v>
+        <v>1.429612523650373e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.522326359522753e-08</v>
+        <v>1.522326359522748e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.704987262587673e-08</v>
+        <v>1.704987262587671e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.573275841694184e-08</v>
+        <v>1.573275841694181e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.825661429843385e-08</v>
+        <v>1.825661429843383e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.035102015557733e-08</v>
+        <v>2.03510201555773e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.448005446199775e-08</v>
+        <v>1.448005446199773e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.492981848184014e-08</v>
+        <v>1.492981848184005e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.687146135144201e-08</v>
+        <v>1.687146135144197e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.501692818120911e-08</v>
+        <v>1.501692818120909e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.450169380102751e-08</v>
+        <v>1.450169380102749e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.695732701490282e-08</v>
+        <v>1.695732701490278e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.499320150077554e-08</v>
+        <v>1.49932015007755e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.937586433393016e-08</v>
+        <v>1.937586433393012e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.643106528144611e-08</v>
+        <v>1.643106528144606e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.566084888144396e-08</v>
+        <v>1.56608488814439e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.823681231695775e-08</v>
+        <v>1.823681231695773e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.203370438684096e-08</v>
+        <v>2.2033704386841e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.567743950649663e-08</v>
+        <v>1.567743950649659e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.544062103318545e-08</v>
+        <v>1.544062103318542e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.492502442661775e-08</v>
+        <v>2.492502442661773e-08</v>
       </c>
     </row>
     <row r="8">
@@ -4554,85 +4554,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.315004107686938e-08</v>
+        <v>3.315004107686935e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.618285064826618e-08</v>
+        <v>4.618285064826615e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.806738190115938e-08</v>
+        <v>4.806738190115927e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.847215795721819e-08</v>
+        <v>3.847215795721815e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.435967507361336e-08</v>
+        <v>3.435967507361333e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.301616113969869e-08</v>
+        <v>5.301616113969866e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.637651298635511e-08</v>
+        <v>4.637651298635517e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.730365134507894e-08</v>
+        <v>4.730365134507892e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.913026037572813e-08</v>
+        <v>4.91302603757281e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.781314616679325e-08</v>
+        <v>4.781314616679323e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.033700204828524e-08</v>
+        <v>5.033700204828522e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.243140790542939e-08</v>
+        <v>5.243140790542937e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.47606224243646e-08</v>
+        <v>3.476062242436459e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.84534992467252e-08</v>
+        <v>3.845349924672518e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.960027972342439e-08</v>
+        <v>3.960027972342436e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.888350097659337e-08</v>
+        <v>2.888350097659333e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.658208155087889e-08</v>
+        <v>4.658208155087886e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.903771476475424e-08</v>
+        <v>4.903771476475421e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.707358925062692e-08</v>
+        <v>4.707358925062697e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.402654253378955e-08</v>
+        <v>4.402654253378954e-08</v>
       </c>
       <c r="V8" t="n">
         <v>4.435224035011287e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.774422824919937e-08</v>
+        <v>4.774422824919934e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.349853805066334e-08</v>
+        <v>3.349853805066338e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.925123343701379e-08</v>
+        <v>6.925123343701381e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.225277750091243e-08</v>
+        <v>3.22527775009124e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.752100878303685e-08</v>
+        <v>4.752100878303682e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.290636480050653e-08</v>
+        <v>7.290636480050654e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4642,85 +4642,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.60824753620956e-08</v>
+        <v>2.608247536209559e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.856398008273306e-08</v>
+        <v>2.856398008273305e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.044851133562627e-08</v>
+        <v>3.044851133562611e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.788066339095136e-08</v>
+        <v>2.788066339095129e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.882374611487602e-08</v>
+        <v>1.8823746114876e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.224085071268904e-08</v>
+        <v>3.224085071268896e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.875764242082203e-08</v>
+        <v>2.875764242082197e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.968478077954578e-08</v>
+        <v>2.968478077954573e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.151138981019499e-08</v>
+        <v>3.151138981019495e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.019427560126009e-08</v>
+        <v>3.019427560126004e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.271813148275211e-08</v>
+        <v>3.271813148275207e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>3.481253733989558e-08</v>
+        <v>3.481253733989552e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.894157164631601e-08</v>
+        <v>2.894157164631597e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.093971415576276e-08</v>
+        <v>3.093971415576269e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.321801131330183e-08</v>
+        <v>3.321801131330175e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.947844607288366e-08</v>
+        <v>2.947844607288357e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.896321098534575e-08</v>
+        <v>2.896321098534574e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.141884419922111e-08</v>
+        <v>3.141884419922101e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.945471868509382e-08</v>
+        <v>2.945471868509373e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.383631779555894e-08</v>
+        <v>3.383631779555887e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.628279292364536e-08</v>
+        <v>3.628279292364529e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.012236606576224e-08</v>
+        <v>3.012236606576219e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.269832950127601e-08</v>
+        <v>3.269832950127597e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.649522157115939e-08</v>
+        <v>3.649522157115923e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.73227695279514e-08</v>
+        <v>2.732276952795134e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.99021382175037e-08</v>
+        <v>2.990213821750366e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.938654161093603e-08</v>
+        <v>3.938654161093596e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4886,31 +4886,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.139152097196642e-08</v>
+        <v>1.13915209719664e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.823024575394107e-09</v>
+        <v>9.823024575394096e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.139493105860044e-08</v>
+        <v>1.139493105860043e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.136361534692923e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.136576876560803e-08</v>
+        <v>1.136576876560802e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.146841185979325e-08</v>
+        <v>1.146841185979324e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.140610300674653e-08</v>
+        <v>1.140610300674652e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.137033077003932e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.144179793753664e-08</v>
+        <v>1.144179793753663e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.139709721850017e-08</v>
@@ -4919,10 +4919,10 @@
         <v>1.14985667609058e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.158560153203674e-08</v>
+        <v>1.158560153203673e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.138690284636507e-08</v>
+        <v>1.138690284636509e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.501488619051582e-08</v>
@@ -4946,13 +4946,13 @@
         <v>1.134597426002129e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.137708083932969e-08</v>
+        <v>1.137708083932968e-08</v>
       </c>
       <c r="W2" t="n">
         <v>1.147076931713041e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.143232596517721e-08</v>
+        <v>1.143232596517719e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.138933582772566e-08</v>
@@ -4974,85 +4974,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.186546744332864e-08</v>
+        <v>1.189007535577525e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.033228345416061e-09</v>
+        <v>9.047007824928098e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.189365468696014e-08</v>
+        <v>1.191941498690199e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.164572436488612e-08</v>
+        <v>1.165993466421395e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.16862765373418e-08</v>
+        <v>1.170469069623869e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.241210638285821e-08</v>
+        <v>1.245596006521851e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.197610968972338e-08</v>
+        <v>1.200485890995789e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.171803781759882e-08</v>
+        <v>1.173757593342843e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.222435374480784e-08</v>
+        <v>1.226165483685065e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.191046346331166e-08</v>
+        <v>1.193674560145199e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.262799659305531e-08</v>
+        <v>1.267965345157803e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.331722314324516e-08</v>
+        <v>1.339427949048379e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.183484020342173e-08</v>
+        <v>1.18584885101593e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.776135030866918e-08</v>
+        <v>1.778199012551125e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.210762999946393e-08</v>
+        <v>1.214072865627379e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.180778489586809e-08</v>
+        <v>1.18304821170307e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.179235396744776e-08</v>
+        <v>1.181455920292281e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.205553054517459e-08</v>
+        <v>1.208689155399881e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.174035676679038e-08</v>
+        <v>1.176063238558046e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.273302400602191e-08</v>
+        <v>1.280091897033811e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.17646588873407e-08</v>
+        <v>1.178569123824791e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.233131684180525e-08</v>
+        <v>1.237139017367469e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.216038973283612e-08</v>
+        <v>1.219561805448516e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.185226282606745e-08</v>
+        <v>1.187649529185383e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.122431254017351e-08</v>
+        <v>1.125417190390084e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.198810333893788e-08</v>
+        <v>1.201714174758694e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.345919398592483e-08</v>
+        <v>1.354038548061355e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5062,85 +5062,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.564312565146811e-09</v>
+        <v>7.564312565146801e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.070291424566473e-09</v>
+        <v>7.070291424566483e-09</v>
       </c>
       <c r="D4" t="n">
         <v>7.602831062395351e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.249105693130086e-09</v>
+        <v>7.249105693130098e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.273429547728547e-09</v>
+        <v>7.273429547728544e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>8.432830514706901e-09</v>
+        <v>8.43283051470691e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.729023356055534e-09</v>
+        <v>7.729023356055535e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.324959486405841e-09</v>
+        <v>7.324959486405843e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.122615418080561e-09</v>
+        <v>8.122615418080571e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.627298834945792e-09</v>
+        <v>7.627298834945787e-09</v>
       </c>
       <c r="L4" t="n">
         <v>8.773443994712947e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>9.872590568035475e-09</v>
+        <v>9.872590568035462e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.512148712037126e-09</v>
+        <v>7.512148712037123e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.385754969108375e-09</v>
+        <v>7.385754969108366e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.950293186420774e-09</v>
+        <v>7.950293186420766e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.468450121701954e-09</v>
+        <v>7.468450121701929e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.441907996426083e-09</v>
+        <v>7.441907996426089e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.865901593467848e-09</v>
+        <v>7.865901593467845e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.358470055284953e-09</v>
+        <v>7.358470055284954e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>9.483341607899915e-09</v>
+        <v>9.48334160789992e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.352371191241011e-09</v>
+        <v>7.352371191241061e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.250893144401382e-09</v>
+        <v>8.250893144401367e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>8.025223734686936e-09</v>
+        <v>8.025223734686913e-09</v>
       </c>
       <c r="Y4" t="n">
         <v>7.5177840480774e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.800374762027606e-09</v>
+        <v>7.800374762027613e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.755485648061491e-09</v>
+        <v>7.755485648061493e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.006774260731739e-08</v>
+        <v>1.006774260731738e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5150,85 +5150,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.487021820880906e-08</v>
+        <v>3.487021820880915e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.77163681150945e-08</v>
+        <v>2.771636811509451e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.773931097784959e-08</v>
+        <v>3.773931097784953e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.746512532678137e-08</v>
+        <v>1.746512532678135e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.193068511352237e-08</v>
+        <v>3.193068511352233e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.010459859076706e-08</v>
+        <v>5.010459859076732e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.16382170361202e-08</v>
+        <v>4.163821703612018e-08</v>
       </c>
       <c r="I5" t="n">
         <v>3.24612139069999e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.563019781389247e-08</v>
+        <v>4.563019781389248e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.895207518848899e-08</v>
+        <v>3.8952075188489e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.691927502483056e-08</v>
+        <v>5.691927502483063e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>8.048449286739721e-08</v>
+        <v>8.048449286739719e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.518116351001796e-08</v>
+        <v>3.518116351001802e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.237458266726176e-08</v>
+        <v>3.237458266726174e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.121185534013219e-08</v>
+        <v>4.121185534013223e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.466396783779092e-08</v>
+        <v>3.466396783779093e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.490721407103543e-08</v>
+        <v>3.490721407103556e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.029662503879374e-08</v>
+        <v>4.029662503879375e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.373176545937035e-08</v>
+        <v>3.373176545937041e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>7.050204348924081e-08</v>
+        <v>7.050204348924073e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.298947132154817e-08</v>
+        <v>3.298947132154795e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.871598499842991e-08</v>
+        <v>4.871598499843001e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>4.564007558867522e-08</v>
+        <v>4.564007558867528e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.573321492585903e-08</v>
+        <v>3.573321492585904e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.896310537840948e-08</v>
+        <v>3.896310537840947e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.950986459975445e-08</v>
+        <v>3.950986459975443e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.857188276608727e-08</v>
+        <v>8.857188276608729e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5238,31 +5238,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.020019378248792e-08</v>
+        <v>1.020019378248791e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.706172641907588e-09</v>
+        <v>9.70617264190758e-09</v>
       </c>
       <c r="D6" t="n">
         <v>1.286890555758839e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.251518018832312e-08</v>
+        <v>1.251518018832313e-08</v>
       </c>
       <c r="F6" t="n">
         <v>9.909310765069648e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.106871173204799e-08</v>
+        <v>1.106871173204801e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.299509785124854e-08</v>
+        <v>1.299509785124857e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.259103398159888e-08</v>
+        <v>1.25910339815989e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.075849663542166e-08</v>
+        <v>1.075849663542167e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.289337333013884e-08</v>
@@ -5271,49 +5271,49 @@
         <v>1.140932521205407e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.513866506322847e-08</v>
+        <v>1.513866506322852e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.015290516965277e-08</v>
+        <v>1.015290516965278e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.266904748197766e-08</v>
+        <v>1.266904748197769e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.323365427952904e-08</v>
+        <v>1.323365427952906e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.273452461689494e-08</v>
+        <v>1.273452461689499e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.270798249161911e-08</v>
+        <v>1.270798249161913e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.050178281080894e-08</v>
+        <v>1.050178281080895e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>9.994351272626068e-09</v>
+        <v>9.994351272626064e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.214106913289511e-08</v>
+        <v>1.214106913289512e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.2618445686434e-08</v>
+        <v>1.261844568643409e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.353416628142604e-08</v>
+        <v>1.353416628142606e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.066110495202804e-08</v>
+        <v>1.066110495202803e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>1.031215330187037e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.043625597936872e-08</v>
+        <v>1.043625597936871e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.302156014325448e-08</v>
+        <v>1.302156014325452e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>1.272120813300683e-08</v>
@@ -5326,52 +5326,52 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.422266331773242e-08</v>
+        <v>1.42226633177324e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.372864217715209e-08</v>
+        <v>1.372864217715208e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.426118181498096e-08</v>
+        <v>1.426118181498095e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.39074564457157e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.393178030031416e-08</v>
+        <v>1.393178030031415e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.509118126729251e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.438737410864114e-08</v>
+        <v>1.438737410864113e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.398331023899145e-08</v>
+        <v>1.398331023899144e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.478096617066616e-08</v>
+        <v>1.478096617066617e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.42856495875314e-08</v>
+        <v>1.428564958753141e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.543179474729857e-08</v>
+        <v>1.543179474729856e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.653094132062109e-08</v>
+        <v>1.653094132062107e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.417049946462273e-08</v>
+        <v>1.417049946462272e-08</v>
       </c>
       <c r="O7" t="n">
         <v>1.404366012687072e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.460819834418312e-08</v>
+        <v>1.460819834418311e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.412680087428754e-08</v>
+        <v>1.412680087428755e-08</v>
       </c>
       <c r="R7" t="n">
         <v>1.41002587490117e-08</v>
@@ -5389,7 +5389,7 @@
         <v>1.401072194382666e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.490924389698699e-08</v>
+        <v>1.490924389698698e-08</v>
       </c>
       <c r="X7" t="n">
         <v>1.468357448727253e-08</v>
@@ -5401,7 +5401,7 @@
         <v>1.445872551461322e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.44138364006471e-08</v>
+        <v>1.441383640064709e-08</v>
       </c>
       <c r="AB7" t="n">
         <v>1.6726093359903e-08</v>
@@ -5414,85 +5414,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.215664446814883e-08</v>
+        <v>3.215664446814888e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.76607022622209e-08</v>
+        <v>4.766070226222097e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.81932419000498e-08</v>
+        <v>4.81932419000499e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.932101141140008e-08</v>
+        <v>3.932101141140013e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.435807517551741e-08</v>
+        <v>3.435807517551744e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.234054723743006e-08</v>
+        <v>5.234054723743014e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.831943419370994e-08</v>
+        <v>4.831943419371002e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.791537032406028e-08</v>
+        <v>4.791537032406029e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.871302625573491e-08</v>
+        <v>4.871302625573499e-08</v>
       </c>
       <c r="K8" t="n">
         <v>4.821770967260028e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.93638548323674e-08</v>
+        <v>4.936385483236748e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.046300140568994e-08</v>
+        <v>5.046300140568995e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.570137195563397e-08</v>
+        <v>3.570137195563406e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.898293224251566e-08</v>
+        <v>3.898293224251568e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.871209857927128e-08</v>
+        <v>3.87120985792713e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.891679437506135e-08</v>
+        <v>2.891679437506139e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.803231883408049e-08</v>
+        <v>4.803231883408051e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.845631243112227e-08</v>
+        <v>4.845631243112233e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.794888089293935e-08</v>
+        <v>4.794888089293944e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.228763371566391e-08</v>
+        <v>4.228763371566397e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.357079941434432e-08</v>
+        <v>4.35707994143444e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.884444806534261e-08</v>
+        <v>4.88444480653427e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.093982371253986e-08</v>
+        <v>3.09398237125399e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.40373945202549e-08</v>
+        <v>6.403739452025493e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.209553413517434e-08</v>
+        <v>3.209553413517436e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.834589648571591e-08</v>
+        <v>4.834589648571595e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.736948463205885e-08</v>
+        <v>6.736948463205887e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5502,7 +5502,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.595479735634811e-08</v>
+        <v>2.595479735634812e-08</v>
       </c>
       <c r="C9" t="n">
         <v>3.070884339499433e-08</v>
@@ -5511,13 +5511,13 @@
         <v>3.12413830328232e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.967642615201772e-08</v>
+        <v>2.967642615201771e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.881375266184436e-08</v>
+        <v>1.881375266184435e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.207138376821319e-08</v>
+        <v>3.207138376821321e-08</v>
       </c>
       <c r="H9" t="n">
         <v>3.136757532648336e-08</v>
@@ -5526,13 +5526,13 @@
         <v>3.096351145683369e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.176116738850839e-08</v>
+        <v>3.176116738850838e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.126585080537363e-08</v>
+        <v>3.126585080537364e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.241199596514079e-08</v>
+        <v>3.241199596514081e-08</v>
       </c>
       <c r="M9" t="n">
         <v>3.351114253846332e-08</v>
@@ -5544,25 +5544,25 @@
         <v>3.276351123926414e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.370629627299877e-08</v>
+        <v>3.370629627299875e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.110700337520821e-08</v>
+        <v>3.110700337520823e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.108045996685393e-08</v>
+        <v>3.108045996685395e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.150445356389568e-08</v>
+        <v>3.150445356389569e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.09970220257128e-08</v>
+        <v>3.099702202571279e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>3.314373988598188e-08</v>
+        <v>3.314373988598189e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.704707754174626e-08</v>
+        <v>3.704707754174632e-08</v>
       </c>
       <c r="W9" t="n">
         <v>3.188944511482921e-08</v>
@@ -5571,16 +5571,16 @@
         <v>3.166377570511478e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.117818232615937e-08</v>
+        <v>3.117818232615934e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.827480940922018e-08</v>
+        <v>2.827480940922016e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.139403761848932e-08</v>
+        <v>3.13940376184893e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.370629457774523e-08</v>
+        <v>3.37062945777452e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5746,43 +5746,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.132508230450343e-08</v>
+        <v>1.132508230450344e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.799869730262634e-09</v>
+        <v>9.799869730262649e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.133706504672695e-08</v>
+        <v>1.133706504672696e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.132080731072434e-08</v>
+        <v>1.132080731072436e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.132870519083257e-08</v>
+        <v>1.132870519083258e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.135741783367119e-08</v>
+        <v>1.13574178336712e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.134765803233253e-08</v>
+        <v>1.134765803233254e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.134232003676063e-08</v>
+        <v>1.134232003676062e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.134960937396413e-08</v>
+        <v>1.134960937396412e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.134434052395287e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.134002813362829e-08</v>
+        <v>1.134002813362828e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.132686932756374e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.134721280151236e-08</v>
+        <v>1.134721280151235e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.499783897017278e-08</v>
@@ -5794,22 +5794,22 @@
         <v>1.132523746462746e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.134571869313343e-08</v>
+        <v>1.134571869313342e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.134261154068105e-08</v>
+        <v>1.134261154068107e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.132321816856013e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.113520624809808e-08</v>
+        <v>1.113520624809807e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.134644148126294e-08</v>
+        <v>1.134644148126295e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.141757258958372e-08</v>
+        <v>1.141757258958373e-08</v>
       </c>
       <c r="X2" t="n">
         <v>1.147935535824727e-08</v>
@@ -5821,10 +5821,10 @@
         <v>1.088688883183394e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.136816116940705e-08</v>
+        <v>1.136816116940707e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.132730600510797e-08</v>
+        <v>1.132730600510798e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5834,85 +5834,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.165977471252854e-08</v>
+        <v>1.167845407153255e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.09410489623254e-09</v>
+        <v>9.110875339061586e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1750009415285e-08</v>
+        <v>1.177192246257849e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.160840457264339e-08</v>
+        <v>1.162259603440479e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.168997874495439e-08</v>
+        <v>1.17098343303515e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.189220345632133e-08</v>
+        <v>1.19189789504763e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.18266906656103e-08</v>
+        <v>1.185141724594421e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.178711025180938e-08</v>
+        <v>1.181038918172619e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.183690615387515e-08</v>
+        <v>1.18617623323251e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.180256942953655e-08</v>
+        <v>1.182630563790685e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.177201016076211e-08</v>
+        <v>1.179452697446875e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.175634319269621e-08</v>
+        <v>1.177886292115282e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.181953161936855e-08</v>
+        <v>1.184394579051511e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.783490123895378e-08</v>
+        <v>1.785866774566099e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.167718439406334e-08</v>
+        <v>1.169645880551565e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.166416989703634e-08</v>
+        <v>1.168304770371363e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.18117527980977e-08</v>
+        <v>1.183593312242114e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.178593831235222e-08</v>
+        <v>1.18090517934692e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.165164985974384e-08</v>
+        <v>1.167005426023768e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.140644567234577e-08</v>
+        <v>1.142765877636973e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.181394391760403e-08</v>
+        <v>1.18380033178987e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.208979845063463e-08</v>
+        <v>1.21212391227844e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.276213069277081e-08</v>
+        <v>1.28201270269777e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.228781268234466e-08</v>
+        <v>1.232876257075576e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.109112149338934e-08</v>
+        <v>1.111689006538274e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.196860166706824e-08</v>
+        <v>1.19982545136588e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.169706250629287e-08</v>
+        <v>1.171715116849002e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5922,85 +5922,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.25263167744964e-09</v>
+        <v>7.252631677449646e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.159758569483855e-09</v>
+        <v>7.159758569483864e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.387982263198002e-09</v>
+        <v>7.387982263197994e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.20434365612052e-09</v>
+        <v>7.204343656120519e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.293553845147255e-09</v>
+        <v>7.293553845147264e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>7.617876354477651e-09</v>
+        <v>7.61787635447765e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.507634908627126e-09</v>
+        <v>7.507634908627121e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.447339793043229e-09</v>
+        <v>7.447339793043232e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.520490638592374e-09</v>
+        <v>7.520490638592381e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.470162125349589e-09</v>
+        <v>7.470162125349584e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.421451692835994e-09</v>
+        <v>7.421451692836007e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>7.412261742261944e-09</v>
+        <v>7.412261742261947e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.502605821696959e-09</v>
+        <v>7.502605821696964e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.483307365920803e-09</v>
+        <v>7.483307365920811e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.280656907009548e-09</v>
+        <v>7.280656907009551e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.254384282427493e-09</v>
+        <v>7.254384282427505e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.485729180233114e-09</v>
+        <v>7.485729180233109e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.450632463922783e-09</v>
+        <v>7.450632463922781e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.231575404425115e-09</v>
+        <v>7.231575404425117e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.35291775193341e-09</v>
+        <v>7.352917751933417e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.447848070989738e-09</v>
+        <v>7.447848070989733e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>7.820208835888847e-09</v>
+        <v>7.820208835888856e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>8.995216788597155e-09</v>
+        <v>8.99521678859713e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>8.233239148537504e-09</v>
+        <v>8.233239148537493e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.571932310978596e-09</v>
+        <v>7.571932310978602e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.73922727379289e-09</v>
+        <v>7.739227273792894e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.306727739816656e-09</v>
+        <v>7.306727739816669e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6010,85 +6010,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.830374784953837e-08</v>
+        <v>2.830374784953838e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.89893216412217e-08</v>
+        <v>2.898932164122177e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.314018127986158e-08</v>
+        <v>3.314018127986157e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.66398924732398e-08</v>
+        <v>1.663989247323979e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.128040831817292e-08</v>
+        <v>3.128040831817296e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.561797538577249e-08</v>
+        <v>3.561797538577306e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.581538459098047e-08</v>
+        <v>3.581538459098054e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.398050444150577e-08</v>
+        <v>3.398050444150581e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.427273081554413e-08</v>
+        <v>3.427273081554424e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.492251789090835e-08</v>
+        <v>3.492251789090834e-08</v>
       </c>
       <c r="L5" t="n">
         <v>3.417421314376581e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.529942179363321e-08</v>
+        <v>3.529942179363317e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.366317110315441e-08</v>
+        <v>3.366317110315448e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.265662412979652e-08</v>
+        <v>3.265662412979656e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>2.864494107873296e-08</v>
+        <v>2.864494107873299e-08</v>
       </c>
       <c r="Q5" t="n">
         <v>3.003856412167311e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.485960502137977e-08</v>
+        <v>3.485960502137979e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.235325776393125e-08</v>
+        <v>3.235325776393129e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.061551824981167e-08</v>
+        <v>3.061551824981169e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.24729889171025e-08</v>
+        <v>3.247298891710249e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.342014885917003e-08</v>
+        <v>3.342014885917009e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>3.920836008844072e-08</v>
+        <v>3.920836008844073e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>5.979871296954571e-08</v>
+        <v>5.979871296954581e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.671783699859968e-08</v>
+        <v>4.671783699859963e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>3.373160446380495e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.762045308419599e-08</v>
+        <v>3.762045308419601e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.22002166661228e-08</v>
+        <v>3.220021666612282e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6101,16 +6101,16 @@
         <v>1.210158425062495e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>9.596205122361243e-09</v>
+        <v>9.596205122361244e-09</v>
       </c>
       <c r="D6" t="n">
-        <v>9.824428816075385e-09</v>
+        <v>9.82442881607539e-09</v>
       </c>
       <c r="E6" t="n">
-        <v>9.640790208997905e-09</v>
+        <v>9.640790208997913e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.214250641832255e-08</v>
+        <v>1.214250641832257e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.246682892765294e-08</v>
@@ -6119,19 +6119,19 @@
         <v>1.235658748180242e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.229629236621854e-08</v>
+        <v>1.229629236621855e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.236944321176767e-08</v>
+        <v>1.236944321176768e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.231911469852488e-08</v>
+        <v>1.23191146985249e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>9.857898245713391e-09</v>
+        <v>9.857898245713396e-09</v>
       </c>
       <c r="M6" t="n">
-        <v>1.226121431543723e-08</v>
+        <v>1.226121431543725e-08</v>
       </c>
       <c r="N6" t="n">
         <v>9.941571840648406e-09</v>
@@ -6140,25 +6140,25 @@
         <v>1.234792732617022e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>9.559032303982316e-09</v>
+        <v>9.559032303982317e-09</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.21033368556028e-08</v>
+        <v>1.210333685560281e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>9.922175733110491e-09</v>
+        <v>9.922175733110499e-09</v>
       </c>
       <c r="S6" t="n">
-        <v>1.229958503709808e-08</v>
+        <v>1.229958503709809e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>9.66802195730252e-09</v>
+        <v>9.668021957302515e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>9.800028805702905e-09</v>
+        <v>9.800028805702915e-09</v>
       </c>
       <c r="V6" t="n">
-        <v>9.884294623867128e-09</v>
+        <v>9.884294623867119e-09</v>
       </c>
       <c r="W6" t="n">
         <v>1.040197468988395e-08</v>
@@ -6167,16 +6167,16 @@
         <v>1.384416936177244e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.080707611605725e-08</v>
+        <v>1.080707611605727e-08</v>
       </c>
       <c r="Z6" t="n">
         <v>1.000837886385599e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.258817984696819e-08</v>
+        <v>1.25881798469682e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.744461638887608e-09</v>
+        <v>9.744461638887606e-09</v>
       </c>
     </row>
     <row r="7">
@@ -6189,82 +6189,82 @@
         <v>1.348348158685519e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.339060847888938e-08</v>
+        <v>1.33906084788894e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.361883217260353e-08</v>
+        <v>1.361883217260356e-08</v>
       </c>
       <c r="E7" t="n">
         <v>1.343519356552606e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.35244037545528e-08</v>
+        <v>1.352440375455282e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.384872626388318e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.373848481803267e-08</v>
+        <v>1.373848481803266e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.367818970244876e-08</v>
+        <v>1.367818970244878e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.375134054799792e-08</v>
+        <v>1.375134054799794e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.37010120347551e-08</v>
+        <v>1.370101203475512e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.365230160224153e-08</v>
+        <v>1.365230160224154e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.364311165166748e-08</v>
+        <v>1.364311165166749e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.373345573110251e-08</v>
+        <v>1.373345573110253e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.371374148949626e-08</v>
+        <v>1.371374148949627e-08</v>
       </c>
       <c r="P7" t="n">
         <v>1.351109103058501e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.348523419183305e-08</v>
+        <v>1.348523419183306e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.371657908963865e-08</v>
+        <v>1.371657908963866e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.368148237332832e-08</v>
+        <v>1.368148237332834e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.346242531383066e-08</v>
+        <v>1.346242531383068e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.359517934686999e-08</v>
+        <v>1.359517934687e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.367869798039529e-08</v>
+        <v>1.36786979803953e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.405105874529439e-08</v>
+        <v>1.40510587452944e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.522606669800269e-08</v>
+        <v>1.522606669800273e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.447475355883515e-08</v>
+        <v>1.447475355883517e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.380278222038414e-08</v>
+        <v>1.380278222038415e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.397007718319843e-08</v>
+        <v>1.397007718319844e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.35375776492222e-08</v>
+        <v>1.353757764922222e-08</v>
       </c>
     </row>
     <row r="8">
@@ -6274,85 +6274,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.016251698340752e-08</v>
+        <v>3.016251698340753e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.498208658184861e-08</v>
+        <v>4.498208658184864e-08</v>
       </c>
       <c r="D8" t="n">
         <v>4.521031027556277e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.708623581641139e-08</v>
+        <v>3.708623581641138e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.252662343961048e-08</v>
+        <v>3.252662343961052e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.853239650770912e-08</v>
+        <v>4.853239650770914e-08</v>
       </c>
       <c r="H8" t="n">
         <v>4.532996292099186e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.526966780540795e-08</v>
+        <v>4.526966780540797e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.534281865095706e-08</v>
+        <v>4.534281865095713e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.529249013771432e-08</v>
+        <v>4.529249013771435e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.524377970520076e-08</v>
+        <v>4.524377970520071e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.523458975462663e-08</v>
+        <v>4.523458975462665e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.376529593983473e-08</v>
+        <v>3.376529593983475e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.692268634921149e-08</v>
+        <v>3.692268634921151e-08</v>
       </c>
       <c r="P8" t="n">
         <v>3.594135268976064e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.723363423607782e-08</v>
+        <v>2.723363423607786e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.530805719259787e-08</v>
+        <v>4.530805719259789e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.527296047628748e-08</v>
+        <v>4.527296047628753e-08</v>
       </c>
       <c r="T8" t="n">
         <v>4.505390341678989e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.79082472892145e-08</v>
+        <v>3.790824728921448e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.119537471893942e-08</v>
+        <v>4.11953747189394e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.564546757274206e-08</v>
+        <v>4.56454675727421e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.034122174912407e-08</v>
+        <v>3.034122174912409e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.0894875833102e-08</v>
+        <v>6.089487583310205e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.0204811337403e-08</v>
+        <v>3.020481133740301e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.556155528615756e-08</v>
+        <v>4.556155528615762e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.070634911927832e-08</v>
+        <v>6.070634911927837e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6362,28 +6362,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.329408471883078e-08</v>
+        <v>2.329408471883081e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.779240389437172e-08</v>
+        <v>2.779240389437169e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.802062758808584e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.677736179095788e-08</v>
+        <v>2.677736179095789e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.734224576004133e-08</v>
+        <v>1.734224576004134e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.825052331982826e-08</v>
+        <v>2.825052331982829e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.814028023351494e-08</v>
+        <v>2.814028023351499e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.807998511793109e-08</v>
+        <v>2.80799851179311e-08</v>
       </c>
       <c r="J9" t="n">
         <v>2.815313596348024e-08</v>
@@ -6392,55 +6392,55 @@
         <v>2.810280745023745e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.805409701772386e-08</v>
+        <v>2.805409701772389e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.804490706714982e-08</v>
+        <v>2.804490706714983e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.813525114658483e-08</v>
+        <v>2.813525114658485e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>2.963746998602038e-08</v>
+        <v>2.963746998602043e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.976572307720409e-08</v>
+        <v>2.976572307720412e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.788703124777811e-08</v>
+        <v>2.788703124777815e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.811837450512097e-08</v>
+        <v>2.811837450512098e-08</v>
       </c>
       <c r="S9" t="n">
         <v>2.808327778881064e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.786422072931298e-08</v>
+        <v>2.786422072931305e-08</v>
       </c>
       <c r="U9" t="n">
-        <v>2.799622757771338e-08</v>
+        <v>2.79962275777134e-08</v>
       </c>
       <c r="V9" t="n">
         <v>3.337862952345598e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.845285416077671e-08</v>
+        <v>2.845285416077675e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.9627862113485e-08</v>
+        <v>2.962786211348494e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.887654897431748e-08</v>
+        <v>2.887654897431747e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.543649760506879e-08</v>
+        <v>2.543649760506882e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.837187259868075e-08</v>
+        <v>2.837187259868077e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.793937306470452e-08</v>
+        <v>2.793937306470454e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6606,46 +6606,46 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.136347868403525e-08</v>
+        <v>1.136347868403522e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.832431474720821e-09</v>
+        <v>9.83243147472082e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.137330172214623e-08</v>
+        <v>1.137330172214627e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.136531464443593e-08</v>
+        <v>1.136531464443591e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.135602768815522e-08</v>
+        <v>1.135602768815525e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.140248629565285e-08</v>
+        <v>1.140248629565283e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137152179707774e-08</v>
+        <v>1.137152179707773e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.137195043110633e-08</v>
+        <v>1.137195043110636e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.13839065120429e-08</v>
+        <v>1.138390651204291e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.137723181750266e-08</v>
+        <v>1.137723181750265e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.136929609067963e-08</v>
+        <v>1.136929609067962e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.136342634264023e-08</v>
+        <v>1.136342634264024e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.136728580941623e-08</v>
+        <v>1.136728580941621e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.505529870758283e-08</v>
+        <v>1.505529870758282e-08</v>
       </c>
       <c r="P2" t="n">
         <v>1.136483097580237e-08</v>
@@ -6654,34 +6654,34 @@
         <v>1.135685863435409e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.138508614398725e-08</v>
+        <v>1.138508614398728e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.136425318394594e-08</v>
+        <v>1.136425318394596e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.13576900554664e-08</v>
+        <v>1.135769005546641e-08</v>
       </c>
       <c r="U2" t="n">
         <v>1.119530059505075e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.138419227910459e-08</v>
+        <v>1.138419227910458e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.152082241009952e-08</v>
+        <v>1.152082241009949e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.15522410943979e-08</v>
+        <v>1.155224109439793e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.144433348194387e-08</v>
+        <v>1.144433348194385e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.090573677472209e-08</v>
+        <v>1.090573677472212e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.140937137062874e-08</v>
+        <v>1.140937137062875e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.137006682877986e-08</v>
@@ -6694,85 +6694,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.174778152346868e-08</v>
+        <v>1.176867506651289e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.123441869817536e-09</v>
+        <v>9.140207554595136e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.182210332682881e-08</v>
+        <v>1.184571533994367e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.174144674833024e-08</v>
+        <v>1.175940367576363e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.169879727788761e-08</v>
+        <v>1.171808495872964e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.202615690848128e-08</v>
+        <v>1.205681689554238e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.181110236375206e-08</v>
+        <v>1.183437553387341e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.181234615080839e-08</v>
+        <v>1.183564632567599e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.189526999381481e-08</v>
+        <v>1.192135120912141e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.185036762982607e-08</v>
+        <v>1.187495220892953e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.179341187390211e-08</v>
+        <v>1.181585951378861e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.182831281070257e-08</v>
+        <v>1.18525830502679e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.177689437778702e-08</v>
+        <v>1.179891345419411e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.792508990481076e-08</v>
+        <v>1.794974569563551e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.175750612535127e-08</v>
+        <v>1.177870885278346e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.17033182603495e-08</v>
+        <v>1.17227218664873e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.19067398137974e-08</v>
+        <v>1.193342363375756e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.175426384442311e-08</v>
+        <v>1.177539597563288e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.171055801505362e-08</v>
+        <v>1.173021397013289e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.14775011611154e-08</v>
+        <v>1.149856214198317e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.189651787010639e-08</v>
+        <v>1.192263333352026e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.243803584130523e-08</v>
+        <v>1.247877487438316e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.309484535914432e-08</v>
+        <v>1.316383678001281e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.232672782297338e-08</v>
+        <v>1.236816961942047e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.102718832951096e-08</v>
+        <v>1.104967301822796e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.207676489704062e-08</v>
+        <v>1.210936037973937e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.181487849439278e-08</v>
+        <v>1.183826431056946e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6785,10 +6785,10 @@
         <v>7.389327745146007e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.196271382487133e-09</v>
+        <v>7.196271382487138e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.500283479431044e-09</v>
+        <v>7.500283479431054e-09</v>
       </c>
       <c r="E4" t="n">
         <v>7.410065762455408e-09</v>
@@ -6800,67 +6800,67 @@
         <v>7.829936662754799e-09</v>
       </c>
       <c r="H4" t="n">
-        <v>7.480178406975902e-09</v>
+        <v>7.480178406975901e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.485020025510633e-09</v>
+        <v>7.485020025510634e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>7.61090942048623e-09</v>
+        <v>7.610909420486238e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.54467571441457e-09</v>
+        <v>7.544675714414565e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>7.455038029333836e-09</v>
+        <v>7.455038029333841e-09</v>
       </c>
       <c r="M4" t="n">
         <v>7.526575655112833e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.432330977688594e-09</v>
+        <v>7.432330977688598e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.560187720667435e-09</v>
+        <v>7.560187720667433e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>7.404602502740978e-09</v>
+        <v>7.404602502740981e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.314551238624296e-09</v>
+        <v>7.314551238624298e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.633393945227148e-09</v>
+        <v>7.633393945227152e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.398076077925467e-09</v>
+        <v>7.398076077925469e-09</v>
       </c>
       <c r="T4" t="n">
         <v>7.323942522560658e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>7.383405538848841e-09</v>
+        <v>7.383405538848848e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.577426264044642e-09</v>
+        <v>7.577426264044643e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.273646617662584e-09</v>
+        <v>8.273646617662581e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.521486005191631e-09</v>
+        <v>9.521486005191639e-09</v>
       </c>
       <c r="Y4" t="n">
         <v>8.292591621833832e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.460411225207137e-09</v>
+        <v>7.460411225207139e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.907706751898721e-09</v>
+        <v>7.907706751898737e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>7.490085476111157e-09</v>
+        <v>7.490085476111158e-09</v>
       </c>
     </row>
     <row r="5">
@@ -6870,13 +6870,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.996613889101076e-08</v>
+        <v>2.996613889101074e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.870485427196004e-08</v>
+        <v>2.870485427196002e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.411252356525061e-08</v>
+        <v>3.411252356525058e-08</v>
       </c>
       <c r="E5" t="n">
         <v>2.02596135212695e-08</v>
@@ -6885,67 +6885,67 @@
         <v>3.065096141238107e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>3.774665753428606e-08</v>
+        <v>3.774665753428608e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.463918423671086e-08</v>
+        <v>3.463918423671088e-08</v>
       </c>
       <c r="I5" t="n">
         <v>3.378403356670774e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>3.491592196958781e-08</v>
+        <v>3.491592196958783e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.500910035853891e-08</v>
+        <v>3.500910035853895e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>3.325887412708315e-08</v>
+        <v>3.325887412708313e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>3.551024345152284e-08</v>
+        <v>3.551024345152286e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.173270529966528e-08</v>
+        <v>3.173270529966529e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.314066176272287e-08</v>
+        <v>3.314066176272289e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.027424680643416e-08</v>
+        <v>3.027424680643432e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.008651781203388e-08</v>
+        <v>3.008651781203385e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.674171005085942e-08</v>
+        <v>3.674171005085946e-08</v>
       </c>
       <c r="S5" t="n">
         <v>3.061560450400432e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.092934744607919e-08</v>
+        <v>3.092934744607926e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.179382690710687e-08</v>
+        <v>3.179382690710689e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.452604473092634e-08</v>
+        <v>3.452604473092631e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.612673582089247e-08</v>
+        <v>4.612673582089248e-08</v>
       </c>
       <c r="X5" t="n">
         <v>6.760282317377751e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.709429654076314e-08</v>
+        <v>4.709429654076307e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.146556573429791e-08</v>
+        <v>3.146556573429793e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.988335209802858e-08</v>
+        <v>3.988335209802896e-08</v>
       </c>
       <c r="AB5" t="n">
         <v>3.473583889649678e-08</v>
@@ -6958,85 +6958,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.226112346925127e-08</v>
+        <v>1.226112346925129e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.206806710659239e-08</v>
+        <v>1.206806710659241e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.23720792035363e-08</v>
+        <v>1.237207920353633e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.843046358767716e-09</v>
+        <v>9.843046358767721e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>1.217696104315948e-08</v>
+        <v>1.217696104315947e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.270173238686005e-08</v>
+        <v>1.270173238686006e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.235197413108115e-08</v>
+        <v>1.235197413108116e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.235681574961588e-08</v>
+        <v>1.235681574961589e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.004389001679853e-08</v>
+        <v>1.004389001679854e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>9.977656310726866e-09</v>
+        <v>9.977656310726863e-09</v>
       </c>
       <c r="L6" t="n">
-        <v>1.232683375343909e-08</v>
+        <v>1.23268337534391e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.239837137921808e-08</v>
+        <v>1.23983713792181e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>9.867063077064906e-09</v>
+        <v>9.867063077064919e-09</v>
       </c>
       <c r="O6" t="n">
-        <v>9.994869466103749e-09</v>
+        <v>9.994869466103754e-09</v>
       </c>
       <c r="P6" t="n">
-        <v>1.228504245119937e-08</v>
+        <v>1.228504245119945e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.218634696272955e-08</v>
+        <v>1.218634696272956e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>1.250518966933239e-08</v>
+        <v>1.250518966933242e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.226987180203072e-08</v>
+        <v>1.226987180203073e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>9.756923118872956e-09</v>
+        <v>9.756923118872972e-09</v>
       </c>
       <c r="U6" t="n">
         <v>1.2265229523689e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.001040686035695e-08</v>
+        <v>1.001040686035696e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.315400686725218e-08</v>
+        <v>1.31540068672522e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.195446660150393e-08</v>
+        <v>1.195446660150394e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.08622774687039e-08</v>
+        <v>1.086227746870386e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.89339182151945e-09</v>
+        <v>9.893391821519448e-09</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.277950247600397e-08</v>
+        <v>1.2779502476004e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.924171434013683e-09</v>
+        <v>9.924171434013702e-09</v>
       </c>
     </row>
     <row r="7">
@@ -7049,7 +7049,7 @@
         <v>1.366266038616374e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.346960402350487e-08</v>
+        <v>1.346960402350486e-08</v>
       </c>
       <c r="D7" t="n">
         <v>1.377361612044878e-08</v>
@@ -7058,13 +7058,13 @@
         <v>1.368339840347313e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.357849796007194e-08</v>
+        <v>1.357849796007193e-08</v>
       </c>
       <c r="G7" t="n">
         <v>1.410326930377251e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.375351104799363e-08</v>
+        <v>1.375351104799362e-08</v>
       </c>
       <c r="I7" t="n">
         <v>1.375835266652836e-08</v>
@@ -7076,10 +7076,10 @@
         <v>1.38180083554323e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.372837067035156e-08</v>
+        <v>1.372837067035155e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>1.379990829613055e-08</v>
+        <v>1.379990829613056e-08</v>
       </c>
       <c r="N7" t="n">
         <v>1.370566361870631e-08</v>
@@ -7094,13 +7094,13 @@
         <v>1.358788387964201e-08</v>
       </c>
       <c r="R7" t="n">
-        <v>1.390672658624488e-08</v>
+        <v>1.390672658624486e-08</v>
       </c>
       <c r="S7" t="n">
         <v>1.367140871894318e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.359727516357838e-08</v>
+        <v>1.359727516357839e-08</v>
       </c>
       <c r="U7" t="n">
         <v>1.36677599657366e-08</v>
@@ -7109,22 +7109,22 @@
         <v>1.385075890506238e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.454697925868031e-08</v>
+        <v>1.45469792586803e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.579481864620935e-08</v>
+        <v>1.579481864620936e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.457595252358645e-08</v>
+        <v>1.457595252358646e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>1.373374386622485e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.418103939291645e-08</v>
+        <v>1.418103939291648e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.376341811712887e-08</v>
+        <v>1.376341811712889e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7134,85 +7134,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.035160454078116e-08</v>
+        <v>3.035160454078117e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.511648438427387e-08</v>
+        <v>4.51164843842739e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.542049648121779e-08</v>
+        <v>4.542049648121783e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.736561896553153e-08</v>
+        <v>3.736561896553154e-08</v>
       </c>
       <c r="F8" t="n">
         <v>3.259771375875929e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.885177517894172e-08</v>
+        <v>4.885177517894177e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.540039140876261e-08</v>
+        <v>4.540039140876267e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.540523302729734e-08</v>
+        <v>4.540523302729742e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.553112242227299e-08</v>
+        <v>4.5531122422273e-08</v>
       </c>
       <c r="K8" t="n">
         <v>4.54648887162013e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.537525103112055e-08</v>
+        <v>4.537525103112057e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.544678865689977e-08</v>
+        <v>4.544678865689979e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.375764101204525e-08</v>
+        <v>3.375764101204526e-08</v>
       </c>
       <c r="O8" t="n">
         <v>3.707187776848681e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.613523381539985e-08</v>
+        <v>3.613523381539984e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.733725217091752e-08</v>
+        <v>2.733725217091753e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.55536069470139e-08</v>
+        <v>4.555360694701394e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.531828907971218e-08</v>
+        <v>4.531828907971219e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.524415552434741e-08</v>
+        <v>4.524415552434744e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.801397016230656e-08</v>
+        <v>3.801397016230655e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.141061462734274e-08</v>
+        <v>4.141061462734276e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.619679928469848e-08</v>
+        <v>4.619679928469851e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.091511151400055e-08</v>
+        <v>3.091511151400058e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.109703713534907e-08</v>
+        <v>6.109703713534914e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.014483667619574e-08</v>
+        <v>3.014483667619576e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.582791975368546e-08</v>
+        <v>4.58279197536855e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.103511360956856e-08</v>
+        <v>6.103511360956857e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7222,22 +7222,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.273800599071787e-08</v>
+        <v>2.273800599071786e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.694986364064063e-08</v>
+        <v>2.694986364064065e-08</v>
       </c>
       <c r="D9" t="n">
         <v>2.725387573758456e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.614702306434123e-08</v>
+        <v>2.614702306434124e-08</v>
       </c>
       <c r="F9" t="n">
         <v>1.690422647502653e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>2.758353052063875e-08</v>
+        <v>2.758353052063877e-08</v>
       </c>
       <c r="H9" t="n">
         <v>2.723377066512939e-08</v>
@@ -7246,43 +7246,43 @@
         <v>2.723861228366413e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.736450167863972e-08</v>
+        <v>2.736450167863971e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.729826797256807e-08</v>
+        <v>2.729826797256808e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>2.720863028748732e-08</v>
+        <v>2.720863028748733e-08</v>
       </c>
       <c r="M9" t="n">
         <v>2.728016791326632e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.718592323584211e-08</v>
+        <v>2.718592323584212e-08</v>
       </c>
       <c r="O9" t="n">
         <v>2.877356484472778e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.893545744153118e-08</v>
+        <v>2.893545744153117e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.706814509650826e-08</v>
+        <v>2.706814509650829e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.738698620338064e-08</v>
+        <v>2.738698620338067e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.715166833607897e-08</v>
+        <v>2.715166833607898e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.707753478071414e-08</v>
+        <v>2.707753478071416e-08</v>
       </c>
       <c r="U9" t="n">
         <v>2.714702605773723e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.241419343496684e-08</v>
+        <v>3.241419343496682e-08</v>
       </c>
       <c r="W9" t="n">
         <v>2.802723887581607e-08</v>
@@ -7291,13 +7291,13 @@
         <v>2.927507826334514e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.805621214072222e-08</v>
+        <v>2.80562121407222e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.455823266924628e-08</v>
+        <v>2.455823266924629e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.76612990100522e-08</v>
+        <v>2.766129901005223e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>2.724367773426467e-08</v>
@@ -7466,40 +7466,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.182515898979018e-08</v>
+        <v>1.182515898979017e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.012334221802107e-08</v>
+        <v>1.012334221802108e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.175121739092232e-08</v>
+        <v>1.175121739092231e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.171453041263725e-08</v>
+        <v>1.171453041263723e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.169494209875711e-08</v>
+        <v>1.16949420987571e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.204635952616789e-08</v>
+        <v>1.204635952616788e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168604762169306e-08</v>
+        <v>1.168604762169305e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.169189195763748e-08</v>
+        <v>1.169189195763746e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.19225497045582e-08</v>
+        <v>1.192254970455814e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.171672598127539e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.211465150114137e-08</v>
+        <v>1.211465150114122e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.239238733461688e-08</v>
+        <v>1.239238733461689e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.172792325041903e-08</v>
@@ -7508,43 +7508,43 @@
         <v>1.548402403326667e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.18676912838783e-08</v>
+        <v>1.186769128387828e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.172090661454947e-08</v>
+        <v>1.172090661454944e-08</v>
       </c>
       <c r="R2" t="n">
         <v>1.169685947059103e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.184068035338279e-08</v>
+        <v>1.184068035338277e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.170665369549358e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.194694681892618e-08</v>
+        <v>1.194694681892612e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.171983037736195e-08</v>
+        <v>1.171983037736194e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.180819010187412e-08</v>
+        <v>1.180819010187409e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.190544905555671e-08</v>
+        <v>1.190544905555665e-08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.188313410759305e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.132247279419927e-08</v>
+        <v>1.132247279419925e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.175256204942341e-08</v>
+        <v>1.17525620494234e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.26610445845591e-08</v>
+        <v>1.266104458455911e-08</v>
       </c>
     </row>
     <row r="3">
@@ -7554,85 +7554,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.302763865951015e-08</v>
+        <v>1.308474340628441e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.302877504323117e-09</v>
+        <v>9.318294063456551e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.250886602985088e-08</v>
+        <v>1.254798792983617e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.222163998258097e-08</v>
+        <v>1.224773085027056e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.210758190533288e-08</v>
+        <v>1.213250405017699e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.459849001789457e-08</v>
+        <v>1.471095993644313e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.204479749458612e-08</v>
+        <v>1.2067480839003e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.208501641716593e-08</v>
+        <v>1.210910647043423e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.372306889732792e-08</v>
+        <v>1.38049334918052e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.226321434740069e-08</v>
+        <v>1.229354367251346e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.509336781809775e-08</v>
+        <v>1.522363096935631e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7118554514268e-08</v>
+        <v>1.732280566329259e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.234059518048295e-08</v>
+        <v>1.237368880830046e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.857665093290621e-08</v>
+        <v>1.861121293068148e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.333051928247929e-08</v>
+        <v>1.33981370940859e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.229074728174922e-08</v>
+        <v>1.232210813034251e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.212089252639542e-08</v>
+        <v>1.21462858671853e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.313729087950686e-08</v>
+        <v>1.319844553204225e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.219018737043759e-08</v>
+        <v>1.221800648838857e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.498027687111413e-08</v>
+        <v>1.511781811536616e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.228103794727286e-08</v>
+        <v>1.231185837377607e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.272252103833586e-08</v>
+        <v>1.27670309639376e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.361107600179863e-08</v>
+        <v>1.36892939920122e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.344746419162536e-08</v>
+        <v>1.351969218943856e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.196270414297066e-08</v>
+        <v>1.2009056320605e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.251571766884469e-08</v>
+        <v>1.255495864493562e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.898398892515777e-08</v>
+        <v>1.925185553440463e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7642,85 +7642,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.23717677718754e-09</v>
+        <v>9.237176777187183e-09</v>
       </c>
       <c r="C4" t="n">
-        <v>7.34799451722983e-09</v>
+        <v>7.34799451722984e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>8.401972403158889e-09</v>
+        <v>8.401972403158891e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.987576106585356e-09</v>
+        <v>7.987576106585291e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.766317090239568e-09</v>
+        <v>7.766317090239583e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.173573859284786e-08</v>
+        <v>1.173573859284787e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.665849880139611e-09</v>
+        <v>7.665849880139606e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.731864343159105e-09</v>
+        <v>7.731864343159099e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>1.032661704927854e-08</v>
+        <v>1.032661704927851e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>8.012376064364662e-09</v>
+        <v>8.012376064364661e-09</v>
       </c>
       <c r="L4" t="n">
-        <v>1.250712786603384e-08</v>
+        <v>1.250712786603304e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.571369464450889e-08</v>
+        <v>1.57136946445089e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>8.138854370340337e-09</v>
+        <v>8.13885437034034e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>8.22015401827609e-09</v>
+        <v>8.220154018276094e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>9.717598604734596e-09</v>
+        <v>9.717598604734563e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>8.059598240381581e-09</v>
+        <v>8.059598240381556e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.787974687138311e-09</v>
+        <v>7.787974687138319e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>9.412497719146038e-09</v>
+        <v>9.412497719145975e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.898604962978724e-09</v>
+        <v>7.898604962978714e-09</v>
       </c>
       <c r="U4" t="n">
         <v>1.27932551418476e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>7.991622908752981e-09</v>
+        <v>7.991622908752989e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.654514941950365e-09</v>
+        <v>8.654514941950355e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>1.014409000527547e-08</v>
+        <v>1.014409000527522e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>9.845543404240843e-09</v>
       </c>
       <c r="Z4" t="n">
-        <v>8.749403763149065e-09</v>
+        <v>8.749403763148961e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.417160939502257e-09</v>
+        <v>8.417160939502229e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.857415643334285e-08</v>
+        <v>1.857415643334288e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7730,85 +7730,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6.037594539556023e-08</v>
+        <v>6.037594539555688e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.925077311402724e-08</v>
+        <v>2.925077311402728e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.956279350589453e-08</v>
+        <v>4.95627935058947e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>2.760713693427339e-08</v>
+        <v>2.760713693427252e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.774156291727799e-08</v>
+        <v>3.774156291727802e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.032427649642062e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6228973456337e-08</v>
+        <v>3.622897345633694e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.664717010912992e-08</v>
+        <v>3.66471701091298e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.135884490331815e-08</v>
+        <v>8.135884490331782e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.24828881613575e-08</v>
+        <v>4.248288816135747e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.21985118798789e-07</v>
+        <v>1.21985118798775e-07</v>
       </c>
       <c r="M5" t="n">
-        <v>1.855393013747389e-07</v>
+        <v>1.855393013747387e-07</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346468492927611e-08</v>
+        <v>4.346468492927603e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.301941780749784e-08</v>
+        <v>4.301941780749797e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>6.908460172077908e-08</v>
+        <v>6.908460172077895e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.209413341873268e-08</v>
+        <v>4.209413341873144e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>3.794319672677301e-08</v>
+        <v>3.79431967267731e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>6.306548950494958e-08</v>
+        <v>6.306548950494817e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.969738379107143e-08</v>
+        <v>3.969738379107114e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>1.284060967088337e-07</v>
+        <v>1.284060967088336e-07</v>
       </c>
       <c r="V5" t="n">
-        <v>4.068048432206832e-08</v>
+        <v>4.06804843220684e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.264023867066807e-08</v>
+        <v>5.26402386706673e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>8.330950400950831e-08</v>
+        <v>8.330950400950769e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.612496455197855e-08</v>
+        <v>7.612496455197859e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.213168416670067e-08</v>
+        <v>5.213168416669798e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.832319672667705e-08</v>
+        <v>4.832319672667627e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.633339285935257e-07</v>
+        <v>2.633339285935253e-07</v>
       </c>
     </row>
     <row r="6">
@@ -7818,19 +7818,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.190823528374766e-08</v>
+        <v>1.190823528374745e-08</v>
       </c>
       <c r="C6" t="n">
         <v>1.001905302378994e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.107303090971901e-08</v>
+        <v>1.107303090971903e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.353038222563277e-08</v>
+        <v>1.353038222563271e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.043737559679968e-08</v>
+        <v>1.043737559679969e-08</v>
       </c>
       <c r="G6" t="n">
         <v>1.727854471189527e-08</v>
@@ -7842,58 +7842,58 @@
         <v>1.040292284971922e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.299767555583865e-08</v>
+        <v>1.299767555583862e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.355518218341207e-08</v>
+        <v>1.355518218341206e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.804993398508126e-08</v>
+        <v>1.804993398508001e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8384753151069e-08</v>
+        <v>1.838475315106899e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.081805312911642e-08</v>
+        <v>1.081805312911638e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>1.378351612209462e-08</v>
+        <v>1.37835161220946e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>1.528106238609577e-08</v>
+        <v>1.528106238609573e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.07306567469417e-08</v>
+        <v>1.073065674694163e-08</v>
       </c>
       <c r="R6" t="n">
         <v>1.333078080618571e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>1.208355622570616e-08</v>
+        <v>1.208355622570608e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>1.056966346953885e-08</v>
+        <v>1.056966346953884e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>1.838255025929699e-08</v>
+        <v>1.838255025929701e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>1.06626814153131e-08</v>
+        <v>1.066268141531311e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>1.148626712927294e-08</v>
+        <v>1.14862671292729e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.568689612432286e-08</v>
+        <v>1.568689612432261e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.270196050262276e-08</v>
+        <v>1.270196050262278e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.429220988219647e-08</v>
+        <v>1.429220988219634e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.395996705854965e-08</v>
+        <v>1.395996705854961e-08</v>
       </c>
       <c r="AB6" t="n">
         <v>2.130896310758198e-08</v>
@@ -7906,85 +7906,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.602652099402699e-08</v>
+        <v>1.602652099402672e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.413733873406927e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.519131661999833e-08</v>
+        <v>1.519131661999837e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.477692032342478e-08</v>
+        <v>1.477692032342471e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.455566130707902e-08</v>
+        <v>1.455566130707901e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.85250828096873e-08</v>
+        <v>1.852508280968731e-08</v>
       </c>
       <c r="H7" t="n">
         <v>1.445519409697903e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.452120855999854e-08</v>
+        <v>1.452120855999855e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.711596126611798e-08</v>
+        <v>1.711596126611792e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.48017202812041e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.929647208287328e-08</v>
+        <v>1.929647208287207e-08</v>
       </c>
       <c r="M7" t="n">
-        <v>2.250303886134831e-08</v>
+        <v>2.250303886134834e-08</v>
       </c>
       <c r="N7" t="n">
-        <v>1.492819858717977e-08</v>
+        <v>1.492819858717978e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.500905212588541e-08</v>
+        <v>1.500905212588543e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.650649671234393e-08</v>
+        <v>1.650649671234392e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.484894245722104e-08</v>
+        <v>1.484894245722096e-08</v>
       </c>
       <c r="R7" t="n">
         <v>1.457731890397776e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.620184193598549e-08</v>
+        <v>1.620184193598543e-08</v>
       </c>
       <c r="T7" t="n">
-        <v>1.468794917981817e-08</v>
+        <v>1.468794917981815e-08</v>
       </c>
       <c r="U7" t="n">
-        <v>1.962780345691808e-08</v>
+        <v>1.962780345691807e-08</v>
       </c>
       <c r="V7" t="n">
-        <v>1.478096712559243e-08</v>
+        <v>1.478096712559242e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.544385915878979e-08</v>
+        <v>1.544385915878978e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.693343422211491e-08</v>
+        <v>1.693343422211464e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.668137661948225e-08</v>
+        <v>1.668137661948227e-08</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.553874797998849e-08</v>
+        <v>1.553874797998843e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.52065051563417e-08</v>
+        <v>1.520650515634169e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.536350065018232e-08</v>
+        <v>2.536350065018234e-08</v>
       </c>
     </row>
     <row r="8">
@@ -7994,85 +7994,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.408507699147708e-08</v>
+        <v>3.408507699147682e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.838620458284032e-08</v>
+        <v>4.838620458284033e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.944018246876936e-08</v>
+        <v>4.944018246876944e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.040492376015136e-08</v>
+        <v>4.040492376015132e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.51364783594783e-08</v>
+        <v>3.513647835947831e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.613111487636445e-08</v>
+        <v>5.613111487636451e-08</v>
       </c>
       <c r="H8" t="n">
         <v>4.870405994575007e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.87700744087696e-08</v>
+        <v>4.877007440876961e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.136482711488897e-08</v>
+        <v>5.136482711488899e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.905058612997516e-08</v>
+        <v>4.905058612997517e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.354533793164424e-08</v>
+        <v>5.354533793164357e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>5.675190471011977e-08</v>
+        <v>5.67519047101198e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.662686572193296e-08</v>
+        <v>3.662686572193297e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>4.015706894926511e-08</v>
+        <v>4.015706894926513e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>4.080910393108603e-08</v>
+        <v>4.080910393108604e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.972573304245814e-08</v>
+        <v>2.972573304245816e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.88261847527488e-08</v>
+        <v>4.882618475274883e-08</v>
       </c>
       <c r="S8" t="n">
         <v>5.045070778475655e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.893681502858918e-08</v>
+        <v>4.893681502858924e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>4.597503001607974e-08</v>
+        <v>4.597503001607976e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.46040601953214e-08</v>
+        <v>4.460406019532144e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.969590686968991e-08</v>
+        <v>4.969590686968995e-08</v>
       </c>
       <c r="X8" t="n">
-        <v>3.329409887730179e-08</v>
+        <v>3.329409887730163e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.702678700540243e-08</v>
+        <v>6.702678700540253e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.329656065961862e-08</v>
+        <v>3.329656065961853e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.945537100511271e-08</v>
+        <v>4.94553710051127e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>7.652449895255086e-08</v>
+        <v>7.652449895255087e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8082,85 +8082,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.848781709571492e-08</v>
+        <v>2.848781709571451e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.209757381581579e-08</v>
+        <v>3.209757381581578e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.315155170174486e-08</v>
+        <v>3.315155170174491e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.146802297714107e-08</v>
+        <v>3.146802297714097e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.983934079778504e-08</v>
+        <v>1.983934079778502e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.648531822789036e-08</v>
+        <v>3.648531822789037e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>3.241542917872556e-08</v>
+        <v>3.241542917872558e-08</v>
       </c>
       <c r="I9" t="n">
         <v>3.248144364174506e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.507619634786448e-08</v>
+        <v>3.507619634786445e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>3.276195536295064e-08</v>
+        <v>3.276195536295062e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.725670716461982e-08</v>
+        <v>3.725670716461852e-08</v>
       </c>
       <c r="M9" t="n">
         <v>4.046327394309484e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>3.288843366892628e-08</v>
+        <v>3.288843366892626e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.479207494256601e-08</v>
+        <v>3.479207494256598e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.668584749332425e-08</v>
+        <v>3.668584749332419e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.28091778754241e-08</v>
+        <v>3.280917787542405e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>3.253755398572427e-08</v>
+        <v>3.253755398572425e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>3.416207701773199e-08</v>
+        <v>3.416207701773185e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>3.26481842615647e-08</v>
+        <v>3.264818426156464e-08</v>
       </c>
       <c r="U9" t="n">
         <v>3.758932343883554e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.908685458360674e-08</v>
+        <v>3.908685458360676e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>3.340409424053632e-08</v>
+        <v>3.340409424053626e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.489366930386142e-08</v>
+        <v>3.489366930386105e-08</v>
       </c>
       <c r="Y9" t="n">
         <v>3.464161170122878e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.01836119750959e-08</v>
+        <v>3.018361197509573e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>3.316674023808822e-08</v>
+        <v>3.316674023808816e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.332373573192881e-08</v>
+        <v>4.332373573192878e-08</v>
       </c>
     </row>
   </sheetData>
@@ -8326,85 +8326,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.150683444692226e-08</v>
+        <v>1.150683444692187e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.990809444543549e-09</v>
+        <v>9.990809444543273e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.153418132619901e-08</v>
+        <v>1.153418132619857e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.150719421263916e-08</v>
+        <v>1.150719421263895e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150444061250385e-08</v>
+        <v>1.15044406125038e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.180482269958055e-08</v>
+        <v>1.180482269958011e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.15182671391071e-08</v>
+        <v>1.151826713910669e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.152464354379546e-08</v>
+        <v>1.152464354379501e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.16276058309565e-08</v>
+        <v>1.162760583095649e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.154169108628347e-08</v>
+        <v>1.154169108628309e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.165633947842667e-08</v>
+        <v>1.165633947842621e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.156932722540707e-08</v>
+        <v>1.156932722540709e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.153426215837317e-08</v>
+        <v>1.1534262158373e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.521009847628119e-08</v>
+        <v>1.521009847628127e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.159854189259925e-08</v>
+        <v>1.159854189259903e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.152304939976447e-08</v>
+        <v>1.152304939976419e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.152977646085343e-08</v>
+        <v>1.152977646085345e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.153861708506017e-08</v>
+        <v>1.153861708505978e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.151733410953986e-08</v>
+        <v>1.15173341095394e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.139196849473929e-08</v>
+        <v>1.139196849473928e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.152741363227078e-08</v>
+        <v>1.152741363227034e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.16276109648485e-08</v>
+        <v>1.162761096484846e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.170865765343972e-08</v>
+        <v>1.170865765343933e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.188171722040811e-08</v>
+        <v>1.188171722040763e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.104470275799158e-08</v>
+        <v>1.104470275799143e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.154525614555169e-08</v>
+        <v>1.154525614555184e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.207702470959155e-08</v>
+        <v>1.207702470959156e-08</v>
       </c>
     </row>
     <row r="3">
@@ -8414,85 +8414,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.177361747046473e-08</v>
+        <v>1.179126893962079e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>9.268261867399515e-09</v>
+        <v>9.286067856752524e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.197240652144311e-08</v>
+        <v>1.199717641560461e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.175495000635697e-08</v>
+        <v>1.176926750985805e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17606343788412e-08</v>
+        <v>1.177790454226981e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.38875265397059e-08</v>
+        <v>1.397973082055969e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.185972951523388e-08</v>
+        <v>1.188055512776761e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.19040401300355e-08</v>
+        <v>1.192641767602935e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.263297088293375e-08</v>
+        <v>1.268092975954811e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.202752320767787e-08</v>
+        <v>1.205417169376581e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.283847557574318e-08</v>
+        <v>1.289381360001005e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.230083978482899e-08</v>
+        <v>1.233777649317368e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.197106997821983e-08</v>
+        <v>1.199578354657225e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.794458355738258e-08</v>
+        <v>1.796481522769667e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.242491814857642e-08</v>
+        <v>1.246543173276985e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.189192518314324e-08</v>
+        <v>1.191382887249402e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.194125647215699e-08</v>
+        <v>1.19649755819637e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.200059311120198e-08</v>
+        <v>1.202625014568356e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.185171685500682e-08</v>
+        <v>1.187221750196086e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.197954681556747e-08</v>
+        <v>1.201527473484847e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.192222790215638e-08</v>
+        <v>1.194506222694595e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.231574704086637e-08</v>
+        <v>1.234919234005312e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.321690401367102e-08</v>
+        <v>1.328591990941675e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.444992516529109e-08</v>
+        <v>1.456231676945154e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.113702913167075e-08</v>
+        <v>1.116045371887518e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.204899770069507e-08</v>
+        <v>1.207643850025824e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.583547458346432e-08</v>
+        <v>1.599694234639717e-08</v>
       </c>
     </row>
     <row r="4">
@@ -8502,82 +8502,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.318261802764509e-09</v>
+        <v>7.318261802764504e-09</v>
       </c>
       <c r="C4" t="n">
         <v>7.317971317189422e-09</v>
       </c>
       <c r="D4" t="n">
-        <v>7.627157384381411e-09</v>
+        <v>7.627157384381402e-09</v>
       </c>
       <c r="E4" t="n">
-        <v>7.322325522037303e-09</v>
+        <v>7.322325522037298e-09</v>
       </c>
       <c r="F4" t="n">
-        <v>7.291222341790344e-09</v>
+        <v>7.291222341790334e-09</v>
       </c>
       <c r="G4" t="n">
-        <v>1.068417619790878e-08</v>
+        <v>1.068417619790873e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>7.447399320290531e-09</v>
+        <v>7.447399320290529e-09</v>
       </c>
       <c r="I4" t="n">
-        <v>7.519423744536578e-09</v>
+        <v>7.519423744536569e-09</v>
       </c>
       <c r="J4" t="n">
-        <v>8.672189363129404e-09</v>
+        <v>8.672189363129384e-09</v>
       </c>
       <c r="K4" t="n">
-        <v>7.711983579195716e-09</v>
+        <v>7.711983579195711e-09</v>
       </c>
       <c r="L4" t="n">
         <v>9.006989909319249e-09</v>
       </c>
       <c r="M4" t="n">
-        <v>8.16321813448244e-09</v>
+        <v>8.16321813448243e-09</v>
       </c>
       <c r="N4" t="n">
-        <v>7.62807042097332e-09</v>
+        <v>7.628070420973315e-09</v>
       </c>
       <c r="O4" t="n">
-        <v>7.435505048282283e-09</v>
+        <v>7.435505048282276e-09</v>
       </c>
       <c r="P4" t="n">
-        <v>8.354139589195454e-09</v>
+        <v>8.354139589195444e-09</v>
       </c>
       <c r="Q4" t="n">
-        <v>7.501417154364161e-09</v>
+        <v>7.501417154364151e-09</v>
       </c>
       <c r="R4" t="n">
-        <v>7.577402403964959e-09</v>
+        <v>7.577402403964954e-09</v>
       </c>
       <c r="S4" t="n">
-        <v>7.677261321268003e-09</v>
+        <v>7.677261321267995e-09</v>
       </c>
       <c r="T4" t="n">
-        <v>7.436860322113743e-09</v>
+        <v>7.436860322113746e-09</v>
       </c>
       <c r="U4" t="n">
-        <v>8.093063170937316e-09</v>
+        <v>8.093063170937311e-09</v>
       </c>
       <c r="V4" t="n">
-        <v>7.497518142677776e-09</v>
+        <v>7.497518142677777e-09</v>
       </c>
       <c r="W4" t="n">
-        <v>8.022137137335018e-09</v>
+        <v>8.022137137335013e-09</v>
       </c>
       <c r="X4" t="n">
-        <v>9.597947763641265e-09</v>
+        <v>9.597947763641252e-09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.15178669843725e-08</v>
+        <v>1.151786698437248e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>7.57822487721006e-09</v>
+        <v>7.578224877210053e-09</v>
       </c>
       <c r="AA4" t="n">
-        <v>7.752252563638551e-09</v>
+        <v>7.75225256363854e-09</v>
       </c>
       <c r="AB4" t="n">
         <v>1.370608329672734e-08</v>
@@ -8590,85 +8590,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2.762798926739042e-08</v>
+        <v>2.762798926739036e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>2.989989265070109e-08</v>
+        <v>2.989989265070108e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>3.496366843744505e-08</v>
+        <v>3.496366843744502e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.669529446228951e-08</v>
+        <v>1.66952944622895e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>2.9275418180894e-08</v>
+        <v>2.927541818089397e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.050161724006531e-08</v>
+        <v>8.050161724006439e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>3.225248374744857e-08</v>
+        <v>3.225248374744852e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>3.290546782483973e-08</v>
+        <v>3.290546782483967e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.039898132698175e-08</v>
+        <v>5.039898132698133e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>3.725122282971933e-08</v>
+        <v>3.725122282971932e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.637306514933903e-08</v>
+        <v>5.637306514933902e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.549927774436542e-08</v>
+        <v>4.54992777443654e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.398822181042189e-08</v>
+        <v>3.39882218104218e-08</v>
       </c>
       <c r="O5" t="n">
         <v>3.02738146621315e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.428054826316841e-08</v>
+        <v>4.428054826316831e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.220482083065173e-08</v>
+        <v>3.220482083065171e-08</v>
       </c>
       <c r="R5" t="n">
         <v>3.423275978029461e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>3.405074849320636e-08</v>
+        <v>3.405074849320632e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>3.136462473744216e-08</v>
+        <v>3.136462473744229e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.211569432911151e-08</v>
+        <v>4.211569432911155e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>3.258559387043525e-08</v>
+        <v>3.258559387043518e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.053502791387539e-08</v>
+        <v>4.053502791387532e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>6.943232593119837e-08</v>
+        <v>6.943232593119833e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.029106447432134e-07</v>
+        <v>1.029106447432133e-07</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.221385590195877e-08</v>
+        <v>3.221385590195876e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.590634682552631e-08</v>
+        <v>3.590634682552611e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.515082094970004e-07</v>
+        <v>1.515082094970006e-07</v>
       </c>
     </row>
     <row r="6">
@@ -8678,43 +8678,43 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.233728891984336e-08</v>
+        <v>1.233728891984337e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.233699843426827e-08</v>
+        <v>1.233699843426828e-08</v>
       </c>
       <c r="D6" t="n">
         <v>1.264618450146027e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>9.751347477647746e-09</v>
+        <v>9.751347477647736e-09</v>
       </c>
       <c r="F6" t="n">
-        <v>9.720244297400786e-09</v>
+        <v>9.720244297400781e-09</v>
       </c>
       <c r="G6" t="n">
-        <v>1.311319815351923e-08</v>
+        <v>1.311319815351918e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>9.876421275900964e-09</v>
+        <v>9.876421275900959e-09</v>
       </c>
       <c r="I6" t="n">
         <v>1.253845086161543e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.369121648020827e-08</v>
+        <v>1.369121648020826e-08</v>
       </c>
       <c r="K6" t="n">
         <v>1.014100553480614e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>1.402601702639809e-08</v>
+        <v>1.40260170263981e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>1.059224009009288e-08</v>
+        <v>1.059224009009287e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>1.006127790294228e-08</v>
+        <v>1.006127790294227e-08</v>
       </c>
       <c r="O6" t="n">
         <v>1.247255280927768e-08</v>
@@ -8723,7 +8723,7 @@
         <v>1.062543258212337e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>9.930439109974592e-09</v>
+        <v>9.930439109974587e-09</v>
       </c>
       <c r="R6" t="n">
         <v>1.259642952104382e-08</v>
@@ -8732,31 +8732,31 @@
         <v>1.010628327687844e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>9.865882277724171e-09</v>
+        <v>9.865882277724164e-09</v>
       </c>
       <c r="U6" t="n">
-        <v>1.314695848752691e-08</v>
+        <v>1.314695848752692e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>9.92654009828822e-09</v>
+        <v>9.926540098288215e-09</v>
       </c>
       <c r="W6" t="n">
-        <v>1.059828537453165e-08</v>
+        <v>1.059828537453159e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>1.461697488072013e-08</v>
+        <v>1.461697488072014e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.410673024402372e-08</v>
+        <v>1.410673024402371e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.259725199428891e-08</v>
+        <v>1.259725199428893e-08</v>
       </c>
       <c r="AA6" t="n">
         <v>1.018127451924899e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.617117919554211e-08</v>
+        <v>1.617117919554209e-08</v>
       </c>
     </row>
     <row r="7">
@@ -8766,7 +8766,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.361729755403593e-08</v>
+        <v>1.361729755403592e-08</v>
       </c>
       <c r="C7" t="n">
         <v>1.361700706846085e-08</v>
@@ -8775,28 +8775,28 @@
         <v>1.392619313565283e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>1.362136127330872e-08</v>
+        <v>1.362136127330871e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.359025809306177e-08</v>
+        <v>1.359025809306176e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.698321194918019e-08</v>
+        <v>1.698321194918015e-08</v>
       </c>
       <c r="H7" t="n">
         <v>1.374643507156196e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3818459495808e-08</v>
+        <v>1.381845949580799e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.497122511440083e-08</v>
+        <v>1.49712251144008e-08</v>
       </c>
       <c r="K7" t="n">
         <v>1.401101933046712e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.530602566059067e-08</v>
+        <v>1.530602566059069e-08</v>
       </c>
       <c r="M7" t="n">
         <v>1.446225388575387e-08</v>
@@ -8805,19 +8805,19 @@
         <v>1.392710617224476e-08</v>
       </c>
       <c r="O7" t="n">
-        <v>1.373412480277861e-08</v>
+        <v>1.37341248027786e-08</v>
       </c>
       <c r="P7" t="n">
-        <v>1.46527593436918e-08</v>
+        <v>1.465275934369178e-08</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.380045290563557e-08</v>
+        <v>1.380045290563558e-08</v>
       </c>
       <c r="R7" t="n">
         <v>1.387643815523639e-08</v>
       </c>
       <c r="S7" t="n">
-        <v>1.397629707253942e-08</v>
+        <v>1.397629707253941e-08</v>
       </c>
       <c r="T7" t="n">
         <v>1.373589607338516e-08</v>
@@ -8829,22 +8829,22 @@
         <v>1.379655389394921e-08</v>
       </c>
       <c r="W7" t="n">
-        <v>1.432117288860645e-08</v>
+        <v>1.432117288860644e-08</v>
       </c>
       <c r="X7" t="n">
-        <v>1.589698351491271e-08</v>
+        <v>1.589698351491269e-08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.785177093515465e-08</v>
+        <v>1.785177093515464e-08</v>
       </c>
       <c r="Z7" t="n">
         <v>1.387726062848149e-08</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.405128831490998e-08</v>
+        <v>1.405128831490997e-08</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.000511904799876e-08</v>
+        <v>2.000511904799877e-08</v>
       </c>
     </row>
     <row r="8">
@@ -8854,85 +8854,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.037103661239461e-08</v>
+        <v>3.037103661239458e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.539505026988952e-08</v>
+        <v>4.539505026988939e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.57042363370815e-08</v>
+        <v>4.570423633708139e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.739940570735151e-08</v>
+        <v>3.739940570735143e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.268460814440337e-08</v>
+        <v>3.268460814440331e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.187664248907665e-08</v>
+        <v>5.18766424890765e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.552447827299064e-08</v>
+        <v>4.552447827299054e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.559650269723669e-08</v>
+        <v>4.559650269723658e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.674926831582947e-08</v>
+        <v>4.674926831582941e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.57890625318958e-08</v>
+        <v>4.578906253189573e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.708406886201931e-08</v>
+        <v>4.708406886201921e-08</v>
       </c>
       <c r="M8" t="n">
-        <v>4.624029708718236e-08</v>
+        <v>4.624029708718228e-08</v>
       </c>
       <c r="N8" t="n">
-        <v>3.405880015201632e-08</v>
+        <v>3.405880015201625e-08</v>
       </c>
       <c r="O8" t="n">
-        <v>3.706675267014583e-08</v>
+        <v>3.706675267014578e-08</v>
       </c>
       <c r="P8" t="n">
-        <v>3.720086294053998e-08</v>
+        <v>3.720086294053994e-08</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.760157328627687e-08</v>
+        <v>2.760157328627684e-08</v>
       </c>
       <c r="R8" t="n">
-        <v>4.565448135666504e-08</v>
+        <v>4.565448135666495e-08</v>
       </c>
       <c r="S8" t="n">
-        <v>4.57543402739681e-08</v>
+        <v>4.575434027396799e-08</v>
       </c>
       <c r="T8" t="n">
-        <v>4.551393927481381e-08</v>
+        <v>4.551393927481372e-08</v>
       </c>
       <c r="U8" t="n">
-        <v>3.887173362208809e-08</v>
+        <v>3.887173362208803e-08</v>
       </c>
       <c r="V8" t="n">
-        <v>4.146810208049767e-08</v>
+        <v>4.146810208049761e-08</v>
       </c>
       <c r="W8" t="n">
-        <v>4.610216879847808e-08</v>
+        <v>4.610216879847798e-08</v>
       </c>
       <c r="X8" t="n">
         <v>3.107511122535831e-08</v>
       </c>
       <c r="Y8" t="n">
-        <v>6.456794210515113e-08</v>
+        <v>6.456794210515107e-08</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.035191552369346e-08</v>
+        <v>3.035191552369342e-08</v>
       </c>
       <c r="AA8" t="n">
-        <v>4.582933151633863e-08</v>
+        <v>4.582933151633856e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>6.747730424079996e-08</v>
+        <v>6.747730424079988e-08</v>
       </c>
     </row>
     <row r="9">
@@ -8942,82 +8942,82 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.389618095214516e-08</v>
+        <v>2.389618095214517e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.864461640074104e-08</v>
+        <v>2.864461640074105e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>2.895380246793303e-08</v>
+        <v>2.895380246793305e-08</v>
       </c>
       <c r="E9" t="n">
         <v>2.755298532658427e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.767075589607594e-08</v>
+        <v>1.767075589607595e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.201082296749122e-08</v>
+        <v>3.201082296749113e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>2.877404440384214e-08</v>
+        <v>2.877404440384215e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.884606882808822e-08</v>
+        <v>2.884606882808821e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>2.999883444668101e-08</v>
+        <v>2.9998834446681e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.903862866274734e-08</v>
+        <v>2.903862866274733e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.033363499287083e-08</v>
+        <v>3.033363499287091e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>2.94898632180341e-08</v>
+        <v>2.948986321803409e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.895471550452492e-08</v>
+        <v>2.895471550452494e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>3.033587393327219e-08</v>
+        <v>3.033587393327225e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>3.159676603376157e-08</v>
+        <v>3.159676603376163e-08</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.882806392394653e-08</v>
+        <v>2.882806392394655e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>2.890404748751661e-08</v>
+        <v>2.890404748751659e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>2.900390640481963e-08</v>
+        <v>2.900390640481962e-08</v>
       </c>
       <c r="T9" t="n">
-        <v>2.876350540566535e-08</v>
+        <v>2.876350540566536e-08</v>
       </c>
       <c r="U9" t="n">
         <v>2.945457645399968e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>3.430408957565152e-08</v>
+        <v>3.430408957565156e-08</v>
       </c>
       <c r="W9" t="n">
-        <v>2.934878222088663e-08</v>
+        <v>2.934878222088659e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>3.09245928471929e-08</v>
+        <v>3.092459284719289e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.287938026743488e-08</v>
+        <v>3.287938026743487e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.604181116514683e-08</v>
+        <v>2.604181116514685e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.907889764719019e-08</v>
+        <v>2.907889764719016e-08</v>
       </c>
       <c r="AB9" t="n">
         <v>3.503272838027894e-08</v>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.213865291037204e-08</v>
+        <v>1.213865291037207e-08</v>
       </c>
       <c r="C2" t="n">
         <v>1.025308702849027e-08</v>
@@ -598,28 +598,28 @@
         <v>1.187299594628183e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.185131203875434e-08</v>
+        <v>1.185131203875437e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.219613403884773e-08</v>
+        <v>1.219613403884776e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.184068895291672e-08</v>
+        <v>1.184068895291673e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.183362529011217e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.208287922756941e-08</v>
+        <v>1.208287922756942e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.186953817672823e-08</v>
+        <v>1.186953817672821e-08</v>
       </c>
       <c r="L2" t="n">
         <v>1.230312452242549e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.259351219136386e-08</v>
+        <v>1.259351219136385e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.185262907761089e-08</v>
@@ -628,43 +628,43 @@
         <v>1.581343175363934e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.200823482323903e-08</v>
+        <v>1.200823482323904e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.186785267238393e-08</v>
+        <v>1.186785267238392e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.182117453065316e-08</v>
+        <v>1.182117453065323e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.208451858537175e-08</v>
+        <v>1.208451858537172e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.185187494012947e-08</v>
+        <v>1.185187494012945e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.231928390110745e-08</v>
+        <v>1.231928390110746e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.192518963052711e-08</v>
+        <v>1.192518963052715e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.200665471067467e-08</v>
+        <v>1.200665471067464e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.200732940840247e-08</v>
+        <v>1.200732940840248e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.204580064465203e-08</v>
+        <v>1.204580064465206e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.15516404092926e-08</v>
+        <v>1.155164040929256e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.193985004639764e-08</v>
+        <v>1.193985004639768e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.297684091735405e-08</v>
+        <v>1.297684091735404e-08</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2.08471157689174e-08</v>
+        <v>1.474551043498321e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.134631920831849e-08</v>
+        <v>1.053120689570204e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.504123692388045e-08</v>
+        <v>1.282331151944325e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.367025566153545e-08</v>
+        <v>1.171804155706566e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.427648763113113e-08</v>
+        <v>1.256619437951606e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.217885538165744e-08</v>
+        <v>1.52221463044772e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.403178149318982e-08</v>
+        <v>1.248736109265397e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.385603331542582e-08</v>
+        <v>1.241237104232806e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.959877505163212e-08</v>
+        <v>1.436507013688196e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.468733236285469e-08</v>
+        <v>1.269674605721136e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.470970814283461e-08</v>
+        <v>1.613425311666506e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.179452682474557e-08</v>
+        <v>1.869614891337414e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.428665917548833e-08</v>
+        <v>1.255107445731123e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>2.050596608362158e-08</v>
+        <v>1.718145691302671e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.783562119715427e-08</v>
+        <v>1.373414551957832e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.464496415348396e-08</v>
+        <v>1.26784980013903e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.35682899382605e-08</v>
+        <v>1.231509230020409e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.962264242673535e-08</v>
+        <v>1.435251965884765e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.428001679186049e-08</v>
+        <v>1.255848841919765e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.861093754284418e-08</v>
+        <v>1.734162426803542e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.593938176740796e-08</v>
+        <v>1.309595594496861e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.631954492009331e-08</v>
+        <v>1.329195483969284e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.790230957552507e-08</v>
+        <v>1.381575887181605e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.876890881744066e-08</v>
+        <v>1.40947308189532e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.649742903186367e-08</v>
+        <v>1.301079214390994e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.630551709921521e-08</v>
+        <v>1.324460752630709e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.032443259181341e-08</v>
+        <v>2.184237828770481e-08</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.044267412487091e-07</v>
+        <v>1.044267412487089e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.288416047604669e-08</v>
+        <v>3.288416047604672e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.502564677895002e-08</v>
+        <v>5.502564677895001e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.711569738866993e-08</v>
+        <v>3.711569738867007e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.812509830034585e-08</v>
+        <v>4.81250983003458e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.188372299508602e-07</v>
+        <v>1.188372299508601e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.618246107271513e-08</v>
+        <v>4.618246107271511e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.315009182699523e-08</v>
+        <v>4.315009182699526e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.676676854868946e-08</v>
+        <v>9.676676854868951e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.110645637896072e-08</v>
+        <v>5.110645637896064e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.475164342881764e-07</v>
+        <v>1.475164342881753e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.299961227913909e-07</v>
+        <v>2.299961227913912e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.645639674541526e-08</v>
+        <v>4.645639674541527e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>6.570335064605319e-08</v>
+        <v>6.570335064605326e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>7.718803059222007e-08</v>
+        <v>7.718803059222e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.035596801741587e-08</v>
+        <v>5.035596801741585e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>4.049338728589629e-08</v>
+        <v>4.049338728589632e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>9.517018991446338e-08</v>
+        <v>9.517018991446341e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.73161591654935e-08</v>
+        <v>4.731615916549332e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.844339919233371e-07</v>
+        <v>1.844339919233369e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.020551430599566e-08</v>
+        <v>6.020551430599564e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>6.520180227248392e-08</v>
+        <v>6.520180227248397e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>8.377012388165884e-08</v>
+        <v>8.377012388165842e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>9.033036304513649e-08</v>
+        <v>9.033036304513652e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>6.92905787567866e-08</v>
+        <v>6.929057875678666e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>6.600482779799036e-08</v>
+        <v>6.600482779799032e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.290201742866338e-07</v>
+        <v>3.290201742866337e-07</v>
       </c>
     </row>
     <row r="5">
@@ -850,25 +850,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.819488019003747e-08</v>
+        <v>3.819488019003737e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>5.164560202293805e-08</v>
+        <v>5.164560202293803e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.268810673248047e-08</v>
+        <v>5.268810673248048e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.331213198533713e-08</v>
+        <v>4.331213198533711e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.765427021884332e-08</v>
+        <v>3.765427021884326e-08</v>
       </c>
       <c r="G5" t="n">
         <v>5.980814497577369e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>5.21927850779824e-08</v>
+        <v>5.219278507798244e-08</v>
       </c>
       <c r="I5" t="n">
         <v>5.211299775715948e-08</v>
@@ -877,58 +877,58 @@
         <v>5.491807503583928e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>5.251865033223197e-08</v>
+        <v>5.251865033223207e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.741620756645598e-08</v>
+        <v>5.741620756645597e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>6.076578706877899e-08</v>
+        <v>6.076578706877906e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.645639674541526e-08</v>
+        <v>3.886800215735484e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.374037796785073e-08</v>
+        <v>4.374037796785065e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.341779747789595e-08</v>
+        <v>4.341779747789591e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.172373405892045e-08</v>
+        <v>3.172373405892043e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>5.197236070143768e-08</v>
+        <v>5.197236070143772e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>5.494695294373456e-08</v>
+        <v>5.49469529437346e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>5.23191359493586e-08</v>
+        <v>5.23191359493587e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>5.092997527082239e-08</v>
+        <v>5.092997527082234e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.83469246191376e-08</v>
+        <v>4.834692461913765e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.3291083802363e-08</v>
+        <v>5.329108380236292e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.489059134435562e-08</v>
+        <v>3.489059134435555e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>7.177278194214742e-08</v>
+        <v>7.17727819421475e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.593963919981976e-08</v>
+        <v>3.593963919981973e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>5.331285524520605e-08</v>
+        <v>5.331285524520614e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.303839315834561e-08</v>
+        <v>8.303839315834565e-08</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.402471437820306e-08</v>
+        <v>3.402471437820305e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.651615515703712e-08</v>
+        <v>3.651615515703708e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.755865986657957e-08</v>
+        <v>3.755865986657949e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.595018285987868e-08</v>
+        <v>3.59501828598787e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>2.241975445720664e-08</v>
+        <v>2.24197544572066e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>4.107825430736469e-08</v>
+        <v>4.107825430736461e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.706333821208153e-08</v>
+        <v>3.706333821208154e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.698355089125855e-08</v>
+        <v>3.698355089125857e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.978862816993834e-08</v>
+        <v>3.978862816993829e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.738920346633106e-08</v>
+        <v>3.738920346633108e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>4.228676070055505e-08</v>
+        <v>4.228676070055497e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.563634020287798e-08</v>
+        <v>4.563634020287795e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.645639674541526e-08</v>
+        <v>3.719820741323082e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>4.049411903846932e-08</v>
+        <v>4.04941190384693e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>4.153978889919542e-08</v>
+        <v>4.153978889919537e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.737016525626659e-08</v>
+        <v>3.737016525626644e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.684291383553683e-08</v>
+        <v>3.684291383553675e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.981750607783366e-08</v>
+        <v>3.981750607783365e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.718968908345771e-08</v>
+        <v>3.718968908345765e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>4.427603416502333e-08</v>
+        <v>4.427603416502338e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>4.53542258557264e-08</v>
+        <v>4.535422585572637e-08</v>
       </c>
       <c r="W6" t="n">
         <v>3.815822449985911e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.894561881518967e-08</v>
+        <v>3.89456188151896e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.938016912627159e-08</v>
+        <v>3.938016912627151e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.463507250153074e-08</v>
+        <v>3.463507250153062e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.818340837930516e-08</v>
+        <v>3.818340837930512e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.977127177031129e-08</v>
+        <v>4.977127177031125e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1182,82 +1182,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.134762365869345e-08</v>
+        <v>1.13476236586934e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.828775943552293e-09</v>
+        <v>9.828775943552291e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.136979469707404e-08</v>
+        <v>1.136979469707399e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.133862939251851e-08</v>
+        <v>1.133862939251845e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.135051244107921e-08</v>
+        <v>1.135051244107916e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.139449799014905e-08</v>
+        <v>1.1394497990149e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.136812993694071e-08</v>
+        <v>1.136812993694066e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.136775044338865e-08</v>
+        <v>1.136775044338862e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.138110433251294e-08</v>
+        <v>1.138110433251285e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.137416663440041e-08</v>
+        <v>1.137416663440039e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.137264989325482e-08</v>
+        <v>1.137264989325477e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.137174279354702e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.136197552008248e-08</v>
+        <v>1.136197552008244e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.501377936816862e-08</v>
+        <v>1.501377936816857e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.135882106154844e-08</v>
+        <v>1.135882106154828e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.135704423371348e-08</v>
+        <v>1.135704423371342e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.137034897720797e-08</v>
+        <v>1.137034897720793e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.13730623337907e-08</v>
+        <v>1.137306233379065e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.135986529328682e-08</v>
+        <v>1.135986529328678e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.124191740573242e-08</v>
+        <v>1.124191740573236e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.13810206909245e-08</v>
+        <v>1.138102069092445e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.151381354246878e-08</v>
+        <v>1.151381354246871e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.15669487472918e-08</v>
+        <v>1.156694874729176e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.155213011398591e-08</v>
+        <v>1.155213011398585e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.089028292891308e-08</v>
+        <v>1.089028292891306e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.141157853357006e-08</v>
+        <v>1.141157853357001e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.137864578109887e-08</v>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.246118167014548e-08</v>
+        <v>1.168980418004102e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.086452777260054e-08</v>
+        <v>1.017250586520077e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.29942707357562e-08</v>
+        <v>1.189617841632426e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.121422431209951e-08</v>
+        <v>1.068594010132659e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.254856884779191e-08</v>
+        <v>1.174161266211665e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.354225128945099e-08</v>
+        <v>1.206128472643276e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.29646755075821e-08</v>
+        <v>1.189351518608967e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.294854562381338e-08</v>
+        <v>1.187842806107555e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.324004756187293e-08</v>
+        <v>1.196587190802232e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.309548877989825e-08</v>
+        <v>1.193884886703311e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.304778899263815e-08</v>
+        <v>1.190536660753766e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.331354797400736e-08</v>
+        <v>1.200482823130175e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.280496965864201e-08</v>
+        <v>1.18143161189586e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.615483818954916e-08</v>
+        <v>1.537196255327783e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.271698460296894e-08</v>
+        <v>1.177611693562029e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.269273004541926e-08</v>
+        <v>1.178132600812828e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.301194369372885e-08</v>
+        <v>1.190090677519346e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.305123013706667e-08</v>
+        <v>1.189191156990013e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.276221965264556e-08</v>
+        <v>1.180853664705447e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.356803872953276e-08</v>
+        <v>1.197056419312729e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.323446867452783e-08</v>
+        <v>1.195997969471102e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.441665115917812e-08</v>
+        <v>1.242260395078581e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.758546617971267e-08</v>
+        <v>1.344920055313837e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.721953471322873e-08</v>
+        <v>1.334076016931392e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.2229716833045e-08</v>
+        <v>1.130671875060935e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.395307666767515e-08</v>
+        <v>1.22077757527494e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.324811697980454e-08</v>
+        <v>1.199451757565515e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1358,82 +1358,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.77098815952212e-08</v>
+        <v>2.770988159522119e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.894732433433878e-08</v>
+        <v>2.894732433433879e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.409347295360887e-08</v>
+        <v>3.409347295360888e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.600870994792589e-08</v>
+        <v>1.600870994792587e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.02117675657291e-08</v>
+        <v>3.021176756572907e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.68594745892586e-08</v>
+        <v>3.685947458925853e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.447239498849872e-08</v>
+        <v>3.447239498849875e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.358669151694465e-08</v>
+        <v>3.358669151694463e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.495688173991382e-08</v>
+        <v>3.49568817399138e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.549282809956271e-08</v>
+        <v>3.549282809956267e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.375414002930823e-08</v>
+        <v>3.375414002930822e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.749788334955862e-08</v>
+        <v>3.749788334955858e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>3.122557469609028e-08</v>
       </c>
       <c r="O4" t="n">
         <v>2.845616345653514e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.973395643077936e-08</v>
+        <v>2.973395643077938e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.067565988914389e-08</v>
+        <v>3.067565988914386e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.421702061522115e-08</v>
+        <v>3.421702061522111e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.270462069851469e-08</v>
+        <v>3.270462069851463e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.155018276657902e-08</v>
+        <v>3.155018276657899e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.893975583514387e-08</v>
+        <v>3.893975583514381e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.455335514672665e-08</v>
+        <v>3.455335514672656e-08</v>
       </c>
       <c r="W4" t="n">
         <v>4.406982322154622e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>7.186641741551296e-08</v>
+        <v>7.186641741551299e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.962404487899696e-08</v>
+        <v>6.962404487899697e-08</v>
       </c>
       <c r="Z4" t="n">
         <v>2.995215196572591e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.092561328125656e-08</v>
+        <v>4.09256132812565e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>3.717151784110143e-08</v>
@@ -1449,82 +1449,82 @@
         <v>3.022213888769809e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.514411447139258e-08</v>
+        <v>4.514411447139264e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.544166296541992e-08</v>
+        <v>4.544166296541999e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7119036583833e-08</v>
+        <v>3.711903658383298e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.258677860003039e-08</v>
+        <v>3.258677860003046e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.882463676571549e-08</v>
+        <v>4.882463676571554e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.542285873388655e-08</v>
+        <v>4.542285873388657e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.541857217964026e-08</v>
+        <v>4.541857217964018e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.556029319569839e-08</v>
+        <v>4.556029319569842e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.549104600871199e-08</v>
+        <v>4.549104600871202e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.547391371973699e-08</v>
+        <v>4.547391371973709e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.559885243338283e-08</v>
+        <v>4.559885243338289e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>3.374979119029939e-08</v>
       </c>
       <c r="O5" t="n">
         <v>3.679047823461338e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.612127532349661e-08</v>
+        <v>3.612127532349658e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.738678038476011e-08</v>
+        <v>2.738678038476013e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.544792381451423e-08</v>
+        <v>4.54479238145142e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.547857242532161e-08</v>
+        <v>4.547857242532167e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.532950578189182e-08</v>
+        <v>4.532950578189188e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.850189900942179e-08</v>
+        <v>3.850189900942181e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.143253476212328e-08</v>
+        <v>4.14325347621232e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.610140623408479e-08</v>
+        <v>4.610140623408482e-08</v>
       </c>
       <c r="X5" t="n">
         <v>3.11296954536875e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.238609708938815e-08</v>
+        <v>6.238609708938818e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>3.00590178246992e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.591363062015689e-08</v>
+        <v>4.591363062015696e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.12010985905967e-08</v>
+        <v>6.120109859059665e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1534,49 +1534,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.258278115982267e-08</v>
+        <v>2.258278115982264e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.693831059837476e-08</v>
+        <v>2.693831059837472e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.723585909240211e-08</v>
+        <v>2.723585909240206e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.586772110849263e-08</v>
+        <v>2.586772110849262e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.686875485854568e-08</v>
+        <v>1.686875485854566e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.751489567676154e-08</v>
+        <v>2.75148956767615e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.721705486086863e-08</v>
+        <v>2.721705486086862e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.721276830662232e-08</v>
+        <v>2.72127683066223e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.735448932268053e-08</v>
+        <v>2.735448932268052e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.728524213569411e-08</v>
+        <v>2.72852421356941e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.726810984671918e-08</v>
+        <v>2.726810984671915e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.739304856036512e-08</v>
+        <v>2.739304856036507e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.12255746960903e-08</v>
+        <v>2.714753789128344e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.845850158666731e-08</v>
+        <v>2.845850158666728e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.888825426815359e-08</v>
+        <v>2.88882542681536e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>2.709183826824243e-08</v>
@@ -1588,31 +1588,31 @@
         <v>2.727276855230374e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.712370190887399e-08</v>
+        <v>2.712370190887397e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.760146490725333e-08</v>
+        <v>2.760146490725329e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.239763564882839e-08</v>
+        <v>3.239763564882833e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.789266050334949e-08</v>
+        <v>2.789266050334945e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.946280478495562e-08</v>
+        <v>2.946280478495558e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.929542150485738e-08</v>
+        <v>2.929542150485737e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.444596117456894e-08</v>
+        <v>2.444596117456892e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.770782674713905e-08</v>
+        <v>2.7707826747139e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.735882642633472e-08</v>
+        <v>2.735882642633467e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1778,76 +1778,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.203346931499851e-08</v>
+        <v>1.20334693149985e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.020238665030074e-08</v>
+        <v>1.020238665030076e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.192210603746631e-08</v>
+        <v>1.19221060374663e-08</v>
       </c>
       <c r="E2" t="n">
         <v>1.181456428875208e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.179781392370277e-08</v>
+        <v>1.179781392370273e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.214371165378672e-08</v>
+        <v>1.214371165378669e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.176341002612216e-08</v>
+        <v>1.176341002612218e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.177312139330817e-08</v>
+        <v>1.177312139330814e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.20416188979692e-08</v>
+        <v>1.204161889796918e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.18158317737317e-08</v>
+        <v>1.181583177373168e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.225733564115021e-08</v>
+        <v>1.225733564115027e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.249587348173707e-08</v>
+        <v>1.249587348173708e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.180660666306633e-08</v>
+        <v>1.180660666306631e-08</v>
       </c>
       <c r="O2" t="n">
         <v>1.572702033415187e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.201907951416345e-08</v>
+        <v>1.20190795141634e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.181640103162668e-08</v>
+        <v>1.181640103162667e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.176734484146559e-08</v>
+        <v>1.176734484146557e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.204340987798241e-08</v>
+        <v>1.204340987798244e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.180964025493745e-08</v>
+        <v>1.180964025493744e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.219476483951509e-08</v>
+        <v>1.21947648395151e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.182276677862168e-08</v>
+        <v>1.182276677862166e-08</v>
       </c>
       <c r="W2" t="n">
         <v>1.193529609496817e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.198970410693888e-08</v>
+        <v>1.198970410693889e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.197640786662191e-08</v>
+        <v>1.197640786662189e-08</v>
       </c>
       <c r="Z2" t="n">
         <v>1.145469409999427e-08</v>
@@ -1856,7 +1856,7 @@
         <v>1.185049277404948e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.2899086218504e-08</v>
+        <v>1.289908621850402e-08</v>
       </c>
     </row>
     <row r="3">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.937951322268044e-08</v>
+        <v>1.421967082616675e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.108605975710243e-08</v>
+        <v>1.042378185430192e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.688701575836914e-08</v>
+        <v>1.344288879662928e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.32838233170632e-08</v>
+        <v>1.156307098558914e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.399498185090499e-08</v>
+        <v>1.244034102008706e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.192532864554448e-08</v>
+        <v>1.510168195520778e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.31916377871134e-08</v>
+        <v>1.216573283813002e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.341145970748911e-08</v>
+        <v>1.223072226836933e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.96087225727045e-08</v>
+        <v>1.43422170868372e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.440303123203976e-08</v>
+        <v>1.257616980343486e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.460983209803408e-08</v>
+        <v>1.607384790038181e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>3.048479866951819e-08</v>
+        <v>1.8200370919023e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.41810898414755e-08</v>
+        <v>1.248851458824959e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.995135731361269e-08</v>
+        <v>1.695306372961908e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.903834192203623e-08</v>
+        <v>1.411570419124904e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.441276248387751e-08</v>
+        <v>1.257134947053065e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.32793473697277e-08</v>
+        <v>1.218772011819929e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.963010512047502e-08</v>
+        <v>1.432227891391477e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.426272222060901e-08</v>
+        <v>1.252713648218805e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.689828134079828e-08</v>
+        <v>1.671921525325953e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.453419519324842e-08</v>
+        <v>1.259631000646501e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.579391304887418e-08</v>
+        <v>1.307953856204834e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.845851834244526e-08</v>
+        <v>1.398055690353183e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.812010781386818e-08</v>
+        <v>1.384046766084495e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.57033399584274e-08</v>
+        <v>1.269754291092261e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.519419138414902e-08</v>
+        <v>1.283391027137118e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.948107772502754e-08</v>
+        <v>2.151992882377695e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.578911900862367e-08</v>
+        <v>8.57891190086328e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.960898381515031e-08</v>
+        <v>2.960898381515035e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.01613841049758e-08</v>
+        <v>7.016138410497568e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.193975748368151e-08</v>
+        <v>3.193975748368592e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.298781852538601e-08</v>
+        <v>4.29878185253861e-08</v>
       </c>
       <c r="G4" t="n">
         <v>1.093956946945464e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.56826036657614e-08</v>
+        <v>3.568260366576152e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.684032628435437e-08</v>
+        <v>3.684032628435448e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.164861214208128e-08</v>
+        <v>9.164861214208145e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.625055286099941e-08</v>
+        <v>4.625055286100027e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.382399426209136e-07</v>
+        <v>1.382399426209576e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>2.029724422783492e-07</v>
+        <v>2.029724422783493e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.327732681729057e-08</v>
+        <v>4.327732681729097e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>5.772507386104596e-08</v>
+        <v>5.772507386104606e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>8.353845427998989e-08</v>
+        <v>8.353845427998944e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.569264932108301e-08</v>
+        <v>4.569264932108395e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.583624853452061e-08</v>
+        <v>3.583624853452074e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>8.95703041716941e-08</v>
+        <v>8.957030417169483e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.495710568888194e-08</v>
+        <v>4.495710568888292e-08</v>
       </c>
       <c r="U4" t="n">
         <v>1.582100642454846e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>4.514290681932916e-08</v>
+        <v>4.514290681932908e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.707556993478202e-08</v>
+        <v>5.707556993478196e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>8.438802698939677e-08</v>
+        <v>8.438802698940043e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.912784259192335e-08</v>
+        <v>7.912784259192338e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.873051941759033e-08</v>
+        <v>5.873051941759632e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.225703494636989e-08</v>
+        <v>5.225703494637091e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.012199460760801e-07</v>
+        <v>3.012199460760814e-07</v>
       </c>
     </row>
     <row r="5">
@@ -2042,58 +2042,58 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.568688687018105e-08</v>
+        <v>3.568688687018099e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.862181788705422e-08</v>
+        <v>4.862181788705416e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>5.06848497513723e-08</v>
+        <v>5.068484975137224e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.081434905443513e-08</v>
+        <v>4.081434905443541e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.555752418374626e-08</v>
+        <v>3.555752418374622e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.655874608284184e-08</v>
+        <v>5.655874608284176e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.889230529946817e-08</v>
+        <v>4.889230529946807e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.900199965928369e-08</v>
+        <v>4.900199965928356e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.202413349711103e-08</v>
+        <v>5.202413349711095e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.94844330539132e-08</v>
+        <v>4.948443305391319e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.447142233821841e-08</v>
+        <v>5.447142233821995e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.723869389733834e-08</v>
+        <v>5.723869389733821e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.327732681729057e-08</v>
+        <v>3.677921833307225e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.120552135330411e-08</v>
+        <v>4.120552135330397e-08</v>
       </c>
       <c r="P5" t="n">
         <v>4.179323211507967e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.004035278260598e-08</v>
+        <v>3.004035278260606e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.89367508488767e-08</v>
+        <v>4.893675084887664e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>5.205503243252514e-08</v>
+        <v>5.205503243252517e-08</v>
       </c>
       <c r="T5" t="n">
         <v>4.941449700089282e-08</v>
@@ -2102,25 +2102,25 @@
         <v>4.774295679462552e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.506273478795992e-08</v>
+        <v>4.506273478795983e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>5.014245642780963e-08</v>
+        <v>5.014245642780961e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.348777282653996e-08</v>
+        <v>3.348777282654002e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.745948608170784e-08</v>
+        <v>6.745948608170775e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.37937628250458e-08</v>
+        <v>3.379376282504589e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.987594499735052e-08</v>
+        <v>4.987594499735048e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.857734532213395e-08</v>
+        <v>7.857734532213377e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.016577729620916e-08</v>
+        <v>3.016577729620969e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.239337657700114e-08</v>
+        <v>3.239337657700117e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.445640844131927e-08</v>
+        <v>3.44564084413193e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.196109701946447e-08</v>
+        <v>3.196109701946471e-08</v>
       </c>
       <c r="F6" t="n">
         <v>2.026159392008618e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.69595462511793e-08</v>
+        <v>3.695954625117936e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.266386398941507e-08</v>
+        <v>3.266386398941512e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.27735583492306e-08</v>
+        <v>3.277355834923067e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.57956921870579e-08</v>
+        <v>3.579569218705793e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.325599174386008e-08</v>
+        <v>3.325599174386018e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.824298102816536e-08</v>
+        <v>3.824298102816526e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.101025258728495e-08</v>
+        <v>4.101025258728498e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.327732681729057e-08</v>
+        <v>3.315178987513422e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.595400149580495e-08</v>
+        <v>3.595400149580492e-08</v>
       </c>
       <c r="P6" t="n">
         <v>3.77904470305281e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.326242220355652e-08</v>
+        <v>3.326242220355655e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.270830953882361e-08</v>
+        <v>3.270830953882366e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.582659112247208e-08</v>
+        <v>3.582659112247206e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.318605569083977e-08</v>
+        <v>3.318605569083988e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.944969782937019e-08</v>
+        <v>3.944969782937023e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.9681152712793e-08</v>
+        <v>3.968115271279302e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.391082037268224e-08</v>
+        <v>3.391082037268225e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.521995973266025e-08</v>
+        <v>3.52199597326609e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.506977258170733e-08</v>
+        <v>3.506977258170737e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.077787445115796e-08</v>
+        <v>3.0777874451158e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.36475036872974e-08</v>
+        <v>3.364750368729748e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.536829651250801e-08</v>
+        <v>4.536829651250803e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2374,82 +2374,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.200825001805885e-08</v>
+        <v>1.200825001805889e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.024256840721446e-08</v>
+        <v>1.024256840721447e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.198981828295094e-08</v>
+        <v>1.198981828295097e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183524683557806e-08</v>
+        <v>1.183524683557809e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.185249425025795e-08</v>
+        <v>1.185249425025798e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.215013689107323e-08</v>
+        <v>1.215013689107326e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.179102796092953e-08</v>
+        <v>1.179102796092956e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.187815724695634e-08</v>
+        <v>1.187815724695637e-08</v>
       </c>
       <c r="J2" t="n">
         <v>1.206243034609628e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.190202010149282e-08</v>
+        <v>1.190202010149287e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.222703673953923e-08</v>
+        <v>1.222703673953926e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.243087829117756e-08</v>
+        <v>1.243087829117758e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.182363094677182e-08</v>
+        <v>1.182363094677185e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.573923474663775e-08</v>
+        <v>1.573923474663779e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204713299399124e-08</v>
+        <v>1.204713299399127e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.185180741583592e-08</v>
+        <v>1.185180741583595e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.179043105743742e-08</v>
+        <v>1.179043105743746e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205363860561468e-08</v>
+        <v>1.205363860561472e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.184263429953698e-08</v>
+        <v>1.184263429953702e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.210383904541571e-08</v>
+        <v>1.210383904541574e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.18968574443674e-08</v>
+        <v>1.189685744436744e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.201042223607881e-08</v>
+        <v>1.201042223607884e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.210920898499079e-08</v>
+        <v>1.210920898499082e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.222076776491942e-08</v>
+        <v>1.222076776491945e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.151354497640666e-08</v>
+        <v>1.151354497640668e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.188158795141909e-08</v>
+        <v>1.188158795141912e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.284690012958399e-08</v>
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.813818945905351e-08</v>
+        <v>1.383621596104716e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.124239519960109e-08</v>
+        <v>1.051578402725443e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.779572728675042e-08</v>
+        <v>1.378365893008113e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.308564739005988e-08</v>
+        <v>1.151422579772671e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.460175244488215e-08</v>
+        <v>1.267650547974934e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.140935494100157e-08</v>
+        <v>1.494126529875538e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.316413176927868e-08</v>
+        <v>1.218105661780564e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.519492051124191e-08</v>
+        <v>1.288275365508585e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.942918708154187e-08</v>
+        <v>1.43047115148324e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.573971123954314e-08</v>
+        <v>1.305241264760507e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.324131547299077e-08</v>
+        <v>1.562382443524438e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.831400585349223e-08</v>
+        <v>1.747070465664953e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.390806271739484e-08</v>
+        <v>1.242082737545289e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.93754070280394e-08</v>
+        <v>1.679292979011576e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.902162230896517e-08</v>
+        <v>1.413073570393062e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.456709008876351e-08</v>
+        <v>1.264916206930849e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.314606134938784e-08</v>
+        <v>1.216753361206926e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.920177253787729e-08</v>
+        <v>1.419852759452283e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.436135950370204e-08</v>
+        <v>1.258820373965047e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.337642695259262e-08</v>
+        <v>1.555062622826875e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.557887219097271e-08</v>
+        <v>1.297078081748675e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.591358864690942e-08</v>
+        <v>1.31760762885797e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.057419524954712e-08</v>
+        <v>1.473833278640567e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.312639495902745e-08</v>
+        <v>1.559015919592949e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.587253703955136e-08</v>
+        <v>1.278140066444702e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.524842729985915e-08</v>
+        <v>1.287965657834683e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.761730637316998e-08</v>
+        <v>2.089522998662495e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2550,85 +2550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.094813373978432e-08</v>
+        <v>7.094813373978448e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.959534868339293e-08</v>
+        <v>2.959534868339291e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.359442052425184e-08</v>
+        <v>7.359442052425204e-08</v>
       </c>
       <c r="E4" t="n">
         <v>2.834426803809834e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.554619586745796e-08</v>
+        <v>4.554619586745803e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.732317589348228e-08</v>
+        <v>9.732317589348232e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.301181584733112e-08</v>
+        <v>3.301181584733118e-08</v>
       </c>
       <c r="I4" t="n">
         <v>5.07488666948917e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.411469706549073e-08</v>
+        <v>8.411469706549078e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.408987300180276e-08</v>
+        <v>5.408987300180281e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.172257353559268e-07</v>
+        <v>1.172257353559266e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.70377453566421e-07</v>
+        <v>1.703774535664207e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>3.812021875520144e-08</v>
+        <v>3.812021875520145e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>4.946370492984697e-08</v>
+        <v>4.946370492984708e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>7.762982082258618e-08</v>
+        <v>7.762982082258633e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.39490253916905e-08</v>
+        <v>4.394902539169052e-08</v>
       </c>
       <c r="R4" t="n">
         <v>3.230289695639454e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>7.99594542253792e-08</v>
+        <v>7.995945422537928e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.294928031348015e-08</v>
+        <v>4.294928031348022e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.172583620680241e-07</v>
+        <v>1.17258362068024e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>5.031871036616468e-08</v>
+        <v>5.03187103661646e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.409595545904352e-08</v>
+        <v>5.409595545904345e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>9.743946458712612e-08</v>
+        <v>9.743946458712627e-08</v>
       </c>
       <c r="Y4" t="n">
         <v>1.170476729642256e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.504490100546145e-08</v>
+        <v>5.504490100546135e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.939457967731387e-08</v>
+        <v>4.939457967731392e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.649185272091996e-07</v>
+        <v>2.649185272092001e-07</v>
       </c>
     </row>
     <row r="5">
@@ -2638,28 +2638,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.343521350472646e-08</v>
+        <v>3.343521350472649e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.599249870240793e-08</v>
+        <v>4.599249870240795e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.842261724452325e-08</v>
+        <v>4.842261724452329e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.858545359164054e-08</v>
+        <v>3.858545359164059e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.404317713404734e-08</v>
+        <v>3.404317713404737e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.338439604732225e-08</v>
+        <v>5.338439604732222e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.617718910922532e-08</v>
+        <v>4.617718910922534e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.716135447634988e-08</v>
+        <v>4.716135447634992e-08</v>
       </c>
       <c r="J5" t="n">
         <v>4.923252244240045e-08</v>
@@ -2674,13 +2674,13 @@
         <v>5.348990760274125e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.812021875520144e-08</v>
+        <v>3.476632369788128e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.881188474643174e-08</v>
+        <v>3.881188474643178e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.973442089192104e-08</v>
+        <v>3.97344208919211e-08</v>
       </c>
       <c r="Q5" t="n">
         <v>2.868184038422193e-08</v>
@@ -2689,34 +2689,34 @@
         <v>4.617044680969286e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.914349714780926e-08</v>
+        <v>4.914349714780928e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.676010644388525e-08</v>
+        <v>4.676010644388522e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.382363995249534e-08</v>
+        <v>4.382363995249536e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.316568455088882e-08</v>
+        <v>4.316568455088888e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.747730864454603e-08</v>
+        <v>4.747730864454608e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.298201633166409e-08</v>
+        <v>3.298201633166411e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.613951221391057e-08</v>
+        <v>6.613951221391067e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.224375640259736e-08</v>
+        <v>3.224375640259739e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.720010586145867e-08</v>
+        <v>4.72001058614587e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.386670147097993e-08</v>
+        <v>7.386670147097989e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.72145300083769e-08</v>
+        <v>2.721453000837691e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.946979270155142e-08</v>
+        <v>2.94697927015514e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.18999112436668e-08</v>
+        <v>3.189991124366679e-08</v>
       </c>
       <c r="E6" t="n">
         <v>2.902453869142526e-08</v>
@@ -2741,70 +2741,70 @@
         <v>1.906774368688869e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.371078428356896e-08</v>
+        <v>3.371078428356898e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.965448310836873e-08</v>
+        <v>2.965448310836872e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.063864847549339e-08</v>
+        <v>3.063864847549337e-08</v>
       </c>
       <c r="J6" t="n">
         <v>3.27098164415439e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.09081903949385e-08</v>
+        <v>3.090819039493848e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.457940283671298e-08</v>
+        <v>3.457940283671299e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.696720160188441e-08</v>
+        <v>3.696720160188442e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.812021875520144e-08</v>
+        <v>3.002274883157191e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.245302791276357e-08</v>
+        <v>3.24530279127636e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.452173016624357e-08</v>
+        <v>3.452173016624359e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.034101562242463e-08</v>
+        <v>3.034101562242465e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.964774080883633e-08</v>
+        <v>2.964774080883635e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.262079114695272e-08</v>
+        <v>3.262079114695273e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.023740044302871e-08</v>
+        <v>3.02374004430287e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.471795043502039e-08</v>
+        <v>3.471795043502038e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.644351541880989e-08</v>
+        <v>3.644351541880998e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.09516162709824e-08</v>
+        <v>3.095161627098242e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.324848414564337e-08</v>
+        <v>3.324848414564336e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>3.450859188451129e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.824852408594425e-08</v>
+        <v>2.824852408594427e-08</v>
       </c>
       <c r="AA6" t="n">
         <v>3.067739986060217e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.147092202525391e-08</v>
+        <v>4.147092202525393e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2970,85 +2970,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.199563586921689e-08</v>
+        <v>1.199563586921687e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.027110172678947e-08</v>
+        <v>1.027110172678946e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.196863855200409e-08</v>
+        <v>1.196863855200407e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.183674444224599e-08</v>
+        <v>1.183674444224596e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1892778565856e-08</v>
+        <v>1.189277856585597e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.212731634521484e-08</v>
+        <v>1.212731634521481e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.181894399229587e-08</v>
+        <v>1.181894399229584e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.190102461201904e-08</v>
+        <v>1.190102461201901e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.206357142694365e-08</v>
+        <v>1.206357142694362e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.194613077154588e-08</v>
+        <v>1.194613077154586e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.216957062051298e-08</v>
+        <v>1.216957062051295e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.234646677195876e-08</v>
+        <v>1.234646677195875e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.183522745707941e-08</v>
+        <v>1.183522745707938e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.570773927726701e-08</v>
+        <v>1.570773927726697e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.204697861659763e-08</v>
+        <v>1.20469786165976e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.188275750172841e-08</v>
+        <v>1.188275750172839e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.18371432125233e-08</v>
+        <v>1.183714321252327e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.205454323066636e-08</v>
+        <v>1.205454323066634e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.188065695156173e-08</v>
+        <v>1.188065695156171e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.217517741405799e-08</v>
+        <v>1.217517741405796e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.201217435493646e-08</v>
+        <v>1.201217435493644e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.208838183292688e-08</v>
+        <v>1.208838183292686e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.21678175284356e-08</v>
+        <v>1.216781752843558e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.250396072776025e-08</v>
+        <v>1.250396072776022e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.154580000128325e-08</v>
+        <v>1.154580000128322e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.192026751470034e-08</v>
+        <v>1.192026751470031e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.276852037689611e-08</v>
+        <v>1.276852037689609e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.734456033179355e-08</v>
+        <v>1.358486390875774e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.136788462415823e-08</v>
+        <v>1.058964823060446e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.679081584283868e-08</v>
+        <v>1.345165078535199e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.260152743256865e-08</v>
+        <v>1.13740734849121e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.503425399381305e-08</v>
+        <v>1.285338352162828e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.037904291797306e-08</v>
+        <v>1.460113458046376e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.330725678034059e-08</v>
+        <v>1.225945171376848e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.521951095035246e-08</v>
+        <v>1.291896524728543e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.895363797767514e-08</v>
+        <v>1.415589110332137e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.625883725202623e-08</v>
+        <v>1.325469498059845e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.140144018991549e-08</v>
+        <v>1.498840876951963e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.583982467450747e-08</v>
+        <v>1.657271962499279e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.367072861303387e-08</v>
+        <v>1.23672729053578e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.840052036080896e-08</v>
+        <v>1.648958486439478e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.851521648383956e-08</v>
+        <v>1.397262596151308e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.477956826866273e-08</v>
+        <v>1.274734255070833e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.372939817241892e-08</v>
+        <v>1.240137489751208e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.871873035316308e-08</v>
+        <v>1.405650596514968e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.474012137684755e-08</v>
+        <v>1.274922061335342e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.358618866594523e-08</v>
+        <v>1.564112161987688e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.773327704732034e-08</v>
+        <v>1.371226462832327e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.623846743079568e-08</v>
+        <v>1.334621191240435e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>2.142847191847135e-08</v>
+        <v>1.503410881188124e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.920080360880828e-08</v>
+        <v>1.774368488913168e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.569826370489467e-08</v>
+        <v>1.275230919581267e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.564036266895897e-08</v>
+        <v>1.304432947682048e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.529591111216693e-08</v>
+        <v>2.005468588278217e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3146,40 +3146,40 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.341512229210379e-08</v>
+        <v>6.341512229210382e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.042270222857074e-08</v>
+        <v>3.042270222857079e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.354031694097899e-08</v>
+        <v>6.354031694097918e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.455490968527829e-08</v>
+        <v>2.45549096852783e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.894294785913378e-08</v>
+        <v>4.894294785913375e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.726220613583519e-08</v>
+        <v>8.72622061358332e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.396908495784158e-08</v>
+        <v>3.396908495784153e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>5.057586720185798e-08</v>
+        <v>5.057586720185809e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.882477978732833e-08</v>
+        <v>7.882477978732823e-08</v>
       </c>
       <c r="K4" t="n">
         <v>5.790083103727863e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>9.900686848048316e-08</v>
+        <v>9.900686848048315e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>1.433430311188779e-07</v>
+        <v>1.433430311188778e-07</v>
       </c>
       <c r="N4" t="n">
         <v>3.5720000539158e-08</v>
@@ -3188,43 +3188,43 @@
         <v>4.174851038037545e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>7.215426934161182e-08</v>
+        <v>7.215426934161189e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.520928039612582e-08</v>
+        <v>4.52092803961258e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.736064411184848e-08</v>
+        <v>3.736064411184846e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>7.521652377281525e-08</v>
+        <v>7.521652377281521e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>4.604751520502842e-08</v>
+        <v>4.604751520502848e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.157192804354308e-07</v>
+        <v>1.157192804354305e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>6.633452097336517e-08</v>
+        <v>6.633452097336565e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.623933264954414e-08</v>
+        <v>5.62393326495441e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>1.026210065344772e-07</v>
+        <v>1.026210065344773e-07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.71312480279395e-07</v>
+        <v>1.713124802793949e-07</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.238281442699084e-08</v>
+        <v>5.238281442699082e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>5.251847744302988e-08</v>
+        <v>5.251847744302998e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.396508982675624e-07</v>
+        <v>2.396508982675627e-07</v>
       </c>
     </row>
     <row r="5">
@@ -3234,85 +3234,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.31500410768694e-08</v>
+        <v>3.315004107686946e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.618285064826631e-08</v>
+        <v>4.618285064826633e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.806738190115945e-08</v>
+        <v>4.806738190115948e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.84721579572183e-08</v>
+        <v>3.847215795721829e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.435967507361342e-08</v>
+        <v>3.435967507361345e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.301616113969885e-08</v>
+        <v>5.301616113969881e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.637651298635528e-08</v>
+        <v>4.637651298635529e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.730365134507906e-08</v>
+        <v>4.730365134507907e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.913026037572828e-08</v>
+        <v>4.913026037572827e-08</v>
       </c>
       <c r="K5" t="n">
         <v>4.781314616679339e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.033700204828538e-08</v>
+        <v>5.033700204828539e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.243140790542952e-08</v>
+        <v>5.243140790542951e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.5720000539158e-08</v>
+        <v>3.476062242436469e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.84534992467254e-08</v>
+        <v>3.845349924672533e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.960027972342454e-08</v>
+        <v>3.960027972342445e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.888350097659345e-08</v>
+        <v>2.888350097659343e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.658208155087901e-08</v>
+        <v>4.658208155087905e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.903771476475438e-08</v>
+        <v>4.903771476475439e-08</v>
       </c>
       <c r="T5" t="n">
         <v>4.707358925062707e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.402654253378962e-08</v>
+        <v>4.402654253378966e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.435224035011303e-08</v>
+        <v>4.4352240350113e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.774422824919954e-08</v>
+        <v>4.774422824919948e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.349853805066347e-08</v>
+        <v>3.349853805066351e-08</v>
       </c>
       <c r="Y5" t="n">
         <v>6.925123343701412e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.225277750091252e-08</v>
+        <v>3.225277750091249e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.752100878303693e-08</v>
+        <v>4.752100878303698e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.290636480050677e-08</v>
+        <v>7.290636480050673e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.608247536209569e-08</v>
+        <v>2.608247536209563e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.856398008273313e-08</v>
+        <v>2.856398008273309e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.044851133562629e-08</v>
+        <v>3.044851133562624e-08</v>
       </c>
       <c r="E6" t="n">
         <v>2.788066339095136e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.882374611487608e-08</v>
+        <v>1.882374611487603e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.224085071268901e-08</v>
+        <v>3.224085071268903e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.875764242082204e-08</v>
+        <v>2.875764242082202e-08</v>
       </c>
       <c r="I6" t="n">
         <v>2.968478077954581e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.151138981019504e-08</v>
+        <v>3.151138981019501e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.019427560126011e-08</v>
+        <v>3.01942756012601e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.271813148275212e-08</v>
+        <v>3.271813148275215e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.481253733989559e-08</v>
+        <v>3.48125373398956e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.5720000539158e-08</v>
+        <v>2.894157164631603e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.093971415576291e-08</v>
+        <v>3.093971415576281e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.321801131330193e-08</v>
+        <v>3.321801131330186e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.947844607288366e-08</v>
+        <v>2.947844607288368e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.896321098534582e-08</v>
+        <v>2.896321098534579e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.141884419922107e-08</v>
+        <v>3.141884419922109e-08</v>
       </c>
       <c r="T6" t="n">
         <v>2.945471868509382e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.383631779555898e-08</v>
+        <v>3.383631779555894e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.628279292364544e-08</v>
+        <v>3.628279292364536e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.012236606576226e-08</v>
+        <v>3.012236606576222e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.26983295012761e-08</v>
+        <v>3.269832950127608e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.649522157115936e-08</v>
+        <v>3.649522157115934e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.732276952795146e-08</v>
+        <v>2.732276952795141e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.99021382175037e-08</v>
+        <v>2.990213821750372e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.938654161093608e-08</v>
+        <v>3.938654161093601e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3566,85 +3566,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.139152097196643e-08</v>
+        <v>1.139152097196641e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.823024575394119e-09</v>
+        <v>9.823024575394094e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.139493105860045e-08</v>
+        <v>1.139493105860044e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.136361534692925e-08</v>
+        <v>1.136361534692923e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.136576876560804e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.146841185979327e-08</v>
+        <v>1.146841185979325e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.140610300674654e-08</v>
+        <v>1.140610300674652e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.137033077003934e-08</v>
+        <v>1.137033077003933e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.144179793753666e-08</v>
+        <v>1.144179793753665e-08</v>
       </c>
       <c r="K2" t="n">
         <v>1.139709721850018e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.149856676090581e-08</v>
+        <v>1.14985667609058e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.158560153203676e-08</v>
+        <v>1.158560153203674e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.13869028463651e-08</v>
+        <v>1.138690284636508e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.501488619051585e-08</v>
+        <v>1.501488619051582e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.142569227800419e-08</v>
+        <v>1.142569227800418e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.138303416016311e-08</v>
+        <v>1.138303416016309e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.138068435544312e-08</v>
+        <v>1.13806843554431e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14182209937198e-08</v>
+        <v>1.141822099371978e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.137329749904477e-08</v>
+        <v>1.137329749904475e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.13459742600213e-08</v>
+        <v>1.134597426002129e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.137708083932971e-08</v>
+        <v>1.13770808393297e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.147076931713043e-08</v>
+        <v>1.147076931713041e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.143232596517722e-08</v>
+        <v>1.14323259651772e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.138933582772568e-08</v>
+        <v>1.138933582772567e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.093404526010629e-08</v>
+        <v>1.093404526010627e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.140844574373579e-08</v>
+        <v>1.140844574373578e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.161363539958099e-08</v>
+        <v>1.161363539958098e-08</v>
       </c>
     </row>
     <row r="3">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.311454472959842e-08</v>
+        <v>1.190409057793427e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.059291694932301e-08</v>
+        <v>1.005995567511345e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.321793469162887e-08</v>
+        <v>1.196118311714262e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.143699830579094e-08</v>
+        <v>1.074381046784118e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.254258867941802e-08</v>
+        <v>1.173378587500323e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.488643378479383e-08</v>
+        <v>1.250235353701227e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.349185873510809e-08</v>
+        <v>1.207153165431064e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.264579465693926e-08</v>
+        <v>1.17641317567398e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.42821907838763e-08</v>
+        <v>1.230653751399895e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.32678402724848e-08</v>
+        <v>1.19887542431081e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.560067092989915e-08</v>
+        <v>1.274890531370061e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.791332440221573e-08</v>
+        <v>1.355618805002521e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.302403308537244e-08</v>
+        <v>1.188528459359017e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.638978704197148e-08</v>
+        <v>1.542897933144105e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.389687314141895e-08</v>
+        <v>1.216398719500839e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.2936534552715e-08</v>
+        <v>1.185863068226258e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.289037361371732e-08</v>
+        <v>1.185022235141194e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.373496354502537e-08</v>
+        <v>1.211381532667423e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.271503433694838e-08</v>
+        <v>1.179657276490882e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.687910917290964e-08</v>
+        <v>1.304586971831711e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.278626767924215e-08</v>
+        <v>1.180591473157603e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.455450503898203e-08</v>
+        <v>1.242061827051051e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.408810035652204e-08</v>
+        <v>1.225905614781748e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.307849260953753e-08</v>
+        <v>1.190513606652537e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.311911984755299e-08</v>
+        <v>1.15876997321105e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.352043532483628e-08</v>
+        <v>1.205372827564668e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.831734593486609e-08</v>
+        <v>1.37650573345623e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3742,85 +3742,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.487021820880911e-08</v>
+        <v>3.487021820880906e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.77163681150945e-08</v>
+        <v>2.771636811509449e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.773931097784954e-08</v>
+        <v>3.77393109778496e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.746512532678136e-08</v>
+        <v>1.746512532678131e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.193068511352238e-08</v>
+        <v>3.193068511352236e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.010459859076707e-08</v>
+        <v>5.010459859076704e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.163821703612024e-08</v>
+        <v>4.163821703612016e-08</v>
       </c>
       <c r="I4" t="n">
         <v>3.24612139069999e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.563019781389244e-08</v>
+        <v>4.563019781389238e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.895207518848892e-08</v>
+        <v>3.895207518848893e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.691927502483065e-08</v>
+        <v>5.691927502483057e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>8.048449286739712e-08</v>
+        <v>8.048449286739708e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.518116351001804e-08</v>
+        <v>3.51811635100179e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.237458266726175e-08</v>
+        <v>3.237458266726168e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>4.121185534013212e-08</v>
+        <v>4.121185534013221e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.466396783779092e-08</v>
+        <v>3.46639678377909e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.490721407103547e-08</v>
+        <v>3.490721407103541e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>4.029662503879373e-08</v>
+        <v>4.029662503879379e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.37317654593704e-08</v>
+        <v>3.373176545937037e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>7.050204348924087e-08</v>
+        <v>7.050204348924093e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.298947132154801e-08</v>
+        <v>3.298947132154751e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.871598499842995e-08</v>
+        <v>4.871598499842997e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>4.564007558867508e-08</v>
+        <v>4.564007558867527e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>3.573321492585913e-08</v>
+        <v>3.573321492585907e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.896310537840948e-08</v>
+        <v>3.896310537840944e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.950986459975446e-08</v>
+        <v>3.950986459975443e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.857188276608738e-08</v>
+        <v>8.857188276608728e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3830,85 +3830,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.215664446814888e-08</v>
+        <v>3.215664446814884e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.766070226222093e-08</v>
+        <v>4.766070226222076e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.819324190004985e-08</v>
+        <v>4.819324190004969e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.932101141140009e-08</v>
+        <v>3.932101141140005e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.435807517551745e-08</v>
+        <v>3.435807517551739e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.23405472374301e-08</v>
+        <v>5.234054723742997e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.831943419371001e-08</v>
+        <v>4.831943419370985e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.791537032406034e-08</v>
+        <v>4.791537032406016e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.871302625573493e-08</v>
+        <v>4.871302625573491e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.821770967260028e-08</v>
+        <v>4.821770967260027e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.936385483236744e-08</v>
+        <v>4.936385483236729e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>5.046300140568994e-08</v>
+        <v>5.046300140568975e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.518116351001804e-08</v>
+        <v>3.570137195563397e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.898293224251567e-08</v>
+        <v>3.898293224251561e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.871209857927127e-08</v>
+        <v>3.871209857927126e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.89167943750614e-08</v>
+        <v>2.891679437506132e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.80323188340805e-08</v>
+        <v>4.803231883408048e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.84563124311223e-08</v>
+        <v>4.84563124311222e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.794888089293938e-08</v>
+        <v>4.79488808929393e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.228763371566397e-08</v>
+        <v>4.228763371566383e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.357079941434437e-08</v>
+        <v>4.357079941434431e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.884444806534257e-08</v>
+        <v>4.884444806534249e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.09398237125399e-08</v>
+        <v>3.093982371253983e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.403739452025491e-08</v>
+        <v>6.403739452025486e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.209553413517435e-08</v>
+        <v>3.20955341351743e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.834589648571598e-08</v>
+        <v>4.834589648571588e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.736948463205896e-08</v>
+        <v>6.736948463205875e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3918,28 +3918,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.595479735634816e-08</v>
+        <v>2.595479735634813e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.070884339499433e-08</v>
+        <v>3.070884339499431e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.12413830328232e-08</v>
+        <v>3.124138303282322e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.967642615201773e-08</v>
+        <v>2.967642615201772e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.881375266184438e-08</v>
+        <v>1.881375266184435e-08</v>
       </c>
       <c r="G6" t="n">
         <v>3.207138376821319e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.136757532648337e-08</v>
+        <v>3.136757532648338e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.096351145683369e-08</v>
+        <v>3.096351145683367e-08</v>
       </c>
       <c r="J6" t="n">
         <v>3.17611673885084e-08</v>
@@ -3948,13 +3948,13 @@
         <v>3.126585080537367e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.24119959651408e-08</v>
+        <v>3.241199596514082e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>3.351114253846334e-08</v>
+        <v>3.351114253846333e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.518116351001804e-08</v>
+        <v>3.115070068246496e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.276351123926417e-08</v>
@@ -3963,40 +3963,40 @@
         <v>3.370629627299876e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.110700337520823e-08</v>
+        <v>3.110700337520825e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.108045996685397e-08</v>
+        <v>3.108045996685393e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.150445356389567e-08</v>
+        <v>3.150445356389568e-08</v>
       </c>
       <c r="T6" t="n">
         <v>3.099702202571281e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.314373988598189e-08</v>
+        <v>3.314373988598186e-08</v>
       </c>
       <c r="V6" t="n">
         <v>3.704707754174635e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.188944511482921e-08</v>
+        <v>3.188944511482919e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.166377570511478e-08</v>
+        <v>3.16637757051148e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.117818232615937e-08</v>
+        <v>3.117818232615936e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.827480940922015e-08</v>
+        <v>2.827480940922018e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.139403761848934e-08</v>
+        <v>3.139403761848932e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.370629457774523e-08</v>
+        <v>3.370629457774522e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4162,85 +4162,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.132508230450345e-08</v>
+        <v>1.132508230450341e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.799869730262659e-09</v>
+        <v>9.799869730262639e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.133706504672696e-08</v>
+        <v>1.133706504672694e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.132080731072436e-08</v>
+        <v>1.132080731072433e-08</v>
       </c>
       <c r="F2" t="n">
         <v>1.132870519083258e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.135741783367121e-08</v>
+        <v>1.135741783367117e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.134765803233254e-08</v>
+        <v>1.134765803233251e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.134232003676065e-08</v>
+        <v>1.134232003676062e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.134960937396415e-08</v>
+        <v>1.134960937396414e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.134434052395288e-08</v>
+        <v>1.134434052395285e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.13400281336283e-08</v>
+        <v>1.134002813362827e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.132686932756375e-08</v>
+        <v>1.132686932756374e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.134721280151237e-08</v>
+        <v>1.134721280151233e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.499783897017278e-08</v>
+        <v>1.499783897017276e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.132756341014266e-08</v>
+        <v>1.132756341014265e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.132523746462747e-08</v>
+        <v>1.132523746462744e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.134571869313344e-08</v>
+        <v>1.13457186931334e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.134261154068106e-08</v>
+        <v>1.134261154068103e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.132321816856014e-08</v>
+        <v>1.132321816856012e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.113520624809811e-08</v>
+        <v>1.113520624809806e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.134644148126296e-08</v>
+        <v>1.134644148126293e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.141757258958375e-08</v>
+        <v>1.141757258958369e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.147935535824728e-08</v>
+        <v>1.147935535824725e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.141284074638944e-08</v>
+        <v>1.141284074638941e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.088688883183396e-08</v>
+        <v>1.088688883183393e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.136816116940707e-08</v>
+        <v>1.136816116940704e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.1327306005108e-08</v>
+        <v>1.132730600510798e-08</v>
       </c>
     </row>
     <row r="3">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.25254852834834e-08</v>
+        <v>1.168732800466368e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.083368728715692e-08</v>
+        <v>1.013913138962796e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.282302900686224e-08</v>
+        <v>1.181942775751606e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.139361982250014e-08</v>
+        <v>1.071487850755442e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.263222873638533e-08</v>
+        <v>1.174987453813873e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.327335633381901e-08</v>
+        <v>1.195835093720235e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.307982615089854e-08</v>
+        <v>1.191257641000618e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.294739743665245e-08</v>
+        <v>1.185842363085585e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.309608554131829e-08</v>
+        <v>1.189929323102992e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.299167052848727e-08</v>
+        <v>1.188242175476213e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.288261949802264e-08</v>
+        <v>1.184940119531091e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.286839929227515e-08</v>
+        <v>1.18498363833604e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.305154214414237e-08</v>
+        <v>1.187832666286222e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.664781379756122e-08</v>
+        <v>1.550686634921286e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.258061829138874e-08</v>
+        <v>1.170484322007445e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.254349591402294e-08</v>
+        <v>1.171390255864216e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.302973763708092e-08</v>
+        <v>1.188861345147159e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.293422624551444e-08</v>
+        <v>1.183556489997541e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.250103419880468e-08</v>
+        <v>1.171224637244305e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.256191834695022e-08</v>
+        <v>1.159874422082436e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.302231944049208e-08</v>
+        <v>1.187127591778524e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.374158342446149e-08</v>
+        <v>1.214422061675901e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.613521142025981e-08</v>
+        <v>1.293139487481782e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.457321292235781e-08</v>
+        <v>1.24022009954294e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.271176833171893e-08</v>
+        <v>1.144358977912631e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.353409489333465e-08</v>
+        <v>1.204239664401546e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.265373050981309e-08</v>
+        <v>1.176664902850858e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4338,49 +4338,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.830374784953838e-08</v>
+        <v>2.83037478495384e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.898932164122182e-08</v>
+        <v>2.898932164122174e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.314018127986164e-08</v>
+        <v>3.314018127986158e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.66398924732398e-08</v>
+        <v>1.663989247323978e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.128040831817298e-08</v>
+        <v>3.128040831817294e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.561797538577303e-08</v>
+        <v>3.561797538577305e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.581538459098051e-08</v>
+        <v>3.581538459098052e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.398050444150585e-08</v>
+        <v>3.398050444150573e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.427273081554421e-08</v>
+        <v>3.427273081554419e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.492251789090839e-08</v>
+        <v>3.492251789090838e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.417421314376585e-08</v>
+        <v>3.417421314376583e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.529942179363321e-08</v>
+        <v>3.529942179363318e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.36631711031545e-08</v>
+        <v>3.366317110315448e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.265662412979657e-08</v>
+        <v>3.265662412979652e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>2.864494107873306e-08</v>
+        <v>2.8644941078733e-08</v>
       </c>
       <c r="Q4" t="n">
         <v>3.003856412167315e-08</v>
@@ -4389,34 +4389,34 @@
         <v>3.485960502137982e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.235325776393133e-08</v>
+        <v>3.235325776393129e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.061551824981174e-08</v>
+        <v>3.061551824981169e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>3.247298891710255e-08</v>
+        <v>3.247298891710252e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.342014885917003e-08</v>
+        <v>3.34201488591699e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>3.920836008844076e-08</v>
+        <v>3.920836008844067e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>5.979871296954548e-08</v>
+        <v>5.979871296954559e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.671783699859977e-08</v>
+        <v>4.671783699859966e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.373160446380497e-08</v>
+        <v>3.373160446380491e-08</v>
       </c>
       <c r="AA4" t="n">
         <v>3.762045308419599e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.220021666612287e-08</v>
+        <v>3.220021666612288e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4426,85 +4426,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.016251698340766e-08</v>
+        <v>3.016251698340756e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.498208658184883e-08</v>
+        <v>4.498208658184866e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.521031027556296e-08</v>
+        <v>4.52103102755628e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.708623581641153e-08</v>
+        <v>3.708623581641139e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.25266234396106e-08</v>
+        <v>3.25266234396105e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.853239650770935e-08</v>
+        <v>4.853239650770911e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.532996292099205e-08</v>
+        <v>4.532996292099186e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.526966780540814e-08</v>
+        <v>4.526966780540801e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.534281865095729e-08</v>
+        <v>4.53428186509571e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.529249013771454e-08</v>
+        <v>4.529249013771434e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.524377970520095e-08</v>
+        <v>4.524377970520076e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.523458975462683e-08</v>
+        <v>4.523458975462665e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.36631711031545e-08</v>
+        <v>3.376529593983477e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.692268634921165e-08</v>
+        <v>3.692268634921153e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.594135268976077e-08</v>
+        <v>3.594135268976066e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.723363423607794e-08</v>
+        <v>2.723363423607785e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.53080571925981e-08</v>
+        <v>4.530805719259788e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.52729604762877e-08</v>
+        <v>4.527296047628754e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.505390341679007e-08</v>
+        <v>4.505390341678991e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.790824728921466e-08</v>
+        <v>3.790824728921451e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.119537471893957e-08</v>
+        <v>4.119537471893943e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.564546757274227e-08</v>
+        <v>4.56454675727421e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.034122174912421e-08</v>
+        <v>3.03412217491241e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.08948758331023e-08</v>
+        <v>6.089487583310206e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.020481133740313e-08</v>
+        <v>3.020481133740299e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.556155528615782e-08</v>
+        <v>4.556155528615764e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.070634911927862e-08</v>
+        <v>6.070634911927837e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4514,85 +4514,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.329408471883083e-08</v>
+        <v>2.32940847188308e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.779240389437174e-08</v>
+        <v>2.779240389437171e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.802062758808592e-08</v>
+        <v>2.802062758808583e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.677736179095791e-08</v>
+        <v>2.677736179095785e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.734224576004135e-08</v>
+        <v>1.734224576004132e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.825052331982844e-08</v>
+        <v>2.825052331982827e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.814028023351504e-08</v>
+        <v>2.814028023351498e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.807998511793112e-08</v>
+        <v>2.807998511793109e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.815313596348025e-08</v>
+        <v>2.815313596348022e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>2.810280745023753e-08</v>
+        <v>2.810280745023745e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.805409701772393e-08</v>
+        <v>2.805409701772383e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.804490706714984e-08</v>
+        <v>2.80449070671498e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.36631711031545e-08</v>
+        <v>2.813525114658481e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.963746998602043e-08</v>
+        <v>2.963746998602037e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.976572307720415e-08</v>
+        <v>2.976572307720408e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.788703124777816e-08</v>
+        <v>2.788703124777814e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.811837450512102e-08</v>
+        <v>2.811837450512095e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.808327778881069e-08</v>
+        <v>2.808327778881063e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.786422072931302e-08</v>
+        <v>2.786422072931299e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.799622757771342e-08</v>
+        <v>2.799622757771339e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.337862952345601e-08</v>
+        <v>3.337862952345595e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.845285416077675e-08</v>
+        <v>2.845285416077671e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.962786211348504e-08</v>
+        <v>2.962786211348503e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.887654897431754e-08</v>
+        <v>2.887654897431748e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.543649760506885e-08</v>
+        <v>2.543649760506881e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.837187259868077e-08</v>
+        <v>2.837187259868075e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.793937306470458e-08</v>
+        <v>2.793937306470451e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4758,82 +4758,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.136347868403526e-08</v>
+        <v>1.136347868403522e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.832431474720823e-09</v>
+        <v>9.832431474720826e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.137330172214631e-08</v>
+        <v>1.137330172214627e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.136531464443595e-08</v>
+        <v>1.136531464443592e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.135602768815527e-08</v>
+        <v>1.135602768815524e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.140248629565286e-08</v>
+        <v>1.140248629565283e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.137152179707776e-08</v>
+        <v>1.137152179707773e-08</v>
       </c>
       <c r="I2" t="n">
         <v>1.137195043110635e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.138390651204292e-08</v>
+        <v>1.13839065120429e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.137723181750269e-08</v>
+        <v>1.137723181750265e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.136929609067965e-08</v>
+        <v>1.136929609067963e-08</v>
       </c>
       <c r="M2" t="n">
         <v>1.136342634264024e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.13672858094162e-08</v>
+        <v>1.136728580941621e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.505529870758286e-08</v>
+        <v>1.505529870758282e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.136483097580231e-08</v>
+        <v>1.136483097580237e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.135685863435413e-08</v>
+        <v>1.135685863435409e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.138508614398731e-08</v>
+        <v>1.138508614398728e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.1364253183946e-08</v>
+        <v>1.136425318394597e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.135769005546647e-08</v>
+        <v>1.135769005546642e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.119530059505071e-08</v>
+        <v>1.119530059505074e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.138419227910454e-08</v>
+        <v>1.138419227910458e-08</v>
       </c>
       <c r="W2" t="n">
         <v>1.152082241009949e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.155224109439796e-08</v>
+        <v>1.155224109439792e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.144433348194389e-08</v>
+        <v>1.144433348194386e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.090573677472215e-08</v>
+        <v>1.090573677472212e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.140937137062877e-08</v>
+        <v>1.140937137062874e-08</v>
       </c>
       <c r="AB2" t="n">
         <v>1.137006682877986e-08</v>
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.275488607297263e-08</v>
+        <v>1.178741584468491e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.086122517860995e-08</v>
+        <v>1.016879157838902e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.300387231753435e-08</v>
+        <v>1.189848721223808e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.176433678640743e-08</v>
+        <v>1.087207240239203e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.260526085686621e-08</v>
+        <v>1.17602673416695e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.365504304545008e-08</v>
+        <v>1.209900746368585e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.297195550618928e-08</v>
+        <v>1.189741733265944e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.297442477197837e-08</v>
+        <v>1.188686686672471e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.323309782983589e-08</v>
+        <v>1.196372735203219e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.309398493513326e-08</v>
+        <v>1.193152145924785e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.2900058126483e-08</v>
+        <v>1.186543111021573e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.305244251968475e-08</v>
+        <v>1.191873814707609e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.285671569339736e-08</v>
+        <v>1.18329259733181e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.677920249644673e-08</v>
+        <v>1.55872164625657e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.278411422922756e-08</v>
+        <v>1.179873661316764e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.261659586240498e-08</v>
+        <v>1.175601028848743e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.328482162689425e-08</v>
+        <v>1.199691399532562e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.277683280827896e-08</v>
+        <v>1.180095985807424e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.264017309593277e-08</v>
+        <v>1.177268771695874e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.260345539374325e-08</v>
+        <v>1.164773756549124e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.323624606506881e-08</v>
+        <v>1.195991297985865e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.46586664357199e-08</v>
+        <v>1.250025042502274e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.716925324348413e-08</v>
+        <v>1.329635363092516e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.464391127883324e-08</v>
+        <v>1.244849336548334e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.243763858468652e-08</v>
+        <v>1.137726935061245e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.383017633571725e-08</v>
+        <v>1.216557687029314e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.298218609909204e-08</v>
+        <v>1.190077043289267e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4937,7 +4937,7 @@
         <v>2.996613889101078e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.870485427196003e-08</v>
+        <v>2.870485427196004e-08</v>
       </c>
       <c r="D4" t="n">
         <v>3.411252356525063e-08</v>
@@ -4946,73 +4946,73 @@
         <v>2.025961352126952e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.065096141238107e-08</v>
+        <v>3.065096141238109e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>3.77466575342853e-08</v>
+        <v>3.774665753428596e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>3.463918423671087e-08</v>
+        <v>3.46391842367109e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.378403356670777e-08</v>
+        <v>3.378403356670779e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>3.49159219695879e-08</v>
+        <v>3.491592196958783e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.500910035853893e-08</v>
+        <v>3.500910035853895e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>3.325887412708317e-08</v>
+        <v>3.325887412708319e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>3.551024345152284e-08</v>
+        <v>3.551024345152287e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>3.173270529966531e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.314066176272288e-08</v>
+        <v>3.314066176272289e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>3.02742468064342e-08</v>
+        <v>3.027424680643419e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.008651781203387e-08</v>
+        <v>3.008651781203388e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.674171005085948e-08</v>
+        <v>3.674171005085946e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.06156045040043e-08</v>
+        <v>3.061560450400436e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.092934744607925e-08</v>
+        <v>3.092934744607924e-08</v>
       </c>
       <c r="U4" t="n">
         <v>3.179382690710692e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.452604473092631e-08</v>
+        <v>3.452604473092634e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.612673582089244e-08</v>
+        <v>4.612673582089251e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.760282317377751e-08</v>
+        <v>6.760282317377747e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>4.709429654076308e-08</v>
+        <v>4.709429654076316e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.146556573429792e-08</v>
+        <v>3.146556573429793e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.988335209802856e-08</v>
+        <v>3.988335209802862e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>3.473583889649682e-08</v>
+        <v>3.473583889649683e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5022,85 +5022,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.035160454078117e-08</v>
+        <v>3.035160454078121e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.511648438427389e-08</v>
+        <v>4.511648438427394e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.542049648121783e-08</v>
+        <v>4.542049648121785e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.736561896553157e-08</v>
+        <v>3.736561896553155e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.259771375875929e-08</v>
+        <v>3.259771375875931e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>4.885177517894174e-08</v>
+        <v>4.885177517894177e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.540039140876268e-08</v>
+        <v>4.540039140876269e-08</v>
       </c>
       <c r="I5" t="n">
         <v>4.540523302729742e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.553112242227297e-08</v>
+        <v>4.553112242227301e-08</v>
       </c>
       <c r="K5" t="n">
         <v>4.546488871620133e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.537525103112058e-08</v>
+        <v>4.537525103112062e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.544678865689981e-08</v>
+        <v>4.544678865689985e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>3.37576410120453e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.707187776848681e-08</v>
+        <v>3.707187776848682e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.613523381539983e-08</v>
+        <v>3.613523381539985e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.733725217091753e-08</v>
+        <v>2.733725217091755e-08</v>
       </c>
       <c r="R5" t="n">
         <v>4.555360694701394e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.531828907971217e-08</v>
+        <v>4.531828907971222e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.524415552434742e-08</v>
+        <v>4.524415552434743e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.801397016230656e-08</v>
+        <v>3.801397016230658e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.141061462734279e-08</v>
+        <v>4.14106146273428e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.619679928469851e-08</v>
+        <v>4.619679928469852e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.091511151400056e-08</v>
+        <v>3.091511151400059e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.109703713534912e-08</v>
+        <v>6.109703713534919e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.014483667619575e-08</v>
+        <v>3.014483667619578e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.582791975368549e-08</v>
+        <v>4.582791975368551e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.103511360956857e-08</v>
+        <v>6.10351136095686e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5113,82 +5113,82 @@
         <v>2.273800599071786e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.694986364064068e-08</v>
+        <v>2.694986364064067e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.725387573758458e-08</v>
+        <v>2.725387573758457e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.614702306434126e-08</v>
+        <v>2.614702306434125e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.690422647502654e-08</v>
+        <v>1.690422647502656e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.758353052063871e-08</v>
+        <v>2.758353052063877e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.723377066512945e-08</v>
+        <v>2.723377066512942e-08</v>
       </c>
       <c r="I6" t="n">
         <v>2.723861228366414e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.736450167863972e-08</v>
+        <v>2.736450167863973e-08</v>
       </c>
       <c r="K6" t="n">
         <v>2.729826797256809e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.720863028748737e-08</v>
+        <v>2.720863028748736e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>2.728016791326635e-08</v>
+        <v>2.728016791326634e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.173270529966527e-08</v>
+        <v>2.718592323584212e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>2.877356484472778e-08</v>
+        <v>2.87735648447278e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>2.893545744153119e-08</v>
+        <v>2.893545744153116e-08</v>
       </c>
       <c r="Q6" t="n">
         <v>2.706814509650827e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>2.738698620338068e-08</v>
+        <v>2.738698620338066e-08</v>
       </c>
       <c r="S6" t="n">
         <v>2.715166833607899e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>2.707753478071416e-08</v>
+        <v>2.707753478071415e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.714702605773725e-08</v>
+        <v>2.714702605773726e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.241419343496681e-08</v>
+        <v>3.241419343496683e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.802723887581609e-08</v>
+        <v>2.802723887581608e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>2.927507826334516e-08</v>
+        <v>2.927507826334515e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.805621214072222e-08</v>
+        <v>2.805621214072224e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.455823266924631e-08</v>
+        <v>2.45582326692463e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.766129901005224e-08</v>
+        <v>2.766129901005223e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.724367773426468e-08</v>
+        <v>2.724367773426467e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5354,85 +5354,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.182515898979022e-08</v>
+        <v>1.182515898979015e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.012334221802101e-08</v>
+        <v>1.012334221802108e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.175121739092223e-08</v>
+        <v>1.175121739092227e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.171453041263728e-08</v>
+        <v>1.171453041263722e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.169494209875713e-08</v>
+        <v>1.169494209875707e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.204635952616785e-08</v>
+        <v>1.204635952616786e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.168604762169298e-08</v>
+        <v>1.168604762169316e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.169189195763751e-08</v>
+        <v>1.169189195763757e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.192254970455822e-08</v>
+        <v>1.192254970455815e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.171672598127548e-08</v>
+        <v>1.171672598127541e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.211465150114136e-08</v>
+        <v>1.211465150114147e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.239238733461699e-08</v>
+        <v>1.239238733461689e-08</v>
       </c>
       <c r="N2" t="n">
-        <v>1.17279232504189e-08</v>
+        <v>1.172792325041902e-08</v>
       </c>
       <c r="O2" t="n">
-        <v>1.548402403326671e-08</v>
+        <v>1.548402403326676e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.186769128387828e-08</v>
+        <v>1.186769128387821e-08</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.172090661454937e-08</v>
+        <v>1.172090661454954e-08</v>
       </c>
       <c r="R2" t="n">
-        <v>1.169685947059116e-08</v>
+        <v>1.169685947059112e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.184068035338293e-08</v>
+        <v>1.184068035338279e-08</v>
       </c>
       <c r="T2" t="n">
-        <v>1.170665369549361e-08</v>
+        <v>1.170665369549371e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.194694681892624e-08</v>
+        <v>1.194694681892627e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.171983037736198e-08</v>
+        <v>1.171983037736191e-08</v>
       </c>
       <c r="W2" t="n">
-        <v>1.180819010187425e-08</v>
+        <v>1.18081901018742e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.190544905555667e-08</v>
+        <v>1.190544905555674e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.188313410759309e-08</v>
+        <v>1.188313410759302e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.132247279419923e-08</v>
+        <v>1.13224727941992e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.175256204942339e-08</v>
+        <v>1.175256204942343e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.266104458455911e-08</v>
+        <v>1.26610445845591e-08</v>
       </c>
     </row>
     <row r="3">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.635053819788713e-08</v>
+        <v>1.315149803396599e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.097759750451921e-08</v>
+        <v>1.034348348701521e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.469014445801067e-08</v>
+        <v>1.26296421441639e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.275392429622137e-08</v>
+        <v>1.13409343642781e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.338415499357409e-08</v>
+        <v>1.218239252058434e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>2.14461154403434e-08</v>
+        <v>1.485942169992046e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.317876410089745e-08</v>
+        <v>1.211659271824648e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.330819362923317e-08</v>
+        <v>1.215182964773419e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.862461835310832e-08</v>
+        <v>1.393315269482186e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.388374787902207e-08</v>
+        <v>1.235764843926937e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>2.307807156336083e-08</v>
+        <v>1.54633735523628e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>2.983162108616732e-08</v>
+        <v>1.777089319731278e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.413687747710799e-08</v>
+        <v>1.242774537679987e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.802501768391113e-08</v>
+        <v>1.620645555898231e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.732189919442017e-08</v>
+        <v>1.348608374309316e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.397685948364511e-08</v>
+        <v>1.237345779663512e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.342740988426287e-08</v>
+        <v>1.219485198130336e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.671903515528027e-08</v>
+        <v>1.326723343474763e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.365097966077355e-08</v>
+        <v>1.226846098463172e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>2.355410023529124e-08</v>
+        <v>1.550324087426077e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.393095051518591e-08</v>
+        <v>1.23489559027607e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.522301580033447e-08</v>
+        <v>1.281933786517566e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.828436758621564e-08</v>
+        <v>1.387418641580772e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.773692477489086e-08</v>
+        <v>1.366201806762807e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.490040159165237e-08</v>
+        <v>1.236036414991946e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.470323931235512e-08</v>
+        <v>1.261910293236093e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>3.57484149548218e-08</v>
+        <v>2.013593656918053e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5530,85 +5530,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>6.0375945395559e-08</v>
+        <v>6.037594539556029e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.925077311402729e-08</v>
+        <v>2.925077311402732e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.95627935058945e-08</v>
+        <v>4.956279350589455e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>2.760713693427225e-08</v>
+        <v>2.760713693427339e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.774156291727798e-08</v>
+        <v>3.774156291727799e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.032427649642062e-07</v>
+        <v>1.032427649642065e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>3.622897345633702e-08</v>
+        <v>3.622897345633706e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.664717010912988e-08</v>
+        <v>3.664717010912995e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.135884490331781e-08</v>
+        <v>8.135884490331819e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.24828881613575e-08</v>
+        <v>4.248288816135757e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>1.219851187987831e-07</v>
+        <v>1.219851187987891e-07</v>
       </c>
       <c r="M4" t="n">
-        <v>1.855393013747388e-07</v>
+        <v>1.855393013747389e-07</v>
       </c>
       <c r="N4" t="n">
-        <v>4.346468492927616e-08</v>
+        <v>4.34646849292762e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>4.301941780749778e-08</v>
+        <v>4.301941780749783e-08</v>
       </c>
       <c r="P4" t="n">
-        <v>6.908460172077896e-08</v>
+        <v>6.908460172077912e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.209413341873296e-08</v>
+        <v>4.209413341873275e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.794319672677305e-08</v>
+        <v>3.794319672677304e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>6.306548950494926e-08</v>
+        <v>6.30654895049496e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.96973837910714e-08</v>
+        <v>3.969738379107145e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>1.284060967088337e-07</v>
+        <v>1.284060967088343e-07</v>
       </c>
       <c r="V4" t="n">
-        <v>4.068048432206846e-08</v>
+        <v>4.068048432206847e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>5.264023867066806e-08</v>
+        <v>5.264023867066805e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>8.330950400950887e-08</v>
+        <v>8.330950400950839e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>7.61249645519785e-08</v>
+        <v>7.612496455197853e-08</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.213168416670093e-08</v>
+        <v>5.213168416670065e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>4.832319672667668e-08</v>
+        <v>4.832319672667721e-08</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.633339285935259e-07</v>
+        <v>2.633339285935254e-07</v>
       </c>
     </row>
     <row r="5">
@@ -5621,82 +5621,82 @@
         <v>3.408507699147714e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.838620458284031e-08</v>
+        <v>4.838620458284041e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.944018246876936e-08</v>
+        <v>4.944018246876949e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>4.040492376015134e-08</v>
+        <v>4.040492376015138e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.513647835947828e-08</v>
+        <v>3.513647835947831e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.613111487636448e-08</v>
+        <v>5.613111487636449e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.870405994575001e-08</v>
+        <v>4.870405994575011e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.877007440876959e-08</v>
+        <v>4.877007440876965e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>5.136482711488895e-08</v>
+        <v>5.136482711488896e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.905058612997512e-08</v>
+        <v>4.905058612997523e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>5.354533793164424e-08</v>
+        <v>5.35453379316443e-08</v>
       </c>
       <c r="M5" t="n">
         <v>5.675190471011973e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>4.346468492927616e-08</v>
+        <v>3.6626865721933e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>4.015706894926509e-08</v>
+        <v>4.015706894926515e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>4.080910393108602e-08</v>
+        <v>4.080910393108605e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.972573304245814e-08</v>
+        <v>2.972573304245818e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.882618475274878e-08</v>
+        <v>4.882618475274873e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>5.045070778475648e-08</v>
+        <v>5.045070778475647e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.893681502858918e-08</v>
+        <v>4.893681502858921e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>4.597503001607972e-08</v>
+        <v>4.597503001607982e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.460406019532139e-08</v>
+        <v>4.460406019532142e-08</v>
       </c>
       <c r="W5" t="n">
-        <v>4.969590686968992e-08</v>
+        <v>4.969590686968993e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.329409887730167e-08</v>
+        <v>3.329409887730179e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.702678700540241e-08</v>
+        <v>6.702678700540251e-08</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.329656065961856e-08</v>
+        <v>3.329656065961868e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.94553710051127e-08</v>
+        <v>4.945537100511272e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>7.652449895255079e-08</v>
+        <v>7.652449895255082e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5706,85 +5706,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.848781709571488e-08</v>
+        <v>2.848781709571494e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>3.209757381581577e-08</v>
+        <v>3.209757381581581e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>3.315155170174484e-08</v>
+        <v>3.315155170174488e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>3.146802297714107e-08</v>
+        <v>3.146802297714109e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.983934079778503e-08</v>
+        <v>1.983934079778505e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.648531822789037e-08</v>
+        <v>3.648531822789039e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>3.241542917872554e-08</v>
+        <v>3.241542917872563e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>3.248144364174505e-08</v>
+        <v>3.248144364174508e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>3.507619634786448e-08</v>
+        <v>3.507619634786454e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>3.276195536295061e-08</v>
+        <v>3.276195536295067e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.725670716461979e-08</v>
+        <v>3.725670716461987e-08</v>
       </c>
       <c r="M6" t="n">
-        <v>4.046327394309484e-08</v>
+        <v>4.046327394309489e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>4.346468492927616e-08</v>
+        <v>3.288843366892632e-08</v>
       </c>
       <c r="O6" t="n">
-        <v>3.479207494256602e-08</v>
+        <v>3.479207494256603e-08</v>
       </c>
       <c r="P6" t="n">
-        <v>3.668584749332421e-08</v>
+        <v>3.668584749332425e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.280917787542408e-08</v>
+        <v>3.280917787542412e-08</v>
       </c>
       <c r="R6" t="n">
-        <v>3.253755398572426e-08</v>
+        <v>3.253755398572429e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>3.416207701773198e-08</v>
+        <v>3.416207701773204e-08</v>
       </c>
       <c r="T6" t="n">
-        <v>3.264818426156471e-08</v>
+        <v>3.264818426156472e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>3.758932343883555e-08</v>
+        <v>3.758932343883558e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.908685458360676e-08</v>
+        <v>3.908685458360674e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>3.340409424053627e-08</v>
+        <v>3.34040942405363e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.489366930386146e-08</v>
+        <v>3.489366930386145e-08</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.464161170122876e-08</v>
+        <v>3.464161170122882e-08</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.018361197509586e-08</v>
+        <v>3.018361197509592e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.316674023808821e-08</v>
+        <v>3.316674023808827e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>4.332373573192879e-08</v>
+        <v>4.332373573192884e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5953,16 +5953,16 @@
         <v>1.150683444692225e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>9.990809444543537e-09</v>
+        <v>9.990809444543532e-09</v>
       </c>
       <c r="D2" t="n">
-        <v>1.1534181326199e-08</v>
+        <v>1.153418132619899e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.150719421263915e-08</v>
+        <v>1.150719421263914e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.150444061250384e-08</v>
+        <v>1.150444061250383e-08</v>
       </c>
       <c r="G2" t="n">
         <v>1.180482269958054e-08</v>
@@ -5980,10 +5980,10 @@
         <v>1.154169108628346e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.165633947842667e-08</v>
+        <v>1.165633947842666e-08</v>
       </c>
       <c r="M2" t="n">
-        <v>1.156932722540706e-08</v>
+        <v>1.156932722540705e-08</v>
       </c>
       <c r="N2" t="n">
         <v>1.153426215837316e-08</v>
@@ -5992,7 +5992,7 @@
         <v>1.521009847628117e-08</v>
       </c>
       <c r="P2" t="n">
-        <v>1.159854189259925e-08</v>
+        <v>1.159854189259924e-08</v>
       </c>
       <c r="Q2" t="n">
         <v>1.152304939976446e-08</v>
@@ -6001,34 +6001,34 @@
         <v>1.152977646085342e-08</v>
       </c>
       <c r="S2" t="n">
-        <v>1.153861708506016e-08</v>
+        <v>1.153861708506015e-08</v>
       </c>
       <c r="T2" t="n">
         <v>1.151733410953985e-08</v>
       </c>
       <c r="U2" t="n">
-        <v>1.139196849473929e-08</v>
+        <v>1.139196849473928e-08</v>
       </c>
       <c r="V2" t="n">
-        <v>1.152741363227077e-08</v>
+        <v>1.152741363227076e-08</v>
       </c>
       <c r="W2" t="n">
         <v>1.162761096484849e-08</v>
       </c>
       <c r="X2" t="n">
-        <v>1.170865765343972e-08</v>
+        <v>1.170865765343971e-08</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.188171722040811e-08</v>
+        <v>1.18817172204081e-08</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.104470275799156e-08</v>
+        <v>1.104470275799157e-08</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.154525614555168e-08</v>
+        <v>1.154525614555167e-08</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.207702470959154e-08</v>
+        <v>1.207702470959153e-08</v>
       </c>
     </row>
     <row r="3">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.257300225389047e-08</v>
+        <v>1.179570547608454e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.107202873854138e-08</v>
+        <v>1.031327600928884e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.322665608908544e-08</v>
+        <v>1.204227097891663e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.153437046542429e-08</v>
+        <v>1.084452810644132e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.253708386301772e-08</v>
+        <v>1.18082091787426e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.943298752156742e-08</v>
+        <v>1.407931255583528e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.286311300387778e-08</v>
+        <v>1.192202961045494e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.300595380267169e-08</v>
+        <v>1.196378327429728e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.536230839185346e-08</v>
+        <v>1.274127693285983e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.340136345379461e-08</v>
+        <v>1.211388105237268e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.603874507769255e-08</v>
+        <v>1.297451583045589e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.433143117384032e-08</v>
+        <v>1.242524616500215e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.322126282653857e-08</v>
+        <v>1.202819851535715e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.650522558727113e-08</v>
+        <v>1.5579945140144e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.467921430786963e-08</v>
+        <v>1.250396902416113e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.296321127764105e-08</v>
+        <v>1.19452979850499e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.312892787272501e-08</v>
+        <v>1.200934133108003e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33099487580375e-08</v>
+        <v>1.20508868788366e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.28338496662933e-08</v>
+        <v>1.190410170693778e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.405000469516729e-08</v>
+        <v>1.218474658217162e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.305166112344496e-08</v>
+        <v>1.197347773389324e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.408378784976578e-08</v>
+        <v>1.235926997848452e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.729153576328821e-08</v>
+        <v>1.34319700005027e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.128636191775241e-08</v>
+        <v>1.479912087445806e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.261971042419171e-08</v>
+        <v>1.149434847544303e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.3472664149562e-08</v>
+        <v>1.211193338633184e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.580458699535806e-08</v>
+        <v>1.648436793846961e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6126,22 +6126,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.762798926739034e-08</v>
+        <v>2.762798926739037e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>2.989989265070105e-08</v>
+        <v>2.989989265070107e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>3.496366843744499e-08</v>
+        <v>3.496366843744495e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>1.669529446228946e-08</v>
+        <v>1.669529446228948e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>2.927541818089398e-08</v>
+        <v>2.927541818089394e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.050161724006441e-08</v>
+        <v>8.050161724006433e-08</v>
       </c>
       <c r="H4" t="n">
         <v>3.225248374744854e-08</v>
@@ -6153,55 +6153,55 @@
         <v>5.039898132698142e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>3.725122282971933e-08</v>
+        <v>3.72512228297193e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.637306514933906e-08</v>
+        <v>5.637306514933904e-08</v>
       </c>
       <c r="M4" t="n">
-        <v>4.549927774436539e-08</v>
+        <v>4.549927774436538e-08</v>
       </c>
       <c r="N4" t="n">
-        <v>3.398822181042182e-08</v>
+        <v>3.398822181042183e-08</v>
       </c>
       <c r="O4" t="n">
-        <v>3.027381466213145e-08</v>
+        <v>3.02738146621315e-08</v>
       </c>
       <c r="P4" t="n">
         <v>4.428054826316838e-08</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.220482083065169e-08</v>
+        <v>3.220482083065165e-08</v>
       </c>
       <c r="R4" t="n">
-        <v>3.423275978029458e-08</v>
+        <v>3.423275978029462e-08</v>
       </c>
       <c r="S4" t="n">
-        <v>3.405074849320633e-08</v>
+        <v>3.40507484932063e-08</v>
       </c>
       <c r="T4" t="n">
-        <v>3.136462473744228e-08</v>
+        <v>3.136462473744223e-08</v>
       </c>
       <c r="U4" t="n">
-        <v>4.211569432911151e-08</v>
+        <v>4.211569432911146e-08</v>
       </c>
       <c r="V4" t="n">
-        <v>3.258559387043519e-08</v>
+        <v>3.258559387043517e-08</v>
       </c>
       <c r="W4" t="n">
-        <v>4.053502791387531e-08</v>
+        <v>4.05350279138753e-08</v>
       </c>
       <c r="X4" t="n">
-        <v>6.943232593119853e-08</v>
+        <v>6.943232593119849e-08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.029106447432134e-07</v>
+        <v>1.029106447432133e-07</v>
       </c>
       <c r="Z4" t="n">
         <v>3.221385590195874e-08</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.590634682552615e-08</v>
+        <v>3.590634682552611e-08</v>
       </c>
       <c r="AB4" t="n">
         <v>1.515082094970003e-07</v>
@@ -6214,85 +6214,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.037103661239454e-08</v>
+        <v>3.037103661239458e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>4.539505026988938e-08</v>
+        <v>4.539505026988943e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>4.570423633708135e-08</v>
+        <v>4.570423633708142e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>3.73994057073514e-08</v>
+        <v>3.739940570735144e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.268460814440326e-08</v>
+        <v>3.268460814440331e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>5.187664248907647e-08</v>
+        <v>5.187664248907643e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>4.552447827299049e-08</v>
+        <v>4.552447827299054e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>4.559650269723655e-08</v>
+        <v>4.55965026972366e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>4.674926831582933e-08</v>
+        <v>4.674926831582939e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>4.578906253189572e-08</v>
+        <v>4.578906253189575e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>4.708406886201919e-08</v>
+        <v>4.708406886201922e-08</v>
       </c>
       <c r="M5" t="n">
-        <v>4.624029708718222e-08</v>
+        <v>4.624029708718226e-08</v>
       </c>
       <c r="N5" t="n">
-        <v>3.398822181042182e-08</v>
+        <v>3.405880015201625e-08</v>
       </c>
       <c r="O5" t="n">
-        <v>3.706675267014572e-08</v>
+        <v>3.706675267014577e-08</v>
       </c>
       <c r="P5" t="n">
-        <v>3.720086294053992e-08</v>
+        <v>3.720086294053993e-08</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.760157328627682e-08</v>
+        <v>2.760157328627683e-08</v>
       </c>
       <c r="R5" t="n">
-        <v>4.565448135666494e-08</v>
+        <v>4.565448135666493e-08</v>
       </c>
       <c r="S5" t="n">
-        <v>4.575434027396797e-08</v>
+        <v>4.575434027396803e-08</v>
       </c>
       <c r="T5" t="n">
-        <v>4.55139392748137e-08</v>
+        <v>4.551393927481374e-08</v>
       </c>
       <c r="U5" t="n">
-        <v>3.887173362208805e-08</v>
+        <v>3.887173362208803e-08</v>
       </c>
       <c r="V5" t="n">
-        <v>4.146810208049756e-08</v>
+        <v>4.146810208049759e-08</v>
       </c>
       <c r="W5" t="n">
         <v>4.610216879847797e-08</v>
       </c>
       <c r="X5" t="n">
-        <v>3.107511122535826e-08</v>
+        <v>3.107511122535829e-08</v>
       </c>
       <c r="Y5" t="n">
-        <v>6.456794210515096e-08</v>
+        <v>6.456794210515103e-08</v>
       </c>
       <c r="Z5" t="n">
         <v>3.035191552369339e-08</v>
       </c>
       <c r="AA5" t="n">
-        <v>4.582933151633852e-08</v>
+        <v>4.582933151633853e-08</v>
       </c>
       <c r="AB5" t="n">
-        <v>6.74773042407998e-08</v>
+        <v>6.747730424079987e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6305,40 +6305,40 @@
         <v>2.389618095214511e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.864461640074097e-08</v>
+        <v>2.864461640074096e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.895380246793297e-08</v>
+        <v>2.895380246793295e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.75529853265842e-08</v>
+        <v>2.755298532658421e-08</v>
       </c>
       <c r="F6" t="n">
         <v>1.767075589607591e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>3.201082296749108e-08</v>
+        <v>3.201082296749107e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.877404440384207e-08</v>
+        <v>2.877404440384205e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.884606882808813e-08</v>
+        <v>2.884606882808812e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.999883444668096e-08</v>
+        <v>2.999883444668095e-08</v>
       </c>
       <c r="K6" t="n">
         <v>2.903862866274726e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.033363499287081e-08</v>
+        <v>3.03336349928708e-08</v>
       </c>
       <c r="M6" t="n">
         <v>2.9489863218034e-08</v>
       </c>
       <c r="N6" t="n">
-        <v>3.398822181042182e-08</v>
+        <v>2.895471550452488e-08</v>
       </c>
       <c r="O6" t="n">
         <v>3.033587393327217e-08</v>
@@ -6347,28 +6347,28 @@
         <v>3.159676603376154e-08</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.882806392394649e-08</v>
+        <v>2.882806392394648e-08</v>
       </c>
       <c r="R6" t="n">
         <v>2.890404748751653e-08</v>
       </c>
       <c r="S6" t="n">
-        <v>2.900390640481956e-08</v>
+        <v>2.900390640481954e-08</v>
       </c>
       <c r="T6" t="n">
         <v>2.87635054056653e-08</v>
       </c>
       <c r="U6" t="n">
-        <v>2.945457645399961e-08</v>
+        <v>2.94545764539996e-08</v>
       </c>
       <c r="V6" t="n">
-        <v>3.430408957565149e-08</v>
+        <v>3.430408957565148e-08</v>
       </c>
       <c r="W6" t="n">
-        <v>2.934878222088657e-08</v>
+        <v>2.934878222088656e-08</v>
       </c>
       <c r="X6" t="n">
-        <v>3.092459284719283e-08</v>
+        <v>3.092459284719286e-08</v>
       </c>
       <c r="Y6" t="n">
         <v>3.287938026743479e-08</v>
@@ -6377,10 +6377,10 @@
         <v>2.604181116514679e-08</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.907889764719011e-08</v>
+        <v>2.907889764719009e-08</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.503272838027888e-08</v>
+        <v>3.50327283802789e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
+++ b/Results/Phase 2/Ammonia/ammonia human toxicity non-carcinogenic results.xlsx
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.474551043498321e-08</v>
+        <v>1.370198583494525e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.053120689570204e-08</v>
+        <v>1.02419986336249e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.282331151944325e-08</v>
+        <v>1.2298773321844e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.171804155706566e-08</v>
+        <v>1.139180963113449e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.256619437951606e-08</v>
+        <v>1.211443597317306e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.52221463044772e-08</v>
+        <v>1.402513442197086e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.248736109265397e-08</v>
+        <v>1.20559317638572e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.241237104232806e-08</v>
+        <v>1.201387367808773e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.436507013688196e-08</v>
+        <v>1.339983971172153e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.269674605721136e-08</v>
+        <v>1.221403095218554e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.613425311666506e-08</v>
+        <v>1.463084362591127e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.869614891337414e-08</v>
+        <v>1.631015258464244e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.255107445731123e-08</v>
+        <v>1.211809403451311e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.718145691302671e-08</v>
+        <v>1.654689264740105e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.373414551957832e-08</v>
+        <v>1.297800028280375e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.26784980013903e-08</v>
+        <v>1.220394120661022e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.231509230020409e-08</v>
+        <v>1.194465818614877e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.435251965884765e-08</v>
+        <v>1.340541895153927e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.255848841919765e-08</v>
+        <v>1.211582352646567e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.734162426803542e-08</v>
+        <v>1.544863811333621e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.309595594496861e-08</v>
+        <v>1.251816281340679e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.329195483969284e-08</v>
+        <v>1.266060302648405e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.381575887181605e-08</v>
+        <v>1.298608542611195e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.40947308189532e-08</v>
+        <v>1.319673379297183e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.301079214390994e-08</v>
+        <v>1.23376061622248e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.324460752630709e-08</v>
+        <v>1.260457996618588e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.184237828770481e-08</v>
+        <v>1.839802516693771e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.168980418004102e-08</v>
+        <v>1.142057399177585e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.017250586520077e-08</v>
+        <v>9.886843550950851e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.189617841632426e-08</v>
+        <v>1.154849263840643e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.068594010132659e-08</v>
+        <v>1.056509211431306e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.174161266211665e-08</v>
+        <v>1.144079566607077e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.206128472643276e-08</v>
+        <v>1.168178558442974e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.189351518608967e-08</v>
+        <v>1.15407416797558e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.187842806107555e-08</v>
+        <v>1.153692967100919e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.196587190802232e-08</v>
+        <v>1.160865889656964e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.193884886703311e-08</v>
+        <v>1.157389419840469e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.190536660753766e-08</v>
+        <v>1.15624341411314e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.200482823130175e-08</v>
+        <v>1.16156038888403e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18143161189586e-08</v>
+        <v>1.15021867886992e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.537196255327783e-08</v>
+        <v>1.509336552012307e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.177611693562029e-08</v>
+        <v>1.148261264499714e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.178132600812828e-08</v>
+        <v>1.14755186764098e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.190090677519346e-08</v>
+        <v>1.15517206602367e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.189191156990013e-08</v>
+        <v>1.156246418608471e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.180853664705447e-08</v>
+        <v>1.149195000819114e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.197056419312729e-08</v>
+        <v>1.156556143627233e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.195997969471102e-08</v>
+        <v>1.160745004606342e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.242260395078581e-08</v>
+        <v>1.195570217546629e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.344920055313837e-08</v>
+        <v>1.26468091063137e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.334076016931392e-08</v>
+        <v>1.256491205818043e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.130671875060935e-08</v>
+        <v>1.10102756453769e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.22077757527494e-08</v>
+        <v>1.177873042186572e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.199451757565515e-08</v>
+        <v>1.160903034153456e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1866,85 +1866,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.421967082616675e-08</v>
+        <v>1.331751473247386e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.042378185430192e-08</v>
+        <v>1.015168974513325e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.344288879662928e-08</v>
+        <v>1.271201632279321e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.156307098558914e-08</v>
+        <v>1.127330826764648e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.244034102008706e-08</v>
+        <v>1.201663388211492e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.510168195520778e-08</v>
+        <v>1.393298621408737e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.216573283813002e-08</v>
+        <v>1.182446933631143e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.223072226836933e-08</v>
+        <v>1.187696662115024e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.43422170868372e-08</v>
+        <v>1.337118787342819e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.257616980343486e-08</v>
+        <v>1.211599785531837e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.607384790038181e-08</v>
+        <v>1.457663651384437e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.8200370919023e-08</v>
+        <v>1.596455479287702e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.248851458824959e-08</v>
+        <v>1.206254044620482e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.695306372961908e-08</v>
+        <v>1.636636111309249e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.411570419124904e-08</v>
+        <v>1.32384378510055e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.257134947053065e-08</v>
+        <v>1.211790418932238e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.218772011819929e-08</v>
+        <v>1.184515499711276e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.432227891391477e-08</v>
+        <v>1.337639073952478e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.252713648218805e-08</v>
+        <v>1.208154837632086e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.671921525325953e-08</v>
+        <v>1.499835037331907e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.259631000646501e-08</v>
+        <v>1.214960640889857e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.307953856204834e-08</v>
+        <v>1.249814137812301e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.398055690353183e-08</v>
+        <v>1.30892088925982e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.384046766084495e-08</v>
+        <v>1.301002910351149e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.269754291092261e-08</v>
+        <v>1.209895012051256e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.283391027137118e-08</v>
+        <v>1.230680976207813e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.151992882377695e-08</v>
+        <v>1.816498182069535e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2462,85 +2462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.383621596104716e-08</v>
+        <v>1.305042211823229e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.051578402725443e-08</v>
+        <v>1.022522706929026e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.378365893008113e-08</v>
+        <v>1.296135045661978e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.151422579772671e-08</v>
+        <v>1.124842454387414e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.267650547974934e-08</v>
+        <v>1.219314867101172e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.494126529875538e-08</v>
+        <v>1.383858249433056e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.218105661780564e-08</v>
+        <v>1.184915865767582e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.288275365508585e-08</v>
+        <v>1.233655219351468e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.43047115148324e-08</v>
+        <v>1.335818762895098e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.305241264760507e-08</v>
+        <v>1.246692090535029e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.562382443524438e-08</v>
+        <v>1.427765879576264e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.747070465664953e-08</v>
+        <v>1.54751651706908e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.242082737545289e-08</v>
+        <v>1.202829341341325e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.679292979011576e-08</v>
+        <v>1.62656325984982e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.413073570393062e-08</v>
+        <v>1.326508776043975e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.264916206930849e-08</v>
+        <v>1.218613707955537e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.216753361206926e-08</v>
+        <v>1.184461791964155e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.419852759452283e-08</v>
+        <v>1.330401890677819e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.258820373965047e-08</v>
+        <v>1.21366420829582e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.555062622826875e-08</v>
+        <v>1.420581553249608e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.297078081748675e-08</v>
+        <v>1.243210037831964e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.31760762885797e-08</v>
+        <v>1.259106224465426e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.473833278640567e-08</v>
+        <v>1.362824866107323e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.559015919592949e-08</v>
+        <v>1.424536552064139e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.278140066444702e-08</v>
+        <v>1.218741113118425e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.287965657834683e-08</v>
+        <v>1.235127491311381e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.089522998662495e-08</v>
+        <v>1.774792950534608e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3058,85 +3058,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.358486390875774e-08</v>
+        <v>1.289124735301838e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.058964823060446e-08</v>
+        <v>1.029006399050923e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.345165078535199e-08</v>
+        <v>1.275253184098144e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.13740734849121e-08</v>
+        <v>1.115459961050418e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.285338352162828e-08</v>
+        <v>1.233003348171548e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.460113458046376e-08</v>
+        <v>1.362149205297302e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.225945171376848e-08</v>
+        <v>1.191697935627857e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.291896524728543e-08</v>
+        <v>1.237591833266055e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.415589110332137e-08</v>
+        <v>1.327484915049505e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.325469498059845e-08</v>
+        <v>1.26244643461715e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.498840876951963e-08</v>
+        <v>1.386463350891014e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657271962499279e-08</v>
+        <v>1.490858632302811e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.23672729053578e-08</v>
+        <v>1.200475560318326e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.648958486439478e-08</v>
+        <v>1.60557094200388e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.397262596151308e-08</v>
+        <v>1.317463654103078e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.274734255070833e-08</v>
+        <v>1.22703057537347e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.240137489751208e-08</v>
+        <v>1.201814723612645e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.405650596514968e-08</v>
+        <v>1.322043710369989e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.274922061335342e-08</v>
+        <v>1.22611575746325e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.564112161987688e-08</v>
+        <v>1.431786447530896e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.371226462832327e-08</v>
+        <v>1.298308270104792e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.334621191240435e-08</v>
+        <v>1.273631535459269e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.503410881188124e-08</v>
+        <v>1.386384806227712e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.774368488913168e-08</v>
+        <v>1.574329036384023e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.275230919581267e-08</v>
+        <v>1.219195758286885e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.304432947682048e-08</v>
+        <v>1.247921306753857e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.005468588278217e-08</v>
+        <v>1.721708977416382e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3654,85 +3654,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.190409057793427e-08</v>
+        <v>1.157162732738749e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.005995567511345e-08</v>
+        <v>9.80687535239138e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.196118311714262e-08</v>
+        <v>1.159498037047643e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.074381046784118e-08</v>
+        <v>1.061505292763807e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.173378587500323e-08</v>
+        <v>1.143289364519046e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.250235353701227e-08</v>
+        <v>1.199865402369715e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.207153165431064e-08</v>
+        <v>1.166035942470622e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.17641317567398e-08</v>
+        <v>1.145753002120454e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.230653751399895e-08</v>
+        <v>1.185247369758087e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.19887542431081e-08</v>
+        <v>1.160838740138136e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.274890531370061e-08</v>
+        <v>1.216803714097526e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.355618805002521e-08</v>
+        <v>1.270753184150771e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.188528459359017e-08</v>
+        <v>1.154849320368835e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.542897933144105e-08</v>
+        <v>1.512413487299944e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.216398719500839e-08</v>
+        <v>1.176053451602235e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.185863068226258e-08</v>
+        <v>1.152748321879515e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.185022235141194e-08</v>
+        <v>1.151585910118136e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.211381532667423e-08</v>
+        <v>1.172026596648001e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.179657276490882e-08</v>
+        <v>1.147522591567774e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.304586971831711e-08</v>
+        <v>1.231182164247492e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.180591473157603e-08</v>
+        <v>1.14933430831338e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.242061827051051e-08</v>
+        <v>1.193130193311708e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.225905614781748e-08</v>
+        <v>1.180371371542951e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.190513606652537e-08</v>
+        <v>1.156209198084798e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.15876997321105e-08</v>
+        <v>1.120926442123055e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.205372827564668e-08</v>
+        <v>1.166824071501224e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.37650573345623e-08</v>
+        <v>1.282232829733135e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4250,85 +4250,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.168732800466368e-08</v>
+        <v>1.141087887166411e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.013913138962796e-08</v>
+        <v>9.852724336455422e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.181942775751606e-08</v>
+        <v>1.148284220710141e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.071487850755442e-08</v>
+        <v>1.058701612149492e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.174987453813873e-08</v>
+        <v>1.143587133733742e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.195835093720235e-08</v>
+        <v>1.159301017058403e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.191257641000618e-08</v>
+        <v>1.154330016541784e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.185842363085585e-08</v>
+        <v>1.151184794055783e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.189929323102992e-08</v>
+        <v>1.154991511885119e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.188242175476213e-08</v>
+        <v>1.152408773930169e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.184940119531091e-08</v>
+        <v>1.150001641497708e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.18498363833604e-08</v>
+        <v>1.148594033615324e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.187832666286222e-08</v>
+        <v>1.153651727679741e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.550686634921286e-08</v>
+        <v>1.517768588097582e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.170484322007445e-08</v>
+        <v>1.142438803098743e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.171390255864216e-08</v>
+        <v>1.141528401413874e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.188861345147159e-08</v>
+        <v>1.153128335396989e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.183556489997541e-08</v>
+        <v>1.15098471264834e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.171224637244305e-08</v>
+        <v>1.140595563842928e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.159874422082436e-08</v>
+        <v>1.12703812928336e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.187127591778524e-08</v>
+        <v>1.153187481775294e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.214422061675901e-08</v>
+        <v>1.173553976673061e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.293139487481782e-08</v>
+        <v>1.227435224826406e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.24022009954294e-08</v>
+        <v>1.190287857111642e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.144358977912631e-08</v>
+        <v>1.110179181799443e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.204239664401546e-08</v>
+        <v>1.165299243734742e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.176664902850858e-08</v>
+        <v>1.144104812783092e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4846,85 +4846,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.178741584468491e-08</v>
+        <v>1.149120425815991e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.016879157838902e-08</v>
+        <v>9.886244805364417e-09</v>
       </c>
       <c r="D3" t="n">
-        <v>1.189848721223808e-08</v>
+        <v>1.155065427650373e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.087207240239203e-08</v>
+        <v>1.070029231190523e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.17602673416695e-08</v>
+        <v>1.145421887259736e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.209900746368585e-08</v>
+        <v>1.170890349329e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.189741733265944e-08</v>
+        <v>1.154259015026076e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.188686686672471e-08</v>
+        <v>1.154304073598735e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.196372735203219e-08</v>
+        <v>1.160703244653406e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.193152145924785e-08</v>
+        <v>1.157278734861248e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.186543111021573e-08</v>
+        <v>1.152793930678512e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.191873814707609e-08</v>
+        <v>1.155336185973844e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.18329259733181e-08</v>
+        <v>1.151466650590551e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.55872164625657e-08</v>
+        <v>1.525258191442286e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.179873661316764e-08</v>
+        <v>1.149877909456821e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.175601028848743e-08</v>
+        <v>1.145730226685597e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.199691399532562e-08</v>
+        <v>1.161715116718353e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.180095985807424e-08</v>
+        <v>1.149655219352172e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.177268771695874e-08</v>
+        <v>1.146331832258213e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.164773756549124e-08</v>
+        <v>1.132819865424926e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.195991297985865e-08</v>
+        <v>1.16077770800197e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.250025042502274e-08</v>
+        <v>1.200862415124831e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.329635363092516e-08</v>
+        <v>1.254596689632971e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.244849336548334e-08</v>
+        <v>1.194486064790897e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.137726935061245e-08</v>
+        <v>1.106278634544992e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.216557687029314e-08</v>
+        <v>1.174913506546124e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.190077043289267e-08</v>
+        <v>1.15448335722574e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5442,85 +5442,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.315149803396599e-08</v>
+        <v>1.253439515268832e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.034348348701521e-08</v>
+        <v>1.007486380284354e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.26296421441639e-08</v>
+        <v>1.213147305128332e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.13409343642781e-08</v>
+        <v>1.109952987026352e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.218239252058434e-08</v>
+        <v>1.181755173403674e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.485942169992046e-08</v>
+        <v>1.376114272325565e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.211659271824648e-08</v>
+        <v>1.176858395539003e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.215182964773419e-08</v>
+        <v>1.179962299127588e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.393315269482186e-08</v>
+        <v>1.307892645049658e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.235764843926937e-08</v>
+        <v>1.193922558621933e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54633735523628e-08</v>
+        <v>1.415088670448118e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.777089319731278e-08</v>
+        <v>1.573908300600054e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.242774537679987e-08</v>
+        <v>1.199912741450471e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.620645555898231e-08</v>
+        <v>1.578411409600395e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.348608374309316e-08</v>
+        <v>1.277090306584655e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.237345779663512e-08</v>
+        <v>1.19602316422557e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.219485198130336e-08</v>
+        <v>1.182786593865453e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.326723343474763e-08</v>
+        <v>1.262016185642984e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.226846098463172e-08</v>
+        <v>1.188188429621235e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.550324087426077e-08</v>
+        <v>1.411818279734186e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.23489559027607e-08</v>
+        <v>1.19517697284043e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.281933786517566e-08</v>
+        <v>1.228749688029177e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.387418641580772e-08</v>
+        <v>1.299453330791158e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.366201806762807e-08</v>
+        <v>1.28649978187145e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.236036414991946e-08</v>
+        <v>1.183571600711381e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.261910293236093e-08</v>
+        <v>1.213589045966402e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.013593656918053e-08</v>
+        <v>1.721093625424913e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6038,85 +6038,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.179570547608454e-08</v>
+        <v>1.152831599709476e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>1.031327600928884e-08</v>
+        <v>1.001682054625562e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>1.204227097891663e-08</v>
+        <v>1.168499463663805e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>1.084452810644132e-08</v>
+        <v>1.071704202790928e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>1.18082091787426e-08</v>
+        <v>1.151939984129784e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>1.407931255583528e-08</v>
+        <v>1.317861866009831e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>1.192202961045494e-08</v>
+        <v>1.159713536678303e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>1.196378327429728e-08</v>
+        <v>1.163145737426918e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>1.274127693285983e-08</v>
+        <v>1.219991961005359e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>1.211388105237268e-08</v>
+        <v>1.172842733336754e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>1.297451583045589e-08</v>
+        <v>1.236102059725124e-08</v>
       </c>
       <c r="M3" t="n">
-        <v>1.242524616500215e-08</v>
+        <v>1.194005524519832e-08</v>
       </c>
       <c r="N3" t="n">
-        <v>1.202819851535715e-08</v>
+        <v>1.168341180030269e-08</v>
       </c>
       <c r="O3" t="n">
-        <v>1.5579945140144e-08</v>
+        <v>1.528020994919354e-08</v>
       </c>
       <c r="P3" t="n">
-        <v>1.250396902416113e-08</v>
+        <v>1.203681040880588e-08</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.19452979850499e-08</v>
+        <v>1.162170444512637e-08</v>
       </c>
       <c r="R3" t="n">
-        <v>1.200934133108003e-08</v>
+        <v>1.166077833063825e-08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.20508868788366e-08</v>
+        <v>1.170592957198257e-08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.190410170693778e-08</v>
+        <v>1.159043017177415e-08</v>
       </c>
       <c r="U3" t="n">
-        <v>1.218474658217162e-08</v>
+        <v>1.174238719112493e-08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.197347773389324e-08</v>
+        <v>1.164496345553138e-08</v>
       </c>
       <c r="W3" t="n">
-        <v>1.235926997848452e-08</v>
+        <v>1.193577720436641e-08</v>
       </c>
       <c r="X3" t="n">
-        <v>1.34319700005027e-08</v>
+        <v>1.265897979686307e-08</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.479912087445806e-08</v>
+        <v>1.362288054635823e-08</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.149434847544303e-08</v>
+        <v>1.117162188566631e-08</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.211193338633184e-08</v>
+        <v>1.174419849083417e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.648436793846961e-08</v>
+        <v>1.471401155439375e-08</v>
       </c>
     </row>
     <row r="4">
